--- a/Excel/一方通行/酒神.xlsx
+++ b/Excel/一方通行/酒神.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F4A4FF-1202-46EB-A1AB-2B9191E225D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C5D2D3-C75E-4199-A082-FB6B2E1551A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -105,7 +105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="BB1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -132,7 +132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BP1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+    <comment ref="BR1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -156,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CR1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+    <comment ref="CT1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="573">
   <si>
     <t>Id</t>
   </si>
@@ -2015,6 +2015,26 @@
   </si>
   <si>
     <t>不可阻挡</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>优先Buff</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义优先级</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>OrderBuff</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>OrderExpression</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -6535,7 +6555,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DH707"/>
+  <dimension ref="A1:DJ707"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -6575,54 +6595,54 @@
     <col min="38" max="39" width="8.33203125" customWidth="1"/>
     <col min="40" max="40" width="15" customWidth="1"/>
     <col min="41" max="41" width="13.25" customWidth="1"/>
-    <col min="42" max="43" width="11.83203125" customWidth="1"/>
-    <col min="44" max="44" width="18.4140625" customWidth="1"/>
-    <col min="45" max="45" width="12.25" customWidth="1"/>
-    <col min="46" max="46" width="11.9140625" customWidth="1"/>
-    <col min="47" max="47" width="19.58203125" customWidth="1"/>
-    <col min="48" max="48" width="12.6640625" customWidth="1"/>
-    <col min="50" max="50" width="7" customWidth="1"/>
-    <col min="51" max="51" width="11.75" customWidth="1"/>
-    <col min="52" max="52" width="19.75" customWidth="1"/>
-    <col min="53" max="53" width="5.08203125" customWidth="1"/>
-    <col min="54" max="54" width="8.5" customWidth="1"/>
-    <col min="55" max="55" width="13.5" customWidth="1"/>
-    <col min="56" max="56" width="14.6640625" customWidth="1"/>
-    <col min="57" max="57" width="10.1640625" customWidth="1"/>
-    <col min="58" max="58" width="8.25" customWidth="1"/>
-    <col min="59" max="65" width="8.33203125" customWidth="1"/>
-    <col min="66" max="68" width="11.25" customWidth="1"/>
-    <col min="69" max="69" width="6.58203125" customWidth="1"/>
-    <col min="70" max="71" width="8" customWidth="1"/>
-    <col min="72" max="72" width="7.33203125" style="5" customWidth="1"/>
-    <col min="73" max="74" width="8.5" style="5" customWidth="1"/>
-    <col min="75" max="76" width="7.83203125" style="5" customWidth="1"/>
-    <col min="77" max="77" width="22.1640625" style="5" customWidth="1"/>
-    <col min="78" max="78" width="13.5" customWidth="1"/>
-    <col min="79" max="79" width="21.1640625" customWidth="1"/>
-    <col min="80" max="80" width="15.75" customWidth="1"/>
-    <col min="81" max="81" width="15.58203125" customWidth="1"/>
-    <col min="82" max="82" width="12.83203125" customWidth="1"/>
-    <col min="83" max="83" width="16.1640625" customWidth="1"/>
-    <col min="85" max="85" width="16" customWidth="1"/>
-    <col min="86" max="87" width="12.83203125" customWidth="1"/>
-    <col min="88" max="88" width="23.58203125" customWidth="1"/>
-    <col min="89" max="89" width="12.83203125" customWidth="1"/>
-    <col min="90" max="90" width="21.25" customWidth="1"/>
-    <col min="91" max="91" width="9.5"/>
-    <col min="97" max="97" width="14" customWidth="1"/>
-    <col min="98" max="98" width="8" customWidth="1"/>
-    <col min="100" max="100" width="11.08203125" customWidth="1"/>
-    <col min="101" max="101" width="13.75" customWidth="1"/>
-    <col min="102" max="102" width="9.5"/>
-    <col min="105" max="106" width="9.5"/>
-    <col min="108" max="108" width="15.5" customWidth="1"/>
-    <col min="110" max="111" width="9.5"/>
-    <col min="112" max="112" width="9" hidden="1" customWidth="1"/>
-    <col min="117" max="117" width="9.5"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1"/>
+    <col min="47" max="47" width="12.25" customWidth="1"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1"/>
+    <col min="52" max="52" width="7" customWidth="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1"/>
+    <col min="54" max="54" width="19.75" customWidth="1"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1"/>
+    <col min="56" max="56" width="8.5" customWidth="1"/>
+    <col min="57" max="57" width="13.5" customWidth="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1"/>
+    <col min="60" max="60" width="8.25" customWidth="1"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1"/>
+    <col min="68" max="70" width="11.25" customWidth="1"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1"/>
+    <col min="72" max="73" width="8" customWidth="1"/>
+    <col min="74" max="74" width="7.33203125" style="5" customWidth="1"/>
+    <col min="75" max="76" width="8.5" style="5" customWidth="1"/>
+    <col min="77" max="78" width="7.83203125" style="5" customWidth="1"/>
+    <col min="79" max="79" width="22.1640625" style="5" customWidth="1"/>
+    <col min="80" max="80" width="13.5" customWidth="1"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1"/>
+    <col min="82" max="82" width="15.75" customWidth="1"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1"/>
+    <col min="87" max="87" width="16" customWidth="1"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1"/>
+    <col min="92" max="92" width="21.25" customWidth="1"/>
+    <col min="93" max="93" width="9.5"/>
+    <col min="99" max="99" width="14" customWidth="1"/>
+    <col min="100" max="100" width="8" customWidth="1"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1"/>
+    <col min="103" max="103" width="13.75" customWidth="1"/>
+    <col min="104" max="104" width="9.5"/>
+    <col min="107" max="108" width="9.5"/>
+    <col min="110" max="110" width="15.5" customWidth="1"/>
+    <col min="112" max="113" width="9.5"/>
+    <col min="114" max="114" width="9" hidden="1" customWidth="1"/>
+    <col min="119" max="119" width="9.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>158</v>
       </c>
@@ -6746,209 +6766,215 @@
       <c r="AQ1" t="s">
         <v>197</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AR1" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="AS1" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="AT1" t="s">
         <v>198</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>199</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>200</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>201</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>202</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>203</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>204</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>205</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>206</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>207</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>208</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>209</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>210</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>211</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>212</v>
       </c>
       <c r="BH1" t="s">
         <v>212</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
+        <v>212</v>
+      </c>
+      <c r="BK1" t="s">
         <v>213</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>214</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>215</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>216</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>217</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>218</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>219</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>220</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>221</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BT1" t="s">
         <v>222</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BU1" t="s">
         <v>223</v>
       </c>
-      <c r="BT1" s="5" t="s">
+      <c r="BV1" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="BU1" s="5" t="s">
+      <c r="BW1" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="BV1" s="5" t="s">
+      <c r="BX1" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="BW1" s="5" t="s">
+      <c r="BY1" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="BX1" s="5" t="s">
+      <c r="BZ1" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="BY1" s="5" t="s">
+      <c r="CA1" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CB1" t="s">
         <v>230</v>
       </c>
-      <c r="CA1" s="5" t="s">
+      <c r="CC1" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CD1" t="s">
         <v>232</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CE1" t="s">
         <v>233</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CF1" t="s">
         <v>234</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CG1" t="s">
         <v>235</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CH1" t="s">
         <v>236</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CI1" t="s">
         <v>237</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CJ1" t="s">
         <v>238</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CK1" t="s">
         <v>239</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CL1" t="s">
         <v>240</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CM1" t="s">
         <v>241</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CN1" t="s">
         <v>242</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CO1" t="s">
         <v>243</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CP1" t="s">
         <v>244</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CQ1" t="s">
         <v>245</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CR1" t="s">
         <v>222</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CS1" t="s">
         <v>246</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CT1" t="s">
         <v>247</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CU1" t="s">
         <v>248</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CV1" t="s">
         <v>249</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CW1" t="s">
         <v>250</v>
-      </c>
-      <c r="CV1" t="s">
-        <v>251</v>
-      </c>
-      <c r="CW1" t="s">
-        <v>252</v>
       </c>
       <c r="CX1" t="s">
         <v>251</v>
       </c>
       <c r="CY1" t="s">
+        <v>252</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>251</v>
+      </c>
+      <c r="DA1" t="s">
         <v>253</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DB1" t="s">
         <v>254</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DC1" t="s">
         <v>255</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DD1" t="s">
         <v>256</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DE1" t="s">
         <v>257</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DF1" t="s">
         <v>258</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DG1" t="s">
         <v>259</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DH1" t="s">
         <v>260</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DI1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="2" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -7075,212 +7101,218 @@
       <c r="AQ2" t="s">
         <v>299</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AR2" s="8" t="s">
+        <v>570</v>
+      </c>
+      <c r="AS2" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="AT2" t="s">
         <v>300</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AU2" t="s">
         <v>301</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AV2" t="s">
         <v>302</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AW2" t="s">
         <v>303</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AX2" t="s">
         <v>304</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AY2" t="s">
         <v>305</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AZ2" t="s">
         <v>306</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BA2" t="s">
         <v>307</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BB2" t="s">
         <v>308</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BC2" t="s">
         <v>309</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BD2" t="s">
         <v>310</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BE2" t="s">
         <v>311</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BF2" t="s">
         <v>312</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BG2" t="s">
         <v>313</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BH2" t="s">
         <v>314</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BI2" t="s">
         <v>315</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BJ2" t="s">
         <v>316</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BK2" t="s">
         <v>317</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BL2" t="s">
         <v>318</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BM2" t="s">
         <v>319</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BN2" t="s">
         <v>320</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BO2" t="s">
         <v>79</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BP2" t="s">
         <v>321</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BQ2" t="s">
         <v>322</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BR2" t="s">
         <v>323</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BS2" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BT2" t="s">
         <v>325</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BU2" t="s">
         <v>95</v>
       </c>
-      <c r="BT2" s="5" t="s">
+      <c r="BV2" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="BU2" s="5" t="s">
+      <c r="BW2" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="BV2" s="5" t="s">
+      <c r="BX2" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="BW2" s="5" t="s">
+      <c r="BY2" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="BX2" s="5" t="s">
+      <c r="BZ2" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="BY2" s="5" t="s">
+      <c r="CA2" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CB2" t="s">
         <v>332</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CC2" t="s">
         <v>333</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CD2" t="s">
         <v>334</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CE2" t="s">
         <v>335</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CF2" t="s">
         <v>336</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CG2" t="s">
         <v>337</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CH2" t="s">
         <v>338</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CI2" t="s">
         <v>339</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CJ2" t="s">
         <v>340</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CK2" t="s">
         <v>341</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CL2" t="s">
         <v>342</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CM2" t="s">
         <v>343</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CN2" t="s">
         <v>344</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CO2" t="s">
         <v>345</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CP2" t="s">
         <v>346</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CQ2" t="s">
         <v>347</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CR2" t="s">
         <v>348</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CS2" t="s">
         <v>349</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CT2" t="s">
         <v>350</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CU2" t="s">
         <v>351</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CV2" t="s">
         <v>352</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CW2" t="s">
         <v>353</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CX2" t="s">
         <v>354</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CY2" t="s">
         <v>355</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CZ2" t="s">
         <v>356</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DA2" t="s">
         <v>357</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DB2" t="s">
         <v>358</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DC2" t="s">
         <v>359</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DD2" t="s">
         <v>360</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DE2" t="s">
         <v>361</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DF2" t="s">
         <v>362</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DG2" t="s">
         <v>363</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DH2" t="s">
         <v>364</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DI2" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="3" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7407,182 +7439,182 @@
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
-      <c r="AR3" t="s">
+      <c r="AR3" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="AS3" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="AT3" t="s">
         <v>372</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>117</v>
       </c>
       <c r="AU3" t="s">
         <v>116</v>
       </c>
       <c r="AV3" t="s">
-        <v>373</v>
+        <v>117</v>
       </c>
       <c r="AW3" t="s">
         <v>116</v>
       </c>
       <c r="AX3" t="s">
-        <v>117</v>
+        <v>373</v>
       </c>
       <c r="AY3" t="s">
         <v>116</v>
       </c>
       <c r="AZ3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BA3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="BB3" t="s">
         <v>118</v>
       </c>
       <c r="BC3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD3" t="s">
         <v>118</v>
       </c>
-      <c r="BD3" t="s">
+      <c r="BE3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BF3" t="s">
         <v>117</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>372</v>
       </c>
       <c r="BG3" t="s">
         <v>116</v>
       </c>
       <c r="BH3" t="s">
-        <v>117</v>
+        <v>372</v>
       </c>
       <c r="BI3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="BJ3" t="s">
         <v>117</v>
       </c>
       <c r="BK3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BM3" t="s">
         <v>118</v>
       </c>
-      <c r="BL3" t="s">
+      <c r="BN3" t="s">
         <v>118</v>
       </c>
-      <c r="BM3" t="s">
+      <c r="BO3" t="s">
         <v>119</v>
       </c>
-      <c r="BN3" t="s">
+      <c r="BP3" t="s">
         <v>119</v>
       </c>
-      <c r="BO3" t="s">
+      <c r="BQ3" t="s">
         <v>374</v>
       </c>
-      <c r="BP3" t="s">
+      <c r="BR3" t="s">
         <v>375</v>
       </c>
-      <c r="BQ3" t="s">
+      <c r="BS3" t="s">
         <v>117</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="BT3" t="s">
         <v>117</v>
       </c>
-      <c r="BS3" t="s">
+      <c r="BU3" t="s">
         <v>116</v>
       </c>
-      <c r="BT3" s="5" t="s">
+      <c r="BV3" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="BU3" s="5" t="s">
+      <c r="BW3" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="BV3" s="5" t="s">
+      <c r="BX3" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="BW3" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="BX3" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="BY3" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="BZ3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>377</v>
+      <c r="BZ3" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="CA3" s="5" t="s">
+        <v>376</v>
       </c>
       <c r="CB3" t="s">
         <v>124</v>
       </c>
       <c r="CC3" t="s">
-        <v>124</v>
+        <v>377</v>
       </c>
       <c r="CD3" t="s">
         <v>124</v>
       </c>
       <c r="CE3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CG3" t="s">
         <v>378</v>
       </c>
-      <c r="CF3" t="s">
+      <c r="CH3" t="s">
         <v>379</v>
       </c>
-      <c r="CG3" t="s">
+      <c r="CI3" t="s">
         <v>2</v>
       </c>
-      <c r="CH3" t="s">
+      <c r="CJ3" t="s">
         <v>380</v>
       </c>
-      <c r="CI3" t="s">
+      <c r="CK3" t="s">
         <v>380</v>
       </c>
-      <c r="CJ3" t="s">
+      <c r="CL3" t="s">
         <v>125</v>
       </c>
-      <c r="CK3" t="s">
+      <c r="CM3" t="s">
         <v>120</v>
       </c>
-      <c r="CL3" t="s">
+      <c r="CN3" t="s">
         <v>120</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>123</v>
       </c>
       <c r="CO3" t="s">
         <v>123</v>
       </c>
       <c r="CP3" t="s">
-        <v>377</v>
+        <v>123</v>
       </c>
       <c r="CQ3" t="s">
         <v>123</v>
       </c>
       <c r="CR3" t="s">
+        <v>377</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>123</v>
+      </c>
+      <c r="CT3" t="s">
         <v>116</v>
       </c>
-      <c r="CS3" t="s">
+      <c r="CU3" t="s">
         <v>125</v>
       </c>
-      <c r="CT3" t="s">
+      <c r="CV3" t="s">
         <v>381</v>
       </c>
-      <c r="CU3" t="s">
+      <c r="CW3" t="s">
         <v>382</v>
       </c>
-      <c r="CV3" t="s">
+      <c r="CX3" t="s">
         <v>382</v>
-      </c>
-      <c r="CW3" t="s">
-        <v>381</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>381</v>
       </c>
       <c r="CY3" t="s">
         <v>381</v>
@@ -7594,10 +7626,10 @@
         <v>381</v>
       </c>
       <c r="DB3" t="s">
-        <v>116</v>
+        <v>381</v>
       </c>
       <c r="DC3" t="s">
-        <v>116</v>
+        <v>381</v>
       </c>
       <c r="DD3" t="s">
         <v>116</v>
@@ -7611,13 +7643,19 @@
       <c r="DG3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="4" spans="1:111" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="DH3" t="s">
+        <v>116</v>
+      </c>
+      <c r="DI3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:113" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="5" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -7639,50 +7677,50 @@
       <c r="AO5" t="s">
         <v>386</v>
       </c>
-      <c r="AR5" t="s">
+      <c r="AT5" t="s">
         <v>387</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AX5" t="s">
         <v>388</v>
       </c>
-      <c r="AX5">
-        <v>1</v>
-      </c>
-      <c r="BB5">
-        <v>1</v>
-      </c>
-      <c r="BH5">
+      <c r="AZ5">
+        <v>1</v>
+      </c>
+      <c r="BD5">
+        <v>1</v>
+      </c>
+      <c r="BJ5">
         <v>1.3</v>
       </c>
-      <c r="BI5">
-        <v>1</v>
-      </c>
-      <c r="BJ5">
+      <c r="BK5">
+        <v>1</v>
+      </c>
+      <c r="BL5">
         <v>0</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BO5" t="s">
         <v>389</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BP5" t="s">
         <v>390</v>
       </c>
-      <c r="BZ5" t="s">
+      <c r="CB5" t="s">
         <v>391</v>
       </c>
-      <c r="CE5" t="s">
+      <c r="CG5" t="s">
         <v>392</v>
       </c>
-      <c r="CL5" t="s">
+      <c r="CN5" t="s">
         <v>393</v>
       </c>
-      <c r="CP5">
+      <c r="CR5">
         <v>0.1</v>
       </c>
-      <c r="CW5" t="s">
+      <c r="CY5" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="6" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>395</v>
       </c>
@@ -7704,20 +7742,20 @@
       <c r="AO6" t="s">
         <v>386</v>
       </c>
-      <c r="AR6" t="s">
+      <c r="AT6" t="s">
         <v>387</v>
       </c>
-      <c r="BB6">
-        <v>1</v>
-      </c>
-      <c r="CJ6" t="s">
+      <c r="BD6">
+        <v>1</v>
+      </c>
+      <c r="CL6" t="s">
         <v>398</v>
       </c>
-      <c r="CK6" t="s">
+      <c r="CM6" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="7" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>389</v>
       </c>
@@ -7740,23 +7778,23 @@
       <c r="AO7" t="s">
         <v>386</v>
       </c>
-      <c r="AT7">
+      <c r="AV7">
         <v>99</v>
       </c>
-      <c r="BB7">
+      <c r="BD7">
         <v>99</v>
       </c>
-      <c r="BQ7">
+      <c r="BS7">
         <v>0.1</v>
       </c>
-      <c r="CJ7" t="s">
+      <c r="CL7" t="s">
         <v>399</v>
       </c>
-      <c r="CK7" t="s">
+      <c r="CM7" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="10" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>400</v>
       </c>
@@ -7790,81 +7828,81 @@
       <c r="AO10" t="s">
         <v>405</v>
       </c>
-      <c r="AR10" t="s">
+      <c r="AT10" t="s">
         <v>387</v>
       </c>
-      <c r="AV10" t="s">
+      <c r="AX10" t="s">
         <v>388</v>
       </c>
-      <c r="AX10">
+      <c r="AZ10">
         <v>1.5</v>
       </c>
-      <c r="BB10">
-        <v>1</v>
-      </c>
-      <c r="BC10">
-        <v>1</v>
-      </c>
       <c r="BD10">
+        <v>1</v>
+      </c>
+      <c r="BE10">
+        <v>1</v>
+      </c>
+      <c r="BF10">
         <v>0.1</v>
       </c>
-      <c r="BH10">
+      <c r="BJ10">
         <v>1.3</v>
       </c>
-      <c r="BI10">
-        <v>1</v>
-      </c>
-      <c r="BJ10">
+      <c r="BK10">
+        <v>1</v>
+      </c>
+      <c r="BL10">
         <v>0</v>
       </c>
-      <c r="BM10" t="s">
+      <c r="BO10" t="s">
         <v>389</v>
       </c>
-      <c r="BN10" t="s">
+      <c r="BP10" t="s">
         <v>406</v>
       </c>
-      <c r="BR10">
+      <c r="BT10">
         <v>0.3</v>
       </c>
-      <c r="BT10" s="5">
+      <c r="BV10" s="5">
         <v>2</v>
       </c>
-      <c r="BU10" s="5">
+      <c r="BW10" s="5">
         <v>2</v>
       </c>
-      <c r="BV10" s="5">
-        <v>1</v>
-      </c>
-      <c r="BW10" s="5" t="s">
+      <c r="BX10" s="5">
+        <v>1</v>
+      </c>
+      <c r="BY10" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="BZ10" t="s">
+      <c r="CB10" t="s">
         <v>408</v>
       </c>
-      <c r="CE10" t="s">
+      <c r="CG10" t="s">
         <v>392</v>
       </c>
-      <c r="CJ10" s="4"/>
-      <c r="CL10" t="s">
+      <c r="CL10" s="4"/>
+      <c r="CN10" t="s">
         <v>393</v>
       </c>
-      <c r="CP10">
+      <c r="CR10">
         <v>0.1</v>
       </c>
-      <c r="CW10" t="s">
+      <c r="CY10" t="s">
         <v>394</v>
       </c>
-      <c r="DB10">
-        <v>1</v>
-      </c>
-      <c r="DE10">
-        <v>1</v>
-      </c>
-      <c r="DF10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="DD10">
+        <v>1</v>
+      </c>
+      <c r="DG10">
+        <v>1</v>
+      </c>
+      <c r="DH10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>406</v>
       </c>
@@ -7883,32 +7921,32 @@
       <c r="AO11" t="s">
         <v>405</v>
       </c>
-      <c r="AR11" t="s">
+      <c r="AT11" t="s">
         <v>387</v>
       </c>
-      <c r="BB11">
-        <v>1</v>
-      </c>
-      <c r="BC11">
-        <v>1</v>
-      </c>
       <c r="BD11">
+        <v>1</v>
+      </c>
+      <c r="BE11">
+        <v>1</v>
+      </c>
+      <c r="BF11">
         <v>0.1</v>
       </c>
-      <c r="CJ11" t="s">
+      <c r="CL11" t="s">
         <v>409</v>
       </c>
-      <c r="CK11" t="s">
+      <c r="CM11" t="s">
         <v>393</v>
       </c>
-      <c r="CL11" t="s">
+      <c r="CN11" t="s">
         <v>397</v>
       </c>
-      <c r="CP11">
+      <c r="CR11">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>410</v>
       </c>
@@ -7930,26 +7968,26 @@
       <c r="AO12" t="s">
         <v>386</v>
       </c>
-      <c r="AR12" t="s">
+      <c r="AT12" t="s">
         <v>387</v>
       </c>
-      <c r="BB12">
-        <v>1</v>
-      </c>
-      <c r="BC12">
-        <v>1</v>
-      </c>
       <c r="BD12">
+        <v>1</v>
+      </c>
+      <c r="BE12">
+        <v>1</v>
+      </c>
+      <c r="BF12">
         <v>0.1</v>
       </c>
-      <c r="CJ12" t="s">
+      <c r="CL12" t="s">
         <v>409</v>
       </c>
-      <c r="CK12" t="s">
+      <c r="CM12" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="14" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>412</v>
       </c>
@@ -7983,54 +8021,54 @@
       <c r="AG14" t="s">
         <v>417</v>
       </c>
-      <c r="BB14">
-        <v>1</v>
-      </c>
-      <c r="BM14" t="s">
+      <c r="BD14">
+        <v>1</v>
+      </c>
+      <c r="BO14" t="s">
         <v>418</v>
       </c>
-      <c r="BN14" t="s">
+      <c r="BP14" t="s">
         <v>419</v>
       </c>
-      <c r="BR14">
+      <c r="BT14">
         <v>9999</v>
       </c>
-      <c r="BT14" s="5">
+      <c r="BV14" s="5">
         <v>0</v>
       </c>
-      <c r="BU14" s="5">
+      <c r="BW14" s="5">
         <v>25</v>
       </c>
-      <c r="BV14" s="5">
-        <v>1</v>
-      </c>
-      <c r="BW14" s="5" t="s">
+      <c r="BX14" s="5">
+        <v>1</v>
+      </c>
+      <c r="BY14" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="CJ14" s="4"/>
-      <c r="CL14" t="s">
+      <c r="CL14" s="4"/>
+      <c r="CN14" t="s">
         <v>420</v>
       </c>
-      <c r="CM14">
+      <c r="CO14">
         <v>35</v>
       </c>
-      <c r="CP14">
+      <c r="CR14">
         <v>9999</v>
       </c>
-      <c r="CS14" t="s">
+      <c r="CU14" t="s">
         <v>421</v>
       </c>
-      <c r="DB14">
-        <v>1</v>
-      </c>
-      <c r="DE14">
-        <v>1</v>
-      </c>
-      <c r="DF14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="DD14">
+        <v>1</v>
+      </c>
+      <c r="DG14">
+        <v>1</v>
+      </c>
+      <c r="DH14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>418</v>
       </c>
@@ -8052,50 +8090,50 @@
       <c r="AO15" t="s">
         <v>386</v>
       </c>
-      <c r="AR15" t="s">
+      <c r="AT15" t="s">
         <v>387</v>
       </c>
-      <c r="AV15" t="s">
+      <c r="AX15" t="s">
         <v>388</v>
       </c>
-      <c r="AX15">
-        <v>1</v>
-      </c>
-      <c r="BB15">
-        <v>1</v>
-      </c>
-      <c r="BH15">
+      <c r="AZ15">
+        <v>1</v>
+      </c>
+      <c r="BD15">
+        <v>1</v>
+      </c>
+      <c r="BJ15">
         <v>1.5</v>
       </c>
-      <c r="BI15">
-        <v>1</v>
-      </c>
-      <c r="BJ15">
+      <c r="BK15">
+        <v>1</v>
+      </c>
+      <c r="BL15">
         <v>0</v>
       </c>
-      <c r="BM15" t="s">
+      <c r="BO15" t="s">
         <v>389</v>
       </c>
-      <c r="BN15" t="s">
+      <c r="BP15" t="s">
         <v>395</v>
       </c>
-      <c r="BZ15" t="s">
+      <c r="CB15" t="s">
         <v>423</v>
       </c>
-      <c r="CE15" t="s">
+      <c r="CG15" t="s">
         <v>392</v>
       </c>
-      <c r="CL15" t="s">
+      <c r="CN15" t="s">
         <v>393</v>
       </c>
-      <c r="CP15">
+      <c r="CR15">
         <v>0.1</v>
       </c>
-      <c r="CW15" t="s">
+      <c r="CY15" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="16" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>419</v>
       </c>
@@ -8121,36 +8159,36 @@
       <c r="AG16" t="s">
         <v>417</v>
       </c>
-      <c r="BB16">
-        <v>1</v>
-      </c>
-      <c r="BQ16">
+      <c r="BD16">
+        <v>1</v>
+      </c>
+      <c r="BS16">
         <v>0.33300000000000002</v>
       </c>
-      <c r="BX16"/>
-      <c r="BZ16" t="s">
+      <c r="BZ16"/>
+      <c r="CB16" t="s">
         <v>425</v>
       </c>
-      <c r="CE16" t="s">
+      <c r="CG16" t="s">
         <v>392</v>
       </c>
-      <c r="DB16">
-        <v>1</v>
-      </c>
       <c r="DD16">
         <v>1</v>
       </c>
-      <c r="DE16">
-        <v>1</v>
-      </c>
       <c r="DF16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="BT17"/>
-    </row>
-    <row r="18" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DG16">
+        <v>1</v>
+      </c>
+      <c r="DH16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="BV17"/>
+    </row>
+    <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>426</v>
       </c>
@@ -8184,57 +8222,57 @@
       <c r="AG18" t="s">
         <v>417</v>
       </c>
-      <c r="AR18" t="s">
+      <c r="AT18" t="s">
         <v>431</v>
       </c>
-      <c r="BB18">
-        <v>1</v>
-      </c>
-      <c r="BM18" s="8" t="s">
+      <c r="BD18">
+        <v>1</v>
+      </c>
+      <c r="BO18" s="8" t="s">
         <v>566</v>
       </c>
-      <c r="BN18" t="s">
+      <c r="BP18" t="s">
         <v>432</v>
       </c>
-      <c r="BR18">
+      <c r="BT18">
         <v>30</v>
       </c>
-      <c r="BT18" s="5">
+      <c r="BV18" s="5">
         <v>30</v>
       </c>
-      <c r="BU18" s="5">
+      <c r="BW18" s="5">
         <v>40</v>
       </c>
-      <c r="BV18" s="5">
-        <v>1</v>
-      </c>
-      <c r="BW18" s="5" t="s">
+      <c r="BX18" s="5">
+        <v>1</v>
+      </c>
+      <c r="BY18" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="CJ18" s="4"/>
-      <c r="CL18" t="s">
+      <c r="CL18" s="4"/>
+      <c r="CN18" t="s">
         <v>433</v>
       </c>
-      <c r="CM18">
+      <c r="CO18">
         <v>1.25</v>
       </c>
-      <c r="CP18">
+      <c r="CR18">
         <v>30</v>
       </c>
-      <c r="CS18" t="s">
+      <c r="CU18" t="s">
         <v>434</v>
       </c>
-      <c r="DB18">
-        <v>1</v>
-      </c>
-      <c r="DE18">
-        <v>1</v>
-      </c>
-      <c r="DF18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DD18">
+        <v>1</v>
+      </c>
+      <c r="DG18">
+        <v>1</v>
+      </c>
+      <c r="DH18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>435</v>
       </c>
@@ -8256,47 +8294,47 @@
       <c r="AO19" t="s">
         <v>405</v>
       </c>
-      <c r="AR19" t="s">
+      <c r="AT19" t="s">
         <v>431</v>
       </c>
-      <c r="AV19" t="s">
+      <c r="AX19" t="s">
         <v>388</v>
       </c>
-      <c r="AX19">
-        <v>1</v>
-      </c>
-      <c r="BB19">
-        <v>1</v>
-      </c>
-      <c r="BH19">
+      <c r="AZ19">
+        <v>1</v>
+      </c>
+      <c r="BD19">
+        <v>1</v>
+      </c>
+      <c r="BJ19">
         <v>1.5</v>
       </c>
-      <c r="BI19">
-        <v>1</v>
-      </c>
-      <c r="BJ19">
+      <c r="BK19">
+        <v>1</v>
+      </c>
+      <c r="BL19">
         <v>0</v>
       </c>
-      <c r="BM19" t="s">
+      <c r="BO19" t="s">
         <v>389</v>
       </c>
-      <c r="BN19" t="s">
+      <c r="BP19" t="s">
         <v>395</v>
       </c>
-      <c r="CE19" t="s">
+      <c r="CG19" t="s">
         <v>392</v>
       </c>
-      <c r="CL19" t="s">
+      <c r="CN19" t="s">
         <v>437</v>
       </c>
-      <c r="CP19">
+      <c r="CR19">
         <v>9999</v>
       </c>
-      <c r="CW19" t="s">
+      <c r="CY19" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="20" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>432</v>
       </c>
@@ -8322,33 +8360,33 @@
       <c r="AG20" t="s">
         <v>417</v>
       </c>
-      <c r="BB20">
-        <v>1</v>
-      </c>
-      <c r="BQ20">
+      <c r="BD20">
+        <v>1</v>
+      </c>
+      <c r="BS20">
         <v>0.33300000000000002</v>
       </c>
-      <c r="BX20"/>
-      <c r="BZ20" t="s">
+      <c r="BZ20"/>
+      <c r="CB20" t="s">
         <v>438</v>
       </c>
-      <c r="CE20" t="s">
+      <c r="CG20" t="s">
         <v>392</v>
       </c>
-      <c r="DB20">
-        <v>1</v>
-      </c>
       <c r="DD20">
         <v>1</v>
       </c>
-      <c r="DE20">
-        <v>1</v>
-      </c>
       <c r="DF20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DG20">
+        <v>1</v>
+      </c>
+      <c r="DH20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>439</v>
       </c>
@@ -8377,33 +8415,33 @@
       <c r="AG21" t="s">
         <v>417</v>
       </c>
-      <c r="BB21">
-        <v>1</v>
-      </c>
-      <c r="BQ21">
+      <c r="BD21">
+        <v>1</v>
+      </c>
+      <c r="BS21">
         <v>0.33300000000000002</v>
       </c>
-      <c r="BX21"/>
-      <c r="BZ21" t="s">
+      <c r="BZ21"/>
+      <c r="CB21" t="s">
         <v>441</v>
       </c>
-      <c r="CE21" t="s">
+      <c r="CG21" t="s">
         <v>392</v>
       </c>
-      <c r="DB21">
-        <v>1</v>
-      </c>
       <c r="DD21">
         <v>1</v>
       </c>
-      <c r="DE21">
-        <v>1</v>
-      </c>
       <c r="DF21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DG21">
+        <v>1</v>
+      </c>
+      <c r="DH21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>442</v>
       </c>
@@ -8427,20 +8465,20 @@
       <c r="AO22" t="s">
         <v>386</v>
       </c>
-      <c r="AT22">
+      <c r="AV22">
         <v>99</v>
       </c>
-      <c r="BB22">
+      <c r="BD22">
         <v>99</v>
       </c>
-      <c r="BQ22">
-        <v>1</v>
-      </c>
-      <c r="CJ22" t="s">
+      <c r="BS22">
+        <v>1</v>
+      </c>
+      <c r="CL22" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="23" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>445</v>
       </c>
@@ -8469,23 +8507,23 @@
       <c r="AO23" t="s">
         <v>386</v>
       </c>
-      <c r="AT23">
+      <c r="AV23">
         <v>99</v>
       </c>
-      <c r="BB23">
+      <c r="BD23">
         <v>99</v>
       </c>
-      <c r="BQ23">
+      <c r="BS23">
         <v>0.1</v>
       </c>
-      <c r="CK23" t="s">
+      <c r="CM23" t="s">
         <v>443</v>
       </c>
-      <c r="CS23" s="8" t="s">
+      <c r="CU23" s="8" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="24" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>448</v>
       </c>
@@ -8506,26 +8544,26 @@
       <c r="AO24" t="s">
         <v>386</v>
       </c>
-      <c r="AR24" t="s">
+      <c r="AT24" t="s">
         <v>431</v>
       </c>
-      <c r="BB24">
+      <c r="BD24">
         <v>99</v>
       </c>
-      <c r="BQ24">
+      <c r="BS24">
         <v>0.1</v>
       </c>
-      <c r="CL24" t="s">
+      <c r="CN24" t="s">
         <v>448</v>
       </c>
-      <c r="CM24">
+      <c r="CO24">
         <v>-0.5</v>
       </c>
-      <c r="CP24">
+      <c r="CR24">
         <v>0.2</v>
       </c>
     </row>
-    <row r="25" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>565</v>
       </c>
@@ -8552,26 +8590,26 @@
       <c r="AO25" t="s">
         <v>386</v>
       </c>
-      <c r="AR25" t="s">
+      <c r="AT25" t="s">
         <v>431</v>
       </c>
-      <c r="BB25">
+      <c r="BD25">
         <v>99</v>
       </c>
-      <c r="BQ25">
+      <c r="BS25">
         <v>0.1</v>
       </c>
-      <c r="CS25" t="s">
+      <c r="CU25" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="26" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ26" s="4"/>
-    </row>
-    <row r="27" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ27" s="4"/>
-    </row>
-    <row r="28" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="CL26" s="4"/>
+    </row>
+    <row r="27" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="CL27" s="4"/>
+    </row>
+    <row r="28" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>142</v>
       </c>
@@ -8590,16 +8628,16 @@
       <c r="AG28" t="s">
         <v>417</v>
       </c>
-      <c r="BB28">
-        <v>1</v>
-      </c>
-      <c r="BT28"/>
-      <c r="CJ28" s="4"/>
-      <c r="CS28" t="s">
+      <c r="BD28">
+        <v>1</v>
+      </c>
+      <c r="BV28"/>
+      <c r="CL28" s="4"/>
+      <c r="CU28" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="29" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>149</v>
       </c>
@@ -8621,30 +8659,30 @@
       <c r="AO29" t="s">
         <v>386</v>
       </c>
-      <c r="AR29" t="s">
+      <c r="AT29" t="s">
         <v>454</v>
       </c>
-      <c r="BB29">
+      <c r="BD29">
         <v>4</v>
       </c>
-      <c r="BR29">
+      <c r="BT29">
         <v>0.2</v>
       </c>
-      <c r="CJ29" s="4"/>
-      <c r="CL29" s="8" t="s">
+      <c r="CL29" s="4"/>
+      <c r="CN29" s="8" t="s">
         <v>567</v>
       </c>
-      <c r="CP29">
+      <c r="CR29">
         <v>5</v>
       </c>
-      <c r="CS29" t="s">
+      <c r="CU29" t="s">
         <v>455</v>
       </c>
-      <c r="CW29" t="s">
+      <c r="CY29" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="30" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>457</v>
       </c>
@@ -8663,19 +8701,19 @@
       <c r="AG30" t="s">
         <v>417</v>
       </c>
-      <c r="BB30">
-        <v>1</v>
-      </c>
-      <c r="BT30"/>
-      <c r="CJ30" s="4"/>
-      <c r="CS30" t="s">
+      <c r="BD30">
+        <v>1</v>
+      </c>
+      <c r="BV30"/>
+      <c r="CL30" s="4"/>
+      <c r="CU30" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="31" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ31" s="4"/>
-    </row>
-    <row r="32" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="CL31" s="4"/>
+    </row>
+    <row r="32" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>460</v>
       </c>
@@ -8697,39 +8735,39 @@
       <c r="AD32">
         <v>1</v>
       </c>
-      <c r="AT32">
+      <c r="AV32">
         <v>0.4</v>
       </c>
-      <c r="BB32">
-        <v>1</v>
-      </c>
-      <c r="BM32" t="s">
+      <c r="BD32">
+        <v>1</v>
+      </c>
+      <c r="BO32" t="s">
         <v>461</v>
       </c>
-      <c r="BN32" t="s">
+      <c r="BP32" t="s">
         <v>462</v>
       </c>
-      <c r="BR32">
+      <c r="BT32">
         <v>6</v>
       </c>
-      <c r="BT32" s="5">
-        <v>1</v>
-      </c>
-      <c r="BU32" s="5">
-        <v>1</v>
-      </c>
       <c r="BV32" s="5">
         <v>1</v>
       </c>
-      <c r="BW32" s="5" t="s">
+      <c r="BW32" s="5">
+        <v>1</v>
+      </c>
+      <c r="BX32" s="5">
+        <v>1</v>
+      </c>
+      <c r="BY32" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="CJ32" s="4"/>
-      <c r="DF32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CL32" s="4"/>
+      <c r="DH32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>462</v>
       </c>
@@ -8763,38 +8801,38 @@
       <c r="AG33" t="s">
         <v>417</v>
       </c>
-      <c r="AR33" t="s">
+      <c r="AT33" t="s">
         <v>464</v>
       </c>
-      <c r="AV33" t="s">
+      <c r="AX33" t="s">
         <v>465</v>
       </c>
-      <c r="AX33">
+      <c r="AZ33">
         <v>999</v>
       </c>
-      <c r="AZ33">
+      <c r="BB33">
         <v>2</v>
       </c>
-      <c r="BB33">
-        <v>1</v>
-      </c>
-      <c r="BT33" s="7"/>
-      <c r="BU33" s="7"/>
+      <c r="BD33">
+        <v>1</v>
+      </c>
       <c r="BV33" s="7"/>
       <c r="BW33" s="7"/>
       <c r="BX33" s="7"/>
       <c r="BY33" s="7"/>
-      <c r="DB33">
-        <v>1</v>
-      </c>
-      <c r="DE33">
-        <v>1</v>
-      </c>
-      <c r="DF33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="BZ33" s="7"/>
+      <c r="CA33" s="7"/>
+      <c r="DD33">
+        <v>1</v>
+      </c>
+      <c r="DG33">
+        <v>1</v>
+      </c>
+      <c r="DH33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>466</v>
       </c>
@@ -8813,16 +8851,16 @@
       <c r="AG34" t="s">
         <v>417</v>
       </c>
-      <c r="BB34">
-        <v>1</v>
-      </c>
-      <c r="BT34"/>
-      <c r="CJ34" s="4"/>
-      <c r="CS34" t="s">
+      <c r="BD34">
+        <v>1</v>
+      </c>
+      <c r="BV34"/>
+      <c r="CL34" s="4"/>
+      <c r="CU34" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="35" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>469</v>
       </c>
@@ -8841,19 +8879,19 @@
       <c r="AG35" t="s">
         <v>417</v>
       </c>
-      <c r="BB35">
-        <v>1</v>
-      </c>
-      <c r="BT35"/>
-      <c r="CJ35" s="4"/>
-      <c r="CS35" t="s">
+      <c r="BD35">
+        <v>1</v>
+      </c>
+      <c r="BV35"/>
+      <c r="CL35" s="4"/>
+      <c r="CU35" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="36" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ36" s="4"/>
-    </row>
-    <row r="37" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="CL36" s="4"/>
+    </row>
+    <row r="37" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>471</v>
       </c>
@@ -8875,14 +8913,14 @@
       <c r="AG37" t="s">
         <v>417</v>
       </c>
-      <c r="BB37">
-        <v>1</v>
-      </c>
-      <c r="CW37" t="s">
+      <c r="BD37">
+        <v>1</v>
+      </c>
+      <c r="CY37" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="38" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>473</v>
       </c>
@@ -8922,53 +8960,53 @@
       <c r="AO38" t="s">
         <v>386</v>
       </c>
-      <c r="AR38" t="s">
+      <c r="AT38" t="s">
         <v>454</v>
       </c>
-      <c r="AV38" t="s">
+      <c r="AX38" t="s">
         <v>388</v>
       </c>
-      <c r="AX38">
+      <c r="AZ38">
         <v>1.5</v>
       </c>
-      <c r="BB38">
+      <c r="BD38">
         <v>99</v>
       </c>
-      <c r="BC38">
+      <c r="BE38">
         <v>11</v>
       </c>
-      <c r="BD38">
+      <c r="BF38">
         <v>0.5</v>
       </c>
-      <c r="BM38" t="s">
+      <c r="BO38" t="s">
         <v>474</v>
       </c>
-      <c r="BN38" t="s">
+      <c r="BP38" t="s">
         <v>475</v>
       </c>
-      <c r="BT38" s="7"/>
-      <c r="BU38" s="7"/>
       <c r="BV38" s="7"/>
       <c r="BW38" s="7"/>
       <c r="BX38" s="7"/>
       <c r="BY38" s="7"/>
-      <c r="BZ38" t="s">
+      <c r="BZ38" s="7"/>
+      <c r="CA38" s="7"/>
+      <c r="CB38" t="s">
         <v>57</v>
       </c>
-      <c r="CE38" t="s">
+      <c r="CG38" t="s">
         <v>392</v>
       </c>
-      <c r="CJ38" s="4" t="s">
+      <c r="CL38" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="CS38" t="s">
+      <c r="CU38" t="s">
         <v>477</v>
       </c>
-      <c r="CW38" t="s">
+      <c r="CY38" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="39" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>474</v>
       </c>
@@ -8996,28 +9034,28 @@
       <c r="AO39" t="s">
         <v>386</v>
       </c>
-      <c r="AR39" t="s">
+      <c r="AT39" t="s">
         <v>454</v>
       </c>
-      <c r="BB39">
+      <c r="BD39">
         <v>99</v>
       </c>
-      <c r="BT39"/>
-      <c r="CJ39" s="4"/>
-      <c r="CL39" t="s">
+      <c r="BV39"/>
+      <c r="CL39" s="4"/>
+      <c r="CN39" t="s">
         <v>479</v>
       </c>
-      <c r="CM39">
+      <c r="CO39">
         <v>-0.8</v>
       </c>
-      <c r="CP39">
+      <c r="CR39">
         <v>6</v>
       </c>
-      <c r="CW39" t="s">
+      <c r="CY39" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="40" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>475</v>
       </c>
@@ -9036,1181 +9074,1181 @@
       <c r="AG40" t="s">
         <v>417</v>
       </c>
-      <c r="AR40" t="s">
+      <c r="AT40" t="s">
         <v>464</v>
       </c>
-      <c r="AV40" t="s">
+      <c r="AX40" t="s">
         <v>465</v>
       </c>
-      <c r="AX40">
+      <c r="AZ40">
         <v>0.09</v>
       </c>
-      <c r="AZ40">
-        <v>1</v>
-      </c>
       <c r="BB40">
         <v>1</v>
       </c>
-      <c r="BC40">
+      <c r="BD40">
+        <v>1</v>
+      </c>
+      <c r="BE40">
         <v>11</v>
       </c>
-      <c r="BD40">
+      <c r="BF40">
         <v>0.5</v>
       </c>
-      <c r="BT40"/>
-      <c r="CJ40" s="4"/>
-      <c r="CW40" t="s">
+      <c r="BV40"/>
+      <c r="CL40" s="4"/>
+      <c r="CY40" t="s">
         <v>478</v>
       </c>
-      <c r="DB40">
-        <v>1</v>
-      </c>
-      <c r="DE40">
-        <v>1</v>
-      </c>
-      <c r="DF40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ45" s="4"/>
-    </row>
-    <row r="46" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ46" s="4"/>
-    </row>
-    <row r="49" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ49" s="4"/>
-    </row>
-    <row r="50" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ50" s="4"/>
-    </row>
-    <row r="54" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ54" s="4"/>
-    </row>
-    <row r="58" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ58" s="4"/>
-    </row>
-    <row r="60" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ60" s="4"/>
-    </row>
-    <row r="61" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ61" s="4"/>
-    </row>
-    <row r="63" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ63" s="4"/>
-    </row>
-    <row r="64" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ64" s="4"/>
-    </row>
-    <row r="66" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT66"/>
-    </row>
-    <row r="67" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT67"/>
-      <c r="CJ67" s="4"/>
-    </row>
-    <row r="68" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ68" s="4"/>
-    </row>
-    <row r="70" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ70" s="4"/>
-    </row>
-    <row r="79" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT79"/>
-    </row>
-    <row r="80" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT80"/>
-      <c r="CJ80" s="4"/>
-    </row>
-    <row r="81" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ81" s="4"/>
-    </row>
-    <row r="82" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ82" s="4"/>
-    </row>
-    <row r="83" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT83"/>
-    </row>
-    <row r="84" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT84"/>
-      <c r="CJ84" s="4"/>
-    </row>
-    <row r="85" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ85" s="4"/>
-    </row>
-    <row r="87" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT87"/>
-    </row>
-    <row r="88" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT88"/>
-      <c r="CJ88" s="4"/>
-    </row>
-    <row r="89" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ89" s="4"/>
-    </row>
-    <row r="91" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT91"/>
-    </row>
-    <row r="92" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ92" s="4"/>
-    </row>
-    <row r="95" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ95" s="4"/>
-    </row>
-    <row r="99" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ99" s="4"/>
-    </row>
-    <row r="101" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT101"/>
-    </row>
-    <row r="102" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ102" s="4"/>
-    </row>
-    <row r="109" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT109"/>
-    </row>
-    <row r="110" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ110" s="4"/>
-    </row>
-    <row r="111" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ111" s="4"/>
-    </row>
-    <row r="113" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT113"/>
-    </row>
-    <row r="114" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT114"/>
-      <c r="CJ114" s="4"/>
-    </row>
-    <row r="115" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ115" s="4"/>
-    </row>
-    <row r="121" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT121"/>
-    </row>
-    <row r="122" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT122"/>
-      <c r="CJ122" s="4"/>
-    </row>
-    <row r="123" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT123"/>
-      <c r="CJ123" s="4"/>
-    </row>
-    <row r="124" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ124" s="4"/>
-    </row>
-    <row r="129" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT129"/>
-    </row>
-    <row r="130" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT130"/>
-    </row>
-    <row r="134" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT134"/>
-    </row>
-    <row r="135" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ135" s="4"/>
-    </row>
-    <row r="136" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT136"/>
-    </row>
-    <row r="137" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ137" s="4"/>
-    </row>
-    <row r="147" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT147"/>
-    </row>
-    <row r="148" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ148" s="4"/>
-    </row>
-    <row r="150" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT150"/>
-    </row>
-    <row r="151" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ151" s="4"/>
-    </row>
-    <row r="159" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT159"/>
-    </row>
-    <row r="160" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ160" s="4"/>
-    </row>
-    <row r="164" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT164"/>
-    </row>
-    <row r="165" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ165" s="4"/>
-    </row>
-    <row r="167" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT167"/>
-    </row>
-    <row r="168" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ168" s="4"/>
-    </row>
-    <row r="184" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT184"/>
-    </row>
-    <row r="185" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT185"/>
-      <c r="CJ185" s="4"/>
-    </row>
-    <row r="186" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT186"/>
-      <c r="CJ186" s="4"/>
-    </row>
-    <row r="187" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT187"/>
-      <c r="CJ187" s="4"/>
-    </row>
-    <row r="188" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT188"/>
-    </row>
-    <row r="190" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT190"/>
-    </row>
-    <row r="191" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT191"/>
-      <c r="CJ191" s="4"/>
-    </row>
-    <row r="192" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT192"/>
-      <c r="CJ192" s="4"/>
-    </row>
-    <row r="193" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ193" s="4"/>
-    </row>
-    <row r="197" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT197"/>
-    </row>
-    <row r="198" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ198" s="4"/>
-    </row>
-    <row r="200" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT200"/>
-    </row>
-    <row r="201" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT201"/>
-      <c r="CJ201" s="4"/>
-    </row>
-    <row r="202" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT202"/>
-      <c r="CJ202" s="4"/>
-    </row>
-    <row r="203" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ203" s="4"/>
-    </row>
-    <row r="219" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT219"/>
-    </row>
-    <row r="220" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ220" s="4"/>
-    </row>
-    <row r="228" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ228" s="4"/>
-    </row>
-    <row r="229" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ229" s="4"/>
-    </row>
-    <row r="230" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ230" s="4"/>
-    </row>
-    <row r="231" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ231" s="4"/>
-    </row>
-    <row r="232" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ232" s="4"/>
-    </row>
-    <row r="234" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT234"/>
-    </row>
-    <row r="235" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ235" s="4"/>
-    </row>
-    <row r="236" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT236"/>
-    </row>
-    <row r="237" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT237"/>
-      <c r="CJ237" s="4"/>
-    </row>
-    <row r="238" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ238" s="4"/>
-    </row>
-    <row r="240" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT240"/>
-    </row>
-    <row r="241" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT241"/>
-      <c r="CJ241" s="4"/>
-    </row>
-    <row r="242" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT242"/>
-      <c r="CJ242" s="4"/>
-    </row>
-    <row r="243" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ243" s="4"/>
-    </row>
-    <row r="245" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ245" s="4"/>
-    </row>
-    <row r="247" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ247" s="4"/>
-    </row>
-    <row r="249" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ249" s="4"/>
-    </row>
-    <row r="252" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ252" s="4"/>
-    </row>
-    <row r="253" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ253" s="4"/>
-    </row>
-    <row r="254" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ254" s="4"/>
-    </row>
-    <row r="255" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ255" s="4"/>
-    </row>
-    <row r="256" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ256" s="4"/>
-    </row>
-    <row r="257" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ257" s="4"/>
-    </row>
-    <row r="258" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT258"/>
-    </row>
-    <row r="259" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT259"/>
-      <c r="CJ259" s="4"/>
-    </row>
-    <row r="260" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT260"/>
-      <c r="CJ260" s="4"/>
-    </row>
-    <row r="261" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ261" s="4"/>
-    </row>
-    <row r="262" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ262" s="4"/>
-    </row>
-    <row r="263" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ263" s="4"/>
-    </row>
-    <row r="264" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ264" s="4"/>
-    </row>
-    <row r="266" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ266" s="4"/>
-    </row>
-    <row r="267" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ267" s="4"/>
-    </row>
-    <row r="268" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT268"/>
-    </row>
-    <row r="269" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT269"/>
-      <c r="CJ269" s="4"/>
-    </row>
-    <row r="270" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT270"/>
-      <c r="CJ270" s="4"/>
-    </row>
-    <row r="271" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ271" s="4"/>
-    </row>
-    <row r="272" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ272" s="4"/>
-    </row>
-    <row r="274" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ274" s="4"/>
-    </row>
-    <row r="275" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ275" s="4"/>
-    </row>
-    <row r="276" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT276"/>
-      <c r="CJ276" s="4"/>
-    </row>
-    <row r="277" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT277"/>
-      <c r="CJ277" s="4"/>
-    </row>
-    <row r="278" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ278" s="4"/>
-    </row>
-    <row r="279" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ279" s="4"/>
-    </row>
-    <row r="280" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ280" s="4"/>
-    </row>
-    <row r="282" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT282"/>
-      <c r="CJ282" s="4"/>
-    </row>
-    <row r="283" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ283" s="4"/>
-    </row>
-    <row r="284" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ284" s="4"/>
-    </row>
-    <row r="286" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT286"/>
-      <c r="CJ286" s="4"/>
-    </row>
-    <row r="287" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT287"/>
-      <c r="CJ287" s="4"/>
-    </row>
-    <row r="288" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ288" s="4"/>
-    </row>
-    <row r="290" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ290" s="4"/>
-    </row>
-    <row r="292" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ292" s="4"/>
-    </row>
-    <row r="295" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ295" s="4"/>
-    </row>
-    <row r="296" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ296" s="4"/>
-    </row>
-    <row r="300" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT300"/>
-    </row>
-    <row r="301" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT301"/>
-      <c r="CJ301" s="4"/>
-    </row>
-    <row r="302" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT302"/>
-      <c r="CJ302" s="4"/>
-    </row>
-    <row r="303" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ303" s="4"/>
-    </row>
-    <row r="304" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ304" s="4"/>
-    </row>
-    <row r="305" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT305"/>
-    </row>
-    <row r="306" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ306" s="4"/>
-    </row>
-    <row r="308" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ308" s="4"/>
-    </row>
-    <row r="309" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ309" s="4"/>
-    </row>
-    <row r="311" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ311" s="4"/>
-    </row>
-    <row r="312" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ312" s="4"/>
-    </row>
-    <row r="313" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ313" s="4"/>
-    </row>
-    <row r="314" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ314" s="4"/>
-    </row>
-    <row r="315" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ315" s="4"/>
-    </row>
-    <row r="316" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ316" s="4"/>
-    </row>
-    <row r="317" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ317" s="4"/>
-    </row>
-    <row r="319" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT319"/>
-    </row>
-    <row r="320" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ320" s="4"/>
-    </row>
-    <row r="321" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ321" s="4"/>
-    </row>
-    <row r="354" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS354" s="9"/>
-      <c r="BT354" s="10"/>
-    </row>
-    <row r="355" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="DD40">
+        <v>1</v>
+      </c>
+      <c r="DG40">
+        <v>1</v>
+      </c>
+      <c r="DH40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="CL45" s="4"/>
+    </row>
+    <row r="46" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="CL46" s="4"/>
+    </row>
+    <row r="49" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL49" s="4"/>
+    </row>
+    <row r="50" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL50" s="4"/>
+    </row>
+    <row r="54" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL54" s="4"/>
+    </row>
+    <row r="58" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL58" s="4"/>
+    </row>
+    <row r="60" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL60" s="4"/>
+    </row>
+    <row r="61" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL61" s="4"/>
+    </row>
+    <row r="63" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL63" s="4"/>
+    </row>
+    <row r="64" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL64" s="4"/>
+    </row>
+    <row r="66" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV66"/>
+    </row>
+    <row r="67" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV67"/>
+      <c r="CL67" s="4"/>
+    </row>
+    <row r="68" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL68" s="4"/>
+    </row>
+    <row r="70" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL70" s="4"/>
+    </row>
+    <row r="79" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV79"/>
+    </row>
+    <row r="80" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV80"/>
+      <c r="CL80" s="4"/>
+    </row>
+    <row r="81" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL81" s="4"/>
+    </row>
+    <row r="82" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL82" s="4"/>
+    </row>
+    <row r="83" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV83"/>
+    </row>
+    <row r="84" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV84"/>
+      <c r="CL84" s="4"/>
+    </row>
+    <row r="85" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL85" s="4"/>
+    </row>
+    <row r="87" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV87"/>
+    </row>
+    <row r="88" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV88"/>
+      <c r="CL88" s="4"/>
+    </row>
+    <row r="89" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL89" s="4"/>
+    </row>
+    <row r="91" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV91"/>
+    </row>
+    <row r="92" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL92" s="4"/>
+    </row>
+    <row r="95" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL95" s="4"/>
+    </row>
+    <row r="99" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL99" s="4"/>
+    </row>
+    <row r="101" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV101"/>
+    </row>
+    <row r="102" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL102" s="4"/>
+    </row>
+    <row r="109" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV109"/>
+    </row>
+    <row r="110" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL110" s="4"/>
+    </row>
+    <row r="111" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL111" s="4"/>
+    </row>
+    <row r="113" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV113"/>
+    </row>
+    <row r="114" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV114"/>
+      <c r="CL114" s="4"/>
+    </row>
+    <row r="115" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL115" s="4"/>
+    </row>
+    <row r="121" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV121"/>
+    </row>
+    <row r="122" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV122"/>
+      <c r="CL122" s="4"/>
+    </row>
+    <row r="123" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV123"/>
+      <c r="CL123" s="4"/>
+    </row>
+    <row r="124" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL124" s="4"/>
+    </row>
+    <row r="129" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV129"/>
+    </row>
+    <row r="130" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV130"/>
+    </row>
+    <row r="134" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV134"/>
+    </row>
+    <row r="135" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL135" s="4"/>
+    </row>
+    <row r="136" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV136"/>
+    </row>
+    <row r="137" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL137" s="4"/>
+    </row>
+    <row r="147" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV147"/>
+    </row>
+    <row r="148" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL148" s="4"/>
+    </row>
+    <row r="150" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV150"/>
+    </row>
+    <row r="151" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL151" s="4"/>
+    </row>
+    <row r="159" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV159"/>
+    </row>
+    <row r="160" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL160" s="4"/>
+    </row>
+    <row r="164" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV164"/>
+    </row>
+    <row r="165" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL165" s="4"/>
+    </row>
+    <row r="167" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV167"/>
+    </row>
+    <row r="168" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL168" s="4"/>
+    </row>
+    <row r="184" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV184"/>
+    </row>
+    <row r="185" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV185"/>
+      <c r="CL185" s="4"/>
+    </row>
+    <row r="186" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV186"/>
+      <c r="CL186" s="4"/>
+    </row>
+    <row r="187" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV187"/>
+      <c r="CL187" s="4"/>
+    </row>
+    <row r="188" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV188"/>
+    </row>
+    <row r="190" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV190"/>
+    </row>
+    <row r="191" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV191"/>
+      <c r="CL191" s="4"/>
+    </row>
+    <row r="192" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV192"/>
+      <c r="CL192" s="4"/>
+    </row>
+    <row r="193" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL193" s="4"/>
+    </row>
+    <row r="197" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV197"/>
+    </row>
+    <row r="198" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL198" s="4"/>
+    </row>
+    <row r="200" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV200"/>
+    </row>
+    <row r="201" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV201"/>
+      <c r="CL201" s="4"/>
+    </row>
+    <row r="202" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV202"/>
+      <c r="CL202" s="4"/>
+    </row>
+    <row r="203" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL203" s="4"/>
+    </row>
+    <row r="219" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV219"/>
+    </row>
+    <row r="220" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL220" s="4"/>
+    </row>
+    <row r="228" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL228" s="4"/>
+    </row>
+    <row r="229" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL229" s="4"/>
+    </row>
+    <row r="230" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL230" s="4"/>
+    </row>
+    <row r="231" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL231" s="4"/>
+    </row>
+    <row r="232" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL232" s="4"/>
+    </row>
+    <row r="234" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV234"/>
+    </row>
+    <row r="235" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL235" s="4"/>
+    </row>
+    <row r="236" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV236"/>
+    </row>
+    <row r="237" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV237"/>
+      <c r="CL237" s="4"/>
+    </row>
+    <row r="238" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL238" s="4"/>
+    </row>
+    <row r="240" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV240"/>
+    </row>
+    <row r="241" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV241"/>
+      <c r="CL241" s="4"/>
+    </row>
+    <row r="242" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV242"/>
+      <c r="CL242" s="4"/>
+    </row>
+    <row r="243" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL243" s="4"/>
+    </row>
+    <row r="245" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL245" s="4"/>
+    </row>
+    <row r="247" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL247" s="4"/>
+    </row>
+    <row r="249" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL249" s="4"/>
+    </row>
+    <row r="252" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL252" s="4"/>
+    </row>
+    <row r="253" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL253" s="4"/>
+    </row>
+    <row r="254" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL254" s="4"/>
+    </row>
+    <row r="255" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL255" s="4"/>
+    </row>
+    <row r="256" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL256" s="4"/>
+    </row>
+    <row r="257" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL257" s="4"/>
+    </row>
+    <row r="258" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV258"/>
+    </row>
+    <row r="259" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV259"/>
+      <c r="CL259" s="4"/>
+    </row>
+    <row r="260" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV260"/>
+      <c r="CL260" s="4"/>
+    </row>
+    <row r="261" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL261" s="4"/>
+    </row>
+    <row r="262" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL262" s="4"/>
+    </row>
+    <row r="263" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL263" s="4"/>
+    </row>
+    <row r="264" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL264" s="4"/>
+    </row>
+    <row r="266" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL266" s="4"/>
+    </row>
+    <row r="267" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL267" s="4"/>
+    </row>
+    <row r="268" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV268"/>
+    </row>
+    <row r="269" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV269"/>
+      <c r="CL269" s="4"/>
+    </row>
+    <row r="270" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV270"/>
+      <c r="CL270" s="4"/>
+    </row>
+    <row r="271" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL271" s="4"/>
+    </row>
+    <row r="272" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL272" s="4"/>
+    </row>
+    <row r="274" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL274" s="4"/>
+    </row>
+    <row r="275" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL275" s="4"/>
+    </row>
+    <row r="276" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV276"/>
+      <c r="CL276" s="4"/>
+    </row>
+    <row r="277" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV277"/>
+      <c r="CL277" s="4"/>
+    </row>
+    <row r="278" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL278" s="4"/>
+    </row>
+    <row r="279" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL279" s="4"/>
+    </row>
+    <row r="280" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL280" s="4"/>
+    </row>
+    <row r="282" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV282"/>
+      <c r="CL282" s="4"/>
+    </row>
+    <row r="283" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL283" s="4"/>
+    </row>
+    <row r="284" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL284" s="4"/>
+    </row>
+    <row r="286" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV286"/>
+      <c r="CL286" s="4"/>
+    </row>
+    <row r="287" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV287"/>
+      <c r="CL287" s="4"/>
+    </row>
+    <row r="288" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL288" s="4"/>
+    </row>
+    <row r="290" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL290" s="4"/>
+    </row>
+    <row r="292" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL292" s="4"/>
+    </row>
+    <row r="295" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL295" s="4"/>
+    </row>
+    <row r="296" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL296" s="4"/>
+    </row>
+    <row r="300" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV300"/>
+    </row>
+    <row r="301" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV301"/>
+      <c r="CL301" s="4"/>
+    </row>
+    <row r="302" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV302"/>
+      <c r="CL302" s="4"/>
+    </row>
+    <row r="303" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL303" s="4"/>
+    </row>
+    <row r="304" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL304" s="4"/>
+    </row>
+    <row r="305" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV305"/>
+    </row>
+    <row r="306" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL306" s="4"/>
+    </row>
+    <row r="308" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL308" s="4"/>
+    </row>
+    <row r="309" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL309" s="4"/>
+    </row>
+    <row r="311" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL311" s="4"/>
+    </row>
+    <row r="312" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL312" s="4"/>
+    </row>
+    <row r="313" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL313" s="4"/>
+    </row>
+    <row r="314" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL314" s="4"/>
+    </row>
+    <row r="315" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL315" s="4"/>
+    </row>
+    <row r="316" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL316" s="4"/>
+    </row>
+    <row r="317" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL317" s="4"/>
+    </row>
+    <row r="319" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV319"/>
+    </row>
+    <row r="320" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL320" s="4"/>
+    </row>
+    <row r="321" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL321" s="4"/>
+    </row>
+    <row r="354" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU354" s="9"/>
+      <c r="BV354" s="10"/>
+    </row>
+    <row r="355" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H355" s="9"/>
-      <c r="CJ355" s="9"/>
-    </row>
-    <row r="361" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT361"/>
-    </row>
-    <row r="362" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT362"/>
-      <c r="CJ362" s="4"/>
-    </row>
-    <row r="363" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT363"/>
-      <c r="CJ363" s="4"/>
-    </row>
-    <row r="364" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ364" s="4"/>
-    </row>
-    <row r="381" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT381"/>
-    </row>
-    <row r="382" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ382" s="4"/>
-    </row>
-    <row r="414" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT414"/>
-    </row>
-    <row r="415" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT415"/>
-      <c r="CJ415" s="4"/>
-    </row>
-    <row r="416" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ416" s="4"/>
-    </row>
-    <row r="432" spans="72:72" x14ac:dyDescent="0.25">
-      <c r="BT432"/>
-    </row>
-    <row r="433" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ433" s="4"/>
-    </row>
-    <row r="439" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT439"/>
-    </row>
-    <row r="440" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT440"/>
-      <c r="CJ440" s="4"/>
-    </row>
-    <row r="441" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ441" s="4"/>
-    </row>
-    <row r="446" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT446"/>
-    </row>
-    <row r="447" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT447"/>
-      <c r="CJ447" s="4"/>
-    </row>
-    <row r="448" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT448"/>
-      <c r="CJ448" s="4"/>
-    </row>
-    <row r="449" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT449"/>
-      <c r="CJ449" s="4"/>
-    </row>
-    <row r="450" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT450"/>
-      <c r="CJ450" s="4"/>
-    </row>
-    <row r="451" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT451"/>
-      <c r="CJ451" s="4"/>
-    </row>
-    <row r="452" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT452"/>
-      <c r="CJ452" s="4"/>
-    </row>
-    <row r="453" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT453"/>
-      <c r="CJ453" s="4"/>
-    </row>
-    <row r="454" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT454"/>
-      <c r="CJ454" s="4"/>
-    </row>
-    <row r="455" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT455"/>
-      <c r="CJ455" s="4"/>
-    </row>
-    <row r="456" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT456"/>
-      <c r="CJ456" s="4"/>
-    </row>
-    <row r="457" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT457"/>
-      <c r="CJ457" s="4"/>
-    </row>
-    <row r="458" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT458"/>
-      <c r="CJ458" s="4"/>
-    </row>
-    <row r="459" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT459"/>
-      <c r="CJ459" s="4"/>
-    </row>
-    <row r="460" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT460"/>
-      <c r="CJ460" s="4"/>
-    </row>
-    <row r="461" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT461"/>
-      <c r="CJ461" s="4"/>
-    </row>
-    <row r="462" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ462" s="4"/>
-    </row>
-    <row r="466" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT466"/>
-    </row>
-    <row r="467" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT467"/>
-      <c r="CJ467" s="4"/>
-    </row>
-    <row r="468" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ468" s="4"/>
-    </row>
-    <row r="469" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT469"/>
-    </row>
-    <row r="470" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ470" s="4"/>
-    </row>
-    <row r="473" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT473"/>
-    </row>
-    <row r="474" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT474"/>
-      <c r="CJ474" s="4"/>
-    </row>
-    <row r="475" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ475" s="4"/>
-    </row>
-    <row r="506" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT506"/>
-    </row>
-    <row r="507" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT507"/>
-      <c r="CJ507" s="4"/>
-    </row>
-    <row r="508" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT508"/>
-      <c r="CJ508" s="4"/>
-    </row>
-    <row r="509" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT509"/>
-      <c r="CJ509" s="4"/>
-    </row>
-    <row r="510" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT510"/>
-      <c r="CJ510" s="4"/>
-    </row>
-    <row r="511" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT511"/>
-      <c r="CJ511" s="4"/>
-    </row>
-    <row r="512" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT512"/>
-      <c r="CJ512" s="4"/>
-    </row>
-    <row r="513" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT513"/>
-      <c r="CJ513" s="4"/>
-    </row>
-    <row r="514" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ514" s="4"/>
-    </row>
-    <row r="516" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT516"/>
-    </row>
-    <row r="517" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ517" s="4"/>
-    </row>
-    <row r="521" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT521"/>
-    </row>
-    <row r="522" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ522" s="4"/>
-    </row>
-    <row r="525" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT525"/>
-    </row>
-    <row r="526" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT526"/>
-      <c r="CJ526" s="4"/>
-    </row>
-    <row r="527" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT527"/>
-      <c r="CJ527" s="4"/>
-    </row>
-    <row r="528" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT528"/>
-      <c r="CJ528" s="4"/>
-    </row>
-    <row r="529" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ529" s="4"/>
-    </row>
-    <row r="536" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT536"/>
-    </row>
-    <row r="537" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ537" s="4"/>
-    </row>
-    <row r="540" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT540"/>
-    </row>
-    <row r="541" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT541"/>
-      <c r="CJ541" s="4"/>
-    </row>
-    <row r="542" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT542"/>
-      <c r="CJ542" s="4"/>
-    </row>
-    <row r="543" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT543"/>
-      <c r="CJ543" s="4"/>
-    </row>
-    <row r="544" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ544" s="4"/>
-    </row>
-    <row r="546" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT546"/>
-    </row>
-    <row r="547" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT547"/>
-      <c r="CJ547" s="4"/>
-    </row>
-    <row r="548" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ548" s="4"/>
-    </row>
-    <row r="549" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ549">
+      <c r="CL355" s="9"/>
+    </row>
+    <row r="361" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV361"/>
+    </row>
+    <row r="362" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV362"/>
+      <c r="CL362" s="4"/>
+    </row>
+    <row r="363" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV363"/>
+      <c r="CL363" s="4"/>
+    </row>
+    <row r="364" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL364" s="4"/>
+    </row>
+    <row r="381" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV381"/>
+    </row>
+    <row r="382" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL382" s="4"/>
+    </row>
+    <row r="414" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV414"/>
+    </row>
+    <row r="415" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV415"/>
+      <c r="CL415" s="4"/>
+    </row>
+    <row r="416" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL416" s="4"/>
+    </row>
+    <row r="432" spans="74:74" x14ac:dyDescent="0.25">
+      <c r="BV432"/>
+    </row>
+    <row r="433" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL433" s="4"/>
+    </row>
+    <row r="439" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV439"/>
+    </row>
+    <row r="440" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV440"/>
+      <c r="CL440" s="4"/>
+    </row>
+    <row r="441" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL441" s="4"/>
+    </row>
+    <row r="446" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV446"/>
+    </row>
+    <row r="447" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV447"/>
+      <c r="CL447" s="4"/>
+    </row>
+    <row r="448" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV448"/>
+      <c r="CL448" s="4"/>
+    </row>
+    <row r="449" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV449"/>
+      <c r="CL449" s="4"/>
+    </row>
+    <row r="450" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV450"/>
+      <c r="CL450" s="4"/>
+    </row>
+    <row r="451" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV451"/>
+      <c r="CL451" s="4"/>
+    </row>
+    <row r="452" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV452"/>
+      <c r="CL452" s="4"/>
+    </row>
+    <row r="453" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV453"/>
+      <c r="CL453" s="4"/>
+    </row>
+    <row r="454" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV454"/>
+      <c r="CL454" s="4"/>
+    </row>
+    <row r="455" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV455"/>
+      <c r="CL455" s="4"/>
+    </row>
+    <row r="456" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV456"/>
+      <c r="CL456" s="4"/>
+    </row>
+    <row r="457" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV457"/>
+      <c r="CL457" s="4"/>
+    </row>
+    <row r="458" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV458"/>
+      <c r="CL458" s="4"/>
+    </row>
+    <row r="459" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV459"/>
+      <c r="CL459" s="4"/>
+    </row>
+    <row r="460" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV460"/>
+      <c r="CL460" s="4"/>
+    </row>
+    <row r="461" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV461"/>
+      <c r="CL461" s="4"/>
+    </row>
+    <row r="462" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL462" s="4"/>
+    </row>
+    <row r="466" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV466"/>
+    </row>
+    <row r="467" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV467"/>
+      <c r="CL467" s="4"/>
+    </row>
+    <row r="468" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL468" s="4"/>
+    </row>
+    <row r="469" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV469"/>
+    </row>
+    <row r="470" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL470" s="4"/>
+    </row>
+    <row r="473" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV473"/>
+    </row>
+    <row r="474" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV474"/>
+      <c r="CL474" s="4"/>
+    </row>
+    <row r="475" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL475" s="4"/>
+    </row>
+    <row r="506" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV506"/>
+    </row>
+    <row r="507" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV507"/>
+      <c r="CL507" s="4"/>
+    </row>
+    <row r="508" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV508"/>
+      <c r="CL508" s="4"/>
+    </row>
+    <row r="509" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV509"/>
+      <c r="CL509" s="4"/>
+    </row>
+    <row r="510" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV510"/>
+      <c r="CL510" s="4"/>
+    </row>
+    <row r="511" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV511"/>
+      <c r="CL511" s="4"/>
+    </row>
+    <row r="512" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV512"/>
+      <c r="CL512" s="4"/>
+    </row>
+    <row r="513" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV513"/>
+      <c r="CL513" s="4"/>
+    </row>
+    <row r="514" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL514" s="4"/>
+    </row>
+    <row r="516" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV516"/>
+    </row>
+    <row r="517" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL517" s="4"/>
+    </row>
+    <row r="521" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV521"/>
+    </row>
+    <row r="522" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL522" s="4"/>
+    </row>
+    <row r="525" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV525"/>
+    </row>
+    <row r="526" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV526"/>
+      <c r="CL526" s="4"/>
+    </row>
+    <row r="527" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV527"/>
+      <c r="CL527" s="4"/>
+    </row>
+    <row r="528" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV528"/>
+      <c r="CL528" s="4"/>
+    </row>
+    <row r="529" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL529" s="4"/>
+    </row>
+    <row r="536" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV536"/>
+    </row>
+    <row r="537" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL537" s="4"/>
+    </row>
+    <row r="540" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV540"/>
+    </row>
+    <row r="541" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV541"/>
+      <c r="CL541" s="4"/>
+    </row>
+    <row r="542" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV542"/>
+      <c r="CL542" s="4"/>
+    </row>
+    <row r="543" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV543"/>
+      <c r="CL543" s="4"/>
+    </row>
+    <row r="544" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL544" s="4"/>
+    </row>
+    <row r="546" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV546"/>
+    </row>
+    <row r="547" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV547"/>
+      <c r="CL547" s="4"/>
+    </row>
+    <row r="548" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL548" s="4"/>
+    </row>
+    <row r="549" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL549">
         <v>0.15</v>
       </c>
     </row>
-    <row r="551" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ551">
+    <row r="551" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL551">
         <v>0.2</v>
       </c>
     </row>
-    <row r="552" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ552">
+    <row r="552" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL552">
         <v>0.1</v>
       </c>
     </row>
-    <row r="554" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ554">
+    <row r="554" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL554">
         <v>0.2</v>
       </c>
     </row>
-    <row r="561" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ561">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="563" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ563">
+    <row r="561" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL561">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="563" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL563">
         <v>0.4</v>
       </c>
     </row>
-    <row r="564" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ564">
+    <row r="564" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL564">
         <v>0.6</v>
       </c>
     </row>
-    <row r="567" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ567">
+    <row r="567" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL567">
         <v>0.5</v>
       </c>
     </row>
-    <row r="568" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ568">
+    <row r="568" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL568">
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="569" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ569">
+    <row r="569" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL569">
         <v>0.2</v>
       </c>
     </row>
-    <row r="572" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT572"/>
-    </row>
-    <row r="573" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT573"/>
-      <c r="CJ573" s="4"/>
-    </row>
-    <row r="574" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT574"/>
-      <c r="CJ574" s="4"/>
-    </row>
-    <row r="575" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT575"/>
-      <c r="CJ575" s="4"/>
-    </row>
-    <row r="576" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT576"/>
-      <c r="CJ576" s="4"/>
-    </row>
-    <row r="577" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT577"/>
-      <c r="CJ577" s="4"/>
-    </row>
-    <row r="578" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT578"/>
-      <c r="CJ578" s="4"/>
-    </row>
-    <row r="579" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT579"/>
-      <c r="CJ579" s="4"/>
-    </row>
-    <row r="580" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT580"/>
-      <c r="CJ580" s="4"/>
-    </row>
-    <row r="581" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ581" s="4"/>
-    </row>
-    <row r="582" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT582"/>
-    </row>
-    <row r="583" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ583" s="4"/>
-    </row>
-    <row r="592" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT592"/>
-    </row>
-    <row r="593" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT593"/>
-      <c r="CJ593" s="4"/>
-    </row>
-    <row r="594" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT594"/>
-      <c r="CJ594" s="4"/>
-    </row>
-    <row r="595" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT595"/>
-      <c r="CJ595" s="4"/>
-    </row>
-    <row r="596" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT596"/>
-      <c r="CJ596" s="4"/>
-    </row>
-    <row r="597" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT597"/>
-      <c r="CJ597" s="4"/>
-    </row>
-    <row r="598" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT598"/>
-      <c r="CJ598" s="4"/>
-    </row>
-    <row r="599" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT599"/>
-      <c r="CJ599" s="4"/>
-    </row>
-    <row r="600" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ600" s="4"/>
-    </row>
-    <row r="601" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT601"/>
-    </row>
-    <row r="602" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ602" s="4"/>
-    </row>
-    <row r="607" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT607"/>
-    </row>
-    <row r="608" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT608"/>
-      <c r="CJ608" s="4"/>
-    </row>
-    <row r="609" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ609" s="4"/>
-    </row>
-    <row r="610" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT610"/>
-    </row>
-    <row r="611" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT611"/>
-      <c r="CJ611" s="4"/>
-    </row>
-    <row r="612" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ612" s="4"/>
-    </row>
-    <row r="613" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT613"/>
-    </row>
-    <row r="614" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT614"/>
-      <c r="CJ614" s="4"/>
-    </row>
-    <row r="615" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT615"/>
-      <c r="CJ615" s="4"/>
-    </row>
-    <row r="616" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT616"/>
-      <c r="CJ616" s="4"/>
-    </row>
-    <row r="617" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ617" s="4"/>
-    </row>
-    <row r="621" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT621"/>
-    </row>
-    <row r="622" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT622"/>
-      <c r="CJ622" s="4"/>
-    </row>
-    <row r="623" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT623"/>
-      <c r="CJ623" s="4"/>
-    </row>
-    <row r="624" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ624" s="4"/>
-    </row>
-    <row r="625" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT625"/>
-    </row>
-    <row r="626" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ626" s="4"/>
-    </row>
-    <row r="627" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS627" s="9"/>
-      <c r="BT627" s="10"/>
-    </row>
-    <row r="628" spans="8:88" x14ac:dyDescent="0.25">
+    <row r="572" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV572"/>
+    </row>
+    <row r="573" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV573"/>
+      <c r="CL573" s="4"/>
+    </row>
+    <row r="574" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV574"/>
+      <c r="CL574" s="4"/>
+    </row>
+    <row r="575" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV575"/>
+      <c r="CL575" s="4"/>
+    </row>
+    <row r="576" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV576"/>
+      <c r="CL576" s="4"/>
+    </row>
+    <row r="577" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV577"/>
+      <c r="CL577" s="4"/>
+    </row>
+    <row r="578" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV578"/>
+      <c r="CL578" s="4"/>
+    </row>
+    <row r="579" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV579"/>
+      <c r="CL579" s="4"/>
+    </row>
+    <row r="580" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV580"/>
+      <c r="CL580" s="4"/>
+    </row>
+    <row r="581" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL581" s="4"/>
+    </row>
+    <row r="582" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV582"/>
+    </row>
+    <row r="583" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL583" s="4"/>
+    </row>
+    <row r="592" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV592"/>
+    </row>
+    <row r="593" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV593"/>
+      <c r="CL593" s="4"/>
+    </row>
+    <row r="594" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV594"/>
+      <c r="CL594" s="4"/>
+    </row>
+    <row r="595" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV595"/>
+      <c r="CL595" s="4"/>
+    </row>
+    <row r="596" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV596"/>
+      <c r="CL596" s="4"/>
+    </row>
+    <row r="597" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV597"/>
+      <c r="CL597" s="4"/>
+    </row>
+    <row r="598" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV598"/>
+      <c r="CL598" s="4"/>
+    </row>
+    <row r="599" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV599"/>
+      <c r="CL599" s="4"/>
+    </row>
+    <row r="600" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL600" s="4"/>
+    </row>
+    <row r="601" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV601"/>
+    </row>
+    <row r="602" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL602" s="4"/>
+    </row>
+    <row r="607" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV607"/>
+    </row>
+    <row r="608" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV608"/>
+      <c r="CL608" s="4"/>
+    </row>
+    <row r="609" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL609" s="4"/>
+    </row>
+    <row r="610" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV610"/>
+    </row>
+    <row r="611" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV611"/>
+      <c r="CL611" s="4"/>
+    </row>
+    <row r="612" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL612" s="4"/>
+    </row>
+    <row r="613" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV613"/>
+    </row>
+    <row r="614" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV614"/>
+      <c r="CL614" s="4"/>
+    </row>
+    <row r="615" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV615"/>
+      <c r="CL615" s="4"/>
+    </row>
+    <row r="616" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV616"/>
+      <c r="CL616" s="4"/>
+    </row>
+    <row r="617" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL617" s="4"/>
+    </row>
+    <row r="621" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV621"/>
+    </row>
+    <row r="622" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV622"/>
+      <c r="CL622" s="4"/>
+    </row>
+    <row r="623" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV623"/>
+      <c r="CL623" s="4"/>
+    </row>
+    <row r="624" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL624" s="4"/>
+    </row>
+    <row r="625" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV625"/>
+    </row>
+    <row r="626" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL626" s="4"/>
+    </row>
+    <row r="627" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU627" s="9"/>
+      <c r="BV627" s="10"/>
+    </row>
+    <row r="628" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H628" s="9"/>
-      <c r="CJ628" s="9"/>
-    </row>
-    <row r="645" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT645"/>
-    </row>
-    <row r="646" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT646"/>
-      <c r="CJ646" s="4"/>
-    </row>
-    <row r="647" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT647"/>
-      <c r="CJ647" s="4"/>
-    </row>
-    <row r="648" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT648"/>
-      <c r="CJ648" s="4"/>
-    </row>
-    <row r="649" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ649" s="4"/>
-    </row>
-    <row r="650" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT650"/>
-    </row>
-    <row r="651" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT651"/>
-      <c r="CJ651" s="4"/>
-    </row>
-    <row r="652" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS652" s="9"/>
-      <c r="BT652" s="10"/>
-      <c r="CJ652" s="4"/>
-    </row>
-    <row r="653" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CL628" s="9"/>
+    </row>
+    <row r="645" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV645"/>
+    </row>
+    <row r="646" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV646"/>
+      <c r="CL646" s="4"/>
+    </row>
+    <row r="647" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV647"/>
+      <c r="CL647" s="4"/>
+    </row>
+    <row r="648" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV648"/>
+      <c r="CL648" s="4"/>
+    </row>
+    <row r="649" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL649" s="4"/>
+    </row>
+    <row r="650" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV650"/>
+    </row>
+    <row r="651" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV651"/>
+      <c r="CL651" s="4"/>
+    </row>
+    <row r="652" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU652" s="9"/>
+      <c r="BV652" s="10"/>
+      <c r="CL652" s="4"/>
+    </row>
+    <row r="653" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H653" s="9"/>
-      <c r="CJ653" s="9"/>
-    </row>
-    <row r="656" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT656"/>
-    </row>
-    <row r="657" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT657"/>
-      <c r="CJ657" s="4"/>
-    </row>
-    <row r="658" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT658"/>
-      <c r="CJ658" s="4"/>
-    </row>
-    <row r="659" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT659"/>
-      <c r="CJ659" s="4"/>
-    </row>
-    <row r="660" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT660"/>
-      <c r="CJ660" s="4"/>
-    </row>
-    <row r="661" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT661"/>
-      <c r="CJ661" s="4"/>
-    </row>
-    <row r="662" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT662"/>
-      <c r="CJ662" s="4"/>
-    </row>
-    <row r="663" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT663"/>
-      <c r="CJ663" s="4"/>
-    </row>
-    <row r="664" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ664" s="4"/>
-    </row>
-    <row r="666" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT666"/>
-    </row>
-    <row r="667" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT667"/>
-      <c r="CJ667" s="4"/>
-    </row>
-    <row r="668" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT668"/>
-      <c r="CJ668" s="4"/>
-    </row>
-    <row r="669" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT669"/>
-      <c r="CJ669" s="4"/>
-    </row>
-    <row r="670" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT670"/>
-      <c r="CJ670" s="4"/>
-    </row>
-    <row r="671" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT671"/>
-      <c r="CJ671" s="4"/>
-    </row>
-    <row r="672" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ672" s="4"/>
-    </row>
-    <row r="673" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT673"/>
-    </row>
-    <row r="674" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT674"/>
-      <c r="CJ674" s="4"/>
-    </row>
-    <row r="675" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT675"/>
-      <c r="CJ675" s="4"/>
-    </row>
-    <row r="676" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT676"/>
-      <c r="CJ676" s="4"/>
-    </row>
-    <row r="677" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT677"/>
-      <c r="CJ677" s="4"/>
-    </row>
-    <row r="678" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT678"/>
-      <c r="CJ678" s="4"/>
-    </row>
-    <row r="679" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT679"/>
-      <c r="CJ679" s="4"/>
-    </row>
-    <row r="680" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT680"/>
-      <c r="CJ680" s="4"/>
-    </row>
-    <row r="681" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT681"/>
-      <c r="CJ681" s="4"/>
-    </row>
-    <row r="682" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT682"/>
-      <c r="CJ682" s="4"/>
-    </row>
-    <row r="683" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT683"/>
-      <c r="CJ683" s="4"/>
-    </row>
-    <row r="684" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT684"/>
-      <c r="CJ684" s="4"/>
-    </row>
-    <row r="685" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT685"/>
-      <c r="CJ685" s="4"/>
-    </row>
-    <row r="686" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT686"/>
-      <c r="CJ686" s="4"/>
-    </row>
-    <row r="687" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT687"/>
-      <c r="CJ687" s="4"/>
-    </row>
-    <row r="688" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT688"/>
-      <c r="CJ688" s="4"/>
-    </row>
-    <row r="689" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT689"/>
-      <c r="CJ689" s="4"/>
-    </row>
-    <row r="690" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT690"/>
-      <c r="CJ690" s="4"/>
-    </row>
-    <row r="691" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT691"/>
-      <c r="CJ691" s="4"/>
-    </row>
-    <row r="692" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT692"/>
-      <c r="CJ692" s="4"/>
-    </row>
-    <row r="693" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT693"/>
-      <c r="CJ693" s="4"/>
-    </row>
-    <row r="694" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT694"/>
-      <c r="CJ694" s="4"/>
-    </row>
-    <row r="695" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT695"/>
-      <c r="CJ695" s="4"/>
-    </row>
-    <row r="696" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT696"/>
-      <c r="CJ696" s="4"/>
-    </row>
-    <row r="697" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT697"/>
-      <c r="CJ697" s="4"/>
-    </row>
-    <row r="698" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT698"/>
-      <c r="CJ698" s="4"/>
-    </row>
-    <row r="699" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT699"/>
-      <c r="CJ699" s="4"/>
-    </row>
-    <row r="700" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT700"/>
-      <c r="CJ700" s="4"/>
-    </row>
-    <row r="701" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT701"/>
-      <c r="CJ701" s="4"/>
-    </row>
-    <row r="702" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT702"/>
-      <c r="CJ702" s="4"/>
-    </row>
-    <row r="703" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ703" s="4"/>
-    </row>
-    <row r="704" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT704"/>
-    </row>
-    <row r="705" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT705"/>
-      <c r="CJ705" s="4"/>
-    </row>
-    <row r="706" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT706"/>
-      <c r="CJ706" s="4"/>
-    </row>
-    <row r="707" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ707" s="4"/>
+      <c r="CL653" s="9"/>
+    </row>
+    <row r="656" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV656"/>
+    </row>
+    <row r="657" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV657"/>
+      <c r="CL657" s="4"/>
+    </row>
+    <row r="658" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV658"/>
+      <c r="CL658" s="4"/>
+    </row>
+    <row r="659" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV659"/>
+      <c r="CL659" s="4"/>
+    </row>
+    <row r="660" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV660"/>
+      <c r="CL660" s="4"/>
+    </row>
+    <row r="661" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV661"/>
+      <c r="CL661" s="4"/>
+    </row>
+    <row r="662" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV662"/>
+      <c r="CL662" s="4"/>
+    </row>
+    <row r="663" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV663"/>
+      <c r="CL663" s="4"/>
+    </row>
+    <row r="664" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL664" s="4"/>
+    </row>
+    <row r="666" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV666"/>
+    </row>
+    <row r="667" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV667"/>
+      <c r="CL667" s="4"/>
+    </row>
+    <row r="668" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV668"/>
+      <c r="CL668" s="4"/>
+    </row>
+    <row r="669" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV669"/>
+      <c r="CL669" s="4"/>
+    </row>
+    <row r="670" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV670"/>
+      <c r="CL670" s="4"/>
+    </row>
+    <row r="671" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV671"/>
+      <c r="CL671" s="4"/>
+    </row>
+    <row r="672" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL672" s="4"/>
+    </row>
+    <row r="673" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV673"/>
+    </row>
+    <row r="674" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV674"/>
+      <c r="CL674" s="4"/>
+    </row>
+    <row r="675" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV675"/>
+      <c r="CL675" s="4"/>
+    </row>
+    <row r="676" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV676"/>
+      <c r="CL676" s="4"/>
+    </row>
+    <row r="677" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV677"/>
+      <c r="CL677" s="4"/>
+    </row>
+    <row r="678" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV678"/>
+      <c r="CL678" s="4"/>
+    </row>
+    <row r="679" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV679"/>
+      <c r="CL679" s="4"/>
+    </row>
+    <row r="680" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV680"/>
+      <c r="CL680" s="4"/>
+    </row>
+    <row r="681" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV681"/>
+      <c r="CL681" s="4"/>
+    </row>
+    <row r="682" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV682"/>
+      <c r="CL682" s="4"/>
+    </row>
+    <row r="683" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV683"/>
+      <c r="CL683" s="4"/>
+    </row>
+    <row r="684" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV684"/>
+      <c r="CL684" s="4"/>
+    </row>
+    <row r="685" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV685"/>
+      <c r="CL685" s="4"/>
+    </row>
+    <row r="686" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV686"/>
+      <c r="CL686" s="4"/>
+    </row>
+    <row r="687" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV687"/>
+      <c r="CL687" s="4"/>
+    </row>
+    <row r="688" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV688"/>
+      <c r="CL688" s="4"/>
+    </row>
+    <row r="689" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV689"/>
+      <c r="CL689" s="4"/>
+    </row>
+    <row r="690" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV690"/>
+      <c r="CL690" s="4"/>
+    </row>
+    <row r="691" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV691"/>
+      <c r="CL691" s="4"/>
+    </row>
+    <row r="692" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV692"/>
+      <c r="CL692" s="4"/>
+    </row>
+    <row r="693" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV693"/>
+      <c r="CL693" s="4"/>
+    </row>
+    <row r="694" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV694"/>
+      <c r="CL694" s="4"/>
+    </row>
+    <row r="695" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV695"/>
+      <c r="CL695" s="4"/>
+    </row>
+    <row r="696" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV696"/>
+      <c r="CL696" s="4"/>
+    </row>
+    <row r="697" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV697"/>
+      <c r="CL697" s="4"/>
+    </row>
+    <row r="698" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV698"/>
+      <c r="CL698" s="4"/>
+    </row>
+    <row r="699" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV699"/>
+      <c r="CL699" s="4"/>
+    </row>
+    <row r="700" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV700"/>
+      <c r="CL700" s="4"/>
+    </row>
+    <row r="701" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV701"/>
+      <c r="CL701" s="4"/>
+    </row>
+    <row r="702" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV702"/>
+      <c r="CL702" s="4"/>
+    </row>
+    <row r="703" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL703" s="4"/>
+    </row>
+    <row r="704" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV704"/>
+    </row>
+    <row r="705" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV705"/>
+      <c r="CL705" s="4"/>
+    </row>
+    <row r="706" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV706"/>
+      <c r="CL706" s="4"/>
+    </row>
+    <row r="707" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL707" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>

--- a/Excel/一方通行/酒神.xlsx
+++ b/Excel/一方通行/酒神.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C5D2D3-C75E-4199-A082-FB6B2E1551A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32B0147-6F44-4F70-A1FA-1B73312CA15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1661,15 +1661,9 @@
     <t>部署干员</t>
   </si>
   <si>
-    <t>{"UnitId":"猫牢笼","TargetPos":"useSelfTargetPos","SetMod":"Add","UseMod":"UserDirection","UserName":"酒神","ElementType":"Sanity"}</t>
-  </si>
-  <si>
     <t>自己入场</t>
   </si>
   <si>
-    <t>{"UnitId":"猫诱导","TargetPos":"useSelfPos","SetMod":"Replace","UseMod":"UserDirection","UserName":"本能的召唤"}</t>
-  </si>
-  <si>
     <t>尝试插入临时路径点</t>
   </si>
   <si>
@@ -1694,9 +1688,6 @@
     <t>猫索敌</t>
   </si>
   <si>
-    <t>部署猫后续,部署猫后续2</t>
-  </si>
-  <si>
     <t>猫死亡</t>
   </si>
   <si>
@@ -1713,12 +1704,6 @@
   </si>
   <si>
     <t>离场</t>
-  </si>
-  <si>
-    <t>{"UnitId":"猫诱导后续","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"UserDirection","UserName":"猫诱导"}</t>
-  </si>
-  <si>
-    <t>部署猫后续2</t>
   </si>
   <si>
     <t>撤退</t>
@@ -2035,6 +2020,26 @@
   </si>
   <si>
     <t>string</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>部署猫后续2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤物ID":"猫牢笼","召唤位置":"使用本技能索敌位置","部署模式":"追加","召唤物方向":"固定方向","ElementType":"Sanity"}</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤物ID":"猫诱导","召唤位置":"使用自身位置","部署模式":"替换","部署方向":"固定方向"}</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤物ID":"猫诱导后续","召唤位置":"使用自身位置","部署模式":"追加","召唤物方向":"固定方向"}</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>部署猫后续,部署猫后续2</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -6767,10 +6772,10 @@
         <v>197</v>
       </c>
       <c r="AR1" s="8" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="AS1" s="8" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="AT1" t="s">
         <v>198</v>
@@ -7102,10 +7107,10 @@
         <v>299</v>
       </c>
       <c r="AR2" s="8" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="AS2" s="8" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="AT2" t="s">
         <v>300</v>
@@ -7440,10 +7445,10 @@
         <v>2</v>
       </c>
       <c r="AR3" s="8" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="AS3" s="8" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="AT3" t="s">
         <v>372</v>
@@ -8229,7 +8234,7 @@
         <v>1</v>
       </c>
       <c r="BO18" s="8" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="BP18" t="s">
         <v>432</v>
@@ -8565,7 +8570,7 @@
     </row>
     <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="C25" t="s">
         <v>449</v>
@@ -8599,8 +8604,8 @@
       <c r="BS25">
         <v>0.1</v>
       </c>
-      <c r="CU25" t="s">
-        <v>450</v>
+      <c r="CU25" s="8" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="26" spans="1:112" x14ac:dyDescent="0.25">
@@ -8620,7 +8625,7 @@
         <v>396</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AC28">
         <v>1</v>
@@ -8633,8 +8638,8 @@
       </c>
       <c r="BV28"/>
       <c r="CL28" s="4"/>
-      <c r="CU28" t="s">
-        <v>452</v>
+      <c r="CU28" s="8" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="29" spans="1:112" x14ac:dyDescent="0.25">
@@ -8642,7 +8647,7 @@
         <v>149</v>
       </c>
       <c r="C29" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I29">
         <v>1</v>
@@ -8651,7 +8656,7 @@
         <v>396</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AC29">
         <v>2</v>
@@ -8660,7 +8665,7 @@
         <v>386</v>
       </c>
       <c r="AT29" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="BD29">
         <v>4</v>
@@ -8670,30 +8675,30 @@
       </c>
       <c r="CL29" s="4"/>
       <c r="CN29" s="8" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="CR29">
         <v>5</v>
       </c>
       <c r="CU29" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="CY29" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="30" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C30" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>396</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AC30">
         <v>1</v>
@@ -8707,7 +8712,7 @@
       <c r="BV30"/>
       <c r="CL30" s="4"/>
       <c r="CU30" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="31" spans="1:112" x14ac:dyDescent="0.25">
@@ -8715,7 +8720,7 @@
     </row>
     <row r="32" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C32" t="s">
         <v>384</v>
@@ -8741,11 +8746,11 @@
       <c r="BD32">
         <v>1</v>
       </c>
-      <c r="BO32" t="s">
-        <v>461</v>
+      <c r="BO32" s="8" t="s">
+        <v>572</v>
       </c>
       <c r="BP32" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="BT32">
         <v>6</v>
@@ -8760,7 +8765,7 @@
         <v>1</v>
       </c>
       <c r="BY32" s="5" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="CL32" s="4"/>
       <c r="DH32">
@@ -8769,7 +8774,7 @@
     </row>
     <row r="33" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C33" t="s">
         <v>384</v>
@@ -8802,10 +8807,10 @@
         <v>417</v>
       </c>
       <c r="AT33" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AX33" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AZ33">
         <v>999</v>
@@ -8834,7 +8839,7 @@
     </row>
     <row r="34" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C34" t="s">
         <v>449</v>
@@ -8843,7 +8848,7 @@
         <v>396</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AC34">
         <v>1</v>
@@ -8856,13 +8861,13 @@
       </c>
       <c r="BV34"/>
       <c r="CL34" s="4"/>
-      <c r="CU34" t="s">
-        <v>468</v>
+      <c r="CU34" s="8" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="35" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>469</v>
+      <c r="A35" s="8" t="s">
+        <v>568</v>
       </c>
       <c r="C35" t="s">
         <v>449</v>
@@ -8871,7 +8876,7 @@
         <v>396</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="AC35">
         <v>1</v>
@@ -8884,8 +8889,8 @@
       </c>
       <c r="BV35"/>
       <c r="CL35" s="4"/>
-      <c r="CU35" t="s">
-        <v>468</v>
+      <c r="CU35" s="8" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="36" spans="1:112" x14ac:dyDescent="0.25">
@@ -8893,7 +8898,7 @@
     </row>
     <row r="37" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C37" t="s">
         <v>384</v>
@@ -8905,7 +8910,7 @@
         <v>396</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AC37">
         <v>1</v>
@@ -8917,12 +8922,12 @@
         <v>1</v>
       </c>
       <c r="CY37" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="38" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="C38" t="s">
         <v>384</v>
@@ -8934,7 +8939,7 @@
         <v>396</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="M38"/>
       <c r="N38"/>
@@ -8961,7 +8966,7 @@
         <v>386</v>
       </c>
       <c r="AT38" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AX38" t="s">
         <v>388</v>
@@ -8979,10 +8984,10 @@
         <v>0.5</v>
       </c>
       <c r="BO38" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="BP38" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="BV38" s="7"/>
       <c r="BW38" s="7"/>
@@ -8997,18 +9002,18 @@
         <v>392</v>
       </c>
       <c r="CL38" s="4" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="CU38" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="CY38" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="39" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C39" t="s">
         <v>384</v>
@@ -9020,7 +9025,7 @@
         <v>396</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="X39" s="4">
         <v>1</v>
@@ -9035,7 +9040,7 @@
         <v>386</v>
       </c>
       <c r="AT39" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="BD39">
         <v>99</v>
@@ -9043,7 +9048,7 @@
       <c r="BV39"/>
       <c r="CL39" s="4"/>
       <c r="CN39" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="CO39">
         <v>-0.8</v>
@@ -9052,12 +9057,12 @@
         <v>6</v>
       </c>
       <c r="CY39" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="40" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C40" t="s">
         <v>384</v>
@@ -9075,10 +9080,10 @@
         <v>417</v>
       </c>
       <c r="AT40" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AX40" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AZ40">
         <v>0.09</v>
@@ -9098,7 +9103,7 @@
       <c r="BV40"/>
       <c r="CL40" s="4"/>
       <c r="CY40" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="DD40">
         <v>1</v>
@@ -10282,37 +10287,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F1" t="s">
+        <v>476</v>
+      </c>
+      <c r="G1" t="s">
+        <v>477</v>
+      </c>
+      <c r="H1" t="s">
+        <v>478</v>
+      </c>
+      <c r="I1" t="s">
+        <v>479</v>
+      </c>
+      <c r="J1" t="s">
         <v>480</v>
       </c>
-      <c r="F1" t="s">
+      <c r="L1" t="s">
         <v>481</v>
       </c>
-      <c r="G1" t="s">
+      <c r="M1" t="s">
         <v>482</v>
       </c>
-      <c r="H1" t="s">
+      <c r="N1" t="s">
         <v>483</v>
       </c>
-      <c r="I1" t="s">
+      <c r="O1" t="s">
         <v>484</v>
       </c>
-      <c r="J1" t="s">
+      <c r="P1" t="s">
         <v>485</v>
-      </c>
-      <c r="L1" t="s">
-        <v>486</v>
-      </c>
-      <c r="M1" t="s">
-        <v>487</v>
-      </c>
-      <c r="N1" t="s">
-        <v>488</v>
-      </c>
-      <c r="O1" t="s">
-        <v>489</v>
-      </c>
-      <c r="P1" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -10326,40 +10331,40 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F2" t="s">
+        <v>487</v>
+      </c>
+      <c r="G2" t="s">
+        <v>488</v>
+      </c>
+      <c r="H2" t="s">
+        <v>489</v>
+      </c>
+      <c r="I2" t="s">
+        <v>490</v>
+      </c>
+      <c r="J2" t="s">
         <v>491</v>
       </c>
-      <c r="F2" t="s">
+      <c r="K2" t="s">
         <v>492</v>
-      </c>
-      <c r="G2" t="s">
-        <v>493</v>
-      </c>
-      <c r="H2" t="s">
-        <v>494</v>
-      </c>
-      <c r="I2" t="s">
-        <v>495</v>
-      </c>
-      <c r="J2" t="s">
-        <v>496</v>
-      </c>
-      <c r="K2" t="s">
-        <v>497</v>
       </c>
       <c r="L2" t="s">
         <v>53</v>
       </c>
       <c r="M2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="N2" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="O2" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="P2" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="Q2" t="s">
         <v>351</v>
@@ -10420,12 +10425,12 @@
         <v>393</v>
       </c>
       <c r="C4" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="C5" t="s">
         <v>233</v>
@@ -10434,7 +10439,7 @@
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -10442,7 +10447,7 @@
         <v>443</v>
       </c>
       <c r="C6" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="J6" t="s">
         <v>436</v>
@@ -10453,15 +10458,15 @@
         <v>448</v>
       </c>
       <c r="C7" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="Q7" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C8" t="s">
         <v>233</v>
@@ -10470,7 +10475,7 @@
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="292" spans="16:16" x14ac:dyDescent="0.25">
@@ -10505,7 +10510,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -10516,7 +10521,7 @@
         <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="D2" t="s">
         <v>351</v>
@@ -10565,19 +10570,19 @@
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="G2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="H2" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="I2" t="s">
         <v>351</v>
@@ -10636,34 +10641,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D1" t="s">
+        <v>512</v>
+      </c>
+      <c r="E1" t="s">
+        <v>513</v>
+      </c>
+      <c r="F1" t="s">
+        <v>514</v>
+      </c>
+      <c r="H1" t="s">
         <v>515</v>
       </c>
-      <c r="C1" t="s">
+      <c r="I1" t="s">
         <v>516</v>
       </c>
-      <c r="D1" t="s">
+      <c r="J1" t="s">
         <v>517</v>
       </c>
-      <c r="E1" t="s">
+      <c r="K1" t="s">
         <v>518</v>
       </c>
-      <c r="F1" t="s">
+      <c r="L1" t="s">
         <v>519</v>
-      </c>
-      <c r="H1" t="s">
-        <v>520</v>
-      </c>
-      <c r="I1" t="s">
-        <v>521</v>
-      </c>
-      <c r="J1" t="s">
-        <v>522</v>
-      </c>
-      <c r="K1" t="s">
-        <v>523</v>
-      </c>
-      <c r="L1" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -10671,34 +10676,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F2" t="s">
+        <v>524</v>
+      </c>
+      <c r="G2" t="s">
         <v>525</v>
       </c>
-      <c r="C2" t="s">
+      <c r="H2" t="s">
         <v>526</v>
       </c>
-      <c r="D2" t="s">
+      <c r="I2" t="s">
         <v>527</v>
       </c>
-      <c r="E2" t="s">
+      <c r="J2" t="s">
         <v>528</v>
       </c>
-      <c r="F2" t="s">
-        <v>529</v>
-      </c>
-      <c r="G2" t="s">
-        <v>530</v>
-      </c>
-      <c r="H2" t="s">
-        <v>531</v>
-      </c>
-      <c r="I2" t="s">
-        <v>532</v>
-      </c>
-      <c r="J2" t="s">
-        <v>533</v>
-      </c>
       <c r="K2" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="L2" t="s">
         <v>97</v>
@@ -10715,7 +10720,7 @@
         <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -10775,22 +10780,22 @@
         <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="E2" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="F2" t="s">
         <v>79</v>
       </c>
       <c r="G2" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="H2" t="s">
         <v>291</v>
       </c>
       <c r="I2" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="J2" t="s">
         <v>54</v>
@@ -10819,7 +10824,7 @@
         <v>118</v>
       </c>
       <c r="H3" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="I3" t="s">
         <v>118</v>
@@ -10854,28 +10859,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -10883,28 +10888,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -10944,22 +10949,22 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>556</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -10973,13 +10978,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/一方通行/酒神.xlsx
+++ b/Excel/一方通行/酒神.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32B0147-6F44-4F70-A1FA-1B73312CA15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B6B2C96-361C-42FC-ADCA-9483201D6408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="573">
   <si>
     <t>Id</t>
   </si>
@@ -10550,16 +10550,21 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A2:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="3" max="3" width="27.25" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -10585,10 +10590,13 @@
         <v>509</v>
       </c>
       <c r="I2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J2" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10614,6 +10622,9 @@
         <v>118</v>
       </c>
       <c r="I3" t="s">
+        <v>380</v>
+      </c>
+      <c r="J3" t="s">
         <v>125</v>
       </c>
     </row>

--- a/Excel/一方通行/酒神.xlsx
+++ b/Excel/一方通行/酒神.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B6B2C96-361C-42FC-ADCA-9483201D6408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6518033B-0B6F-4276-978E-34C1055705F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="575">
   <si>
     <t>Id</t>
   </si>
@@ -2041,6 +2041,12 @@
   <si>
     <t>部署猫后续,部署猫后续2</t>
     <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>token_10054_phatm2_encdool</t>
+  </si>
+  <si>
+    <t>char_1042_phatm2</t>
   </si>
 </sst>
 </file>
@@ -3169,7 +3175,7 @@
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="1" t="s">
-        <v>4</v>
+        <v>574</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -3292,7 +3298,7 @@
       </c>
       <c r="E8" s="12"/>
       <c r="F8" t="s">
-        <v>141</v>
+        <v>573</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -3415,7 +3421,7 @@
       </c>
       <c r="E9" s="12"/>
       <c r="F9" t="s">
-        <v>141</v>
+        <v>573</v>
       </c>
       <c r="G9">
         <v>1</v>

--- a/Excel/一方通行/酒神.xlsx
+++ b/Excel/一方通行/酒神.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6518033B-0B6F-4276-978E-34C1055705F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7DE2AD-F1EF-4A15-8E69-363B835CECF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="576">
   <si>
     <t>Id</t>
   </si>
@@ -388,12 +388,6 @@
     <t>高度</t>
   </si>
   <si>
-    <t>高台单位？</t>
-  </si>
-  <si>
-    <t>地面</t>
-  </si>
-  <si>
     <t>阻挡个数</t>
   </si>
   <si>
@@ -548,12 +542,6 @@
   </si>
   <si>
     <t>Height</t>
-  </si>
-  <si>
-    <t>CanSetHigh</t>
-  </si>
-  <si>
-    <t>CanSetGround</t>
   </si>
   <si>
     <t>StopCount</t>
@@ -2047,6 +2035,26 @@
   </si>
   <si>
     <t>char_1042_phatm2</t>
+  </si>
+  <si>
+    <t>可部署位</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>CanSetPos</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>高台位</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>地面位</t>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2572,7 +2580,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BS583"/>
+  <dimension ref="A1:BR583"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -2602,22 +2610,22 @@
     <col min="34" max="34" width="13.83203125" customWidth="1"/>
     <col min="35" max="35" width="34.5" customWidth="1"/>
     <col min="36" max="37" width="9.83203125" customWidth="1"/>
-    <col min="43" max="43" width="12.5" customWidth="1"/>
-    <col min="50" max="50" width="24.33203125" customWidth="1"/>
-    <col min="52" max="52" width="17.75" customWidth="1"/>
-    <col min="53" max="53" width="7.83203125" customWidth="1"/>
-    <col min="56" max="56" width="24.25" customWidth="1"/>
-    <col min="57" max="57" width="13.25" customWidth="1"/>
-    <col min="58" max="58" width="16.08203125" customWidth="1"/>
-    <col min="59" max="59" width="8" customWidth="1"/>
-    <col min="64" max="64" width="39.58203125" customWidth="1"/>
-    <col min="65" max="65" width="14" customWidth="1"/>
-    <col min="66" max="66" width="14.83203125" customWidth="1"/>
-    <col min="67" max="70" width="14" customWidth="1"/>
-    <col min="71" max="71" width="19.1640625" customWidth="1"/>
+    <col min="42" max="42" width="12.5" customWidth="1"/>
+    <col min="49" max="49" width="24.33203125" customWidth="1"/>
+    <col min="51" max="51" width="17.75" customWidth="1"/>
+    <col min="52" max="52" width="7.83203125" customWidth="1"/>
+    <col min="55" max="55" width="24.25" customWidth="1"/>
+    <col min="56" max="56" width="13.25" customWidth="1"/>
+    <col min="57" max="57" width="16.08203125" customWidth="1"/>
+    <col min="58" max="58" width="8" customWidth="1"/>
+    <col min="63" max="63" width="39.58203125" customWidth="1"/>
+    <col min="64" max="64" width="14" customWidth="1"/>
+    <col min="65" max="65" width="14.83203125" customWidth="1"/>
+    <col min="66" max="69" width="14" customWidth="1"/>
+    <col min="70" max="70" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
         <v>5</v>
       </c>
@@ -2693,274 +2701,268 @@
       <c r="AL1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="AN1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>33</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>34</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>35</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>36</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>38</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>39</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>40</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BC1" t="s">
         <v>41</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BD1" t="s">
         <v>42</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>43</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>44</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>45</v>
       </c>
-      <c r="BG1" t="s">
-        <v>46</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>49</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>50</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>51</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>52</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>53</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>54</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>55</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>56</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>57</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>58</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>59</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>60</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>61</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>62</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>63</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>64</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>65</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>66</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>67</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>68</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>69</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>70</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AC2" t="s">
         <v>71</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>72</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AE2" t="s">
         <v>73</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AF2" t="s">
         <v>74</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AG2" t="s">
         <v>75</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AH2" t="s">
         <v>76</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI2" t="s">
         <v>77</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AJ2" t="s">
         <v>78</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AK2" t="s">
         <v>79</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AL2" t="s">
         <v>80</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AM2" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="AN2" t="s">
         <v>81</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AO2" t="s">
         <v>82</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AP2" t="s">
         <v>83</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AQ2" t="s">
         <v>84</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AR2" t="s">
         <v>85</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AS2" t="s">
         <v>86</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AT2" t="s">
         <v>87</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AU2" t="s">
         <v>88</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AV2" t="s">
         <v>89</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AW2" t="s">
         <v>90</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AX2" t="s">
         <v>91</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AY2" t="s">
         <v>92</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AZ2" t="s">
         <v>93</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="BA2" t="s">
         <v>94</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BB2" t="s">
         <v>95</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BC2" t="s">
         <v>96</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BD2" t="s">
         <v>97</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BE2" t="s">
         <v>98</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BF2" t="s">
         <v>99</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BG2" t="s">
         <v>100</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BH2" t="s">
         <v>101</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BI2" t="s">
         <v>102</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BJ2" t="s">
         <v>103</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BK2" t="s">
         <v>104</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BL2" t="s">
         <v>105</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BM2" t="s">
         <v>106</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BN2" t="s">
         <v>107</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BO2" t="s">
         <v>108</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BP2" t="s">
         <v>109</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BQ2" t="s">
         <v>110</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BR2" t="s">
         <v>111</v>
       </c>
-      <c r="BP2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>114</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2968,88 +2970,88 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F3" t="s">
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="O3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Q3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="R3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="S3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="T3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="U3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="V3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="W3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="X3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Y3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Z3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AA3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AB3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AC3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AD3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AE3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AF3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AG3" t="s">
         <v>2</v>
@@ -3058,61 +3060,61 @@
         <v>2</v>
       </c>
       <c r="AI3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AJ3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AK3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AM3" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AU3" t="s">
         <v>116</v>
       </c>
-      <c r="AN3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>118</v>
-      </c>
       <c r="AV3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="AW3" t="s">
         <v>117</v>
       </c>
       <c r="AX3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AZ3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="BA3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BB3" t="s">
-        <v>122</v>
+        <v>2</v>
       </c>
       <c r="BC3" t="s">
         <v>2</v>
@@ -3124,58 +3126,55 @@
         <v>2</v>
       </c>
       <c r="BF3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BH3" t="s">
         <v>2</v>
       </c>
-      <c r="BG3" t="s">
-        <v>123</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>118</v>
-      </c>
       <c r="BI3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BJ3" t="s">
         <v>2</v>
       </c>
-      <c r="BJ3" t="s">
-        <v>124</v>
-      </c>
       <c r="BK3" t="s">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="BL3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="BM3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BN3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BO3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BP3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BQ3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BR3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:71" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="1" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -3226,79 +3225,82 @@
         <v>4</v>
       </c>
       <c r="AH4" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AM4" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="AN4">
+        <v>1</v>
+      </c>
+      <c r="AO4">
+        <v>0.5</v>
+      </c>
+      <c r="AV4">
+        <v>0.25</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>126</v>
+      </c>
+      <c r="BB4" t="s">
         <v>127</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="BC4" t="s">
         <v>128</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="BD4" t="s">
         <v>129</v>
       </c>
-      <c r="AM4">
-        <v>1</v>
-      </c>
-      <c r="AO4">
-        <v>1</v>
-      </c>
-      <c r="AP4">
-        <v>0.5</v>
-      </c>
-      <c r="AW4">
-        <v>0.25</v>
-      </c>
-      <c r="BB4" t="s">
+      <c r="BE4" t="s">
         <v>130</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BF4" t="s">
         <v>131</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BG4">
+        <v>6</v>
+      </c>
+      <c r="BH4" t="s">
         <v>132</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BI4" t="s">
         <v>133</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BL4" t="s">
         <v>134</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BM4" t="s">
         <v>135</v>
       </c>
-      <c r="BH4">
-        <v>6</v>
-      </c>
-      <c r="BI4" t="s">
+      <c r="BO4" t="s">
         <v>136</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BP4" t="s">
+        <v>136</v>
+      </c>
+      <c r="BR4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="AM5" s="8"/>
+    </row>
+    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>137</v>
       </c>
-      <c r="BM4" t="s">
-        <v>138</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>139</v>
-      </c>
-      <c r="BP4" t="s">
-        <v>140</v>
-      </c>
-      <c r="BQ4" t="s">
-        <v>140</v>
-      </c>
-      <c r="BS4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>141</v>
-      </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -3346,13 +3348,13 @@
         <v>-1</v>
       </c>
       <c r="AG8" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AH8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="AI8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AK8">
         <v>3</v>
@@ -3360,68 +3362,68 @@
       <c r="AL8">
         <v>-0.5</v>
       </c>
+      <c r="AM8" s="8" t="s">
+        <v>575</v>
+      </c>
       <c r="AN8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
       </c>
-      <c r="AP8">
+      <c r="AV8">
         <v>0</v>
       </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>1</v>
-      </c>
-      <c r="BB8" t="s">
+      <c r="AY8">
+        <v>1</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>139</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>140</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>141</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>131</v>
+      </c>
+      <c r="BG8">
+        <v>5</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>142</v>
+      </c>
+      <c r="BL8" t="s">
+        <v>134</v>
+      </c>
+      <c r="BM8" t="s">
         <v>143</v>
       </c>
-      <c r="BD8" t="s">
-        <v>132</v>
-      </c>
-      <c r="BE8" t="s">
+      <c r="BO8" t="s">
         <v>144</v>
       </c>
-      <c r="BF8" t="s">
+      <c r="BP8" t="s">
+        <v>144</v>
+      </c>
+      <c r="BR8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>145</v>
       </c>
-      <c r="BG8" t="s">
-        <v>135</v>
-      </c>
-      <c r="BH8">
-        <v>5</v>
-      </c>
-      <c r="BI8" t="s">
-        <v>146</v>
-      </c>
-      <c r="BM8" t="s">
-        <v>138</v>
-      </c>
-      <c r="BN8" t="s">
-        <v>147</v>
-      </c>
-      <c r="BP8" t="s">
-        <v>148</v>
-      </c>
-      <c r="BQ8" t="s">
-        <v>148</v>
-      </c>
-      <c r="BS8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>149</v>
-      </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -3472,13 +3474,13 @@
         <v>-1</v>
       </c>
       <c r="AG9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="AH9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="AI9" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="AK9">
         <v>3</v>
@@ -3486,73 +3488,73 @@
       <c r="AL9">
         <v>-0.5</v>
       </c>
+      <c r="AM9" s="8" t="s">
+        <v>575</v>
+      </c>
       <c r="AN9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9">
         <v>0</v>
       </c>
-      <c r="AP9">
+      <c r="AV9">
         <v>0</v>
       </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>1</v>
-      </c>
-      <c r="BB9" t="s">
+      <c r="AY9">
+        <v>1</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>139</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>140</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>141</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BG9">
+        <v>5</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>142</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>134</v>
+      </c>
+      <c r="BM9" t="s">
         <v>143</v>
       </c>
-      <c r="BD9" t="s">
-        <v>132</v>
-      </c>
-      <c r="BE9" t="s">
+      <c r="BO9" t="s">
         <v>144</v>
       </c>
-      <c r="BF9" t="s">
-        <v>145</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>135</v>
-      </c>
-      <c r="BH9">
-        <v>5</v>
-      </c>
-      <c r="BI9" t="s">
-        <v>146</v>
-      </c>
-      <c r="BM9" t="s">
-        <v>138</v>
-      </c>
-      <c r="BN9" t="s">
+      <c r="BP9" t="s">
+        <v>144</v>
+      </c>
+      <c r="BR9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>147</v>
       </c>
-      <c r="BP9" t="s">
+      <c r="B10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" t="s">
         <v>148</v>
       </c>
-      <c r="BQ9" t="s">
-        <v>148</v>
-      </c>
-      <c r="BS9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>151</v>
-      </c>
-      <c r="B10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D10" t="s">
-        <v>152</v>
-      </c>
       <c r="E10" s="12" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G10">
         <v>0.01</v>
@@ -3603,13 +3605,13 @@
         <v>-1</v>
       </c>
       <c r="AG10" t="s">
+        <v>147</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI10" t="s">
         <v>151</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>127</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>155</v>
       </c>
       <c r="AK10">
         <v>3</v>
@@ -3617,81 +3619,81 @@
       <c r="AL10">
         <v>-0.5</v>
       </c>
+      <c r="AM10" s="8" t="s">
+        <v>575</v>
+      </c>
       <c r="AN10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO10">
         <v>0</v>
       </c>
       <c r="AP10">
+        <v>1</v>
+      </c>
+      <c r="AV10">
         <v>0</v>
       </c>
-      <c r="AQ10">
-        <v>1</v>
-      </c>
-      <c r="AW10">
-        <v>0</v>
-      </c>
-      <c r="AZ10">
-        <v>1</v>
-      </c>
-      <c r="BB10" t="s">
-        <v>143</v>
-      </c>
-      <c r="BD10" t="s">
-        <v>132</v>
-      </c>
-      <c r="BE10" t="str">
+      <c r="AY10">
+        <v>1</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>139</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD10" t="str">
         <f>"half_"&amp;D10</f>
         <v>half_otter</v>
       </c>
-      <c r="BF10" t="str">
+      <c r="BE10" t="str">
         <f>D10</f>
         <v>otter</v>
       </c>
-      <c r="BG10" t="s">
+      <c r="BF10" t="s">
+        <v>131</v>
+      </c>
+      <c r="BG10">
+        <v>5</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>142</v>
+      </c>
+      <c r="BL10" t="s">
+        <v>134</v>
+      </c>
+      <c r="BM10" t="s">
         <v>135</v>
       </c>
-      <c r="BH10">
-        <v>5</v>
-      </c>
-      <c r="BI10" t="s">
-        <v>146</v>
-      </c>
-      <c r="BM10" t="s">
-        <v>138</v>
-      </c>
-      <c r="BN10" t="s">
-        <v>139</v>
+      <c r="BO10" t="s">
+        <v>136</v>
       </c>
       <c r="BP10" t="s">
-        <v>140</v>
-      </c>
-      <c r="BQ10" t="s">
-        <v>140</v>
-      </c>
-      <c r="BS10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:71" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="BR10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:70" x14ac:dyDescent="0.25">
       <c r="E11" s="12"/>
     </row>
-    <row r="12" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -3736,10 +3738,10 @@
         <v>1</v>
       </c>
       <c r="AG12" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AH12" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="AK12">
         <v>3</v>
@@ -3747,2412 +3749,2412 @@
       <c r="AL12">
         <v>-0.5</v>
       </c>
+      <c r="AM12" s="8" t="s">
+        <v>575</v>
+      </c>
       <c r="AN12">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="AO12">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="AP12">
+        <v>1</v>
+      </c>
+      <c r="AV12">
         <v>0</v>
       </c>
-      <c r="AQ12">
-        <v>1</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>1</v>
-      </c>
-      <c r="BB12" t="s">
-        <v>143</v>
-      </c>
-      <c r="BD12" t="s">
-        <v>132</v>
-      </c>
-      <c r="BE12" t="str">
+      <c r="AY12">
+        <v>1</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>139</v>
+      </c>
+      <c r="BC12" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD12" t="str">
         <f>"half_"&amp;D12</f>
         <v>half_otter</v>
       </c>
-      <c r="BF12" t="str">
+      <c r="BE12" t="str">
         <f>D12</f>
         <v>otter</v>
       </c>
-      <c r="BG12" t="s">
+      <c r="BF12" t="s">
+        <v>131</v>
+      </c>
+      <c r="BG12">
+        <v>5</v>
+      </c>
+      <c r="BH12" t="s">
+        <v>142</v>
+      </c>
+      <c r="BL12" t="s">
+        <v>134</v>
+      </c>
+      <c r="BM12" t="s">
         <v>135</v>
       </c>
-      <c r="BH12">
-        <v>5</v>
-      </c>
-      <c r="BI12" t="s">
-        <v>146</v>
-      </c>
-      <c r="BM12" t="s">
-        <v>138</v>
-      </c>
-      <c r="BN12" t="s">
-        <v>139</v>
+      <c r="BO12" t="s">
+        <v>136</v>
       </c>
       <c r="BP12" t="s">
-        <v>140</v>
-      </c>
-      <c r="BQ12" t="s">
-        <v>140</v>
-      </c>
-      <c r="BS12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="BR12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D21" s="13"/>
       <c r="E21" s="12"/>
-      <c r="BO21" s="14"/>
-      <c r="BR21" s="14"/>
-    </row>
-    <row r="22" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN21" s="14"/>
+      <c r="BQ21" s="14"/>
+    </row>
+    <row r="22" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D22" s="13"/>
       <c r="E22" s="12"/>
-      <c r="BO22" s="14"/>
-      <c r="BR22" s="14"/>
-    </row>
-    <row r="23" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN22" s="14"/>
+      <c r="BQ22" s="14"/>
+    </row>
+    <row r="23" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D23" s="13"/>
       <c r="E23" s="12"/>
-      <c r="BO23" s="14"/>
-      <c r="BR23" s="14"/>
-    </row>
-    <row r="24" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN23" s="14"/>
+      <c r="BQ23" s="14"/>
+    </row>
+    <row r="24" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D24" s="13"/>
       <c r="E24" s="12"/>
-      <c r="BO24" s="14"/>
-      <c r="BR24" s="14"/>
-    </row>
-    <row r="25" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN24" s="14"/>
+      <c r="BQ24" s="14"/>
+    </row>
+    <row r="25" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D25" s="13"/>
       <c r="E25" s="12"/>
-      <c r="BO25" s="14"/>
-      <c r="BR25" s="14"/>
-    </row>
-    <row r="26" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN25" s="14"/>
+      <c r="BQ25" s="14"/>
+    </row>
+    <row r="26" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D26" s="13"/>
       <c r="E26" s="12"/>
-      <c r="BO26" s="14"/>
-      <c r="BR26" s="14"/>
-    </row>
-    <row r="27" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN26" s="14"/>
+      <c r="BQ26" s="14"/>
+    </row>
+    <row r="27" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D27" s="13"/>
       <c r="E27" s="12"/>
-      <c r="BO27" s="14"/>
-      <c r="BR27" s="14"/>
-    </row>
-    <row r="28" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN27" s="14"/>
+      <c r="BQ27" s="14"/>
+    </row>
+    <row r="28" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D28" s="13"/>
       <c r="E28" s="12"/>
-      <c r="BR28" s="14"/>
-    </row>
-    <row r="29" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ28" s="14"/>
+    </row>
+    <row r="29" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D29" s="13"/>
       <c r="E29" s="12"/>
-      <c r="BR29" s="14"/>
-    </row>
-    <row r="30" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ29" s="14"/>
+    </row>
+    <row r="30" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D30" s="13"/>
       <c r="E30" s="12"/>
-      <c r="BR30" s="14"/>
-    </row>
-    <row r="31" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ30" s="14"/>
+    </row>
+    <row r="31" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D31" s="13"/>
       <c r="E31" s="12"/>
-      <c r="BO31" s="14"/>
-      <c r="BR31" s="14"/>
-    </row>
-    <row r="32" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN31" s="14"/>
+      <c r="BQ31" s="14"/>
+    </row>
+    <row r="32" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D32" s="13"/>
       <c r="E32" s="12"/>
-      <c r="BO32" s="14"/>
-      <c r="BR32" s="14"/>
-    </row>
-    <row r="33" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN32" s="14"/>
+      <c r="BQ32" s="14"/>
+    </row>
+    <row r="33" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D33" s="13"/>
       <c r="E33" s="12"/>
-      <c r="BO33" s="14"/>
-      <c r="BR33" s="14"/>
-    </row>
-    <row r="34" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN33" s="14"/>
+      <c r="BQ33" s="14"/>
+    </row>
+    <row r="34" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D34" s="13"/>
       <c r="E34" s="12"/>
-      <c r="BO34" s="14"/>
-      <c r="BR34" s="14"/>
-    </row>
-    <row r="35" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN34" s="14"/>
+      <c r="BQ34" s="14"/>
+    </row>
+    <row r="35" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D35" s="13"/>
       <c r="E35" s="12"/>
-      <c r="BO35" s="14"/>
-      <c r="BR35" s="14"/>
-    </row>
-    <row r="36" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN35" s="14"/>
+      <c r="BQ35" s="14"/>
+    </row>
+    <row r="36" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D36" s="13"/>
       <c r="E36" s="12"/>
-      <c r="BO36" s="14"/>
-      <c r="BR36" s="14"/>
-    </row>
-    <row r="37" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN36" s="14"/>
+      <c r="BQ36" s="14"/>
+    </row>
+    <row r="37" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D37" s="13"/>
       <c r="E37" s="12"/>
-      <c r="BO37" s="14"/>
-      <c r="BR37" s="14"/>
-    </row>
-    <row r="38" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN37" s="14"/>
+      <c r="BQ37" s="14"/>
+    </row>
+    <row r="38" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D38" s="13"/>
       <c r="E38" s="12"/>
-      <c r="BO38" s="14"/>
-      <c r="BR38" s="14"/>
-    </row>
-    <row r="39" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN38" s="14"/>
+      <c r="BQ38" s="14"/>
+    </row>
+    <row r="39" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D39" s="13"/>
       <c r="E39" s="12"/>
-      <c r="BO39" s="14"/>
-      <c r="BR39" s="14"/>
-    </row>
-    <row r="40" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN39" s="14"/>
+      <c r="BQ39" s="14"/>
+    </row>
+    <row r="40" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D40" s="13"/>
       <c r="E40" s="12"/>
-      <c r="BO40" s="14"/>
-      <c r="BR40" s="14"/>
-    </row>
-    <row r="41" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN40" s="14"/>
+      <c r="BQ40" s="14"/>
+    </row>
+    <row r="41" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D41" s="13"/>
       <c r="E41" s="12"/>
-      <c r="BO41" s="14"/>
-      <c r="BR41" s="14"/>
-    </row>
-    <row r="42" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN41" s="14"/>
+      <c r="BQ41" s="14"/>
+    </row>
+    <row r="42" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D42" s="13"/>
       <c r="E42" s="12"/>
-      <c r="BO42" s="14"/>
-      <c r="BR42" s="14"/>
-    </row>
-    <row r="43" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN42" s="14"/>
+      <c r="BQ42" s="14"/>
+    </row>
+    <row r="43" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D43" s="13"/>
       <c r="E43" s="12"/>
-      <c r="BO43" s="14"/>
-      <c r="BR43" s="14"/>
-    </row>
-    <row r="44" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN43" s="14"/>
+      <c r="BQ43" s="14"/>
+    </row>
+    <row r="44" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D44" s="13"/>
       <c r="E44" s="12"/>
-      <c r="BO44" s="14"/>
-      <c r="BR44" s="14"/>
-    </row>
-    <row r="45" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN44" s="14"/>
+      <c r="BQ44" s="14"/>
+    </row>
+    <row r="45" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D45" s="13"/>
       <c r="E45" s="12"/>
-      <c r="BO45" s="14"/>
-      <c r="BR45" s="14"/>
-    </row>
-    <row r="46" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN45" s="14"/>
+      <c r="BQ45" s="14"/>
+    </row>
+    <row r="46" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D46" s="13"/>
       <c r="E46" s="12"/>
-      <c r="BO46" s="14"/>
-      <c r="BR46" s="14"/>
-    </row>
-    <row r="47" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN46" s="14"/>
+      <c r="BQ46" s="14"/>
+    </row>
+    <row r="47" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D47" s="13"/>
       <c r="E47" s="12"/>
-      <c r="BO47" s="14"/>
-      <c r="BR47" s="14"/>
-    </row>
-    <row r="48" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN47" s="14"/>
+      <c r="BQ47" s="14"/>
+    </row>
+    <row r="48" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D48" s="13"/>
       <c r="E48" s="12"/>
-      <c r="BO48" s="14"/>
-      <c r="BR48" s="14"/>
-    </row>
-    <row r="49" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN48" s="14"/>
+      <c r="BQ48" s="14"/>
+    </row>
+    <row r="49" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D49" s="13"/>
       <c r="E49" s="12"/>
-      <c r="BO49" s="14"/>
-      <c r="BR49" s="14"/>
-    </row>
-    <row r="50" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN49" s="14"/>
+      <c r="BQ49" s="14"/>
+    </row>
+    <row r="50" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D50" s="13"/>
       <c r="E50" s="12"/>
-      <c r="BO50" s="14"/>
-      <c r="BR50" s="14"/>
-    </row>
-    <row r="51" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN50" s="14"/>
+      <c r="BQ50" s="14"/>
+    </row>
+    <row r="51" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D51" s="13"/>
       <c r="E51" s="12"/>
-      <c r="BO51" s="14"/>
-      <c r="BR51" s="14"/>
-    </row>
-    <row r="52" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN51" s="14"/>
+      <c r="BQ51" s="14"/>
+    </row>
+    <row r="52" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D52" s="13"/>
       <c r="E52" s="12"/>
-      <c r="BO52" s="14"/>
-      <c r="BR52" s="14"/>
-    </row>
-    <row r="53" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN52" s="14"/>
+      <c r="BQ52" s="14"/>
+    </row>
+    <row r="53" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D53" s="13"/>
       <c r="E53" s="12"/>
-      <c r="BO53" s="14"/>
-      <c r="BR53" s="14"/>
-    </row>
-    <row r="54" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN53" s="14"/>
+      <c r="BQ53" s="14"/>
+    </row>
+    <row r="54" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D54" s="13"/>
       <c r="E54" s="12"/>
-      <c r="BO54" s="14"/>
-      <c r="BR54" s="14"/>
-    </row>
-    <row r="55" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN54" s="14"/>
+      <c r="BQ54" s="14"/>
+    </row>
+    <row r="55" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D55" s="13"/>
       <c r="E55" s="12"/>
-      <c r="BO55" s="14"/>
-      <c r="BR55" s="14"/>
-    </row>
-    <row r="56" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN55" s="14"/>
+      <c r="BQ55" s="14"/>
+    </row>
+    <row r="56" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D56" s="13"/>
       <c r="E56" s="12"/>
-      <c r="BO56" s="14"/>
-      <c r="BR56" s="14"/>
-    </row>
-    <row r="57" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN56" s="14"/>
+      <c r="BQ56" s="14"/>
+    </row>
+    <row r="57" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D57" s="13"/>
       <c r="E57" s="12"/>
-      <c r="BO57" s="14"/>
-      <c r="BR57" s="14"/>
-    </row>
-    <row r="58" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN57" s="14"/>
+      <c r="BQ57" s="14"/>
+    </row>
+    <row r="58" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D58" s="13"/>
       <c r="E58" s="12"/>
-      <c r="BO58" s="14"/>
-      <c r="BR58" s="14"/>
-    </row>
-    <row r="59" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN58" s="14"/>
+      <c r="BQ58" s="14"/>
+    </row>
+    <row r="59" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D59" s="13"/>
       <c r="E59" s="12"/>
-      <c r="BO59" s="14"/>
-      <c r="BR59" s="14"/>
-    </row>
-    <row r="60" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN59" s="14"/>
+      <c r="BQ59" s="14"/>
+    </row>
+    <row r="60" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D60" s="13"/>
       <c r="E60" s="12"/>
-      <c r="BO60" s="14"/>
-      <c r="BR60" s="14"/>
-    </row>
-    <row r="61" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN60" s="14"/>
+      <c r="BQ60" s="14"/>
+    </row>
+    <row r="61" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D61" s="13"/>
       <c r="E61" s="12"/>
-      <c r="BO61" s="14"/>
-      <c r="BR61" s="14"/>
-    </row>
-    <row r="62" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN61" s="14"/>
+      <c r="BQ61" s="14"/>
+    </row>
+    <row r="62" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D62" s="13"/>
       <c r="E62" s="12"/>
-      <c r="BO62" s="14"/>
-      <c r="BR62" s="14"/>
-    </row>
-    <row r="63" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN62" s="14"/>
+      <c r="BQ62" s="14"/>
+    </row>
+    <row r="63" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D63" s="13"/>
       <c r="E63" s="12"/>
-      <c r="BO63" s="14"/>
-      <c r="BR63" s="14"/>
-    </row>
-    <row r="64" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN63" s="14"/>
+      <c r="BQ63" s="14"/>
+    </row>
+    <row r="64" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D64" s="13"/>
       <c r="E64" s="12"/>
-      <c r="BO64" s="14"/>
-      <c r="BR64" s="14"/>
-    </row>
-    <row r="65" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN64" s="14"/>
+      <c r="BQ64" s="14"/>
+    </row>
+    <row r="65" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D65" s="13"/>
       <c r="E65" s="12"/>
-      <c r="BO65" s="14"/>
-      <c r="BR65" s="14"/>
-    </row>
-    <row r="66" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN65" s="14"/>
+      <c r="BQ65" s="14"/>
+    </row>
+    <row r="66" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D66" s="13"/>
       <c r="E66" s="12"/>
-      <c r="BO66" s="14"/>
-      <c r="BR66" s="14"/>
-    </row>
-    <row r="67" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN66" s="14"/>
+      <c r="BQ66" s="14"/>
+    </row>
+    <row r="67" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D67" s="13"/>
       <c r="E67" s="12"/>
-      <c r="BO67" s="14"/>
-      <c r="BR67" s="14"/>
-    </row>
-    <row r="68" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN67" s="14"/>
+      <c r="BQ67" s="14"/>
+    </row>
+    <row r="68" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D68" s="13"/>
       <c r="E68" s="12"/>
-      <c r="BO68" s="14"/>
-      <c r="BR68" s="14"/>
-    </row>
-    <row r="69" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN68" s="14"/>
+      <c r="BQ68" s="14"/>
+    </row>
+    <row r="69" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D69" s="13"/>
       <c r="E69" s="12"/>
-      <c r="BO69" s="14"/>
-      <c r="BR69" s="14"/>
-    </row>
-    <row r="70" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN69" s="14"/>
+      <c r="BQ69" s="14"/>
+    </row>
+    <row r="70" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D70" s="13"/>
       <c r="E70" s="12"/>
-      <c r="BO70" s="14"/>
-      <c r="BR70" s="14"/>
-    </row>
-    <row r="71" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN70" s="14"/>
+      <c r="BQ70" s="14"/>
+    </row>
+    <row r="71" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D71" s="13"/>
       <c r="E71" s="12"/>
-      <c r="BO71" s="14"/>
-      <c r="BR71" s="14"/>
-    </row>
-    <row r="72" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN71" s="14"/>
+      <c r="BQ71" s="14"/>
+    </row>
+    <row r="72" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D72" s="13"/>
       <c r="E72" s="12"/>
-      <c r="BO72" s="14"/>
-      <c r="BR72" s="14"/>
-    </row>
-    <row r="73" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN72" s="14"/>
+      <c r="BQ72" s="14"/>
+    </row>
+    <row r="73" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D73" s="13"/>
       <c r="E73" s="12"/>
-      <c r="BO73" s="14"/>
-      <c r="BR73" s="14"/>
-    </row>
-    <row r="74" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN73" s="14"/>
+      <c r="BQ73" s="14"/>
+    </row>
+    <row r="74" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D74" s="13"/>
       <c r="E74" s="12"/>
-      <c r="BO74" s="14"/>
-      <c r="BR74" s="14"/>
-    </row>
-    <row r="75" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN74" s="14"/>
+      <c r="BQ74" s="14"/>
+    </row>
+    <row r="75" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D75" s="13"/>
       <c r="E75" s="12"/>
-      <c r="BO75" s="14"/>
-      <c r="BR75" s="14"/>
-    </row>
-    <row r="76" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN75" s="14"/>
+      <c r="BQ75" s="14"/>
+    </row>
+    <row r="76" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D76" s="13"/>
       <c r="E76" s="12"/>
-      <c r="BO76" s="14"/>
-      <c r="BR76" s="14"/>
-    </row>
-    <row r="77" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN76" s="14"/>
+      <c r="BQ76" s="14"/>
+    </row>
+    <row r="77" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D77" s="13"/>
       <c r="E77" s="12"/>
-      <c r="BO77" s="14"/>
-      <c r="BR77" s="14"/>
-    </row>
-    <row r="78" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN77" s="14"/>
+      <c r="BQ77" s="14"/>
+    </row>
+    <row r="78" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D78" s="13"/>
       <c r="E78" s="12"/>
-      <c r="BO78" s="14"/>
-      <c r="BR78" s="14"/>
-    </row>
-    <row r="79" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN78" s="14"/>
+      <c r="BQ78" s="14"/>
+    </row>
+    <row r="79" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D79" s="13"/>
       <c r="E79" s="12"/>
-      <c r="BO79" s="14"/>
-      <c r="BR79" s="14"/>
-    </row>
-    <row r="80" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN79" s="14"/>
+      <c r="BQ79" s="14"/>
+    </row>
+    <row r="80" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D80" s="13"/>
       <c r="E80" s="12"/>
-      <c r="BO80" s="14"/>
-      <c r="BR80" s="14"/>
-    </row>
-    <row r="81" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN80" s="14"/>
+      <c r="BQ80" s="14"/>
+    </row>
+    <row r="81" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D81" s="13"/>
       <c r="E81" s="12"/>
-      <c r="BO81" s="14"/>
-      <c r="BR81" s="14"/>
-    </row>
-    <row r="82" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN81" s="14"/>
+      <c r="BQ81" s="14"/>
+    </row>
+    <row r="82" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D82" s="13"/>
       <c r="E82" s="12"/>
-      <c r="BO82" s="14"/>
-      <c r="BR82" s="14"/>
-    </row>
-    <row r="83" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN82" s="14"/>
+      <c r="BQ82" s="14"/>
+    </row>
+    <row r="83" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D83" s="13"/>
       <c r="E83" s="12"/>
-      <c r="BO83" s="14"/>
-      <c r="BR83" s="14"/>
-    </row>
-    <row r="84" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN83" s="14"/>
+      <c r="BQ83" s="14"/>
+    </row>
+    <row r="84" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D84" s="13"/>
       <c r="E84" s="12"/>
-      <c r="BO84" s="14"/>
-      <c r="BR84" s="14"/>
-    </row>
-    <row r="85" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN84" s="14"/>
+      <c r="BQ84" s="14"/>
+    </row>
+    <row r="85" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D85" s="13"/>
       <c r="E85" s="12"/>
-      <c r="BO85" s="14"/>
-      <c r="BR85" s="14"/>
-    </row>
-    <row r="86" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN85" s="14"/>
+      <c r="BQ85" s="14"/>
+    </row>
+    <row r="86" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D86" s="13"/>
       <c r="E86" s="12"/>
-      <c r="BO86" s="14"/>
-      <c r="BR86" s="14"/>
-    </row>
-    <row r="87" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN86" s="14"/>
+      <c r="BQ86" s="14"/>
+    </row>
+    <row r="87" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D87" s="13"/>
       <c r="E87" s="12"/>
-      <c r="BO87" s="14"/>
-      <c r="BR87" s="14"/>
-    </row>
-    <row r="88" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN87" s="14"/>
+      <c r="BQ87" s="14"/>
+    </row>
+    <row r="88" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D88" s="13"/>
       <c r="E88" s="12"/>
-      <c r="BO88" s="14"/>
-      <c r="BR88" s="14"/>
-    </row>
-    <row r="89" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN88" s="14"/>
+      <c r="BQ88" s="14"/>
+    </row>
+    <row r="89" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D89" s="13"/>
       <c r="E89" s="12"/>
-      <c r="BO89" s="14"/>
-      <c r="BR89" s="14"/>
-    </row>
-    <row r="90" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN89" s="14"/>
+      <c r="BQ89" s="14"/>
+    </row>
+    <row r="90" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D90" s="13"/>
       <c r="E90" s="12"/>
-      <c r="BO90" s="14"/>
-      <c r="BR90" s="14"/>
-    </row>
-    <row r="91" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN90" s="14"/>
+      <c r="BQ90" s="14"/>
+    </row>
+    <row r="91" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D91" s="13"/>
       <c r="E91" s="12"/>
-      <c r="BO91" s="14"/>
-      <c r="BR91" s="14"/>
-    </row>
-    <row r="92" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN91" s="14"/>
+      <c r="BQ91" s="14"/>
+    </row>
+    <row r="92" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D92" s="13"/>
       <c r="E92" s="12"/>
-      <c r="BO92" s="14"/>
-      <c r="BR92" s="14"/>
-    </row>
-    <row r="93" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN92" s="14"/>
+      <c r="BQ92" s="14"/>
+    </row>
+    <row r="93" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D93" s="13"/>
       <c r="E93" s="12"/>
-      <c r="BO93" s="14"/>
-      <c r="BR93" s="14"/>
-    </row>
-    <row r="94" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN93" s="14"/>
+      <c r="BQ93" s="14"/>
+    </row>
+    <row r="94" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D94" s="13"/>
       <c r="E94" s="12"/>
-      <c r="BO94" s="14"/>
-      <c r="BR94" s="14"/>
-    </row>
-    <row r="95" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN94" s="14"/>
+      <c r="BQ94" s="14"/>
+    </row>
+    <row r="95" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D95" s="13"/>
       <c r="E95" s="12"/>
-      <c r="BO95" s="14"/>
-      <c r="BR95" s="14"/>
-    </row>
-    <row r="96" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN95" s="14"/>
+      <c r="BQ95" s="14"/>
+    </row>
+    <row r="96" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D96" s="13"/>
       <c r="E96" s="12"/>
-      <c r="BO96" s="14"/>
-      <c r="BR96" s="14"/>
-    </row>
-    <row r="97" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN96" s="14"/>
+      <c r="BQ96" s="14"/>
+    </row>
+    <row r="97" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D97" s="13"/>
       <c r="E97" s="12"/>
-      <c r="BO97" s="14"/>
-      <c r="BR97" s="14"/>
-    </row>
-    <row r="98" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN97" s="14"/>
+      <c r="BQ97" s="14"/>
+    </row>
+    <row r="98" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D98" s="13"/>
       <c r="E98" s="12"/>
-      <c r="BO98" s="14"/>
-      <c r="BR98" s="14"/>
-    </row>
-    <row r="99" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN98" s="14"/>
+      <c r="BQ98" s="14"/>
+    </row>
+    <row r="99" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D99" s="13"/>
       <c r="E99" s="12"/>
-      <c r="BO99" s="14"/>
-      <c r="BR99" s="14"/>
-    </row>
-    <row r="100" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN99" s="14"/>
+      <c r="BQ99" s="14"/>
+    </row>
+    <row r="100" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D100" s="13"/>
       <c r="E100" s="12"/>
-      <c r="BO100" s="14"/>
-      <c r="BR100" s="14"/>
-    </row>
-    <row r="101" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN100" s="14"/>
+      <c r="BQ100" s="14"/>
+    </row>
+    <row r="101" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D101" s="13"/>
       <c r="E101" s="12"/>
-      <c r="BO101" s="14"/>
-      <c r="BR101" s="14"/>
-    </row>
-    <row r="102" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN101" s="14"/>
+      <c r="BQ101" s="14"/>
+    </row>
+    <row r="102" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D102" s="13"/>
       <c r="E102" s="12"/>
-      <c r="BO102" s="14"/>
-      <c r="BR102" s="14"/>
-    </row>
-    <row r="103" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN102" s="14"/>
+      <c r="BQ102" s="14"/>
+    </row>
+    <row r="103" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D103" s="13"/>
       <c r="E103" s="12"/>
-      <c r="BO103" s="14"/>
-      <c r="BR103" s="14"/>
-    </row>
-    <row r="104" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN103" s="14"/>
+      <c r="BQ103" s="14"/>
+    </row>
+    <row r="104" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D104" s="13"/>
       <c r="E104" s="12"/>
-      <c r="BO104" s="14"/>
-      <c r="BR104" s="14"/>
-    </row>
-    <row r="105" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN104" s="14"/>
+      <c r="BQ104" s="14"/>
+    </row>
+    <row r="105" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D105" s="13"/>
       <c r="E105" s="12"/>
-      <c r="BO105" s="14"/>
-      <c r="BR105" s="14"/>
-    </row>
-    <row r="106" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN105" s="14"/>
+      <c r="BQ105" s="14"/>
+    </row>
+    <row r="106" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D106" s="13"/>
       <c r="E106" s="12"/>
-      <c r="BO106" s="14"/>
-      <c r="BR106" s="14"/>
-    </row>
-    <row r="107" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN106" s="14"/>
+      <c r="BQ106" s="14"/>
+    </row>
+    <row r="107" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D107" s="13"/>
       <c r="E107" s="12"/>
-      <c r="BO107" s="14"/>
-      <c r="BR107" s="14"/>
-    </row>
-    <row r="108" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN107" s="14"/>
+      <c r="BQ107" s="14"/>
+    </row>
+    <row r="108" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D108" s="13"/>
       <c r="E108" s="12"/>
-      <c r="BO108" s="14"/>
-      <c r="BR108" s="14"/>
-    </row>
-    <row r="109" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN108" s="14"/>
+      <c r="BQ108" s="14"/>
+    </row>
+    <row r="109" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D109" s="13"/>
       <c r="E109" s="12"/>
-      <c r="BO109" s="14"/>
-      <c r="BR109" s="14"/>
-    </row>
-    <row r="110" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN109" s="14"/>
+      <c r="BQ109" s="14"/>
+    </row>
+    <row r="110" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D110" s="13"/>
       <c r="E110" s="12"/>
-      <c r="BO110" s="14"/>
-      <c r="BR110" s="14"/>
-    </row>
-    <row r="111" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN110" s="14"/>
+      <c r="BQ110" s="14"/>
+    </row>
+    <row r="111" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D111" s="13"/>
       <c r="E111" s="12"/>
-      <c r="BO111" s="14"/>
-      <c r="BR111" s="14"/>
-    </row>
-    <row r="112" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN111" s="14"/>
+      <c r="BQ111" s="14"/>
+    </row>
+    <row r="112" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D112" s="13"/>
       <c r="E112" s="12"/>
-      <c r="BO112" s="14"/>
-      <c r="BR112" s="14"/>
-    </row>
-    <row r="113" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN112" s="14"/>
+      <c r="BQ112" s="14"/>
+    </row>
+    <row r="113" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D113" s="13"/>
       <c r="E113" s="12"/>
-      <c r="BO113" s="14"/>
-      <c r="BR113" s="14"/>
-    </row>
-    <row r="114" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN113" s="14"/>
+      <c r="BQ113" s="14"/>
+    </row>
+    <row r="114" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D114" s="13"/>
       <c r="E114" s="12"/>
-      <c r="BO114" s="14"/>
-      <c r="BR114" s="14"/>
-    </row>
-    <row r="115" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN114" s="14"/>
+      <c r="BQ114" s="14"/>
+    </row>
+    <row r="115" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D115" s="13"/>
       <c r="E115" s="12"/>
-      <c r="BO115" s="14"/>
-      <c r="BR115" s="14"/>
-    </row>
-    <row r="116" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN115" s="14"/>
+      <c r="BQ115" s="14"/>
+    </row>
+    <row r="116" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D116" s="13"/>
       <c r="E116" s="12"/>
-      <c r="BO116" s="14"/>
-      <c r="BR116" s="14"/>
-    </row>
-    <row r="117" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN116" s="14"/>
+      <c r="BQ116" s="14"/>
+    </row>
+    <row r="117" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D117" s="13"/>
       <c r="E117" s="12"/>
-      <c r="BO117" s="14"/>
-      <c r="BR117" s="14"/>
-    </row>
-    <row r="118" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN117" s="14"/>
+      <c r="BQ117" s="14"/>
+    </row>
+    <row r="118" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D118" s="13"/>
       <c r="E118" s="12"/>
-      <c r="BO118" s="14"/>
-      <c r="BR118" s="14"/>
-    </row>
-    <row r="119" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN118" s="14"/>
+      <c r="BQ118" s="14"/>
+    </row>
+    <row r="119" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D119" s="13"/>
       <c r="E119" s="12"/>
-      <c r="BO119" s="14"/>
-      <c r="BR119" s="14"/>
-    </row>
-    <row r="120" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN119" s="14"/>
+      <c r="BQ119" s="14"/>
+    </row>
+    <row r="120" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D120" s="13"/>
       <c r="E120" s="12"/>
-      <c r="BO120" s="14"/>
-      <c r="BR120" s="14"/>
-    </row>
-    <row r="121" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN120" s="14"/>
+      <c r="BQ120" s="14"/>
+    </row>
+    <row r="121" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D121" s="13"/>
       <c r="E121" s="12"/>
-      <c r="BO121" s="14"/>
-      <c r="BR121" s="14"/>
-    </row>
-    <row r="122" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN121" s="14"/>
+      <c r="BQ121" s="14"/>
+    </row>
+    <row r="122" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D122" s="13"/>
       <c r="E122" s="12"/>
-      <c r="BO122" s="14"/>
-      <c r="BR122" s="14"/>
-    </row>
-    <row r="123" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN122" s="14"/>
+      <c r="BQ122" s="14"/>
+    </row>
+    <row r="123" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D123" s="13"/>
       <c r="E123" s="12"/>
-      <c r="BO123" s="14"/>
-      <c r="BR123" s="14"/>
-    </row>
-    <row r="124" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN123" s="14"/>
+      <c r="BQ123" s="14"/>
+    </row>
+    <row r="124" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D124" s="13"/>
       <c r="E124" s="12"/>
-      <c r="BO124" s="14"/>
-      <c r="BR124" s="14"/>
-    </row>
-    <row r="125" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN124" s="14"/>
+      <c r="BQ124" s="14"/>
+    </row>
+    <row r="125" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D125" s="13"/>
       <c r="E125" s="12"/>
-      <c r="BO125" s="14"/>
-      <c r="BR125" s="14"/>
-    </row>
-    <row r="126" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN125" s="14"/>
+      <c r="BQ125" s="14"/>
+    </row>
+    <row r="126" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D126" s="13"/>
       <c r="E126" s="12"/>
-      <c r="BO126" s="14"/>
-      <c r="BR126" s="14"/>
-    </row>
-    <row r="127" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN126" s="14"/>
+      <c r="BQ126" s="14"/>
+    </row>
+    <row r="127" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D127" s="13"/>
       <c r="E127" s="12"/>
-      <c r="BO127" s="14"/>
-      <c r="BR127" s="14"/>
-    </row>
-    <row r="128" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN127" s="14"/>
+      <c r="BQ127" s="14"/>
+    </row>
+    <row r="128" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D128" s="13"/>
       <c r="E128" s="12"/>
-      <c r="BO128" s="14"/>
-      <c r="BR128" s="14"/>
-    </row>
-    <row r="129" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN128" s="14"/>
+      <c r="BQ128" s="14"/>
+    </row>
+    <row r="129" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D129" s="13"/>
       <c r="E129" s="12"/>
-      <c r="BO129" s="14"/>
-      <c r="BR129" s="14"/>
-    </row>
-    <row r="130" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN129" s="14"/>
+      <c r="BQ129" s="14"/>
+    </row>
+    <row r="130" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D130" s="13"/>
       <c r="E130" s="12"/>
-      <c r="BO130" s="14"/>
-      <c r="BR130" s="14"/>
-    </row>
-    <row r="131" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN130" s="14"/>
+      <c r="BQ130" s="14"/>
+    </row>
+    <row r="131" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D131" s="13"/>
       <c r="E131" s="12"/>
-      <c r="BO131" s="14"/>
-      <c r="BR131" s="14"/>
-    </row>
-    <row r="132" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN131" s="14"/>
+      <c r="BQ131" s="14"/>
+    </row>
+    <row r="132" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D132" s="13"/>
       <c r="E132" s="12"/>
-      <c r="BO132" s="14"/>
-      <c r="BR132" s="14"/>
-    </row>
-    <row r="133" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN132" s="14"/>
+      <c r="BQ132" s="14"/>
+    </row>
+    <row r="133" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D133" s="13"/>
       <c r="E133" s="12"/>
-      <c r="BO133" s="14"/>
-      <c r="BR133" s="14"/>
-    </row>
-    <row r="134" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN133" s="14"/>
+      <c r="BQ133" s="14"/>
+    </row>
+    <row r="134" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D134" s="13"/>
       <c r="E134" s="12"/>
-      <c r="BO134" s="14"/>
-      <c r="BR134" s="14"/>
-    </row>
-    <row r="135" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN134" s="14"/>
+      <c r="BQ134" s="14"/>
+    </row>
+    <row r="135" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D135" s="13"/>
       <c r="E135" s="12"/>
-      <c r="BO135" s="14"/>
-      <c r="BR135" s="14"/>
-    </row>
-    <row r="136" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN135" s="14"/>
+      <c r="BQ135" s="14"/>
+    </row>
+    <row r="136" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D136" s="13"/>
       <c r="E136" s="12"/>
-      <c r="BO136" s="14"/>
-      <c r="BR136" s="14"/>
-    </row>
-    <row r="137" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN136" s="14"/>
+      <c r="BQ136" s="14"/>
+    </row>
+    <row r="137" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D137" s="13"/>
       <c r="E137" s="12"/>
-      <c r="BO137" s="14"/>
-      <c r="BR137" s="14"/>
-    </row>
-    <row r="138" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN137" s="14"/>
+      <c r="BQ137" s="14"/>
+    </row>
+    <row r="138" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D138" s="13"/>
       <c r="E138" s="12"/>
-      <c r="BO138" s="14"/>
-      <c r="BR138" s="14"/>
-    </row>
-    <row r="139" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN138" s="14"/>
+      <c r="BQ138" s="14"/>
+    </row>
+    <row r="139" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D139" s="13"/>
       <c r="E139" s="12"/>
-      <c r="BO139" s="14"/>
-      <c r="BR139" s="14"/>
-    </row>
-    <row r="140" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN139" s="14"/>
+      <c r="BQ139" s="14"/>
+    </row>
+    <row r="140" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D140" s="13"/>
       <c r="E140" s="12"/>
-      <c r="BO140" s="14"/>
-      <c r="BR140" s="14"/>
-    </row>
-    <row r="141" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN140" s="14"/>
+      <c r="BQ140" s="14"/>
+    </row>
+    <row r="141" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D141" s="13"/>
       <c r="E141" s="12"/>
-      <c r="BO141" s="14"/>
-      <c r="BR141" s="14"/>
-    </row>
-    <row r="142" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN141" s="14"/>
+      <c r="BQ141" s="14"/>
+    </row>
+    <row r="142" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D142" s="13"/>
       <c r="E142" s="12"/>
-      <c r="BO142" s="14"/>
-      <c r="BR142" s="14"/>
-    </row>
-    <row r="143" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN142" s="14"/>
+      <c r="BQ142" s="14"/>
+    </row>
+    <row r="143" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D143" s="13"/>
       <c r="E143" s="12"/>
-      <c r="BO143" s="14"/>
-      <c r="BR143" s="14"/>
-    </row>
-    <row r="144" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN143" s="14"/>
+      <c r="BQ143" s="14"/>
+    </row>
+    <row r="144" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D144" s="13"/>
       <c r="E144" s="12"/>
-      <c r="BO144" s="14"/>
-      <c r="BR144" s="14"/>
-    </row>
-    <row r="145" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN144" s="14"/>
+      <c r="BQ144" s="14"/>
+    </row>
+    <row r="145" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D145" s="13"/>
       <c r="E145" s="12"/>
-      <c r="BO145" s="14"/>
-      <c r="BR145" s="14"/>
-    </row>
-    <row r="146" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN145" s="14"/>
+      <c r="BQ145" s="14"/>
+    </row>
+    <row r="146" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D146" s="13"/>
       <c r="E146" s="12"/>
-      <c r="BO146" s="14"/>
-      <c r="BR146" s="14"/>
-    </row>
-    <row r="147" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN146" s="14"/>
+      <c r="BQ146" s="14"/>
+    </row>
+    <row r="147" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D147" s="13"/>
       <c r="E147" s="12"/>
-      <c r="BO147" s="14"/>
-      <c r="BR147" s="14"/>
-    </row>
-    <row r="148" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN147" s="14"/>
+      <c r="BQ147" s="14"/>
+    </row>
+    <row r="148" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D148" s="13"/>
       <c r="E148" s="12"/>
-      <c r="BO148" s="14"/>
-      <c r="BR148" s="14"/>
-    </row>
-    <row r="149" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN148" s="14"/>
+      <c r="BQ148" s="14"/>
+    </row>
+    <row r="149" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D149" s="13"/>
       <c r="E149" s="12"/>
-      <c r="BO149" s="14"/>
-      <c r="BR149" s="14"/>
-    </row>
-    <row r="150" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN149" s="14"/>
+      <c r="BQ149" s="14"/>
+    </row>
+    <row r="150" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D150" s="13"/>
       <c r="E150" s="12"/>
-      <c r="BO150" s="14"/>
-      <c r="BR150" s="14"/>
-    </row>
-    <row r="151" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN150" s="14"/>
+      <c r="BQ150" s="14"/>
+    </row>
+    <row r="151" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D151" s="13"/>
       <c r="E151" s="12"/>
-      <c r="BO151" s="14"/>
-      <c r="BR151" s="14"/>
-    </row>
-    <row r="152" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN151" s="14"/>
+      <c r="BQ151" s="14"/>
+    </row>
+    <row r="152" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D152" s="13"/>
       <c r="E152" s="12"/>
-      <c r="BO152" s="14"/>
-      <c r="BR152" s="14"/>
-    </row>
-    <row r="153" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN152" s="14"/>
+      <c r="BQ152" s="14"/>
+    </row>
+    <row r="153" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D153" s="13"/>
       <c r="E153" s="12"/>
-      <c r="BO153" s="14"/>
-      <c r="BR153" s="14"/>
-    </row>
-    <row r="154" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN153" s="14"/>
+      <c r="BQ153" s="14"/>
+    </row>
+    <row r="154" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D154" s="13"/>
       <c r="E154" s="12"/>
-      <c r="BO154" s="14"/>
-      <c r="BR154" s="14"/>
-    </row>
-    <row r="155" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN154" s="14"/>
+      <c r="BQ154" s="14"/>
+    </row>
+    <row r="155" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D155" s="13"/>
       <c r="E155" s="12"/>
-      <c r="BO155" s="14"/>
-      <c r="BR155" s="14"/>
-    </row>
-    <row r="156" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN155" s="14"/>
+      <c r="BQ155" s="14"/>
+    </row>
+    <row r="156" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D156" s="13"/>
       <c r="E156" s="12"/>
-      <c r="BO156" s="14"/>
-      <c r="BR156" s="14"/>
-    </row>
-    <row r="157" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN156" s="14"/>
+      <c r="BQ156" s="14"/>
+    </row>
+    <row r="157" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D157" s="13"/>
       <c r="E157" s="12"/>
-      <c r="BO157" s="14"/>
-      <c r="BR157" s="14"/>
-    </row>
-    <row r="158" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN157" s="14"/>
+      <c r="BQ157" s="14"/>
+    </row>
+    <row r="158" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D158" s="13"/>
       <c r="E158" s="12"/>
-      <c r="BO158" s="14"/>
-      <c r="BR158" s="14"/>
-    </row>
-    <row r="159" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN158" s="14"/>
+      <c r="BQ158" s="14"/>
+    </row>
+    <row r="159" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D159" s="13"/>
       <c r="E159" s="12"/>
-      <c r="BO159" s="14"/>
-      <c r="BR159" s="14"/>
-    </row>
-    <row r="160" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN159" s="14"/>
+      <c r="BQ159" s="14"/>
+    </row>
+    <row r="160" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D160" s="13"/>
       <c r="E160" s="12"/>
-      <c r="BO160" s="14"/>
-      <c r="BR160" s="14"/>
-    </row>
-    <row r="161" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN160" s="14"/>
+      <c r="BQ160" s="14"/>
+    </row>
+    <row r="161" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D161" s="13"/>
       <c r="E161" s="12"/>
-      <c r="BO161" s="14"/>
-      <c r="BR161" s="14"/>
-    </row>
-    <row r="162" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN161" s="14"/>
+      <c r="BQ161" s="14"/>
+    </row>
+    <row r="162" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D162" s="13"/>
       <c r="E162" s="12"/>
-      <c r="BO162" s="14"/>
-      <c r="BR162" s="14"/>
-    </row>
-    <row r="163" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN162" s="14"/>
+      <c r="BQ162" s="14"/>
+    </row>
+    <row r="163" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D163" s="13"/>
       <c r="E163" s="12"/>
-      <c r="BO163" s="14"/>
-      <c r="BR163" s="14"/>
-    </row>
-    <row r="164" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN163" s="14"/>
+      <c r="BQ163" s="14"/>
+    </row>
+    <row r="164" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D164" s="13"/>
       <c r="E164" s="12"/>
-      <c r="BO164" s="14"/>
-      <c r="BR164" s="14"/>
-    </row>
-    <row r="165" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN164" s="14"/>
+      <c r="BQ164" s="14"/>
+    </row>
+    <row r="165" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D165" s="13"/>
       <c r="E165" s="12"/>
-      <c r="BO165" s="14"/>
-      <c r="BR165" s="14"/>
-    </row>
-    <row r="166" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN165" s="14"/>
+      <c r="BQ165" s="14"/>
+    </row>
+    <row r="166" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D166" s="13"/>
       <c r="E166" s="12"/>
-      <c r="BO166" s="14"/>
-      <c r="BR166" s="14"/>
-    </row>
-    <row r="167" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN166" s="14"/>
+      <c r="BQ166" s="14"/>
+    </row>
+    <row r="167" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D167" s="13"/>
       <c r="E167" s="12"/>
-      <c r="BO167" s="14"/>
-      <c r="BR167" s="14"/>
-    </row>
-    <row r="168" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN167" s="14"/>
+      <c r="BQ167" s="14"/>
+    </row>
+    <row r="168" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D168" s="13"/>
       <c r="E168" s="12"/>
-      <c r="BO168" s="14"/>
-      <c r="BR168" s="14"/>
-    </row>
-    <row r="169" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN168" s="14"/>
+      <c r="BQ168" s="14"/>
+    </row>
+    <row r="169" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D169" s="13"/>
       <c r="E169" s="12"/>
-      <c r="BO169" s="14"/>
-      <c r="BR169" s="14"/>
-    </row>
-    <row r="170" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN169" s="14"/>
+      <c r="BQ169" s="14"/>
+    </row>
+    <row r="170" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D170" s="13"/>
       <c r="E170" s="12"/>
-      <c r="BO170" s="14"/>
-      <c r="BR170" s="14"/>
-    </row>
-    <row r="171" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN170" s="14"/>
+      <c r="BQ170" s="14"/>
+    </row>
+    <row r="171" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D171" s="13"/>
       <c r="E171" s="12"/>
-      <c r="BO171" s="14"/>
-      <c r="BR171" s="14"/>
-    </row>
-    <row r="172" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN171" s="14"/>
+      <c r="BQ171" s="14"/>
+    </row>
+    <row r="172" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D172" s="13"/>
       <c r="E172" s="12"/>
-      <c r="BO172" s="14"/>
-      <c r="BR172" s="14"/>
-    </row>
-    <row r="173" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN172" s="14"/>
+      <c r="BQ172" s="14"/>
+    </row>
+    <row r="173" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D173" s="13"/>
       <c r="E173" s="12"/>
-      <c r="BO173" s="14"/>
-      <c r="BR173" s="14"/>
-    </row>
-    <row r="174" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN173" s="14"/>
+      <c r="BQ173" s="14"/>
+    </row>
+    <row r="174" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D174" s="13"/>
       <c r="E174" s="12"/>
-      <c r="BO174" s="14"/>
-      <c r="BR174" s="14"/>
-    </row>
-    <row r="175" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN174" s="14"/>
+      <c r="BQ174" s="14"/>
+    </row>
+    <row r="175" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D175" s="13"/>
       <c r="E175" s="12"/>
-      <c r="BO175" s="14"/>
-      <c r="BR175" s="14"/>
-    </row>
-    <row r="176" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN175" s="14"/>
+      <c r="BQ175" s="14"/>
+    </row>
+    <row r="176" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D176" s="13"/>
       <c r="E176" s="12"/>
-      <c r="BO176" s="14"/>
-      <c r="BR176" s="14"/>
-    </row>
-    <row r="177" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN176" s="14"/>
+      <c r="BQ176" s="14"/>
+    </row>
+    <row r="177" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D177" s="13"/>
       <c r="E177" s="12"/>
-      <c r="BO177" s="14"/>
-      <c r="BR177" s="14"/>
-    </row>
-    <row r="178" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN177" s="14"/>
+      <c r="BQ177" s="14"/>
+    </row>
+    <row r="178" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D178" s="13"/>
       <c r="E178" s="12"/>
-      <c r="BO178" s="14"/>
-      <c r="BR178" s="14"/>
-    </row>
-    <row r="179" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN178" s="14"/>
+      <c r="BQ178" s="14"/>
+    </row>
+    <row r="179" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D179" s="13"/>
       <c r="E179" s="12"/>
-      <c r="BO179" s="14"/>
-      <c r="BR179" s="14"/>
-    </row>
-    <row r="180" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN179" s="14"/>
+      <c r="BQ179" s="14"/>
+    </row>
+    <row r="180" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D180" s="13"/>
       <c r="E180" s="12"/>
-      <c r="BO180" s="14"/>
-      <c r="BR180" s="14"/>
-    </row>
-    <row r="181" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN180" s="14"/>
+      <c r="BQ180" s="14"/>
+    </row>
+    <row r="181" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D181" s="13"/>
       <c r="E181" s="12"/>
-      <c r="BO181" s="14"/>
-      <c r="BR181" s="14"/>
-    </row>
-    <row r="182" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN181" s="14"/>
+      <c r="BQ181" s="14"/>
+    </row>
+    <row r="182" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D182" s="13"/>
       <c r="E182" s="12"/>
-      <c r="BO182" s="14"/>
-      <c r="BR182" s="14"/>
-    </row>
-    <row r="183" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN182" s="14"/>
+      <c r="BQ182" s="14"/>
+    </row>
+    <row r="183" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D183" s="13"/>
       <c r="E183" s="12"/>
-      <c r="BO183" s="14"/>
-      <c r="BR183" s="14"/>
-    </row>
-    <row r="184" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN183" s="14"/>
+      <c r="BQ183" s="14"/>
+    </row>
+    <row r="184" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D184" s="13"/>
       <c r="E184" s="12"/>
-      <c r="BO184" s="14"/>
-      <c r="BR184" s="14"/>
-    </row>
-    <row r="185" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN184" s="14"/>
+      <c r="BQ184" s="14"/>
+    </row>
+    <row r="185" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D185" s="13"/>
       <c r="E185" s="12"/>
-      <c r="BO185" s="14"/>
-      <c r="BR185" s="14"/>
-    </row>
-    <row r="186" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN185" s="14"/>
+      <c r="BQ185" s="14"/>
+    </row>
+    <row r="186" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D186" s="13"/>
       <c r="E186" s="12"/>
-      <c r="BO186" s="14"/>
-      <c r="BR186" s="14"/>
-    </row>
-    <row r="187" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN186" s="14"/>
+      <c r="BQ186" s="14"/>
+    </row>
+    <row r="187" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D187" s="13"/>
       <c r="E187" s="12"/>
-      <c r="BO187" s="14"/>
-      <c r="BR187" s="14"/>
-    </row>
-    <row r="188" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN187" s="14"/>
+      <c r="BQ187" s="14"/>
+    </row>
+    <row r="188" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D188" s="13"/>
       <c r="E188" s="12"/>
-      <c r="BO188" s="14"/>
-      <c r="BR188" s="14"/>
-    </row>
-    <row r="189" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN188" s="14"/>
+      <c r="BQ188" s="14"/>
+    </row>
+    <row r="189" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D189" s="13"/>
       <c r="E189" s="12"/>
-      <c r="BO189" s="14"/>
-      <c r="BR189" s="14"/>
-    </row>
-    <row r="190" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN189" s="14"/>
+      <c r="BQ189" s="14"/>
+    </row>
+    <row r="190" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D190" s="13"/>
       <c r="E190" s="12"/>
-      <c r="BO190" s="14"/>
-      <c r="BR190" s="14"/>
-    </row>
-    <row r="191" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN190" s="14"/>
+      <c r="BQ190" s="14"/>
+    </row>
+    <row r="191" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D191" s="13"/>
       <c r="E191" s="12"/>
-      <c r="BO191" s="14"/>
-      <c r="BR191" s="14"/>
-    </row>
-    <row r="192" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN191" s="14"/>
+      <c r="BQ191" s="14"/>
+    </row>
+    <row r="192" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D192" s="13"/>
       <c r="E192" s="12"/>
-      <c r="BO192" s="14"/>
-      <c r="BR192" s="14"/>
-    </row>
-    <row r="193" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN192" s="14"/>
+      <c r="BQ192" s="14"/>
+    </row>
+    <row r="193" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D193" s="13"/>
       <c r="E193" s="12"/>
-      <c r="BO193" s="14"/>
-      <c r="BR193" s="14"/>
-    </row>
-    <row r="194" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN193" s="14"/>
+      <c r="BQ193" s="14"/>
+    </row>
+    <row r="194" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D194" s="13"/>
       <c r="E194" s="12"/>
-      <c r="BO194" s="14"/>
-      <c r="BR194" s="14"/>
-    </row>
-    <row r="195" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN194" s="14"/>
+      <c r="BQ194" s="14"/>
+    </row>
+    <row r="195" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D195" s="13"/>
       <c r="E195" s="12"/>
-      <c r="BO195" s="14"/>
-      <c r="BR195" s="14"/>
-    </row>
-    <row r="196" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN195" s="14"/>
+      <c r="BQ195" s="14"/>
+    </row>
+    <row r="196" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D196" s="13"/>
       <c r="E196" s="12"/>
-      <c r="BO196" s="14"/>
-      <c r="BR196" s="14"/>
-    </row>
-    <row r="197" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN196" s="14"/>
+      <c r="BQ196" s="14"/>
+    </row>
+    <row r="197" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D197" s="13"/>
       <c r="E197" s="12"/>
-      <c r="BO197" s="14"/>
-      <c r="BR197" s="14"/>
-    </row>
-    <row r="198" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN197" s="14"/>
+      <c r="BQ197" s="14"/>
+    </row>
+    <row r="198" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D198" s="13"/>
       <c r="E198" s="12"/>
-      <c r="BO198" s="14"/>
-      <c r="BR198" s="14"/>
-    </row>
-    <row r="199" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN198" s="14"/>
+      <c r="BQ198" s="14"/>
+    </row>
+    <row r="199" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D199" s="13"/>
       <c r="E199" s="12"/>
-      <c r="BO199" s="14"/>
-      <c r="BR199" s="14"/>
-    </row>
-    <row r="200" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN199" s="14"/>
+      <c r="BQ199" s="14"/>
+    </row>
+    <row r="200" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D200" s="13"/>
       <c r="E200" s="12"/>
-      <c r="BO200" s="14"/>
-      <c r="BR200" s="14"/>
-    </row>
-    <row r="201" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN200" s="14"/>
+      <c r="BQ200" s="14"/>
+    </row>
+    <row r="201" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D201" s="13"/>
       <c r="E201" s="12"/>
-      <c r="BO201" s="14"/>
-      <c r="BR201" s="14"/>
-    </row>
-    <row r="202" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN201" s="14"/>
+      <c r="BQ201" s="14"/>
+    </row>
+    <row r="202" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D202" s="13"/>
       <c r="E202" s="12"/>
-      <c r="BO202" s="14"/>
-      <c r="BR202" s="14"/>
-    </row>
-    <row r="203" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN202" s="14"/>
+      <c r="BQ202" s="14"/>
+    </row>
+    <row r="203" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D203" s="13"/>
       <c r="E203" s="12"/>
-      <c r="BO203" s="14"/>
-      <c r="BR203" s="14"/>
-    </row>
-    <row r="204" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN203" s="14"/>
+      <c r="BQ203" s="14"/>
+    </row>
+    <row r="204" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D204" s="13"/>
       <c r="E204" s="12"/>
-      <c r="BO204" s="14"/>
-      <c r="BR204" s="14"/>
-    </row>
-    <row r="205" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN204" s="14"/>
+      <c r="BQ204" s="14"/>
+    </row>
+    <row r="205" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D205" s="13"/>
       <c r="E205" s="12"/>
-      <c r="BO205" s="14"/>
-      <c r="BR205" s="14"/>
-    </row>
-    <row r="206" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN205" s="14"/>
+      <c r="BQ205" s="14"/>
+    </row>
+    <row r="206" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D206" s="13"/>
       <c r="E206" s="12"/>
-      <c r="BO206" s="14"/>
-      <c r="BR206" s="14"/>
-    </row>
-    <row r="207" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN206" s="14"/>
+      <c r="BQ206" s="14"/>
+    </row>
+    <row r="207" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D207" s="13"/>
       <c r="E207" s="12"/>
-      <c r="BO207" s="14"/>
-      <c r="BR207" s="14"/>
-    </row>
-    <row r="208" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN207" s="14"/>
+      <c r="BQ207" s="14"/>
+    </row>
+    <row r="208" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D208" s="13"/>
       <c r="E208" s="12"/>
-      <c r="BO208" s="14"/>
-      <c r="BR208" s="14"/>
-    </row>
-    <row r="209" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN208" s="14"/>
+      <c r="BQ208" s="14"/>
+    </row>
+    <row r="209" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D209" s="13"/>
       <c r="E209" s="12"/>
-      <c r="BO209" s="14"/>
-      <c r="BR209" s="14"/>
-    </row>
-    <row r="210" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN209" s="14"/>
+      <c r="BQ209" s="14"/>
+    </row>
+    <row r="210" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D210" s="13"/>
       <c r="E210" s="12"/>
-      <c r="BO210" s="14"/>
-      <c r="BR210" s="14"/>
-    </row>
-    <row r="211" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN210" s="14"/>
+      <c r="BQ210" s="14"/>
+    </row>
+    <row r="211" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D211" s="13"/>
       <c r="E211" s="12"/>
-      <c r="BO211" s="14"/>
-      <c r="BR211" s="14"/>
-    </row>
-    <row r="212" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN211" s="14"/>
+      <c r="BQ211" s="14"/>
+    </row>
+    <row r="212" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D212" s="13"/>
       <c r="E212" s="12"/>
-      <c r="BO212" s="14"/>
-      <c r="BR212" s="14"/>
-    </row>
-    <row r="213" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN212" s="14"/>
+      <c r="BQ212" s="14"/>
+    </row>
+    <row r="213" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D213" s="13"/>
       <c r="E213" s="12"/>
-      <c r="BO213" s="14"/>
-      <c r="BR213" s="14"/>
-    </row>
-    <row r="214" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN213" s="14"/>
+      <c r="BQ213" s="14"/>
+    </row>
+    <row r="214" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D214" s="13"/>
       <c r="E214" s="12"/>
-      <c r="BO214" s="14"/>
-      <c r="BR214" s="14"/>
-    </row>
-    <row r="215" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN214" s="14"/>
+      <c r="BQ214" s="14"/>
+    </row>
+    <row r="215" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D215" s="13"/>
       <c r="E215" s="12"/>
-      <c r="BO215" s="14"/>
-      <c r="BR215" s="14"/>
-    </row>
-    <row r="216" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN215" s="14"/>
+      <c r="BQ215" s="14"/>
+    </row>
+    <row r="216" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D216" s="13"/>
       <c r="E216" s="12"/>
-      <c r="BO216" s="14"/>
-      <c r="BR216" s="14"/>
-    </row>
-    <row r="217" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN216" s="14"/>
+      <c r="BQ216" s="14"/>
+    </row>
+    <row r="217" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D217" s="13"/>
       <c r="E217" s="12"/>
-      <c r="BO217" s="14"/>
-      <c r="BR217" s="14"/>
-    </row>
-    <row r="218" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN217" s="14"/>
+      <c r="BQ217" s="14"/>
+    </row>
+    <row r="218" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D218" s="13"/>
       <c r="E218" s="12"/>
-      <c r="BO218" s="14"/>
-      <c r="BR218" s="14"/>
-    </row>
-    <row r="219" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN218" s="14"/>
+      <c r="BQ218" s="14"/>
+    </row>
+    <row r="219" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D219" s="13"/>
       <c r="E219" s="12"/>
-      <c r="BO219" s="14"/>
-      <c r="BR219" s="14"/>
-    </row>
-    <row r="220" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN219" s="14"/>
+      <c r="BQ219" s="14"/>
+    </row>
+    <row r="220" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D220" s="13"/>
       <c r="E220" s="12"/>
-      <c r="BO220" s="14"/>
-      <c r="BR220" s="14"/>
-    </row>
-    <row r="221" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN220" s="14"/>
+      <c r="BQ220" s="14"/>
+    </row>
+    <row r="221" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D221" s="13"/>
       <c r="E221" s="12"/>
-      <c r="BO221" s="14"/>
-      <c r="BR221" s="14"/>
-    </row>
-    <row r="222" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN221" s="14"/>
+      <c r="BQ221" s="14"/>
+    </row>
+    <row r="222" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D222" s="13"/>
       <c r="E222" s="12"/>
-      <c r="BO222" s="14"/>
-      <c r="BR222" s="14"/>
-    </row>
-    <row r="223" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN222" s="14"/>
+      <c r="BQ222" s="14"/>
+    </row>
+    <row r="223" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D223" s="13"/>
       <c r="E223" s="12"/>
-      <c r="BO223" s="14"/>
-      <c r="BR223" s="14"/>
-    </row>
-    <row r="224" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN223" s="14"/>
+      <c r="BQ223" s="14"/>
+    </row>
+    <row r="224" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D224" s="13"/>
       <c r="E224" s="12"/>
-      <c r="BO224" s="14"/>
-      <c r="BR224" s="14"/>
-    </row>
-    <row r="225" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN224" s="14"/>
+      <c r="BQ224" s="14"/>
+    </row>
+    <row r="225" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D225" s="13"/>
       <c r="E225" s="12"/>
-      <c r="BO225" s="14"/>
-      <c r="BR225" s="14"/>
-    </row>
-    <row r="226" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN225" s="14"/>
+      <c r="BQ225" s="14"/>
+    </row>
+    <row r="226" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D226" s="13"/>
       <c r="E226" s="12"/>
-      <c r="BO226" s="14"/>
-      <c r="BR226" s="14"/>
-    </row>
-    <row r="227" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN226" s="14"/>
+      <c r="BQ226" s="14"/>
+    </row>
+    <row r="227" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D227" s="13"/>
       <c r="E227" s="12"/>
-      <c r="BO227" s="14"/>
-      <c r="BR227" s="14"/>
-    </row>
-    <row r="228" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN227" s="14"/>
+      <c r="BQ227" s="14"/>
+    </row>
+    <row r="228" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D228" s="13"/>
       <c r="E228" s="12"/>
-      <c r="BR228" s="14"/>
-    </row>
-    <row r="229" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ228" s="14"/>
+    </row>
+    <row r="229" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D229" s="13"/>
       <c r="E229" s="12"/>
-      <c r="BO229" s="14"/>
-      <c r="BR229" s="14"/>
-    </row>
-    <row r="230" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN229" s="14"/>
+      <c r="BQ229" s="14"/>
+    </row>
+    <row r="230" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D230" s="13"/>
       <c r="E230" s="12"/>
-      <c r="BO230" s="14"/>
-      <c r="BR230" s="14"/>
-    </row>
-    <row r="231" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN230" s="14"/>
+      <c r="BQ230" s="14"/>
+    </row>
+    <row r="231" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D231" s="13"/>
       <c r="E231" s="12"/>
-      <c r="BO231" s="14"/>
-      <c r="BR231" s="14"/>
-    </row>
-    <row r="232" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN231" s="14"/>
+      <c r="BQ231" s="14"/>
+    </row>
+    <row r="232" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D232" s="13"/>
       <c r="E232" s="12"/>
-      <c r="BO232" s="14"/>
-      <c r="BR232" s="14"/>
-    </row>
-    <row r="233" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN232" s="14"/>
+      <c r="BQ232" s="14"/>
+    </row>
+    <row r="233" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D233" s="13"/>
       <c r="E233" s="12"/>
-      <c r="BO233" s="14"/>
-      <c r="BR233" s="14"/>
-    </row>
-    <row r="234" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN233" s="14"/>
+      <c r="BQ233" s="14"/>
+    </row>
+    <row r="234" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D234" s="13"/>
       <c r="E234" s="12"/>
-      <c r="BO234" s="14"/>
-      <c r="BR234" s="14"/>
-    </row>
-    <row r="235" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN234" s="14"/>
+      <c r="BQ234" s="14"/>
+    </row>
+    <row r="235" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D235" s="13"/>
       <c r="E235" s="12"/>
-      <c r="BO235" s="14"/>
-      <c r="BR235" s="14"/>
-    </row>
-    <row r="236" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN235" s="14"/>
+      <c r="BQ235" s="14"/>
+    </row>
+    <row r="236" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D236" s="13"/>
       <c r="E236" s="12"/>
-      <c r="BO236" s="14"/>
-      <c r="BR236" s="14"/>
-    </row>
-    <row r="237" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN236" s="14"/>
+      <c r="BQ236" s="14"/>
+    </row>
+    <row r="237" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D237" s="13"/>
       <c r="E237" s="12"/>
-      <c r="BO237" s="14"/>
-      <c r="BR237" s="14"/>
-    </row>
-    <row r="238" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN237" s="14"/>
+      <c r="BQ237" s="14"/>
+    </row>
+    <row r="238" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D238" s="13"/>
       <c r="E238" s="12"/>
-      <c r="BO238" s="14"/>
-      <c r="BR238" s="14"/>
-    </row>
-    <row r="239" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN238" s="14"/>
+      <c r="BQ238" s="14"/>
+    </row>
+    <row r="239" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D239" s="13"/>
       <c r="E239" s="12"/>
-      <c r="BO239" s="14"/>
-      <c r="BR239" s="14"/>
-    </row>
-    <row r="240" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN239" s="14"/>
+      <c r="BQ239" s="14"/>
+    </row>
+    <row r="240" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D240" s="13"/>
       <c r="E240" s="12"/>
-      <c r="BO240" s="14"/>
-      <c r="BR240" s="14"/>
-    </row>
-    <row r="241" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN240" s="14"/>
+      <c r="BQ240" s="14"/>
+    </row>
+    <row r="241" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D241" s="13"/>
       <c r="E241" s="12"/>
-      <c r="BO241" s="14"/>
-      <c r="BR241" s="14"/>
-    </row>
-    <row r="242" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN241" s="14"/>
+      <c r="BQ241" s="14"/>
+    </row>
+    <row r="242" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D242" s="13"/>
       <c r="E242" s="12"/>
-      <c r="BO242" s="14"/>
-      <c r="BR242" s="14"/>
-    </row>
-    <row r="243" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN242" s="14"/>
+      <c r="BQ242" s="14"/>
+    </row>
+    <row r="243" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D243" s="13"/>
       <c r="E243" s="12"/>
-      <c r="BO243" s="14"/>
-      <c r="BR243" s="14"/>
-    </row>
-    <row r="244" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN243" s="14"/>
+      <c r="BQ243" s="14"/>
+    </row>
+    <row r="244" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D244" s="13"/>
       <c r="E244" s="12"/>
-      <c r="BO244" s="14"/>
-      <c r="BR244" s="14"/>
-    </row>
-    <row r="245" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN244" s="14"/>
+      <c r="BQ244" s="14"/>
+    </row>
+    <row r="245" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D245" s="13"/>
       <c r="E245" s="12"/>
-      <c r="BO245" s="14"/>
-      <c r="BR245" s="14"/>
-    </row>
-    <row r="246" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN245" s="14"/>
+      <c r="BQ245" s="14"/>
+    </row>
+    <row r="246" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D246" s="13"/>
       <c r="E246" s="12"/>
-      <c r="BO246" s="14"/>
-      <c r="BR246" s="14"/>
-    </row>
-    <row r="247" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN246" s="14"/>
+      <c r="BQ246" s="14"/>
+    </row>
+    <row r="247" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D247" s="13"/>
       <c r="E247" s="12"/>
-      <c r="BO247" s="14"/>
-      <c r="BR247" s="14"/>
-    </row>
-    <row r="248" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN247" s="14"/>
+      <c r="BQ247" s="14"/>
+    </row>
+    <row r="248" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D248" s="13"/>
       <c r="E248" s="12"/>
-      <c r="BO248" s="14"/>
-      <c r="BR248" s="14"/>
-    </row>
-    <row r="249" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN248" s="14"/>
+      <c r="BQ248" s="14"/>
+    </row>
+    <row r="249" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D249" s="13"/>
       <c r="E249" s="12"/>
-      <c r="BO249" s="14"/>
-      <c r="BR249" s="14"/>
-    </row>
-    <row r="250" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN249" s="14"/>
+      <c r="BQ249" s="14"/>
+    </row>
+    <row r="250" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D250" s="13"/>
       <c r="E250" s="12"/>
-      <c r="BO250" s="14"/>
-      <c r="BR250" s="14"/>
-    </row>
-    <row r="251" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN250" s="14"/>
+      <c r="BQ250" s="14"/>
+    </row>
+    <row r="251" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D251" s="13"/>
       <c r="E251" s="12"/>
-      <c r="BO251" s="14"/>
-      <c r="BR251" s="14"/>
-    </row>
-    <row r="252" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN251" s="14"/>
+      <c r="BQ251" s="14"/>
+    </row>
+    <row r="252" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D252" s="13"/>
       <c r="E252" s="12"/>
-      <c r="BO252" s="14"/>
-      <c r="BR252" s="14"/>
-    </row>
-    <row r="253" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN252" s="14"/>
+      <c r="BQ252" s="14"/>
+    </row>
+    <row r="253" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D253" s="13"/>
       <c r="E253" s="12"/>
-      <c r="BO253" s="14"/>
-      <c r="BR253" s="14"/>
-    </row>
-    <row r="254" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN253" s="14"/>
+      <c r="BQ253" s="14"/>
+    </row>
+    <row r="254" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D254" s="13"/>
       <c r="E254" s="12"/>
-      <c r="BO254" s="14"/>
-      <c r="BR254" s="14"/>
-    </row>
-    <row r="255" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN254" s="14"/>
+      <c r="BQ254" s="14"/>
+    </row>
+    <row r="255" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D255" s="13"/>
       <c r="E255" s="12"/>
-      <c r="BO255" s="14"/>
-      <c r="BR255" s="14"/>
-    </row>
-    <row r="256" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN255" s="14"/>
+      <c r="BQ255" s="14"/>
+    </row>
+    <row r="256" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D256" s="13"/>
       <c r="E256" s="12"/>
-      <c r="BO256" s="14"/>
-      <c r="BR256" s="14"/>
-    </row>
-    <row r="257" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN256" s="14"/>
+      <c r="BQ256" s="14"/>
+    </row>
+    <row r="257" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D257" s="13"/>
       <c r="E257" s="12"/>
-      <c r="BO257" s="14"/>
-      <c r="BR257" s="14"/>
-    </row>
-    <row r="258" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN257" s="14"/>
+      <c r="BQ257" s="14"/>
+    </row>
+    <row r="258" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D258" s="13"/>
       <c r="E258" s="12"/>
-      <c r="BO258" s="14"/>
-      <c r="BR258" s="14"/>
-    </row>
-    <row r="259" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN258" s="14"/>
+      <c r="BQ258" s="14"/>
+    </row>
+    <row r="259" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D259" s="13"/>
       <c r="E259" s="12"/>
-      <c r="BO259" s="14"/>
-      <c r="BR259" s="14"/>
-    </row>
-    <row r="260" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN259" s="14"/>
+      <c r="BQ259" s="14"/>
+    </row>
+    <row r="260" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D260" s="13"/>
       <c r="E260" s="12"/>
-      <c r="BO260" s="14"/>
-      <c r="BR260" s="14"/>
-    </row>
-    <row r="261" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN260" s="14"/>
+      <c r="BQ260" s="14"/>
+    </row>
+    <row r="261" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D261" s="13"/>
       <c r="E261" s="12"/>
-      <c r="BO261" s="14"/>
-      <c r="BR261" s="14"/>
-    </row>
-    <row r="262" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN261" s="14"/>
+      <c r="BQ261" s="14"/>
+    </row>
+    <row r="262" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D262" s="13"/>
       <c r="E262" s="12"/>
-      <c r="BO262" s="14"/>
-      <c r="BR262" s="14"/>
-    </row>
-    <row r="263" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN262" s="14"/>
+      <c r="BQ262" s="14"/>
+    </row>
+    <row r="263" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D263" s="13"/>
       <c r="E263" s="12"/>
-      <c r="BO263" s="14"/>
-      <c r="BR263" s="14"/>
-    </row>
-    <row r="264" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN263" s="14"/>
+      <c r="BQ263" s="14"/>
+    </row>
+    <row r="264" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D264" s="13"/>
       <c r="E264" s="12"/>
-      <c r="BO264" s="14"/>
-      <c r="BR264" s="14"/>
-    </row>
-    <row r="265" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN264" s="14"/>
+      <c r="BQ264" s="14"/>
+    </row>
+    <row r="265" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D265" s="13"/>
       <c r="E265" s="12"/>
-      <c r="BO265" s="14"/>
-      <c r="BR265" s="14"/>
-    </row>
-    <row r="266" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN265" s="14"/>
+      <c r="BQ265" s="14"/>
+    </row>
+    <row r="266" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D266" s="13"/>
       <c r="E266" s="12"/>
-      <c r="BO266" s="14"/>
-      <c r="BR266" s="14"/>
-    </row>
-    <row r="267" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN266" s="14"/>
+      <c r="BQ266" s="14"/>
+    </row>
+    <row r="267" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D267" s="13"/>
       <c r="E267" s="12"/>
-      <c r="BO267" s="14"/>
-      <c r="BR267" s="14"/>
-    </row>
-    <row r="268" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN267" s="14"/>
+      <c r="BQ267" s="14"/>
+    </row>
+    <row r="268" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D268" s="13"/>
       <c r="E268" s="12"/>
-      <c r="BO268" s="14"/>
-      <c r="BR268" s="14"/>
-    </row>
-    <row r="269" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN268" s="14"/>
+      <c r="BQ268" s="14"/>
+    </row>
+    <row r="269" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D269" s="13"/>
       <c r="E269" s="12"/>
-      <c r="BO269" s="14"/>
-      <c r="BR269" s="14"/>
-    </row>
-    <row r="270" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN269" s="14"/>
+      <c r="BQ269" s="14"/>
+    </row>
+    <row r="270" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D270" s="13"/>
       <c r="E270" s="12"/>
-      <c r="BO270" s="14"/>
-      <c r="BR270" s="14"/>
-    </row>
-    <row r="271" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN270" s="14"/>
+      <c r="BQ270" s="14"/>
+    </row>
+    <row r="271" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D271" s="13"/>
       <c r="E271" s="12"/>
-      <c r="BR271" s="14"/>
-    </row>
-    <row r="272" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ271" s="14"/>
+    </row>
+    <row r="272" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D272" s="13"/>
       <c r="E272" s="12"/>
-      <c r="BO272" s="14"/>
-      <c r="BR272" s="14"/>
-    </row>
-    <row r="273" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN272" s="14"/>
+      <c r="BQ272" s="14"/>
+    </row>
+    <row r="273" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D273" s="13"/>
       <c r="E273" s="12"/>
-      <c r="BO273" s="14"/>
-      <c r="BR273" s="14"/>
-    </row>
-    <row r="274" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN273" s="14"/>
+      <c r="BQ273" s="14"/>
+    </row>
+    <row r="274" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D274" s="13"/>
       <c r="E274" s="12"/>
-      <c r="BO274" s="14"/>
-      <c r="BR274" s="14"/>
-    </row>
-    <row r="275" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN274" s="14"/>
+      <c r="BQ274" s="14"/>
+    </row>
+    <row r="275" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D275" s="13"/>
       <c r="E275" s="12"/>
-      <c r="BO275" s="14"/>
-      <c r="BR275" s="14"/>
-    </row>
-    <row r="276" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN275" s="14"/>
+      <c r="BQ275" s="14"/>
+    </row>
+    <row r="276" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D276" s="13"/>
       <c r="E276" s="12"/>
-      <c r="BO276" s="14"/>
-      <c r="BR276" s="14"/>
-    </row>
-    <row r="277" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN276" s="14"/>
+      <c r="BQ276" s="14"/>
+    </row>
+    <row r="277" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D277" s="13"/>
       <c r="E277" s="12"/>
-      <c r="BO277" s="14"/>
-      <c r="BR277" s="14"/>
-    </row>
-    <row r="278" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN277" s="14"/>
+      <c r="BQ277" s="14"/>
+    </row>
+    <row r="278" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D278" s="13"/>
       <c r="E278" s="12"/>
-      <c r="BO278" s="14"/>
-      <c r="BR278" s="14"/>
-    </row>
-    <row r="279" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN278" s="14"/>
+      <c r="BQ278" s="14"/>
+    </row>
+    <row r="279" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D279" s="13"/>
       <c r="E279" s="12"/>
-      <c r="BO279" s="14"/>
-      <c r="BR279" s="14"/>
-    </row>
-    <row r="280" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN279" s="14"/>
+      <c r="BQ279" s="14"/>
+    </row>
+    <row r="280" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D280" s="13"/>
       <c r="E280" s="12"/>
-      <c r="BO280" s="14"/>
-      <c r="BR280" s="14"/>
-    </row>
-    <row r="281" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN280" s="14"/>
+      <c r="BQ280" s="14"/>
+    </row>
+    <row r="281" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D281" s="13"/>
       <c r="E281" s="12"/>
-      <c r="BO281" s="14"/>
-      <c r="BR281" s="14"/>
-    </row>
-    <row r="282" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN281" s="14"/>
+      <c r="BQ281" s="14"/>
+    </row>
+    <row r="282" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D282" s="13"/>
       <c r="E282" s="12"/>
-      <c r="BO282" s="14"/>
-      <c r="BR282" s="14"/>
-    </row>
-    <row r="283" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN282" s="14"/>
+      <c r="BQ282" s="14"/>
+    </row>
+    <row r="283" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D283" s="13"/>
       <c r="E283" s="12"/>
-      <c r="BO283" s="14"/>
-      <c r="BR283" s="14"/>
-    </row>
-    <row r="284" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN283" s="14"/>
+      <c r="BQ283" s="14"/>
+    </row>
+    <row r="284" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D284" s="13"/>
       <c r="E284" s="12"/>
-      <c r="BO284" s="14"/>
-      <c r="BR284" s="14"/>
-    </row>
-    <row r="285" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN284" s="14"/>
+      <c r="BQ284" s="14"/>
+    </row>
+    <row r="285" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D285" s="13"/>
       <c r="E285" s="12"/>
-      <c r="BO285" s="14"/>
-      <c r="BR285" s="14"/>
-    </row>
-    <row r="286" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN285" s="14"/>
+      <c r="BQ285" s="14"/>
+    </row>
+    <row r="286" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D286" s="13"/>
       <c r="E286" s="12"/>
-      <c r="BO286" s="14"/>
-      <c r="BR286" s="14"/>
-    </row>
-    <row r="287" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN286" s="14"/>
+      <c r="BQ286" s="14"/>
+    </row>
+    <row r="287" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D287" s="13"/>
       <c r="E287" s="12"/>
-      <c r="BO287" s="14"/>
-      <c r="BR287" s="14"/>
-    </row>
-    <row r="288" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN287" s="14"/>
+      <c r="BQ287" s="14"/>
+    </row>
+    <row r="288" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D288" s="13"/>
       <c r="E288" s="12"/>
-      <c r="BO288" s="14"/>
-      <c r="BR288" s="14"/>
-    </row>
-    <row r="289" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN288" s="14"/>
+      <c r="BQ288" s="14"/>
+    </row>
+    <row r="289" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D289" s="13"/>
       <c r="E289" s="12"/>
-      <c r="BO289" s="14"/>
-      <c r="BR289" s="14"/>
-    </row>
-    <row r="290" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN289" s="14"/>
+      <c r="BQ289" s="14"/>
+    </row>
+    <row r="290" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D290" s="13"/>
       <c r="E290" s="12"/>
-      <c r="BO290" s="14"/>
-      <c r="BR290" s="14"/>
-    </row>
-    <row r="291" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN290" s="14"/>
+      <c r="BQ290" s="14"/>
+    </row>
+    <row r="291" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D291" s="13"/>
       <c r="E291" s="12"/>
-      <c r="BO291" s="14"/>
-      <c r="BR291" s="14"/>
-    </row>
-    <row r="292" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN291" s="14"/>
+      <c r="BQ291" s="14"/>
+    </row>
+    <row r="292" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D292" s="13"/>
       <c r="E292" s="12"/>
-      <c r="BO292" s="14"/>
-      <c r="BR292" s="14"/>
-    </row>
-    <row r="293" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN292" s="14"/>
+      <c r="BQ292" s="14"/>
+    </row>
+    <row r="293" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D293" s="13"/>
       <c r="E293" s="12"/>
-      <c r="BO293" s="14"/>
-      <c r="BR293" s="14"/>
-    </row>
-    <row r="294" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN293" s="14"/>
+      <c r="BQ293" s="14"/>
+    </row>
+    <row r="294" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D294" s="13"/>
       <c r="E294" s="12"/>
-      <c r="BO294" s="14"/>
-      <c r="BR294" s="14"/>
-    </row>
-    <row r="295" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN294" s="14"/>
+      <c r="BQ294" s="14"/>
+    </row>
+    <row r="295" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D295" s="13"/>
       <c r="E295" s="12"/>
-      <c r="BO295" s="14"/>
-      <c r="BR295" s="14"/>
-    </row>
-    <row r="296" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN295" s="14"/>
+      <c r="BQ295" s="14"/>
+    </row>
+    <row r="296" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D296" s="13"/>
       <c r="E296" s="12"/>
-      <c r="BO296" s="14"/>
-      <c r="BR296" s="14"/>
-    </row>
-    <row r="297" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN296" s="14"/>
+      <c r="BQ296" s="14"/>
+    </row>
+    <row r="297" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D297" s="13"/>
       <c r="E297" s="12"/>
-      <c r="BO297" s="14"/>
-      <c r="BR297" s="14"/>
-    </row>
-    <row r="298" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN297" s="14"/>
+      <c r="BQ297" s="14"/>
+    </row>
+    <row r="298" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D298" s="13"/>
       <c r="E298" s="12"/>
-      <c r="BO298" s="14"/>
-      <c r="BR298" s="14"/>
-    </row>
-    <row r="299" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN298" s="14"/>
+      <c r="BQ298" s="14"/>
+    </row>
+    <row r="299" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D299" s="13"/>
       <c r="E299" s="12"/>
-      <c r="BO299" s="14"/>
-      <c r="BR299" s="14"/>
-    </row>
-    <row r="300" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN299" s="14"/>
+      <c r="BQ299" s="14"/>
+    </row>
+    <row r="300" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D300" s="13"/>
       <c r="E300" s="12"/>
-      <c r="BO300" s="14"/>
-      <c r="BR300" s="14"/>
-    </row>
-    <row r="301" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN300" s="14"/>
+      <c r="BQ300" s="14"/>
+    </row>
+    <row r="301" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D301" s="13"/>
       <c r="E301" s="12"/>
-      <c r="BO301" s="14"/>
-      <c r="BR301" s="14"/>
-    </row>
-    <row r="302" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN301" s="14"/>
+      <c r="BQ301" s="14"/>
+    </row>
+    <row r="302" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D302" s="13"/>
       <c r="E302" s="12"/>
-      <c r="BO302" s="14"/>
-      <c r="BR302" s="14"/>
-    </row>
-    <row r="303" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN302" s="14"/>
+      <c r="BQ302" s="14"/>
+    </row>
+    <row r="303" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D303" s="13"/>
       <c r="E303" s="12"/>
-      <c r="BO303" s="14"/>
-      <c r="BR303" s="14"/>
-    </row>
-    <row r="304" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN303" s="14"/>
+      <c r="BQ303" s="14"/>
+    </row>
+    <row r="304" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D304" s="13"/>
       <c r="E304" s="12"/>
-      <c r="BO304" s="14"/>
-      <c r="BR304" s="14"/>
-    </row>
-    <row r="305" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN304" s="14"/>
+      <c r="BQ304" s="14"/>
+    </row>
+    <row r="305" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D305" s="13"/>
       <c r="E305" s="12"/>
-      <c r="BO305" s="14"/>
-      <c r="BR305" s="14"/>
-    </row>
-    <row r="306" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN305" s="14"/>
+      <c r="BQ305" s="14"/>
+    </row>
+    <row r="306" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D306" s="13"/>
       <c r="E306" s="12"/>
-      <c r="BO306" s="14"/>
-      <c r="BR306" s="14"/>
-    </row>
-    <row r="307" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN306" s="14"/>
+      <c r="BQ306" s="14"/>
+    </row>
+    <row r="307" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D307" s="13"/>
       <c r="E307" s="12"/>
-      <c r="BO307" s="14"/>
-      <c r="BR307" s="14"/>
-    </row>
-    <row r="308" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN307" s="14"/>
+      <c r="BQ307" s="14"/>
+    </row>
+    <row r="308" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D308" s="13"/>
       <c r="E308" s="12"/>
-      <c r="BO308" s="14"/>
-      <c r="BR308" s="14"/>
-    </row>
-    <row r="309" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN308" s="14"/>
+      <c r="BQ308" s="14"/>
+    </row>
+    <row r="309" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D309" s="13"/>
       <c r="E309" s="12"/>
-      <c r="BO309" s="14"/>
-      <c r="BR309" s="14"/>
-    </row>
-    <row r="310" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN309" s="14"/>
+      <c r="BQ309" s="14"/>
+    </row>
+    <row r="310" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D310" s="13"/>
       <c r="E310" s="12"/>
-      <c r="BO310" s="14"/>
-      <c r="BR310" s="14"/>
-    </row>
-    <row r="311" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN310" s="14"/>
+      <c r="BQ310" s="14"/>
+    </row>
+    <row r="311" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D311" s="13"/>
       <c r="E311" s="12"/>
-      <c r="BO311" s="14"/>
-      <c r="BR311" s="14"/>
-    </row>
-    <row r="312" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN311" s="14"/>
+      <c r="BQ311" s="14"/>
+    </row>
+    <row r="312" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D312" s="13"/>
       <c r="E312" s="12"/>
-      <c r="BO312" s="14"/>
-      <c r="BR312" s="14"/>
-    </row>
-    <row r="313" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN312" s="14"/>
+      <c r="BQ312" s="14"/>
+    </row>
+    <row r="313" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D313" s="13"/>
       <c r="E313" s="12"/>
-      <c r="BO313" s="14"/>
-      <c r="BR313" s="14"/>
-    </row>
-    <row r="314" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN313" s="14"/>
+      <c r="BQ313" s="14"/>
+    </row>
+    <row r="314" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D314" s="13"/>
       <c r="E314" s="12"/>
-      <c r="BO314" s="14"/>
-      <c r="BR314" s="14"/>
-    </row>
-    <row r="315" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN314" s="14"/>
+      <c r="BQ314" s="14"/>
+    </row>
+    <row r="315" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D315" s="13"/>
       <c r="E315" s="12"/>
-      <c r="BO315" s="14"/>
-      <c r="BR315" s="14"/>
-    </row>
-    <row r="316" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN315" s="14"/>
+      <c r="BQ315" s="14"/>
+    </row>
+    <row r="316" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D316" s="13"/>
       <c r="E316" s="12"/>
-      <c r="BO316" s="14"/>
-      <c r="BR316" s="14"/>
-    </row>
-    <row r="317" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN316" s="14"/>
+      <c r="BQ316" s="14"/>
+    </row>
+    <row r="317" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D317" s="13"/>
       <c r="E317" s="12"/>
-      <c r="BO317" s="14"/>
-      <c r="BR317" s="14"/>
-    </row>
-    <row r="318" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN317" s="14"/>
+      <c r="BQ317" s="14"/>
+    </row>
+    <row r="318" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D318" s="13"/>
       <c r="E318" s="12"/>
-      <c r="BO318" s="14"/>
-      <c r="BR318" s="14"/>
-    </row>
-    <row r="319" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN318" s="14"/>
+      <c r="BQ318" s="14"/>
+    </row>
+    <row r="319" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D319" s="13"/>
       <c r="E319" s="12"/>
-      <c r="BO319" s="14"/>
-      <c r="BR319" s="14"/>
-    </row>
-    <row r="320" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN319" s="14"/>
+      <c r="BQ319" s="14"/>
+    </row>
+    <row r="320" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D320" s="13"/>
       <c r="E320" s="12"/>
-      <c r="BO320" s="14"/>
-      <c r="BR320" s="14"/>
-    </row>
-    <row r="321" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN320" s="14"/>
+      <c r="BQ320" s="14"/>
+    </row>
+    <row r="321" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D321" s="13"/>
       <c r="E321" s="12"/>
-      <c r="BO321" s="14"/>
-      <c r="BR321" s="14"/>
-    </row>
-    <row r="322" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN321" s="14"/>
+      <c r="BQ321" s="14"/>
+    </row>
+    <row r="322" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D322" s="13"/>
       <c r="E322" s="12"/>
-      <c r="BO322" s="14"/>
-      <c r="BR322" s="14"/>
-    </row>
-    <row r="323" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN322" s="14"/>
+      <c r="BQ322" s="14"/>
+    </row>
+    <row r="323" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D323" s="13"/>
       <c r="E323" s="12"/>
-      <c r="BO323" s="14"/>
-      <c r="BR323" s="14"/>
-    </row>
-    <row r="324" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN323" s="14"/>
+      <c r="BQ323" s="14"/>
+    </row>
+    <row r="324" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D324" s="13"/>
       <c r="E324" s="12"/>
-      <c r="BO324" s="14"/>
-      <c r="BR324" s="14"/>
-    </row>
-    <row r="325" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN324" s="14"/>
+      <c r="BQ324" s="14"/>
+    </row>
+    <row r="325" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D325" s="13"/>
       <c r="E325" s="12"/>
-      <c r="BO325" s="14"/>
-      <c r="BR325" s="14"/>
-    </row>
-    <row r="326" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN325" s="14"/>
+      <c r="BQ325" s="14"/>
+    </row>
+    <row r="326" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D326" s="13"/>
       <c r="E326" s="12"/>
-      <c r="BO326" s="14"/>
-      <c r="BR326" s="14"/>
-    </row>
-    <row r="327" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN326" s="14"/>
+      <c r="BQ326" s="14"/>
+    </row>
+    <row r="327" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D327" s="13"/>
       <c r="E327" s="12"/>
-      <c r="BR327" s="14"/>
-    </row>
-    <row r="328" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ327" s="14"/>
+    </row>
+    <row r="328" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D328" s="13"/>
       <c r="E328" s="12"/>
-      <c r="BR328" s="14"/>
-    </row>
-    <row r="329" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ328" s="14"/>
+    </row>
+    <row r="329" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D329" s="13"/>
       <c r="E329" s="12"/>
-      <c r="BR329" s="14"/>
-    </row>
-    <row r="330" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ329" s="14"/>
+    </row>
+    <row r="330" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D330" s="13"/>
       <c r="E330" s="12"/>
-      <c r="BO330" s="14"/>
-      <c r="BR330" s="14"/>
-    </row>
-    <row r="331" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN330" s="14"/>
+      <c r="BQ330" s="14"/>
+    </row>
+    <row r="331" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D331" s="13"/>
       <c r="E331" s="12"/>
-      <c r="BO331" s="14"/>
-      <c r="BR331" s="14"/>
-    </row>
-    <row r="332" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN331" s="14"/>
+      <c r="BQ331" s="14"/>
+    </row>
+    <row r="332" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D332" s="13"/>
       <c r="E332" s="12"/>
-      <c r="BO332" s="14"/>
-      <c r="BR332" s="14"/>
-    </row>
-    <row r="333" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN332" s="14"/>
+      <c r="BQ332" s="14"/>
+    </row>
+    <row r="333" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D333" s="13"/>
       <c r="E333" s="12"/>
-      <c r="BO333" s="14"/>
-      <c r="BR333" s="14"/>
-    </row>
-    <row r="334" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN333" s="14"/>
+      <c r="BQ333" s="14"/>
+    </row>
+    <row r="334" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D334" s="13"/>
       <c r="E334" s="12"/>
-      <c r="BO334" s="14"/>
-      <c r="BR334" s="14"/>
-    </row>
-    <row r="335" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN334" s="14"/>
+      <c r="BQ334" s="14"/>
+    </row>
+    <row r="335" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D335" s="13"/>
       <c r="E335" s="12"/>
-      <c r="BO335" s="14"/>
-      <c r="BR335" s="14"/>
-    </row>
-    <row r="336" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN335" s="14"/>
+      <c r="BQ335" s="14"/>
+    </row>
+    <row r="336" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D336" s="13"/>
       <c r="E336" s="12"/>
-      <c r="BO336" s="14"/>
-      <c r="BR336" s="14"/>
-    </row>
-    <row r="337" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN336" s="14"/>
+      <c r="BQ336" s="14"/>
+    </row>
+    <row r="337" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D337" s="13"/>
       <c r="E337" s="12"/>
-      <c r="BO337" s="14"/>
-      <c r="BR337" s="14"/>
-    </row>
-    <row r="338" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN337" s="14"/>
+      <c r="BQ337" s="14"/>
+    </row>
+    <row r="338" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D338" s="13"/>
       <c r="E338" s="12"/>
-      <c r="BO338" s="14"/>
-      <c r="BR338" s="14"/>
-    </row>
-    <row r="339" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN338" s="14"/>
+      <c r="BQ338" s="14"/>
+    </row>
+    <row r="339" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D339" s="13"/>
       <c r="E339" s="12"/>
-      <c r="BO339" s="14"/>
-      <c r="BR339" s="14"/>
-    </row>
-    <row r="340" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN339" s="14"/>
+      <c r="BQ339" s="14"/>
+    </row>
+    <row r="340" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D340" s="13"/>
       <c r="E340" s="12"/>
-      <c r="BO340" s="14"/>
-      <c r="BR340" s="14"/>
-    </row>
-    <row r="341" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN340" s="14"/>
+      <c r="BQ340" s="14"/>
+    </row>
+    <row r="341" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D341" s="13"/>
       <c r="E341" s="12"/>
-      <c r="BO341" s="14"/>
-      <c r="BR341" s="14"/>
-    </row>
-    <row r="342" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN341" s="14"/>
+      <c r="BQ341" s="14"/>
+    </row>
+    <row r="342" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D342" s="13"/>
       <c r="E342" s="12"/>
-      <c r="BO342" s="14"/>
-      <c r="BR342" s="14"/>
-    </row>
-    <row r="343" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN342" s="14"/>
+      <c r="BQ342" s="14"/>
+    </row>
+    <row r="343" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D343" s="13"/>
       <c r="E343" s="12"/>
-      <c r="BO343" s="14"/>
-      <c r="BR343" s="14"/>
-    </row>
-    <row r="344" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN343" s="14"/>
+      <c r="BQ343" s="14"/>
+    </row>
+    <row r="344" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D344" s="13"/>
       <c r="E344" s="12"/>
-      <c r="BO344" s="14"/>
-      <c r="BR344" s="14"/>
-    </row>
-    <row r="345" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN344" s="14"/>
+      <c r="BQ344" s="14"/>
+    </row>
+    <row r="345" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D345" s="13"/>
       <c r="E345" s="12"/>
-      <c r="BO345" s="14"/>
-      <c r="BR345" s="14"/>
-    </row>
-    <row r="346" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN345" s="14"/>
+      <c r="BQ345" s="14"/>
+    </row>
+    <row r="346" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D346" s="13"/>
       <c r="E346" s="12"/>
-      <c r="BO346" s="14"/>
-      <c r="BR346" s="14"/>
-    </row>
-    <row r="347" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN346" s="14"/>
+      <c r="BQ346" s="14"/>
+    </row>
+    <row r="347" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D347" s="13"/>
       <c r="E347" s="12"/>
-      <c r="BO347" s="14"/>
-      <c r="BR347" s="14"/>
-    </row>
-    <row r="348" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN347" s="14"/>
+      <c r="BQ347" s="14"/>
+    </row>
+    <row r="348" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D348" s="13"/>
       <c r="E348" s="12"/>
-      <c r="BO348" s="14"/>
-      <c r="BR348" s="14"/>
-    </row>
-    <row r="349" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN348" s="14"/>
+      <c r="BQ348" s="14"/>
+    </row>
+    <row r="349" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D349" s="13"/>
       <c r="E349" s="12"/>
-      <c r="BO349" s="14"/>
-      <c r="BR349" s="14"/>
-    </row>
-    <row r="350" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN349" s="14"/>
+      <c r="BQ349" s="14"/>
+    </row>
+    <row r="350" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D350" s="13"/>
       <c r="E350" s="12"/>
-      <c r="BO350" s="14"/>
-      <c r="BR350" s="14"/>
-    </row>
-    <row r="351" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN350" s="14"/>
+      <c r="BQ350" s="14"/>
+    </row>
+    <row r="351" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D351" s="13"/>
       <c r="E351" s="12"/>
-      <c r="BO351" s="14"/>
-      <c r="BR351" s="14"/>
-    </row>
-    <row r="352" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN351" s="14"/>
+      <c r="BQ351" s="14"/>
+    </row>
+    <row r="352" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D352" s="13"/>
       <c r="E352" s="12"/>
-      <c r="BO352" s="14"/>
-      <c r="BR352" s="14"/>
-    </row>
-    <row r="353" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN352" s="14"/>
+      <c r="BQ352" s="14"/>
+    </row>
+    <row r="353" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D353" s="13"/>
       <c r="E353" s="12"/>
-      <c r="BO353" s="14"/>
-      <c r="BR353" s="14"/>
-    </row>
-    <row r="354" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN353" s="14"/>
+      <c r="BQ353" s="14"/>
+    </row>
+    <row r="354" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D354" s="13"/>
       <c r="E354" s="12"/>
-      <c r="BO354" s="14"/>
-      <c r="BR354" s="14"/>
-    </row>
-    <row r="355" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN354" s="14"/>
+      <c r="BQ354" s="14"/>
+    </row>
+    <row r="355" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D355" s="13"/>
       <c r="E355" s="12"/>
-      <c r="BO355" s="14"/>
-      <c r="BR355" s="14"/>
-    </row>
-    <row r="356" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN355" s="14"/>
+      <c r="BQ355" s="14"/>
+    </row>
+    <row r="356" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D356" s="13"/>
       <c r="E356" s="12"/>
-      <c r="BO356" s="14"/>
-      <c r="BR356" s="14"/>
-    </row>
-    <row r="357" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN356" s="14"/>
+      <c r="BQ356" s="14"/>
+    </row>
+    <row r="357" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D357" s="13"/>
       <c r="E357" s="12"/>
-      <c r="BO357" s="14"/>
-      <c r="BR357" s="14"/>
-    </row>
-    <row r="358" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN357" s="14"/>
+      <c r="BQ357" s="14"/>
+    </row>
+    <row r="358" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D358" s="13"/>
       <c r="E358" s="12"/>
-      <c r="BO358" s="14"/>
-      <c r="BR358" s="14"/>
-    </row>
-    <row r="359" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN358" s="14"/>
+      <c r="BQ358" s="14"/>
+    </row>
+    <row r="359" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D359" s="13"/>
       <c r="E359" s="12"/>
-      <c r="BO359" s="14"/>
-      <c r="BR359" s="14"/>
-    </row>
-    <row r="360" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN359" s="14"/>
+      <c r="BQ359" s="14"/>
+    </row>
+    <row r="360" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D360" s="13"/>
       <c r="E360" s="12"/>
-      <c r="BO360" s="14"/>
-      <c r="BR360" s="14"/>
-    </row>
-    <row r="361" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN360" s="14"/>
+      <c r="BQ360" s="14"/>
+    </row>
+    <row r="361" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D361" s="13"/>
       <c r="E361" s="12"/>
-      <c r="BO361" s="14"/>
-      <c r="BR361" s="14"/>
-    </row>
-    <row r="362" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN361" s="14"/>
+      <c r="BQ361" s="14"/>
+    </row>
+    <row r="362" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D362" s="13"/>
       <c r="E362" s="12"/>
-      <c r="BO362" s="14"/>
-      <c r="BR362" s="14"/>
-    </row>
-    <row r="363" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN362" s="14"/>
+      <c r="BQ362" s="14"/>
+    </row>
+    <row r="363" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D363" s="13"/>
       <c r="E363" s="12"/>
-      <c r="BO363" s="14"/>
-      <c r="BR363" s="14"/>
-    </row>
-    <row r="364" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN363" s="14"/>
+      <c r="BQ363" s="14"/>
+    </row>
+    <row r="364" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D364" s="13"/>
       <c r="E364" s="12"/>
-      <c r="BR364" s="14"/>
-    </row>
-    <row r="365" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ364" s="14"/>
+    </row>
+    <row r="365" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D365" s="13"/>
       <c r="E365" s="12"/>
-      <c r="BR365" s="14"/>
-    </row>
-    <row r="366" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ365" s="14"/>
+    </row>
+    <row r="366" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D366" s="13"/>
       <c r="E366" s="12"/>
-      <c r="BO366" s="14"/>
-      <c r="BR366" s="14"/>
-    </row>
-    <row r="367" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN366" s="14"/>
+      <c r="BQ366" s="14"/>
+    </row>
+    <row r="367" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D367" s="13"/>
       <c r="E367" s="12"/>
-      <c r="BO367" s="14"/>
-      <c r="BR367" s="14"/>
-    </row>
-    <row r="368" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN367" s="14"/>
+      <c r="BQ367" s="14"/>
+    </row>
+    <row r="368" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D368" s="13"/>
       <c r="E368" s="12"/>
-      <c r="BO368" s="14"/>
-      <c r="BR368" s="14"/>
-    </row>
-    <row r="369" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN368" s="14"/>
+      <c r="BQ368" s="14"/>
+    </row>
+    <row r="369" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D369" s="13"/>
       <c r="E369" s="12"/>
-      <c r="BO369" s="14"/>
-      <c r="BR369" s="14"/>
-    </row>
-    <row r="370" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN369" s="14"/>
+      <c r="BQ369" s="14"/>
+    </row>
+    <row r="370" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D370" s="13"/>
       <c r="E370" s="12"/>
-      <c r="BO370" s="14"/>
-      <c r="BR370" s="14"/>
-    </row>
-    <row r="371" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN370" s="14"/>
+      <c r="BQ370" s="14"/>
+    </row>
+    <row r="371" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D371" s="13"/>
       <c r="E371" s="12"/>
-      <c r="BO371" s="14"/>
-      <c r="BR371" s="14"/>
-    </row>
-    <row r="372" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN371" s="14"/>
+      <c r="BQ371" s="14"/>
+    </row>
+    <row r="372" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D372" s="13"/>
       <c r="E372" s="12"/>
-      <c r="BO372" s="14"/>
-      <c r="BR372" s="14"/>
-    </row>
-    <row r="373" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN372" s="14"/>
+      <c r="BQ372" s="14"/>
+    </row>
+    <row r="373" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D373" s="13"/>
       <c r="E373" s="12"/>
-      <c r="BO373" s="14"/>
-      <c r="BR373" s="14"/>
-    </row>
-    <row r="374" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN373" s="14"/>
+      <c r="BQ373" s="14"/>
+    </row>
+    <row r="374" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D374" s="13"/>
       <c r="E374" s="12"/>
-      <c r="BO374" s="14"/>
-      <c r="BR374" s="14"/>
-    </row>
-    <row r="375" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN374" s="14"/>
+      <c r="BQ374" s="14"/>
+    </row>
+    <row r="375" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D375" s="13"/>
       <c r="E375" s="12"/>
-      <c r="BO375" s="14"/>
-      <c r="BR375" s="14"/>
-    </row>
-    <row r="376" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN375" s="14"/>
+      <c r="BQ375" s="14"/>
+    </row>
+    <row r="376" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D376" s="13"/>
       <c r="E376" s="12"/>
-      <c r="BO376" s="14"/>
-      <c r="BR376" s="14"/>
-    </row>
-    <row r="377" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN376" s="14"/>
+      <c r="BQ376" s="14"/>
+    </row>
+    <row r="377" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D377" s="13"/>
       <c r="E377" s="12"/>
-      <c r="BO377" s="14"/>
-      <c r="BR377" s="14"/>
-    </row>
-    <row r="378" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN377" s="14"/>
+      <c r="BQ377" s="14"/>
+    </row>
+    <row r="378" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D378" s="13"/>
       <c r="E378" s="12"/>
-      <c r="BO378" s="14"/>
-      <c r="BR378" s="14"/>
-    </row>
-    <row r="379" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN378" s="14"/>
+      <c r="BQ378" s="14"/>
+    </row>
+    <row r="379" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D379" s="13"/>
       <c r="E379" s="12"/>
-      <c r="BO379" s="14"/>
-      <c r="BR379" s="14"/>
-    </row>
-    <row r="380" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN379" s="14"/>
+      <c r="BQ379" s="14"/>
+    </row>
+    <row r="380" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D380" s="13"/>
       <c r="E380" s="12"/>
-      <c r="BO380" s="14"/>
-      <c r="BR380" s="14"/>
-    </row>
-    <row r="381" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN380" s="14"/>
+      <c r="BQ380" s="14"/>
+    </row>
+    <row r="381" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D381" s="13"/>
       <c r="E381" s="12"/>
-      <c r="BO381" s="14"/>
-      <c r="BR381" s="14"/>
-    </row>
-    <row r="382" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN381" s="14"/>
+      <c r="BQ381" s="14"/>
+    </row>
+    <row r="382" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D382" s="13"/>
       <c r="E382" s="12"/>
-      <c r="BO382" s="14"/>
-      <c r="BR382" s="14"/>
-    </row>
-    <row r="383" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN382" s="14"/>
+      <c r="BQ382" s="14"/>
+    </row>
+    <row r="383" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D383" s="13"/>
       <c r="E383" s="12"/>
-      <c r="BO383" s="14"/>
-      <c r="BR383" s="14"/>
-    </row>
-    <row r="384" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN383" s="14"/>
+      <c r="BQ383" s="14"/>
+    </row>
+    <row r="384" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D384" s="13"/>
       <c r="E384" s="12"/>
-      <c r="BO384" s="14"/>
-      <c r="BR384" s="14"/>
-    </row>
-    <row r="385" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN384" s="14"/>
+      <c r="BQ384" s="14"/>
+    </row>
+    <row r="385" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D385" s="13"/>
       <c r="E385" s="12"/>
-      <c r="BO385" s="14"/>
-      <c r="BR385" s="14"/>
-    </row>
-    <row r="386" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN385" s="14"/>
+      <c r="BQ385" s="14"/>
+    </row>
+    <row r="386" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D386" s="13"/>
       <c r="E386" s="12"/>
-      <c r="BO386" s="14"/>
-      <c r="BR386" s="14"/>
-    </row>
-    <row r="387" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN386" s="14"/>
+      <c r="BQ386" s="14"/>
+    </row>
+    <row r="387" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D387" s="13"/>
       <c r="E387" s="12"/>
-      <c r="BO387" s="14"/>
-      <c r="BR387" s="14"/>
-    </row>
-    <row r="388" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN387" s="14"/>
+      <c r="BQ387" s="14"/>
+    </row>
+    <row r="388" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D388" s="13"/>
       <c r="E388" s="12"/>
-      <c r="BO388" s="14"/>
-      <c r="BR388" s="14"/>
-    </row>
-    <row r="389" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN388" s="14"/>
+      <c r="BQ388" s="14"/>
+    </row>
+    <row r="389" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D389" s="13"/>
       <c r="E389" s="12"/>
-      <c r="BR389" s="14"/>
-    </row>
-    <row r="390" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ389" s="14"/>
+    </row>
+    <row r="390" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D390" s="13"/>
       <c r="E390" s="12"/>
-      <c r="BR390" s="14"/>
-    </row>
-    <row r="391" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ390" s="14"/>
+    </row>
+    <row r="391" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D391" s="13"/>
       <c r="E391" s="12"/>
-      <c r="BO391" s="14"/>
-      <c r="BR391" s="14"/>
-    </row>
-    <row r="392" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN391" s="14"/>
+      <c r="BQ391" s="14"/>
+    </row>
+    <row r="392" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D392" s="13"/>
       <c r="E392" s="12"/>
-      <c r="BO392" s="14"/>
-      <c r="BR392" s="14"/>
-    </row>
-    <row r="393" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN392" s="14"/>
+      <c r="BQ392" s="14"/>
+    </row>
+    <row r="393" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D393" s="13"/>
       <c r="E393" s="12"/>
-      <c r="BR393" s="14"/>
-    </row>
-    <row r="394" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ393" s="14"/>
+    </row>
+    <row r="394" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D394" s="13"/>
       <c r="E394" s="12"/>
-      <c r="BR394" s="14"/>
-    </row>
-    <row r="395" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ394" s="14"/>
+    </row>
+    <row r="395" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D395" s="13"/>
       <c r="E395" s="12"/>
-      <c r="BO395" s="14"/>
-      <c r="BR395" s="14"/>
-    </row>
-    <row r="396" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN395" s="14"/>
+      <c r="BQ395" s="14"/>
+    </row>
+    <row r="396" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D396" s="13"/>
       <c r="E396" s="12"/>
-      <c r="BO396" s="14"/>
-      <c r="BR396" s="14"/>
-    </row>
-    <row r="397" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN396" s="14"/>
+      <c r="BQ396" s="14"/>
+    </row>
+    <row r="397" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D397" s="13"/>
       <c r="E397" s="12"/>
-      <c r="BO397" s="14"/>
-      <c r="BR397" s="14"/>
-    </row>
-    <row r="398" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN397" s="14"/>
+      <c r="BQ397" s="14"/>
+    </row>
+    <row r="398" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D398" s="13"/>
       <c r="E398" s="12"/>
-      <c r="BO398" s="14"/>
-      <c r="BR398" s="14"/>
-    </row>
-    <row r="399" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN398" s="14"/>
+      <c r="BQ398" s="14"/>
+    </row>
+    <row r="399" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D399" s="13"/>
       <c r="E399" s="12"/>
-      <c r="BO399" s="14"/>
-      <c r="BR399" s="14"/>
-    </row>
-    <row r="400" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN399" s="14"/>
+      <c r="BQ399" s="14"/>
+    </row>
+    <row r="400" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D400" s="13"/>
       <c r="E400" s="12"/>
-      <c r="BO400" s="14"/>
-      <c r="BR400" s="14"/>
-    </row>
-    <row r="401" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN400" s="14"/>
+      <c r="BQ400" s="14"/>
+    </row>
+    <row r="401" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D401" s="13"/>
       <c r="E401" s="12"/>
-      <c r="BO401" s="14"/>
-      <c r="BR401" s="14"/>
-    </row>
-    <row r="402" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN401" s="14"/>
+      <c r="BQ401" s="14"/>
+    </row>
+    <row r="402" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D402" s="13"/>
       <c r="E402" s="12"/>
-      <c r="BO402" s="14"/>
-      <c r="BR402" s="14"/>
-    </row>
-    <row r="403" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN402" s="14"/>
+      <c r="BQ402" s="14"/>
+    </row>
+    <row r="403" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D403" s="13"/>
       <c r="E403" s="12"/>
-      <c r="BO403" s="14"/>
-      <c r="BR403" s="14"/>
-    </row>
-    <row r="404" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN403" s="14"/>
+      <c r="BQ403" s="14"/>
+    </row>
+    <row r="404" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D404" s="13"/>
       <c r="E404" s="12"/>
-      <c r="BO404" s="14"/>
-      <c r="BR404" s="14"/>
-    </row>
-    <row r="405" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN404" s="14"/>
+      <c r="BQ404" s="14"/>
+    </row>
+    <row r="405" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D405" s="13"/>
       <c r="E405" s="12"/>
-      <c r="BO405" s="14"/>
-      <c r="BR405" s="14"/>
-    </row>
-    <row r="406" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN405" s="14"/>
+      <c r="BQ405" s="14"/>
+    </row>
+    <row r="406" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D406" s="13"/>
       <c r="E406" s="12"/>
-      <c r="BO406" s="14"/>
-      <c r="BR406" s="14"/>
-    </row>
-    <row r="407" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN406" s="14"/>
+      <c r="BQ406" s="14"/>
+    </row>
+    <row r="407" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D407" s="13"/>
       <c r="E407" s="12"/>
-      <c r="BO407" s="14"/>
-      <c r="BR407" s="14"/>
-    </row>
-    <row r="408" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN407" s="14"/>
+      <c r="BQ407" s="14"/>
+    </row>
+    <row r="408" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D408" s="13"/>
       <c r="E408" s="12"/>
-      <c r="BO408" s="14"/>
-      <c r="BR408" s="14"/>
-    </row>
-    <row r="409" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN408" s="14"/>
+      <c r="BQ408" s="14"/>
+    </row>
+    <row r="409" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D409" s="13"/>
       <c r="E409" s="12"/>
-      <c r="BO409" s="14"/>
-      <c r="BR409" s="14"/>
-    </row>
-    <row r="410" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN409" s="14"/>
+      <c r="BQ409" s="14"/>
+    </row>
+    <row r="410" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D410" s="13"/>
       <c r="E410" s="12"/>
-      <c r="BO410" s="14"/>
-      <c r="BR410" s="14"/>
-    </row>
-    <row r="411" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN410" s="14"/>
+      <c r="BQ410" s="14"/>
+    </row>
+    <row r="411" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D411" s="13"/>
       <c r="E411" s="12"/>
-      <c r="BO411" s="14"/>
-      <c r="BR411" s="14"/>
-    </row>
-    <row r="412" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN411" s="14"/>
+      <c r="BQ411" s="14"/>
+    </row>
+    <row r="412" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D412" s="13"/>
       <c r="E412" s="12"/>
     </row>
-    <row r="413" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="413" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D413" s="13"/>
       <c r="E413" s="12"/>
     </row>
-    <row r="414" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="414" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D414" s="13"/>
       <c r="E414" s="12"/>
     </row>
-    <row r="415" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="415" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D415" s="13"/>
       <c r="E415" s="12"/>
     </row>
-    <row r="416" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="416" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D416" s="13"/>
       <c r="E416" s="12"/>
     </row>
@@ -6655,334 +6657,334 @@
   <sheetData>
     <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G1" t="s">
         <v>158</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>159</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>160</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>161</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="U1" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="V1" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="Y1" t="s">
         <v>175</v>
       </c>
-      <c r="U1" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="V1" s="4" t="s">
+      <c r="Z1" t="s">
         <v>176</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="AB1" t="s">
         <v>178</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AC1" t="s">
         <v>179</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AD1" t="s">
         <v>180</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AE1" t="s">
         <v>181</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AF1" t="s">
         <v>182</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AG1" t="s">
         <v>183</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AH1" t="s">
         <v>184</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AI1" t="s">
         <v>185</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AJ1" t="s">
         <v>186</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AK1" t="s">
         <v>187</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AL1" t="s">
         <v>188</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AM1" t="s">
         <v>189</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AN1" t="s">
         <v>190</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AO1" t="s">
         <v>191</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AP1" t="s">
         <v>192</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AQ1" t="s">
         <v>193</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AR1" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="AS1" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="AT1" t="s">
         <v>194</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AU1" t="s">
         <v>195</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AV1" t="s">
         <v>196</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AW1" t="s">
         <v>197</v>
       </c>
-      <c r="AR1" s="8" t="s">
-        <v>563</v>
-      </c>
-      <c r="AS1" s="8" t="s">
-        <v>564</v>
-      </c>
-      <c r="AT1" t="s">
+      <c r="AX1" t="s">
         <v>198</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AY1" t="s">
         <v>199</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AZ1" t="s">
         <v>200</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="BA1" t="s">
         <v>201</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BB1" t="s">
         <v>202</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BC1" t="s">
         <v>203</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BD1" t="s">
         <v>204</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BE1" t="s">
         <v>205</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BF1" t="s">
         <v>206</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BG1" t="s">
         <v>207</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BH1" t="s">
         <v>208</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BJ1" t="s">
+        <v>208</v>
+      </c>
+      <c r="BK1" t="s">
         <v>209</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BL1" t="s">
         <v>210</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BM1" t="s">
         <v>211</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BN1" t="s">
         <v>212</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>212</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BO1" t="s">
         <v>213</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BP1" t="s">
         <v>214</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BQ1" t="s">
         <v>215</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BR1" t="s">
         <v>216</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BS1" t="s">
         <v>217</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BT1" t="s">
         <v>218</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BU1" t="s">
         <v>219</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BV1" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BW1" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BX1" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BY1" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="BV1" s="5" t="s">
+      <c r="BZ1" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="BW1" s="5" t="s">
+      <c r="CA1" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="BX1" s="5" t="s">
+      <c r="CB1" t="s">
         <v>226</v>
       </c>
-      <c r="BY1" s="5" t="s">
+      <c r="CC1" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="BZ1" s="5" t="s">
+      <c r="CD1" t="s">
         <v>228</v>
       </c>
-      <c r="CA1" s="5" t="s">
+      <c r="CE1" t="s">
         <v>229</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CF1" t="s">
         <v>230</v>
       </c>
-      <c r="CC1" s="5" t="s">
+      <c r="CG1" t="s">
         <v>231</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CH1" t="s">
         <v>232</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CI1" t="s">
         <v>233</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CJ1" t="s">
         <v>234</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CK1" t="s">
         <v>235</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CL1" t="s">
         <v>236</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CM1" t="s">
         <v>237</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CN1" t="s">
         <v>238</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CO1" t="s">
         <v>239</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CP1" t="s">
         <v>240</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CQ1" t="s">
         <v>241</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CR1" t="s">
+        <v>218</v>
+      </c>
+      <c r="CS1" t="s">
         <v>242</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CT1" t="s">
         <v>243</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CU1" t="s">
         <v>244</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CV1" t="s">
         <v>245</v>
       </c>
-      <c r="CR1" t="s">
-        <v>222</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CW1" t="s">
         <v>246</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CX1" t="s">
         <v>247</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CY1" t="s">
         <v>248</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CZ1" t="s">
+        <v>247</v>
+      </c>
+      <c r="DA1" t="s">
         <v>249</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="DB1" t="s">
         <v>250</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="DC1" t="s">
         <v>251</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="DD1" t="s">
         <v>252</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>251</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="DE1" t="s">
         <v>253</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DF1" t="s">
         <v>254</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DG1" t="s">
         <v>255</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DH1" t="s">
         <v>256</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DI1" t="s">
         <v>257</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>258</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>259</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>260</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:113" x14ac:dyDescent="0.25">
@@ -6990,337 +6992,337 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" t="s">
+        <v>260</v>
+      </c>
+      <c r="I2" t="s">
+        <v>261</v>
+      </c>
+      <c r="J2" t="s">
+        <v>262</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>278</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>281</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>282</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>283</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>284</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>285</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>286</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>287</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>288</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>289</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>290</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>291</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>292</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>293</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>294</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>295</v>
+      </c>
+      <c r="AR2" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="AS2" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>296</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>297</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>298</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>299</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>300</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>301</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>302</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>303</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>304</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>305</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>306</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>307</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>308</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>309</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>310</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>311</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>312</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>313</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>314</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>315</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>316</v>
+      </c>
+      <c r="BO2" t="s">
         <v>77</v>
       </c>
-      <c r="E2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F2" t="s">
-        <v>263</v>
-      </c>
-      <c r="G2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" t="s">
-        <v>264</v>
-      </c>
-      <c r="I2" t="s">
-        <v>265</v>
-      </c>
-      <c r="J2" t="s">
-        <v>266</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>281</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>282</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>284</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>285</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>286</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>287</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>288</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>289</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>290</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>291</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>292</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>293</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>294</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>295</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>296</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>297</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>298</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>299</v>
-      </c>
-      <c r="AR2" s="8" t="s">
-        <v>565</v>
-      </c>
-      <c r="AS2" s="8" t="s">
-        <v>566</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>300</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>301</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>302</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>303</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>304</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>305</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>306</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>307</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>308</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>309</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>310</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>311</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>312</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>313</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>314</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>315</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>316</v>
-      </c>
-      <c r="BK2" t="s">
+      <c r="BP2" t="s">
         <v>317</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BQ2" t="s">
         <v>318</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BR2" t="s">
         <v>319</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BS2" t="s">
         <v>320</v>
       </c>
-      <c r="BO2" t="s">
-        <v>79</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="BT2" t="s">
         <v>321</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BU2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV2" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BW2" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BX2" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BY2" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="BU2" t="s">
-        <v>95</v>
-      </c>
-      <c r="BV2" s="5" t="s">
+      <c r="BZ2" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="BW2" s="5" t="s">
+      <c r="CA2" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="BX2" s="5" t="s">
+      <c r="CB2" t="s">
         <v>328</v>
       </c>
-      <c r="BY2" s="5" t="s">
+      <c r="CC2" t="s">
         <v>329</v>
       </c>
-      <c r="BZ2" s="5" t="s">
+      <c r="CD2" t="s">
         <v>330</v>
       </c>
-      <c r="CA2" s="5" t="s">
+      <c r="CE2" t="s">
         <v>331</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CF2" t="s">
         <v>332</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CG2" t="s">
         <v>333</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CH2" t="s">
         <v>334</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CI2" t="s">
         <v>335</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CJ2" t="s">
         <v>336</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CK2" t="s">
         <v>337</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CL2" t="s">
         <v>338</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CM2" t="s">
         <v>339</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CN2" t="s">
         <v>340</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CO2" t="s">
         <v>341</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CP2" t="s">
         <v>342</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CQ2" t="s">
         <v>343</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CR2" t="s">
         <v>344</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CS2" t="s">
         <v>345</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CT2" t="s">
         <v>346</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CU2" t="s">
         <v>347</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CV2" t="s">
         <v>348</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CW2" t="s">
         <v>349</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CX2" t="s">
         <v>350</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CY2" t="s">
         <v>351</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CZ2" t="s">
         <v>352</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="DA2" t="s">
         <v>353</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="DB2" t="s">
         <v>354</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DC2" t="s">
         <v>355</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DD2" t="s">
         <v>356</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DE2" t="s">
         <v>357</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DF2" t="s">
         <v>358</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DG2" t="s">
         <v>359</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DH2" t="s">
         <v>360</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DI2" t="s">
         <v>361</v>
-      </c>
-      <c r="DF2" t="s">
-        <v>362</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>363</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>364</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -7340,341 +7342,341 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" t="s">
+        <v>362</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="O3" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="J3" t="s">
-        <v>366</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="M3" s="4" t="s">
+      <c r="P3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>365</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI3" t="s">
         <v>118</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>369</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>122</v>
       </c>
       <c r="AJ3" t="s">
         <v>3</v>
       </c>
       <c r="AK3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AL3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AM3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AN3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AO3" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="AP3" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
       <c r="AR3" s="8" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="AS3" s="8" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="AT3" t="s">
+        <v>368</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>369</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>368</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>370</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>371</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BV3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="BW3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="BX3" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="BY3" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="AU3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX3" t="s">
+      <c r="BZ3" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="CA3" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CC3" t="s">
         <v>373</v>
       </c>
-      <c r="AY3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>372</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BQ3" t="s">
+      <c r="CD3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CG3" t="s">
         <v>374</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="CH3" t="s">
         <v>375</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BV3" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW3" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="BX3" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="BY3" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="BZ3" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="CA3" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>377</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>378</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>379</v>
       </c>
       <c r="CI3" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="CK3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="CL3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="CM3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="CN3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="CO3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CP3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CQ3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CR3" t="s">
+        <v>373</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>119</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>112</v>
+      </c>
+      <c r="CU3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CV3" t="s">
         <v>377</v>
       </c>
-      <c r="CS3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>125</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>381</v>
-      </c>
       <c r="CW3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="CX3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="CY3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="CZ3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="DA3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="DB3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="DC3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="DD3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DE3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DF3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DG3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DH3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DI3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:113" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C5" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K5" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="S5" s="4">
         <v>1</v>
@@ -7686,13 +7688,13 @@
         <v>1</v>
       </c>
       <c r="AO5" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AT5" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AX5" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AZ5">
         <v>1</v>
@@ -7710,39 +7712,39 @@
         <v>0</v>
       </c>
       <c r="BO5" t="s">
+        <v>385</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>386</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>387</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>388</v>
+      </c>
+      <c r="CN5" t="s">
         <v>389</v>
-      </c>
-      <c r="BP5" t="s">
-        <v>390</v>
-      </c>
-      <c r="CB5" t="s">
-        <v>391</v>
-      </c>
-      <c r="CG5" t="s">
-        <v>392</v>
-      </c>
-      <c r="CN5" t="s">
-        <v>393</v>
       </c>
       <c r="CR5">
         <v>0.1</v>
       </c>
       <c r="CY5" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C6" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K6" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="AC6">
         <v>2</v>
@@ -7751,34 +7753,34 @@
         <v>1</v>
       </c>
       <c r="AO6" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AT6" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BD6">
         <v>1</v>
       </c>
       <c r="CL6" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CM6" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C7" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K7"/>
       <c r="Q7" t="s">
+        <v>389</v>
+      </c>
+      <c r="R7" t="s">
         <v>393</v>
-      </c>
-      <c r="R7" t="s">
-        <v>397</v>
       </c>
       <c r="AC7">
         <v>2</v>
@@ -7787,7 +7789,7 @@
         <v>1</v>
       </c>
       <c r="AO7" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AV7">
         <v>99</v>
@@ -7799,36 +7801,36 @@
         <v>0.1</v>
       </c>
       <c r="CL7" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="CM7" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C10" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D10" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E10" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F10" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="J10" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="AC10">
         <v>2</v>
@@ -7837,13 +7839,13 @@
         <v>1</v>
       </c>
       <c r="AO10" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AT10" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AX10" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AZ10">
         <v>1.5</v>
@@ -7867,10 +7869,10 @@
         <v>0</v>
       </c>
       <c r="BO10" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BP10" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BT10">
         <v>0.3</v>
@@ -7885,23 +7887,23 @@
         <v>1</v>
       </c>
       <c r="BY10" s="5" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="CB10" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="CG10" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="CL10" s="4"/>
       <c r="CN10" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="CR10">
         <v>0.1</v>
       </c>
       <c r="CY10" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="DD10">
         <v>1</v>
@@ -7915,13 +7917,13 @@
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C11" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K11" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="AC11">
         <v>2</v>
@@ -7930,10 +7932,10 @@
         <v>1</v>
       </c>
       <c r="AO11" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AT11" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BD11">
         <v>1</v>
@@ -7945,13 +7947,13 @@
         <v>0.1</v>
       </c>
       <c r="CL11" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="CM11" t="s">
+        <v>389</v>
+      </c>
+      <c r="CN11" t="s">
         <v>393</v>
-      </c>
-      <c r="CN11" t="s">
-        <v>397</v>
       </c>
       <c r="CR11">
         <v>3</v>
@@ -7959,16 +7961,16 @@
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C12" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K12" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AC12">
         <v>2</v>
@@ -7977,10 +7979,10 @@
         <v>1</v>
       </c>
       <c r="AO12" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AT12" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BD12">
         <v>1</v>
@@ -7992,36 +7994,36 @@
         <v>0.1</v>
       </c>
       <c r="CL12" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="CM12" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>408</v>
+      </c>
+      <c r="C14" t="s">
+        <v>409</v>
+      </c>
+      <c r="D14" t="s">
+        <v>410</v>
+      </c>
+      <c r="E14" t="s">
+        <v>411</v>
+      </c>
+      <c r="F14" t="s">
         <v>412</v>
-      </c>
-      <c r="C14" t="s">
-        <v>413</v>
-      </c>
-      <c r="D14" t="s">
-        <v>414</v>
-      </c>
-      <c r="E14" t="s">
-        <v>415</v>
-      </c>
-      <c r="F14" t="s">
-        <v>416</v>
       </c>
       <c r="G14">
         <v>3</v>
       </c>
       <c r="J14" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="AC14">
         <v>1</v>
@@ -8030,16 +8032,16 @@
         <v>1</v>
       </c>
       <c r="AG14" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="BD14">
         <v>1</v>
       </c>
       <c r="BO14" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="BP14" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="BT14">
         <v>9999</v>
@@ -8054,11 +8056,11 @@
         <v>1</v>
       </c>
       <c r="BY14" s="5" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="CL14" s="4"/>
       <c r="CN14" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="CO14">
         <v>35</v>
@@ -8067,7 +8069,7 @@
         <v>9999</v>
       </c>
       <c r="CU14" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="DD14">
         <v>1</v>
@@ -8081,16 +8083,16 @@
     </row>
     <row r="15" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>414</v>
+      </c>
+      <c r="C15" t="s">
+        <v>380</v>
+      </c>
+      <c r="K15" t="s">
+        <v>381</v>
+      </c>
+      <c r="O15" s="4" t="s">
         <v>418</v>
-      </c>
-      <c r="C15" t="s">
-        <v>384</v>
-      </c>
-      <c r="K15" t="s">
-        <v>385</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>422</v>
       </c>
       <c r="AC15">
         <v>2</v>
@@ -8099,13 +8101,13 @@
         <v>1</v>
       </c>
       <c r="AO15" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AT15" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AX15" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AZ15">
         <v>1</v>
@@ -8123,39 +8125,39 @@
         <v>0</v>
       </c>
       <c r="BO15" t="s">
+        <v>385</v>
+      </c>
+      <c r="BP15" t="s">
+        <v>391</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>419</v>
+      </c>
+      <c r="CG15" t="s">
+        <v>388</v>
+      </c>
+      <c r="CN15" t="s">
         <v>389</v>
-      </c>
-      <c r="BP15" t="s">
-        <v>395</v>
-      </c>
-      <c r="CB15" t="s">
-        <v>423</v>
-      </c>
-      <c r="CG15" t="s">
-        <v>392</v>
-      </c>
-      <c r="CN15" t="s">
-        <v>393</v>
       </c>
       <c r="CR15">
         <v>0.1</v>
       </c>
       <c r="CY15" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C16" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I16">
         <v>1</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="M16"/>
       <c r="N16"/>
@@ -8168,7 +8170,7 @@
         <v>1</v>
       </c>
       <c r="AG16" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="BD16">
         <v>1</v>
@@ -8178,10 +8180,10 @@
       </c>
       <c r="BZ16"/>
       <c r="CB16" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="CG16" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="DD16">
         <v>1</v>
@@ -8201,28 +8203,28 @@
     </row>
     <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C18" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D18" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E18" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F18" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="G18">
         <v>3</v>
       </c>
       <c r="J18" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="AC18">
         <v>1</v>
@@ -8231,19 +8233,19 @@
         <v>1</v>
       </c>
       <c r="AG18" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="AT18" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="BD18">
         <v>1</v>
       </c>
       <c r="BO18" s="8" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="BP18" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="BT18">
         <v>30</v>
@@ -8258,11 +8260,11 @@
         <v>1</v>
       </c>
       <c r="BY18" s="5" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="CL18" s="4"/>
       <c r="CN18" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="CO18">
         <v>1.25</v>
@@ -8271,7 +8273,7 @@
         <v>30</v>
       </c>
       <c r="CU18" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="DD18">
         <v>1</v>
@@ -8285,16 +8287,16 @@
     </row>
     <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C19" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K19" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="AC19">
         <v>2</v>
@@ -8303,13 +8305,13 @@
         <v>1</v>
       </c>
       <c r="AO19" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AT19" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AX19" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AZ19">
         <v>1</v>
@@ -8327,36 +8329,36 @@
         <v>0</v>
       </c>
       <c r="BO19" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BP19" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="CG19" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="CN19" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="CR19">
         <v>9999</v>
       </c>
       <c r="CY19" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C20" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="M20"/>
       <c r="N20"/>
@@ -8369,7 +8371,7 @@
         <v>1</v>
       </c>
       <c r="AG20" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="BD20">
         <v>1</v>
@@ -8379,10 +8381,10 @@
       </c>
       <c r="BZ20"/>
       <c r="CB20" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="CG20" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="DD20">
         <v>1</v>
@@ -8399,19 +8401,19 @@
     </row>
     <row r="21" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C21" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I21">
         <v>1</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="M21"/>
       <c r="N21"/>
@@ -8424,7 +8426,7 @@
         <v>1</v>
       </c>
       <c r="AG21" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="BD21">
         <v>1</v>
@@ -8434,10 +8436,10 @@
       </c>
       <c r="BZ21"/>
       <c r="CB21" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="CG21" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="DD21">
         <v>1</v>
@@ -8454,17 +8456,17 @@
     </row>
     <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C22" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K22"/>
       <c r="O22" s="4" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="Q22" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="R22"/>
       <c r="AC22">
@@ -8474,7 +8476,7 @@
         <v>1</v>
       </c>
       <c r="AO22" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AV22">
         <v>99</v>
@@ -8486,27 +8488,27 @@
         <v>1</v>
       </c>
       <c r="CL22" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C23" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="Q23" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="R23"/>
       <c r="AC23">
@@ -8516,7 +8518,7 @@
         <v>1</v>
       </c>
       <c r="AO23" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AV23">
         <v>99</v>
@@ -8528,21 +8530,21 @@
         <v>0.1</v>
       </c>
       <c r="CM23" t="s">
+        <v>439</v>
+      </c>
+      <c r="CU23" s="8" t="s">
         <v>443</v>
-      </c>
-      <c r="CU23" s="8" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="24" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C24" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="Q24"/>
       <c r="R24"/>
@@ -8553,10 +8555,10 @@
         <v>1</v>
       </c>
       <c r="AO24" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AT24" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="BD24">
         <v>99</v>
@@ -8565,7 +8567,7 @@
         <v>0.1</v>
       </c>
       <c r="CN24" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="CO24">
         <v>-0.5</v>
@@ -8576,19 +8578,19 @@
     </row>
     <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C25" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="Q25"/>
       <c r="R25"/>
@@ -8599,10 +8601,10 @@
         <v>1</v>
       </c>
       <c r="AO25" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AT25" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="BD25">
         <v>99</v>
@@ -8611,7 +8613,7 @@
         <v>0.1</v>
       </c>
       <c r="CU25" s="8" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
     </row>
     <row r="26" spans="1:112" x14ac:dyDescent="0.25">
@@ -8622,22 +8624,22 @@
     </row>
     <row r="28" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C28" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AC28">
         <v>1</v>
       </c>
       <c r="AG28" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="BD28">
         <v>1</v>
@@ -8645,33 +8647,33 @@
       <c r="BV28"/>
       <c r="CL28" s="4"/>
       <c r="CU28" s="8" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
     </row>
     <row r="29" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C29" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="I29">
         <v>1</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AC29">
         <v>2</v>
       </c>
       <c r="AO29" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AT29" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="BD29">
         <v>4</v>
@@ -8681,36 +8683,36 @@
       </c>
       <c r="CL29" s="4"/>
       <c r="CN29" s="8" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="CR29">
         <v>5</v>
       </c>
       <c r="CU29" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="CY29" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="30" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C30" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AC30">
         <v>1</v>
       </c>
       <c r="AG30" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="BD30">
         <v>1</v>
@@ -8718,7 +8720,7 @@
       <c r="BV30"/>
       <c r="CL30" s="4"/>
       <c r="CU30" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="31" spans="1:112" x14ac:dyDescent="0.25">
@@ -8726,19 +8728,19 @@
     </row>
     <row r="32" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C32" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I32">
         <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="AC32">
         <v>2</v>
@@ -8753,10 +8755,10 @@
         <v>1</v>
       </c>
       <c r="BO32" s="8" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="BP32" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="BT32">
         <v>6</v>
@@ -8771,7 +8773,7 @@
         <v>1</v>
       </c>
       <c r="BY32" s="5" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="CL32" s="4"/>
       <c r="DH32">
@@ -8780,17 +8782,17 @@
     </row>
     <row r="33" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C33" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I33">
         <v>1</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="6" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L33" s="6"/>
       <c r="M33"/>
@@ -8810,13 +8812,13 @@
         <v>1</v>
       </c>
       <c r="AG33" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="AT33" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="AX33" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="AZ33">
         <v>999</v>
@@ -8845,22 +8847,22 @@
     </row>
     <row r="34" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C34" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="AC34">
         <v>1</v>
       </c>
       <c r="AG34" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="BD34">
         <v>1</v>
@@ -8868,27 +8870,27 @@
       <c r="BV34"/>
       <c r="CL34" s="4"/>
       <c r="CU34" s="8" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="35" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C35" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="AC35">
         <v>1</v>
       </c>
       <c r="AG35" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="BD35">
         <v>1</v>
@@ -8896,7 +8898,7 @@
       <c r="BV35"/>
       <c r="CL35" s="4"/>
       <c r="CU35" s="8" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="36" spans="1:112" x14ac:dyDescent="0.25">
@@ -8904,48 +8906,48 @@
     </row>
     <row r="37" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C37" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I37">
         <v>1</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AC37">
         <v>1</v>
       </c>
       <c r="AG37" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="BD37">
         <v>1</v>
       </c>
       <c r="CY37" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="38" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C38" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I38">
         <v>1</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="M38"/>
       <c r="N38"/>
@@ -8969,13 +8971,13 @@
         <v>1</v>
       </c>
       <c r="AO38" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AT38" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="AX38" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AZ38">
         <v>1.5</v>
@@ -8990,10 +8992,10 @@
         <v>0.5</v>
       </c>
       <c r="BO38" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="BP38" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="BV38" s="7"/>
       <c r="BW38" s="7"/>
@@ -9002,36 +9004,36 @@
       <c r="BZ38" s="7"/>
       <c r="CA38" s="7"/>
       <c r="CB38" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="CG38" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="CL38" s="4" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="CU38" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="CY38" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="39" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C39" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I39">
         <v>1</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="X39" s="4">
         <v>1</v>
@@ -9043,10 +9045,10 @@
         <v>1</v>
       </c>
       <c r="AO39" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AT39" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="BD39">
         <v>99</v>
@@ -9054,7 +9056,7 @@
       <c r="BV39"/>
       <c r="CL39" s="4"/>
       <c r="CN39" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="CO39">
         <v>-0.8</v>
@@ -9063,33 +9065,33 @@
         <v>6</v>
       </c>
       <c r="CY39" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="40" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C40" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I40">
         <v>1</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="AC40">
         <v>1</v>
       </c>
       <c r="AG40" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="AT40" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="AX40" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="AZ40">
         <v>0.09</v>
@@ -9109,7 +9111,7 @@
       <c r="BV40"/>
       <c r="CL40" s="4"/>
       <c r="CY40" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="DD40">
         <v>1</v>
@@ -10293,37 +10295,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>471</v>
+      </c>
+      <c r="F1" t="s">
+        <v>472</v>
+      </c>
+      <c r="G1" t="s">
+        <v>473</v>
+      </c>
+      <c r="H1" t="s">
+        <v>474</v>
+      </c>
+      <c r="I1" t="s">
         <v>475</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>476</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
         <v>477</v>
       </c>
-      <c r="H1" t="s">
+      <c r="M1" t="s">
         <v>478</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
         <v>479</v>
       </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
         <v>480</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>481</v>
-      </c>
-      <c r="M1" t="s">
-        <v>482</v>
-      </c>
-      <c r="N1" t="s">
-        <v>483</v>
-      </c>
-      <c r="O1" t="s">
-        <v>484</v>
-      </c>
-      <c r="P1" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -10331,49 +10333,49 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F2" t="s">
+        <v>483</v>
+      </c>
+      <c r="G2" t="s">
+        <v>484</v>
+      </c>
+      <c r="H2" t="s">
+        <v>485</v>
+      </c>
+      <c r="I2" t="s">
         <v>486</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>487</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
         <v>488</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" t="s">
         <v>489</v>
       </c>
-      <c r="I2" t="s">
+      <c r="N2" t="s">
         <v>490</v>
       </c>
-      <c r="J2" t="s">
+      <c r="O2" t="s">
         <v>491</v>
       </c>
-      <c r="K2" t="s">
+      <c r="P2" t="s">
         <v>492</v>
       </c>
-      <c r="L2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" t="s">
-        <v>493</v>
-      </c>
-      <c r="N2" t="s">
-        <v>494</v>
-      </c>
-      <c r="O2" t="s">
-        <v>495</v>
-      </c>
-      <c r="P2" t="s">
-        <v>496</v>
-      </c>
       <c r="Q2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -10387,101 +10389,101 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="K3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="M3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="N3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="O3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="P3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="Q3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C4" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C5" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C6" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="J6" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C7" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="Q7" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C8" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="292" spans="16:16" x14ac:dyDescent="0.25">
@@ -10516,7 +10518,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -10524,13 +10526,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="D2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10541,10 +10543,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -10567,7 +10569,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -10575,31 +10577,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
       <c r="D2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="G2" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="H2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="I2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="J2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -10616,22 +10618,22 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="J3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -10658,34 +10660,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C1" t="s">
+        <v>507</v>
+      </c>
+      <c r="D1" t="s">
+        <v>508</v>
+      </c>
+      <c r="E1" t="s">
+        <v>509</v>
+      </c>
+      <c r="F1" t="s">
         <v>510</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>511</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>512</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
         <v>513</v>
       </c>
-      <c r="F1" t="s">
+      <c r="K1" t="s">
         <v>514</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>515</v>
-      </c>
-      <c r="I1" t="s">
-        <v>516</v>
-      </c>
-      <c r="J1" t="s">
-        <v>517</v>
-      </c>
-      <c r="K1" t="s">
-        <v>518</v>
-      </c>
-      <c r="L1" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -10693,37 +10695,37 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>516</v>
+      </c>
+      <c r="C2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F2" t="s">
         <v>520</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>521</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>522</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>523</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>524</v>
       </c>
-      <c r="G2" t="s">
-        <v>525</v>
-      </c>
-      <c r="H2" t="s">
-        <v>526</v>
-      </c>
-      <c r="I2" t="s">
-        <v>527</v>
-      </c>
-      <c r="J2" t="s">
-        <v>528</v>
-      </c>
       <c r="K2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -10734,34 +10736,34 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -10791,31 +10793,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F2" t="s">
         <v>77</v>
       </c>
-      <c r="D2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E2" t="s">
-        <v>531</v>
-      </c>
-      <c r="F2" t="s">
-        <v>79</v>
-      </c>
       <c r="G2" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="H2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="I2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="J2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -10832,22 +10834,22 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -10876,28 +10878,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>538</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -10905,28 +10907,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -10934,10 +10936,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
@@ -10966,27 +10968,27 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -10995,13 +10997,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/一方通行/酒神.xlsx
+++ b/Excel/一方通行/酒神.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B80495-0347-4B2F-9527-1AC004C3C467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E9CE42-305D-47A2-845A-3BAF2C1A0628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="578">
   <si>
     <t>Id</t>
   </si>
@@ -2039,8 +2039,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2053,6 +2052,19 @@
       <name val="宋体"/>
       <family val="3"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2080,20 +2092,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2398,37 +2407,36 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1" style="2"/>
+    <col min="1" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -2437,1745 +2445,1239 @@
   <dimension ref="A1:BT12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="8.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="8.58203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="19.58203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="8.25" customWidth="1" style="2"/>
-    <col min="8" max="8" width="9" customWidth="1" style="2"/>
-    <col min="9" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="9" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6" customWidth="1" style="2"/>
-    <col min="12" max="12" width="5.5" customWidth="1" style="2"/>
-    <col min="13" max="13" width="5.58203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="4" customWidth="1" style="2"/>
-    <col min="15" max="15" width="7.75" customWidth="1" style="2"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="3.83203125" customWidth="1" style="2"/>
-    <col min="18" max="18" width="3.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="3.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="3.58203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="10.25" customWidth="1" style="2"/>
-    <col min="22" max="22" width="9.58203125" customWidth="1" style="2"/>
-    <col min="23" max="23" width="10.75" customWidth="1" style="2"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1" style="2"/>
-    <col min="25" max="25" width="13.08203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.75" customWidth="1" style="2"/>
-    <col min="27" max="27" width="9" customWidth="1" style="2"/>
-    <col min="28" max="28" width="9" customWidth="1" style="2"/>
-    <col min="29" max="29" width="8" customWidth="1" style="2"/>
-    <col min="30" max="30" width="17.08203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="9" customWidth="1" style="2"/>
-    <col min="32" max="32" width="9" customWidth="1" style="2"/>
-    <col min="33" max="33" width="9.75" customWidth="1" style="2"/>
-    <col min="34" max="34" width="7.83203125" customWidth="1" style="2"/>
-    <col min="35" max="35" width="15.83203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="13.83203125" customWidth="1" style="2"/>
-    <col min="37" max="37" width="34.5" customWidth="1" style="2"/>
-    <col min="38" max="38" width="9.83203125" customWidth="1" style="2"/>
-    <col min="39" max="39" width="9.83203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="9" customWidth="1" style="2"/>
-    <col min="41" max="41" width="9" customWidth="1" style="2"/>
-    <col min="42" max="42" width="9" customWidth="1" style="2"/>
-    <col min="43" max="43" width="9" customWidth="1" style="2"/>
-    <col min="44" max="44" width="12.5" customWidth="1" style="2"/>
-    <col min="45" max="45" width="9" customWidth="1" style="2"/>
-    <col min="46" max="46" width="9" customWidth="1" style="2"/>
-    <col min="47" max="47" width="9" customWidth="1" style="2"/>
-    <col min="48" max="48" width="9" customWidth="1" style="2"/>
-    <col min="49" max="49" width="9" customWidth="1" style="2"/>
-    <col min="50" max="50" width="9" customWidth="1" style="2"/>
-    <col min="51" max="51" width="24.33203125" customWidth="1" style="2"/>
-    <col min="52" max="52" width="9" customWidth="1" style="2"/>
-    <col min="53" max="53" width="17.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="7.83203125" customWidth="1" style="2"/>
-    <col min="55" max="55" width="9" customWidth="1" style="2"/>
-    <col min="56" max="56" width="9" customWidth="1" style="2"/>
-    <col min="57" max="57" width="24.25" customWidth="1" style="2"/>
-    <col min="58" max="58" width="13.25" customWidth="1" style="2"/>
-    <col min="59" max="59" width="16.08203125" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8" customWidth="1" style="2"/>
-    <col min="61" max="61" width="9" customWidth="1" style="2"/>
-    <col min="62" max="62" width="9" customWidth="1" style="2"/>
-    <col min="63" max="63" width="9" customWidth="1" style="2"/>
-    <col min="64" max="64" width="9" customWidth="1" style="2"/>
-    <col min="65" max="65" width="39.58203125" customWidth="1" style="2"/>
-    <col min="66" max="66" width="14" customWidth="1" style="2"/>
-    <col min="67" max="67" width="14.83203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="14" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14" customWidth="1" style="2"/>
-    <col min="71" max="71" width="14" customWidth="1" style="2"/>
-    <col min="72" max="72" width="19.1640625" customWidth="1" style="2"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1"/>
+    <col min="2" max="3" width="9" customWidth="1"/>
+    <col min="4" max="5" width="8.58203125" customWidth="1"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1"/>
+    <col min="7" max="7" width="8.25" customWidth="1"/>
+    <col min="8" max="10" width="9" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="5.5" customWidth="1"/>
+    <col min="13" max="13" width="5.58203125" customWidth="1"/>
+    <col min="14" max="14" width="4" customWidth="1"/>
+    <col min="15" max="15" width="7.75" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1"/>
+    <col min="17" max="18" width="3.83203125" customWidth="1"/>
+    <col min="19" max="20" width="3.58203125" customWidth="1"/>
+    <col min="21" max="21" width="10.25" customWidth="1"/>
+    <col min="22" max="22" width="9.58203125" customWidth="1"/>
+    <col min="23" max="23" width="10.75" customWidth="1"/>
+    <col min="24" max="24" width="12.83203125" customWidth="1"/>
+    <col min="25" max="25" width="13.08203125" customWidth="1"/>
+    <col min="26" max="26" width="10.75" customWidth="1"/>
+    <col min="27" max="28" width="9" customWidth="1"/>
+    <col min="29" max="29" width="8" customWidth="1"/>
+    <col min="30" max="30" width="17.08203125" customWidth="1"/>
+    <col min="31" max="32" width="9" customWidth="1"/>
+    <col min="33" max="33" width="9.75" customWidth="1"/>
+    <col min="34" max="34" width="7.83203125" customWidth="1"/>
+    <col min="35" max="35" width="15.83203125" customWidth="1"/>
+    <col min="36" max="36" width="13.83203125" customWidth="1"/>
+    <col min="37" max="37" width="34.5" customWidth="1"/>
+    <col min="38" max="39" width="9.83203125" customWidth="1"/>
+    <col min="40" max="43" width="9" customWidth="1"/>
+    <col min="44" max="44" width="12.5" customWidth="1"/>
+    <col min="45" max="50" width="9" customWidth="1"/>
+    <col min="51" max="51" width="24.33203125" customWidth="1"/>
+    <col min="52" max="52" width="9" customWidth="1"/>
+    <col min="53" max="53" width="17.75" customWidth="1"/>
+    <col min="54" max="54" width="7.83203125" customWidth="1"/>
+    <col min="55" max="56" width="9" customWidth="1"/>
+    <col min="57" max="57" width="24.25" customWidth="1"/>
+    <col min="58" max="58" width="13.25" customWidth="1"/>
+    <col min="59" max="59" width="16.08203125" customWidth="1"/>
+    <col min="60" max="60" width="8" customWidth="1"/>
+    <col min="61" max="64" width="9" customWidth="1"/>
+    <col min="65" max="65" width="39.58203125" customWidth="1"/>
+    <col min="66" max="66" width="14" customWidth="1"/>
+    <col min="67" max="67" width="14.83203125" customWidth="1"/>
+    <col min="68" max="71" width="14" customWidth="1"/>
+    <col min="72" max="72" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2" t="s">
+      <c r="S1" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2" t="s">
+      <c r="U1" t="s">
         <v>14</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2" t="s">
+      <c r="X1" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" t="s">
         <v>19</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" t="s">
         <v>20</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" t="s">
         <v>22</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" t="s">
         <v>23</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" t="s">
         <v>24</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" t="s">
         <v>25</v>
       </c>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AO1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AR1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="2"/>
-      <c r="AT1" s="2" t="s">
+      <c r="AT1" t="s">
         <v>35</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AU1" t="s">
         <v>36</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AV1" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AW1" t="s">
         <v>38</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AX1" t="s">
         <v>39</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AY1" t="s">
         <v>40</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AZ1" t="s">
         <v>41</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" t="s">
         <v>42</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BB1" t="s">
         <v>43</v>
       </c>
-      <c r="BC1" s="2"/>
-      <c r="BD1" s="2"/>
-      <c r="BE1" s="2" t="s">
+      <c r="BE1" t="s">
         <v>44</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BF1" t="s">
         <v>45</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BG1" t="s">
         <v>46</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BH1" t="s">
         <v>47</v>
       </c>
-      <c r="BI1" s="2" t="s">
+      <c r="BI1" t="s">
         <v>48</v>
       </c>
-      <c r="BJ1" s="2"/>
-      <c r="BK1" s="2"/>
-      <c r="BL1" s="2"/>
-      <c r="BM1" s="2"/>
-      <c r="BN1" s="2"/>
-      <c r="BO1" s="2"/>
-      <c r="BP1" s="2"/>
-      <c r="BQ1" s="2"/>
-      <c r="BR1" s="2"/>
-      <c r="BS1" s="2"/>
-      <c r="BT1" s="2"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>52</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>53</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>55</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
         <v>56</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" t="s">
         <v>57</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" t="s">
         <v>58</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" t="s">
         <v>59</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" t="s">
         <v>60</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" t="s">
         <v>61</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" t="s">
         <v>62</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" t="s">
         <v>63</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" t="s">
         <v>64</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" t="s">
         <v>65</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" t="s">
         <v>66</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" t="s">
         <v>67</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" t="s">
         <v>68</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" t="s">
         <v>69</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" t="s">
         <v>70</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" t="s">
         <v>71</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AA2" t="s">
         <v>72</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AB2" t="s">
         <v>73</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AC2" t="s">
         <v>74</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AD2" t="s">
         <v>75</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AE2" t="s">
         <v>76</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AF2" t="s">
         <v>77</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AG2" t="s">
         <v>78</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AH2" t="s">
         <v>79</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AI2" t="s">
         <v>80</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AJ2" t="s">
         <v>81</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AK2" t="s">
         <v>82</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AL2" t="s">
         <v>83</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AM2" t="s">
         <v>84</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AN2" t="s">
         <v>85</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AO2" t="s">
         <v>86</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AP2" t="s">
         <v>87</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AQ2" t="s">
         <v>88</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AR2" t="s">
         <v>89</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AS2" t="s">
         <v>90</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AT2" t="s">
         <v>91</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AU2" t="s">
         <v>92</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AV2" t="s">
         <v>93</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AW2" t="s">
         <v>94</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AX2" t="s">
         <v>95</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="AY2" t="s">
         <v>96</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="AZ2" t="s">
         <v>97</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="BA2" t="s">
         <v>98</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="BB2" t="s">
         <v>99</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BC2" t="s">
         <v>100</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BD2" t="s">
         <v>101</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BE2" t="s">
         <v>102</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BF2" t="s">
         <v>103</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BG2" t="s">
         <v>104</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BH2" t="s">
         <v>105</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BI2" t="s">
         <v>106</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BJ2" t="s">
         <v>107</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BK2" t="s">
         <v>108</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BL2" t="s">
         <v>109</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BM2" t="s">
         <v>110</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BN2" t="s">
         <v>111</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BO2" t="s">
         <v>112</v>
       </c>
-      <c r="BP2" s="2" t="s">
+      <c r="BP2" t="s">
         <v>113</v>
       </c>
-      <c r="BQ2" s="2" t="s">
+      <c r="BQ2" t="s">
         <v>114</v>
       </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BR2" t="s">
         <v>115</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BS2" t="s">
         <v>116</v>
       </c>
-      <c r="BT2" s="2" t="s">
+      <c r="BT2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
+    <row r="3" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
         <v>119</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
         <v>120</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>120</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" t="s">
         <v>120</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" t="s">
         <v>120</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" t="s">
         <v>120</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" t="s">
         <v>120</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" t="s">
         <v>120</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" t="s">
         <v>120</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" t="s">
         <v>120</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" t="s">
         <v>120</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" t="s">
         <v>120</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T3" t="s">
         <v>120</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="U3" t="s">
         <v>119</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V3" t="s">
         <v>120</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W3" t="s">
         <v>120</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X3" t="s">
         <v>119</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Y3" t="s">
         <v>119</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="Z3" t="s">
         <v>119</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AA3" t="s">
         <v>120</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AB3" t="s">
         <v>119</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AC3" t="s">
         <v>120</v>
       </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AD3" t="s">
         <v>118</v>
       </c>
-      <c r="AE3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF3" s="2" t="s">
+      <c r="AE3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF3" t="s">
         <v>120</v>
       </c>
-      <c r="AG3" s="2" t="s">
+      <c r="AG3" t="s">
         <v>120</v>
       </c>
-      <c r="AH3" s="2" t="s">
+      <c r="AH3" t="s">
         <v>120</v>
       </c>
-      <c r="AI3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK3" s="2" t="s">
+      <c r="AI3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" t="s">
         <v>121</v>
       </c>
-      <c r="AL3" s="2" t="s">
+      <c r="AL3" t="s">
         <v>121</v>
       </c>
-      <c r="AM3" s="2" t="s">
+      <c r="AM3" t="s">
         <v>120</v>
       </c>
-      <c r="AN3" s="2" t="s">
+      <c r="AN3" t="s">
         <v>119</v>
       </c>
-      <c r="AO3" s="2" t="s">
+      <c r="AO3" t="s">
         <v>122</v>
       </c>
-      <c r="AP3" s="2" t="s">
+      <c r="AP3" t="s">
         <v>120</v>
       </c>
-      <c r="AQ3" s="2" t="s">
+      <c r="AQ3" t="s">
         <v>119</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AR3" t="s">
         <v>118</v>
       </c>
-      <c r="AS3" s="2"/>
-      <c r="AT3" s="2" t="s">
+      <c r="AT3" t="s">
         <v>119</v>
       </c>
-      <c r="AU3" s="2" t="s">
+      <c r="AU3" t="s">
         <v>118</v>
       </c>
-      <c r="AV3" s="2" t="s">
+      <c r="AV3" t="s">
         <v>120</v>
       </c>
-      <c r="AW3" s="2" t="s">
+      <c r="AW3" t="s">
         <v>123</v>
       </c>
-      <c r="AX3" s="2" t="s">
+      <c r="AX3" t="s">
         <v>119</v>
       </c>
-      <c r="AY3" s="2" t="s">
+      <c r="AY3" t="s">
         <v>124</v>
       </c>
-      <c r="AZ3" s="2" t="s">
+      <c r="AZ3" t="s">
         <v>118</v>
       </c>
-      <c r="BA3" s="2" t="s">
+      <c r="BA3" t="s">
         <v>118</v>
       </c>
-      <c r="BB3" s="2" t="s">
+      <c r="BB3" t="s">
         <v>119</v>
       </c>
-      <c r="BC3" s="2" t="s">
+      <c r="BC3" t="s">
         <v>125</v>
       </c>
-      <c r="BD3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BH3" s="2" t="s">
+      <c r="BD3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" t="s">
         <v>126</v>
       </c>
-      <c r="BI3" s="2" t="s">
+      <c r="BI3" t="s">
         <v>120</v>
       </c>
-      <c r="BJ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BK3" s="2" t="s">
+      <c r="BJ3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK3" t="s">
         <v>122</v>
       </c>
-      <c r="BL3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BM3" s="2" t="s">
+      <c r="BL3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM3" t="s">
         <v>127</v>
       </c>
-      <c r="BN3" s="2" t="s">
+      <c r="BN3" t="s">
         <v>122</v>
       </c>
-      <c r="BO3" s="2" t="s">
+      <c r="BO3" t="s">
         <v>122</v>
       </c>
-      <c r="BP3" s="2" t="s">
+      <c r="BP3" t="s">
         <v>122</v>
       </c>
-      <c r="BQ3" s="2" t="s">
+      <c r="BQ3" t="s">
         <v>122</v>
       </c>
-      <c r="BR3" s="2" t="s">
+      <c r="BR3" t="s">
         <v>122</v>
       </c>
-      <c r="BS3" s="2" t="s">
+      <c r="BS3" t="s">
         <v>122</v>
       </c>
-      <c r="BT3" s="2" t="s">
+      <c r="BT3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
+      <c r="F4" t="s">
         <v>129</v>
       </c>
-      <c r="G4" s="2">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2">
-        <v>2</v>
-      </c>
-      <c r="J4" s="2">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
         <v>90</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4">
         <v>1500</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4">
         <v>200</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4">
         <v>553</v>
       </c>
-      <c r="N4" s="2">
+      <c r="N4">
         <v>42</v>
       </c>
-      <c r="O4" s="2">
+      <c r="O4">
         <v>104</v>
       </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2">
+      <c r="Q4">
         <v>15</v>
       </c>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2">
+      <c r="S4">
         <v>14</v>
       </c>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2">
+      <c r="U4">
         <v>0.5</v>
       </c>
-      <c r="V4" s="2">
+      <c r="V4">
         <v>70</v>
       </c>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2">
+      <c r="Y4">
         <v>0.05</v>
       </c>
-      <c r="Z4" s="2">
+      <c r="Z4">
         <v>1.6</v>
       </c>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="2"/>
-      <c r="AE4" s="2"/>
-      <c r="AF4" s="2"/>
-      <c r="AG4" s="2"/>
-      <c r="AH4" s="2"/>
-      <c r="AI4" s="2" t="s">
+      <c r="AC4">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="s">
         <v>4</v>
       </c>
-      <c r="AJ4" s="2" t="s">
+      <c r="AJ4" t="s">
         <v>130</v>
       </c>
-      <c r="AK4" s="2" t="s">
+      <c r="AK4" t="s">
         <v>131</v>
       </c>
-      <c r="AL4" s="2" t="s">
+      <c r="AL4" t="s">
         <v>132</v>
       </c>
-      <c r="AM4" s="2"/>
-      <c r="AN4" s="2"/>
-      <c r="AO4" s="2" t="s">
+      <c r="AO4" t="s">
         <v>133</v>
       </c>
-      <c r="AP4" s="2">
-        <v>1</v>
-      </c>
-      <c r="AQ4" s="2">
+      <c r="AP4">
+        <v>1</v>
+      </c>
+      <c r="AQ4">
         <v>0.5</v>
       </c>
-      <c r="AR4" s="2"/>
-      <c r="AS4" s="2"/>
-      <c r="AT4" s="2"/>
-      <c r="AU4" s="2"/>
-      <c r="AV4" s="2"/>
-      <c r="AW4" s="2"/>
-      <c r="AX4" s="2">
+      <c r="AX4">
         <v>0.25</v>
       </c>
-      <c r="AY4" s="2"/>
-      <c r="AZ4" s="2"/>
-      <c r="BA4" s="2"/>
-      <c r="BB4" s="2"/>
-      <c r="BC4" s="2" t="s">
+      <c r="BC4" t="s">
         <v>134</v>
       </c>
-      <c r="BD4" s="2" t="s">
+      <c r="BD4" t="s">
         <v>135</v>
       </c>
-      <c r="BE4" s="2" t="s">
+      <c r="BE4" t="s">
         <v>136</v>
       </c>
-      <c r="BF4" s="2" t="s">
+      <c r="BF4" t="s">
         <v>137</v>
       </c>
-      <c r="BG4" s="2" t="s">
+      <c r="BG4" t="s">
         <v>138</v>
       </c>
-      <c r="BH4" s="2" t="s">
+      <c r="BH4" t="s">
         <v>139</v>
       </c>
-      <c r="BI4" s="2">
+      <c r="BI4">
         <v>6</v>
       </c>
-      <c r="BJ4" s="2" t="s">
+      <c r="BJ4" t="s">
         <v>140</v>
       </c>
-      <c r="BK4" s="2" t="s">
+      <c r="BK4" t="s">
         <v>141</v>
       </c>
-      <c r="BL4" s="2"/>
-      <c r="BM4" s="2"/>
-      <c r="BN4" s="2" t="s">
+      <c r="BN4" t="s">
         <v>142</v>
       </c>
-      <c r="BO4" s="2" t="s">
+      <c r="BO4" t="s">
         <v>143</v>
       </c>
-      <c r="BP4" s="2"/>
-      <c r="BQ4" s="2" t="s">
+      <c r="BQ4" t="s">
         <v>144</v>
       </c>
-      <c r="BR4" s="2" t="s">
+      <c r="BR4" t="s">
         <v>144</v>
       </c>
-      <c r="BS4" s="2"/>
-      <c r="BT4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-      <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="2"/>
-      <c r="AA5" s="2"/>
-      <c r="AB5" s="2"/>
-      <c r="AC5" s="2"/>
-      <c r="AD5" s="2"/>
-      <c r="AE5" s="2"/>
-      <c r="AF5" s="2"/>
-      <c r="AG5" s="2"/>
-      <c r="AH5" s="2"/>
-      <c r="AI5" s="2"/>
-      <c r="AJ5" s="2"/>
-      <c r="AK5" s="2"/>
-      <c r="AL5" s="2"/>
-      <c r="AM5" s="2"/>
-      <c r="AN5" s="2"/>
-      <c r="AO5" s="2"/>
-      <c r="AP5" s="2"/>
-      <c r="AQ5" s="2"/>
-      <c r="AR5" s="2"/>
-      <c r="AS5" s="2"/>
-      <c r="AT5" s="2"/>
-      <c r="AU5" s="2"/>
-      <c r="AV5" s="2"/>
-      <c r="AW5" s="2"/>
-      <c r="AX5" s="2"/>
-      <c r="AY5" s="2"/>
-      <c r="AZ5" s="2"/>
-      <c r="BA5" s="2"/>
-      <c r="BB5" s="2"/>
-      <c r="BC5" s="2"/>
-      <c r="BD5" s="2"/>
-      <c r="BE5" s="2"/>
-      <c r="BF5" s="2"/>
-      <c r="BG5" s="2"/>
-      <c r="BH5" s="2"/>
-      <c r="BI5" s="2"/>
-      <c r="BJ5" s="2"/>
-      <c r="BK5" s="2"/>
-      <c r="BL5" s="2"/>
-      <c r="BM5" s="2"/>
-      <c r="BN5" s="2"/>
-      <c r="BO5" s="2"/>
-      <c r="BP5" s="2"/>
-      <c r="BQ5" s="2"/>
-      <c r="BR5" s="2"/>
-      <c r="BS5" s="2"/>
-      <c r="BT5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
-      <c r="Z6" s="2"/>
-      <c r="AA6" s="2"/>
-      <c r="AB6" s="2"/>
-      <c r="AC6" s="2"/>
-      <c r="AD6" s="2"/>
-      <c r="AE6" s="2"/>
-      <c r="AF6" s="2"/>
-      <c r="AG6" s="2"/>
-      <c r="AH6" s="2"/>
-      <c r="AI6" s="2"/>
-      <c r="AJ6" s="2"/>
-      <c r="AK6" s="2"/>
-      <c r="AL6" s="2"/>
-      <c r="AM6" s="2"/>
-      <c r="AN6" s="2"/>
-      <c r="AO6" s="2"/>
-      <c r="AP6" s="2"/>
-      <c r="AQ6" s="2"/>
-      <c r="AR6" s="2"/>
-      <c r="AS6" s="2"/>
-      <c r="AT6" s="2"/>
-      <c r="AU6" s="2"/>
-      <c r="AV6" s="2"/>
-      <c r="AW6" s="2"/>
-      <c r="AX6" s="2"/>
-      <c r="AY6" s="2"/>
-      <c r="AZ6" s="2"/>
-      <c r="BA6" s="2"/>
-      <c r="BB6" s="2"/>
-      <c r="BC6" s="2"/>
-      <c r="BD6" s="2"/>
-      <c r="BE6" s="2"/>
-      <c r="BF6" s="2"/>
-      <c r="BG6" s="2"/>
-      <c r="BH6" s="2"/>
-      <c r="BI6" s="2"/>
-      <c r="BJ6" s="2"/>
-      <c r="BK6" s="2"/>
-      <c r="BL6" s="2"/>
-      <c r="BM6" s="2"/>
-      <c r="BN6" s="2"/>
-      <c r="BO6" s="2"/>
-      <c r="BP6" s="2"/>
-      <c r="BQ6" s="2"/>
-      <c r="BR6" s="2"/>
-      <c r="BS6" s="2"/>
-      <c r="BT6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
-      <c r="AA7" s="2"/>
-      <c r="AB7" s="2"/>
-      <c r="AC7" s="2"/>
-      <c r="AD7" s="2"/>
-      <c r="AE7" s="2"/>
-      <c r="AF7" s="2"/>
-      <c r="AG7" s="2"/>
-      <c r="AH7" s="2"/>
-      <c r="AI7" s="2"/>
-      <c r="AJ7" s="2"/>
-      <c r="AK7" s="2"/>
-      <c r="AL7" s="2"/>
-      <c r="AM7" s="2"/>
-      <c r="AN7" s="2"/>
-      <c r="AO7" s="2"/>
-      <c r="AP7" s="2"/>
-      <c r="AQ7" s="2"/>
-      <c r="AR7" s="2"/>
-      <c r="AS7" s="2"/>
-      <c r="AT7" s="2"/>
-      <c r="AU7" s="2"/>
-      <c r="AV7" s="2"/>
-      <c r="AW7" s="2"/>
-      <c r="AX7" s="2"/>
-      <c r="AY7" s="2"/>
-      <c r="AZ7" s="2"/>
-      <c r="BA7" s="2"/>
-      <c r="BB7" s="2"/>
-      <c r="BC7" s="2"/>
-      <c r="BD7" s="2"/>
-      <c r="BE7" s="2"/>
-      <c r="BF7" s="2"/>
-      <c r="BG7" s="2"/>
-      <c r="BH7" s="2"/>
-      <c r="BI7" s="2"/>
-      <c r="BJ7" s="2"/>
-      <c r="BK7" s="2"/>
-      <c r="BL7" s="2"/>
-      <c r="BM7" s="2"/>
-      <c r="BN7" s="2"/>
-      <c r="BO7" s="2"/>
-      <c r="BP7" s="2"/>
-      <c r="BQ7" s="2"/>
-      <c r="BR7" s="2"/>
-      <c r="BS7" s="2"/>
-      <c r="BT7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
+      <c r="BT4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>145</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
+      <c r="F8" t="s">
         <v>146</v>
       </c>
-      <c r="G8" s="2">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2">
-        <v>2</v>
-      </c>
-      <c r="J8" s="2">
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
         <v>90</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8">
         <v>100</v>
       </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2">
+      <c r="M8">
         <v>553</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8">
         <v>42</v>
       </c>
-      <c r="O8" s="2">
+      <c r="O8">
         <v>100</v>
       </c>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2">
+      <c r="Q8">
         <v>0</v>
       </c>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2">
+      <c r="S8">
         <v>5</v>
       </c>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2">
+      <c r="U8">
         <v>0</v>
       </c>
-      <c r="V8" s="2">
+      <c r="V8">
         <v>25</v>
       </c>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
-      <c r="Y8" s="2">
+      <c r="Y8">
         <v>0.05</v>
       </c>
-      <c r="Z8" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="2"/>
-      <c r="AB8" s="2"/>
-      <c r="AC8" s="2">
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
         <v>0</v>
       </c>
-      <c r="AD8" s="2"/>
-      <c r="AE8" s="2"/>
-      <c r="AF8" s="2"/>
-      <c r="AG8" s="2">
+      <c r="AG8">
         <v>-1</v>
       </c>
-      <c r="AH8" s="2"/>
-      <c r="AI8" s="2" t="s">
+      <c r="AI8" t="s">
         <v>145</v>
       </c>
-      <c r="AJ8" s="2" t="s">
+      <c r="AJ8" t="s">
         <v>130</v>
       </c>
-      <c r="AK8" s="2" t="s">
+      <c r="AK8" t="s">
         <v>147</v>
       </c>
-      <c r="AL8" s="2"/>
-      <c r="AM8" s="2">
+      <c r="AM8">
         <v>3</v>
       </c>
-      <c r="AN8" s="2">
+      <c r="AN8">
         <v>-0.5</v>
       </c>
-      <c r="AO8" s="2" t="s">
+      <c r="AO8" t="s">
         <v>148</v>
       </c>
-      <c r="AP8" s="2">
+      <c r="AP8">
         <v>0</v>
       </c>
-      <c r="AQ8" s="2">
+      <c r="AQ8">
         <v>0</v>
       </c>
-      <c r="AR8" s="2"/>
-      <c r="AS8" s="2"/>
-      <c r="AT8" s="2"/>
-      <c r="AU8" s="2"/>
-      <c r="AV8" s="2"/>
-      <c r="AW8" s="2"/>
-      <c r="AX8" s="2">
+      <c r="AX8">
         <v>0</v>
       </c>
-      <c r="AY8" s="2"/>
-      <c r="AZ8" s="2"/>
-      <c r="BA8" s="2">
-        <v>1</v>
-      </c>
-      <c r="BB8" s="2"/>
-      <c r="BC8" s="2" t="s">
+      <c r="BA8">
+        <v>1</v>
+      </c>
+      <c r="BC8" t="s">
         <v>149</v>
       </c>
-      <c r="BD8" s="2"/>
-      <c r="BE8" s="2" t="s">
+      <c r="BE8" t="s">
         <v>136</v>
       </c>
-      <c r="BF8" s="2" t="s">
+      <c r="BF8" t="s">
         <v>150</v>
       </c>
-      <c r="BG8" s="2" t="s">
+      <c r="BG8" t="s">
         <v>151</v>
       </c>
-      <c r="BH8" s="2" t="s">
+      <c r="BH8" t="s">
         <v>139</v>
       </c>
-      <c r="BI8" s="2">
+      <c r="BI8">
         <v>5</v>
       </c>
-      <c r="BJ8" s="2" t="s">
+      <c r="BJ8" t="s">
         <v>152</v>
       </c>
-      <c r="BK8" s="2"/>
-      <c r="BL8" s="2"/>
-      <c r="BM8" s="2"/>
-      <c r="BN8" s="2" t="s">
+      <c r="BN8" t="s">
         <v>142</v>
       </c>
-      <c r="BO8" s="2" t="s">
+      <c r="BO8" t="s">
         <v>153</v>
       </c>
-      <c r="BP8" s="2"/>
-      <c r="BQ8" s="2" t="s">
+      <c r="BQ8" t="s">
         <v>154</v>
       </c>
-      <c r="BR8" s="2" t="s">
+      <c r="BR8" t="s">
         <v>154</v>
       </c>
-      <c r="BS8" s="2"/>
-      <c r="BT8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
+      <c r="BT8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>155</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>128</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
+      <c r="F9" t="s">
         <v>146</v>
       </c>
-      <c r="G9" s="2">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2">
-        <v>2</v>
-      </c>
-      <c r="J9" s="2">
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
         <v>90</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9">
         <v>100</v>
       </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2">
+      <c r="M9">
         <v>553</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9">
         <v>42</v>
       </c>
-      <c r="O9" s="2">
+      <c r="O9">
         <v>100</v>
       </c>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2">
+      <c r="Q9">
         <v>0</v>
       </c>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2">
+      <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2">
+      <c r="U9">
         <v>0</v>
       </c>
-      <c r="V9" s="2">
+      <c r="V9">
         <v>10</v>
       </c>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2">
+      <c r="Y9">
         <v>0.05</v>
       </c>
-      <c r="Z9" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="2"/>
-      <c r="AB9" s="2"/>
-      <c r="AC9" s="2">
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AC9">
         <v>0</v>
       </c>
-      <c r="AD9" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE9" s="2"/>
-      <c r="AF9" s="2"/>
-      <c r="AG9" s="2">
+      <c r="AD9">
+        <v>1</v>
+      </c>
+      <c r="AG9">
         <v>-1</v>
       </c>
-      <c r="AH9" s="2"/>
-      <c r="AI9" s="2" t="s">
+      <c r="AI9" t="s">
         <v>155</v>
       </c>
-      <c r="AJ9" s="2" t="s">
+      <c r="AJ9" t="s">
         <v>130</v>
       </c>
-      <c r="AK9" s="2" t="s">
+      <c r="AK9" t="s">
         <v>156</v>
       </c>
-      <c r="AL9" s="2"/>
-      <c r="AM9" s="2">
+      <c r="AM9">
         <v>3</v>
       </c>
-      <c r="AN9" s="2">
+      <c r="AN9">
         <v>-0.5</v>
       </c>
-      <c r="AO9" s="2" t="s">
+      <c r="AO9" t="s">
         <v>148</v>
       </c>
-      <c r="AP9" s="2">
+      <c r="AP9">
         <v>0</v>
       </c>
-      <c r="AQ9" s="2">
+      <c r="AQ9">
         <v>0</v>
       </c>
-      <c r="AR9" s="2"/>
-      <c r="AS9" s="2"/>
-      <c r="AT9" s="2"/>
-      <c r="AU9" s="2"/>
-      <c r="AV9" s="2"/>
-      <c r="AW9" s="2"/>
-      <c r="AX9" s="2">
+      <c r="AX9">
         <v>0</v>
       </c>
-      <c r="AY9" s="2"/>
-      <c r="AZ9" s="2"/>
-      <c r="BA9" s="2">
-        <v>1</v>
-      </c>
-      <c r="BB9" s="2"/>
-      <c r="BC9" s="2" t="s">
+      <c r="BA9">
+        <v>1</v>
+      </c>
+      <c r="BC9" t="s">
         <v>149</v>
       </c>
-      <c r="BD9" s="2"/>
-      <c r="BE9" s="2" t="s">
+      <c r="BE9" t="s">
         <v>136</v>
       </c>
-      <c r="BF9" s="2" t="s">
+      <c r="BF9" t="s">
         <v>150</v>
       </c>
-      <c r="BG9" s="2" t="s">
+      <c r="BG9" t="s">
         <v>151</v>
       </c>
-      <c r="BH9" s="2" t="s">
+      <c r="BH9" t="s">
         <v>139</v>
       </c>
-      <c r="BI9" s="2">
+      <c r="BI9">
         <v>5</v>
       </c>
-      <c r="BJ9" s="2" t="s">
+      <c r="BJ9" t="s">
         <v>152</v>
       </c>
-      <c r="BK9" s="2"/>
-      <c r="BL9" s="2"/>
-      <c r="BM9" s="2"/>
-      <c r="BN9" s="2" t="s">
+      <c r="BN9" t="s">
         <v>142</v>
       </c>
-      <c r="BO9" s="2" t="s">
+      <c r="BO9" t="s">
         <v>153</v>
       </c>
-      <c r="BP9" s="2"/>
-      <c r="BQ9" s="2" t="s">
+      <c r="BQ9" t="s">
         <v>154</v>
       </c>
-      <c r="BR9" s="2" t="s">
+      <c r="BR9" t="s">
         <v>154</v>
       </c>
-      <c r="BS9" s="2"/>
-      <c r="BT9" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
+      <c r="BT9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>157</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>158</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" t="s">
         <v>158</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" t="s">
         <v>159</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10">
         <v>0.01</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2">
-        <v>2</v>
-      </c>
-      <c r="J10" s="2">
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
         <v>90</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10">
         <v>100</v>
       </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2">
+      <c r="M10">
         <v>553</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10">
         <v>42</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O10">
         <v>100</v>
       </c>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2">
+      <c r="Q10">
         <v>0</v>
       </c>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2">
+      <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2">
+      <c r="U10">
         <v>0</v>
       </c>
-      <c r="V10" s="2">
+      <c r="V10">
         <v>10</v>
       </c>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2">
+      <c r="Y10">
         <v>0.05</v>
       </c>
-      <c r="Z10" s="2">
+      <c r="Z10">
         <v>999</v>
       </c>
-      <c r="AA10" s="2"/>
-      <c r="AB10" s="2"/>
-      <c r="AC10" s="2">
+      <c r="AC10">
         <v>0</v>
       </c>
-      <c r="AD10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="2"/>
-      <c r="AF10" s="2"/>
-      <c r="AG10" s="2">
+      <c r="AD10">
+        <v>1</v>
+      </c>
+      <c r="AG10">
         <v>-1</v>
       </c>
-      <c r="AH10" s="2"/>
-      <c r="AI10" s="2" t="s">
+      <c r="AI10" t="s">
         <v>157</v>
       </c>
-      <c r="AJ10" s="2" t="s">
+      <c r="AJ10" t="s">
         <v>130</v>
       </c>
-      <c r="AK10" s="2" t="s">
+      <c r="AK10" t="s">
         <v>160</v>
       </c>
-      <c r="AL10" s="2"/>
-      <c r="AM10" s="2">
+      <c r="AM10">
         <v>3</v>
       </c>
-      <c r="AN10" s="2">
+      <c r="AN10">
         <v>-0.5</v>
       </c>
-      <c r="AO10" s="2" t="s">
+      <c r="AO10" t="s">
         <v>148</v>
       </c>
-      <c r="AP10" s="2">
+      <c r="AP10">
         <v>0</v>
       </c>
-      <c r="AQ10" s="2">
+      <c r="AQ10">
         <v>0</v>
       </c>
-      <c r="AR10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS10" s="2"/>
-      <c r="AT10" s="2"/>
-      <c r="AU10" s="2"/>
-      <c r="AV10" s="2"/>
-      <c r="AW10" s="2"/>
-      <c r="AX10" s="2">
+      <c r="AR10">
+        <v>1</v>
+      </c>
+      <c r="AX10">
         <v>0</v>
       </c>
-      <c r="AY10" s="2"/>
-      <c r="AZ10" s="2"/>
-      <c r="BA10" s="2">
-        <v>1</v>
-      </c>
-      <c r="BB10" s="2"/>
-      <c r="BC10" s="2" t="s">
+      <c r="BA10">
+        <v>1</v>
+      </c>
+      <c r="BC10" t="s">
         <v>149</v>
       </c>
-      <c r="BD10" s="2"/>
-      <c r="BE10" s="2" t="s">
+      <c r="BE10" t="s">
         <v>136</v>
       </c>
-      <c r="BF10" s="2" t="s">
+      <c r="BF10" t="s">
         <v>161</v>
       </c>
-      <c r="BG10" s="2" t="s">
+      <c r="BG10" t="s">
         <v>158</v>
       </c>
-      <c r="BH10" s="2" t="s">
+      <c r="BH10" t="s">
         <v>139</v>
       </c>
-      <c r="BI10" s="2">
+      <c r="BI10">
         <v>5</v>
       </c>
-      <c r="BJ10" s="2" t="s">
+      <c r="BJ10" t="s">
         <v>152</v>
       </c>
-      <c r="BK10" s="2"/>
-      <c r="BL10" s="2"/>
-      <c r="BM10" s="2"/>
-      <c r="BN10" s="2" t="s">
+      <c r="BN10" t="s">
         <v>142</v>
       </c>
-      <c r="BO10" s="2" t="s">
+      <c r="BO10" t="s">
         <v>143</v>
       </c>
-      <c r="BP10" s="2"/>
-      <c r="BQ10" s="2" t="s">
+      <c r="BQ10" t="s">
         <v>144</v>
       </c>
-      <c r="BR10" s="2" t="s">
+      <c r="BR10" t="s">
         <v>144</v>
       </c>
-      <c r="BS10" s="2"/>
-      <c r="BT10" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2"/>
-      <c r="AA11" s="2"/>
-      <c r="AB11" s="2"/>
-      <c r="AC11" s="2"/>
-      <c r="AD11" s="2"/>
-      <c r="AE11" s="2"/>
-      <c r="AF11" s="2"/>
-      <c r="AG11" s="2"/>
-      <c r="AH11" s="2"/>
-      <c r="AI11" s="2"/>
-      <c r="AJ11" s="2"/>
-      <c r="AK11" s="2"/>
-      <c r="AL11" s="2"/>
-      <c r="AM11" s="2"/>
-      <c r="AN11" s="2"/>
-      <c r="AO11" s="2"/>
-      <c r="AP11" s="2"/>
-      <c r="AQ11" s="2"/>
-      <c r="AR11" s="2"/>
-      <c r="AS11" s="2"/>
-      <c r="AT11" s="2"/>
-      <c r="AU11" s="2"/>
-      <c r="AV11" s="2"/>
-      <c r="AW11" s="2"/>
-      <c r="AX11" s="2"/>
-      <c r="AY11" s="2"/>
-      <c r="AZ11" s="2"/>
-      <c r="BA11" s="2"/>
-      <c r="BB11" s="2"/>
-      <c r="BC11" s="2"/>
-      <c r="BD11" s="2"/>
-      <c r="BE11" s="2"/>
-      <c r="BF11" s="2"/>
-      <c r="BG11" s="2"/>
-      <c r="BH11" s="2"/>
-      <c r="BI11" s="2"/>
-      <c r="BJ11" s="2"/>
-      <c r="BK11" s="2"/>
-      <c r="BL11" s="2"/>
-      <c r="BM11" s="2"/>
-      <c r="BN11" s="2"/>
-      <c r="BO11" s="2"/>
-      <c r="BP11" s="2"/>
-      <c r="BQ11" s="2"/>
-      <c r="BR11" s="2"/>
-      <c r="BS11" s="2"/>
-      <c r="BT11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
+      <c r="BT10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>162</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" t="s">
         <v>128</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="s">
+      <c r="D12" t="s">
         <v>158</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" t="s">
         <v>158</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" t="s">
         <v>159</v>
       </c>
-      <c r="G12" s="2">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2">
-        <v>2</v>
-      </c>
-      <c r="J12" s="2">
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
         <v>90</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12">
         <v>3</v>
       </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2">
+      <c r="M12">
         <v>1000</v>
       </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2">
+      <c r="O12">
         <v>100</v>
       </c>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2">
+      <c r="Q12">
         <v>0</v>
       </c>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2">
+      <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2">
+      <c r="U12">
         <v>0</v>
       </c>
-      <c r="V12" s="2">
+      <c r="V12">
         <v>10</v>
       </c>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
-      <c r="Y12" s="2">
+      <c r="Y12">
         <v>0.05</v>
       </c>
-      <c r="Z12" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="2"/>
-      <c r="AB12" s="2"/>
-      <c r="AC12" s="2">
+      <c r="Z12">
+        <v>1</v>
+      </c>
+      <c r="AC12">
         <v>0</v>
       </c>
-      <c r="AD12" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE12" s="2"/>
-      <c r="AF12" s="2"/>
-      <c r="AG12" s="2"/>
-      <c r="AH12" s="2"/>
-      <c r="AI12" s="2" t="s">
+      <c r="AD12">
+        <v>1</v>
+      </c>
+      <c r="AI12" t="s">
         <v>163</v>
       </c>
-      <c r="AJ12" s="2" t="s">
+      <c r="AJ12" t="s">
         <v>130</v>
       </c>
-      <c r="AK12" s="2"/>
-      <c r="AL12" s="2"/>
-      <c r="AM12" s="2">
+      <c r="AM12">
         <v>3</v>
       </c>
-      <c r="AN12" s="2">
+      <c r="AN12">
         <v>-0.5</v>
       </c>
-      <c r="AO12" s="2" t="s">
+      <c r="AO12" t="s">
         <v>148</v>
       </c>
-      <c r="AP12" s="2">
+      <c r="AP12">
         <v>99</v>
       </c>
-      <c r="AQ12" s="2">
+      <c r="AQ12">
         <v>0</v>
       </c>
-      <c r="AR12" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS12" s="2"/>
-      <c r="AT12" s="2"/>
-      <c r="AU12" s="2"/>
-      <c r="AV12" s="2"/>
-      <c r="AW12" s="2"/>
-      <c r="AX12" s="2">
+      <c r="AR12">
+        <v>1</v>
+      </c>
+      <c r="AX12">
         <v>0</v>
       </c>
-      <c r="AY12" s="2"/>
-      <c r="AZ12" s="2"/>
-      <c r="BA12" s="2">
-        <v>1</v>
-      </c>
-      <c r="BB12" s="2"/>
-      <c r="BC12" s="2" t="s">
+      <c r="BA12">
+        <v>1</v>
+      </c>
+      <c r="BC12" t="s">
         <v>149</v>
       </c>
-      <c r="BD12" s="2"/>
-      <c r="BE12" s="2" t="s">
+      <c r="BE12" t="s">
         <v>136</v>
       </c>
-      <c r="BF12" s="2" t="s">
+      <c r="BF12" t="s">
         <v>161</v>
       </c>
-      <c r="BG12" s="2" t="s">
+      <c r="BG12" t="s">
         <v>158</v>
       </c>
-      <c r="BH12" s="2" t="s">
+      <c r="BH12" t="s">
         <v>139</v>
       </c>
-      <c r="BI12" s="2">
+      <c r="BI12">
         <v>5</v>
       </c>
-      <c r="BJ12" s="2" t="s">
+      <c r="BJ12" t="s">
         <v>152</v>
       </c>
-      <c r="BK12" s="2"/>
-      <c r="BL12" s="2"/>
-      <c r="BM12" s="2"/>
-      <c r="BN12" s="2" t="s">
+      <c r="BN12" t="s">
         <v>142</v>
       </c>
-      <c r="BO12" s="2" t="s">
+      <c r="BO12" t="s">
         <v>143</v>
       </c>
-      <c r="BP12" s="2"/>
-      <c r="BQ12" s="2" t="s">
+      <c r="BQ12" t="s">
         <v>144</v>
       </c>
-      <c r="BR12" s="2" t="s">
+      <c r="BR12" t="s">
         <v>144</v>
       </c>
-      <c r="BS12" s="2"/>
-      <c r="BT12" s="2">
+      <c r="BT12">
         <v>1</v>
       </c>
     </row>
@@ -4183,7 +3685,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -4193,2507 +3694,2510 @@
   <dimension ref="A1:DI569"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="7.75" customWidth="1" style="2"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1" style="2"/>
-    <col min="9" max="9" width="7.33203125" customWidth="1" style="2"/>
-    <col min="10" max="10" width="15.75" customWidth="1" style="2"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="11.75" customWidth="1" style="2"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1" style="2"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="21.5" customWidth="1" style="2"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1" style="2"/>
-    <col min="22" max="22" width="17.75" customWidth="1" style="2"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1" style="2"/>
-    <col min="24" max="24" width="18.5" customWidth="1" style="2"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1" style="2"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1" style="2"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1" style="2"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1" style="2"/>
-    <col min="32" max="32" width="13.75" customWidth="1" style="2"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1" style="2"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1" style="2"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="12.5" customWidth="1" style="2"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1" style="2"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="15" customWidth="1" style="2"/>
-    <col min="41" max="41" width="13.25" customWidth="1" style="2"/>
-    <col min="42" max="45" width="11.83203125" customWidth="1" style="2"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1" style="2"/>
-    <col min="47" max="47" width="12.25" customWidth="1" style="2"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1" style="2"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1" style="2"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1" style="2"/>
-    <col min="51" max="51" width="9" customWidth="1" style="2"/>
-    <col min="52" max="52" width="7" customWidth="1" style="2"/>
-    <col min="53" max="53" width="11.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="19.75" customWidth="1" style="2"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1" style="2"/>
-    <col min="56" max="56" width="8.5" customWidth="1" style="2"/>
-    <col min="57" max="57" width="13.5" customWidth="1" style="2"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1" style="2"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8.25" customWidth="1" style="2"/>
-    <col min="61" max="67" width="8.33203125" customWidth="1" style="2"/>
-    <col min="68" max="70" width="11.25" customWidth="1" style="2"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1" style="2"/>
-    <col min="72" max="73" width="8" customWidth="1" style="2"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1" style="2"/>
-    <col min="75" max="76" width="8.5" customWidth="1" style="2"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1" style="2"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1" style="2"/>
-    <col min="80" max="80" width="13.5" customWidth="1" style="2"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1" style="2"/>
-    <col min="82" max="82" width="15.75" customWidth="1" style="2"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1" style="2"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1" style="2"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1" style="2"/>
-    <col min="86" max="86" width="9" customWidth="1" style="2"/>
-    <col min="87" max="87" width="16" customWidth="1" style="2"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1" style="2"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1" style="2"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1" style="2"/>
-    <col min="92" max="92" width="21.25" customWidth="1" style="2"/>
-    <col min="93" max="93" width="9.5" customWidth="1" style="2"/>
-    <col min="94" max="98" width="9" customWidth="1" style="2"/>
-    <col min="99" max="99" width="14" customWidth="1" style="2"/>
-    <col min="100" max="100" width="8" customWidth="1" style="2"/>
-    <col min="101" max="101" width="9" customWidth="1" style="2"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1" style="2"/>
-    <col min="103" max="103" width="13.75" customWidth="1" style="2"/>
-    <col min="104" max="104" width="9.5" customWidth="1" style="2"/>
-    <col min="105" max="106" width="9" customWidth="1" style="2"/>
-    <col min="107" max="108" width="9.5" customWidth="1" style="2"/>
-    <col min="109" max="109" width="9" customWidth="1" style="2"/>
-    <col min="110" max="110" width="15.5" customWidth="1" style="2"/>
-    <col min="111" max="111" width="9" customWidth="1" style="2"/>
-    <col min="112" max="113" width="9.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1"/>
+    <col min="3" max="3" width="7.75" customWidth="1"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1"/>
+    <col min="14" max="14" width="11.75" customWidth="1"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1"/>
+    <col min="17" max="17" width="21.5" customWidth="1"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1"/>
+    <col min="22" max="22" width="17.75" customWidth="1"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1"/>
+    <col min="24" max="24" width="18.5" customWidth="1"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1"/>
+    <col min="32" max="32" width="13.75" customWidth="1"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1"/>
+    <col min="36" max="36" width="12.5" customWidth="1"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1"/>
+    <col min="40" max="40" width="15" customWidth="1"/>
+    <col min="41" max="41" width="13.25" customWidth="1"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1"/>
+    <col min="47" max="47" width="12.25" customWidth="1"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1"/>
+    <col min="51" max="51" width="9" customWidth="1"/>
+    <col min="52" max="52" width="7" customWidth="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1"/>
+    <col min="54" max="54" width="19.75" customWidth="1"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1"/>
+    <col min="56" max="56" width="8.5" customWidth="1"/>
+    <col min="57" max="57" width="13.5" customWidth="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1"/>
+    <col min="60" max="60" width="8.25" customWidth="1"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1"/>
+    <col min="68" max="70" width="11.25" customWidth="1"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1"/>
+    <col min="72" max="73" width="8" customWidth="1"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1"/>
+    <col min="75" max="76" width="8.5" customWidth="1"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1"/>
+    <col min="80" max="80" width="13.5" customWidth="1"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1"/>
+    <col min="82" max="82" width="15.75" customWidth="1"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1"/>
+    <col min="86" max="86" width="9" customWidth="1"/>
+    <col min="87" max="87" width="16" customWidth="1"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1"/>
+    <col min="92" max="92" width="21.25" customWidth="1"/>
+    <col min="93" max="93" width="9.5" customWidth="1"/>
+    <col min="94" max="98" width="9" customWidth="1"/>
+    <col min="99" max="99" width="14" customWidth="1"/>
+    <col min="100" max="100" width="8" customWidth="1"/>
+    <col min="101" max="101" width="9" customWidth="1"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1"/>
+    <col min="103" max="103" width="13.75" customWidth="1"/>
+    <col min="104" max="104" width="9.5" customWidth="1"/>
+    <col min="105" max="106" width="9" customWidth="1"/>
+    <col min="107" max="108" width="9.5" customWidth="1"/>
+    <col min="109" max="109" width="9" customWidth="1"/>
+    <col min="110" max="110" width="15.5" customWidth="1"/>
+    <col min="111" max="111" width="9" customWidth="1"/>
+    <col min="112" max="113" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
         <v>164</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>165</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>166</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>167</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>168</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>169</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>170</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>171</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>172</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" t="s">
         <v>173</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" t="s">
         <v>174</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" t="s">
         <v>175</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" t="s">
         <v>176</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" t="s">
         <v>177</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" t="s">
         <v>178</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" t="s">
         <v>179</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" t="s">
         <v>180</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" t="s">
         <v>181</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" t="s">
         <v>181</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" t="s">
         <v>182</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" t="s">
         <v>183</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" t="s">
         <v>184</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" t="s">
         <v>185</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" t="s">
         <v>186</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" t="s">
         <v>187</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" t="s">
         <v>188</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" t="s">
         <v>189</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" t="s">
         <v>190</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" t="s">
         <v>191</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" t="s">
         <v>192</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" t="s">
         <v>193</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" t="s">
         <v>194</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AI1" t="s">
         <v>195</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" t="s">
         <v>196</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" t="s">
         <v>197</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" t="s">
         <v>198</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" t="s">
         <v>199</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" t="s">
         <v>200</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AO1" t="s">
         <v>201</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" t="s">
         <v>202</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" t="s">
         <v>203</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AR1" t="s">
         <v>204</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AS1" t="s">
         <v>205</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AT1" t="s">
         <v>206</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AU1" t="s">
         <v>207</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AV1" t="s">
         <v>208</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AW1" t="s">
         <v>209</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AX1" t="s">
         <v>210</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AY1" t="s">
         <v>211</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AZ1" t="s">
         <v>212</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" t="s">
         <v>213</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BB1" t="s">
         <v>214</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BC1" t="s">
         <v>215</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BD1" t="s">
         <v>216</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BE1" t="s">
         <v>217</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BF1" t="s">
         <v>218</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BG1" t="s">
         <v>219</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BH1" t="s">
         <v>220</v>
       </c>
-      <c r="BJ1" s="2" t="s">
+      <c r="BJ1" t="s">
         <v>220</v>
       </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BK1" t="s">
         <v>221</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BL1" t="s">
         <v>222</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BM1" t="s">
         <v>223</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BN1" t="s">
         <v>224</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BO1" t="s">
         <v>225</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BP1" t="s">
         <v>226</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BQ1" t="s">
         <v>227</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BR1" t="s">
         <v>228</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BS1" t="s">
         <v>229</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BT1" t="s">
         <v>230</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BU1" t="s">
         <v>231</v>
       </c>
-      <c r="BV1" s="2" t="s">
+      <c r="BV1" t="s">
         <v>232</v>
       </c>
-      <c r="BW1" s="2" t="s">
+      <c r="BW1" t="s">
         <v>233</v>
       </c>
-      <c r="BX1" s="2" t="s">
+      <c r="BX1" t="s">
         <v>234</v>
       </c>
-      <c r="BY1" s="2" t="s">
+      <c r="BY1" t="s">
         <v>235</v>
       </c>
-      <c r="BZ1" s="2" t="s">
+      <c r="BZ1" t="s">
         <v>236</v>
       </c>
-      <c r="CA1" s="2" t="s">
+      <c r="CA1" t="s">
         <v>237</v>
       </c>
-      <c r="CB1" s="2" t="s">
+      <c r="CB1" t="s">
         <v>238</v>
       </c>
-      <c r="CC1" s="2" t="s">
+      <c r="CC1" t="s">
         <v>239</v>
       </c>
-      <c r="CD1" s="2" t="s">
+      <c r="CD1" t="s">
         <v>240</v>
       </c>
-      <c r="CE1" s="2" t="s">
+      <c r="CE1" t="s">
         <v>241</v>
       </c>
-      <c r="CF1" s="2" t="s">
+      <c r="CF1" t="s">
         <v>242</v>
       </c>
-      <c r="CG1" s="2" t="s">
+      <c r="CG1" t="s">
         <v>243</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CH1" t="s">
         <v>244</v>
       </c>
-      <c r="CI1" s="2" t="s">
+      <c r="CI1" t="s">
         <v>245</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CJ1" t="s">
         <v>246</v>
       </c>
-      <c r="CK1" s="2" t="s">
+      <c r="CK1" t="s">
         <v>247</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CL1" t="s">
         <v>248</v>
       </c>
-      <c r="CM1" s="2" t="s">
+      <c r="CM1" t="s">
         <v>249</v>
       </c>
-      <c r="CN1" s="2" t="s">
+      <c r="CN1" t="s">
         <v>250</v>
       </c>
-      <c r="CO1" s="2" t="s">
+      <c r="CO1" t="s">
         <v>251</v>
       </c>
-      <c r="CP1" s="2" t="s">
+      <c r="CP1" t="s">
         <v>252</v>
       </c>
-      <c r="CQ1" s="2" t="s">
+      <c r="CQ1" t="s">
         <v>253</v>
       </c>
-      <c r="CR1" s="2" t="s">
+      <c r="CR1" t="s">
         <v>230</v>
       </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CS1" t="s">
         <v>254</v>
       </c>
-      <c r="CT1" s="2" t="s">
+      <c r="CT1" t="s">
         <v>255</v>
       </c>
-      <c r="CU1" s="2" t="s">
+      <c r="CU1" t="s">
         <v>256</v>
       </c>
-      <c r="CV1" s="2" t="s">
+      <c r="CV1" t="s">
         <v>257</v>
       </c>
-      <c r="CW1" s="2" t="s">
+      <c r="CW1" t="s">
         <v>258</v>
       </c>
-      <c r="CX1" s="2" t="s">
+      <c r="CX1" t="s">
         <v>259</v>
       </c>
-      <c r="CY1" s="2" t="s">
+      <c r="CY1" t="s">
         <v>260</v>
       </c>
-      <c r="CZ1" s="2" t="s">
+      <c r="CZ1" t="s">
         <v>259</v>
       </c>
-      <c r="DA1" s="2" t="s">
+      <c r="DA1" t="s">
         <v>261</v>
       </c>
-      <c r="DB1" s="2" t="s">
+      <c r="DB1" t="s">
         <v>262</v>
       </c>
-      <c r="DC1" s="2" t="s">
+      <c r="DC1" t="s">
         <v>263</v>
       </c>
-      <c r="DD1" s="2" t="s">
+      <c r="DD1" t="s">
         <v>264</v>
       </c>
-      <c r="DE1" s="2" t="s">
+      <c r="DE1" t="s">
         <v>265</v>
       </c>
-      <c r="DF1" s="2" t="s">
+      <c r="DF1" t="s">
         <v>266</v>
       </c>
-      <c r="DG1" s="2" t="s">
+      <c r="DG1" t="s">
         <v>267</v>
       </c>
-      <c r="DH1" s="2" t="s">
+      <c r="DH1" t="s">
         <v>268</v>
       </c>
-      <c r="DI1" s="2" t="s">
+      <c r="DI1" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>270</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>271</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>272</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>273</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>274</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
         <v>275</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" t="s">
         <v>276</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" t="s">
         <v>277</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" t="s">
         <v>278</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" t="s">
         <v>279</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" t="s">
         <v>280</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" t="s">
         <v>281</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" t="s">
         <v>282</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" t="s">
         <v>283</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" t="s">
         <v>284</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" t="s">
         <v>285</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" t="s">
         <v>286</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" t="s">
         <v>287</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" t="s">
         <v>288</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" t="s">
         <v>289</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" t="s">
         <v>290</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AA2" t="s">
         <v>291</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AB2" t="s">
         <v>292</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AC2" t="s">
         <v>293</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AD2" t="s">
         <v>294</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AE2" t="s">
         <v>295</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AF2" t="s">
         <v>296</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AG2" t="s">
         <v>297</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AH2" t="s">
         <v>298</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AI2" t="s">
         <v>299</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AJ2" t="s">
         <v>300</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AK2" t="s">
         <v>301</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AL2" t="s">
         <v>302</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AM2" t="s">
         <v>303</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AN2" t="s">
         <v>304</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AO2" t="s">
         <v>305</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AP2" t="s">
         <v>306</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AQ2" t="s">
         <v>307</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AR2" t="s">
         <v>308</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AS2" t="s">
         <v>309</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AT2" t="s">
         <v>310</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AU2" t="s">
         <v>311</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AV2" t="s">
         <v>312</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AW2" t="s">
         <v>313</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AX2" t="s">
         <v>314</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="AY2" t="s">
         <v>315</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="AZ2" t="s">
         <v>316</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="BA2" t="s">
         <v>317</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="BB2" t="s">
         <v>318</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BC2" t="s">
         <v>319</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BD2" t="s">
         <v>320</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BE2" t="s">
         <v>321</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BF2" t="s">
         <v>322</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BG2" t="s">
         <v>323</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BH2" t="s">
         <v>324</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BI2" t="s">
         <v>325</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BJ2" t="s">
         <v>326</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BK2" t="s">
         <v>327</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BL2" t="s">
         <v>328</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BM2" t="s">
         <v>329</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BN2" t="s">
         <v>330</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BO2" t="s">
         <v>82</v>
       </c>
-      <c r="BP2" s="2" t="s">
+      <c r="BP2" t="s">
         <v>331</v>
       </c>
-      <c r="BQ2" s="2" t="s">
+      <c r="BQ2" t="s">
         <v>332</v>
       </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BR2" t="s">
         <v>333</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BS2" t="s">
         <v>334</v>
       </c>
-      <c r="BT2" s="2" t="s">
+      <c r="BT2" t="s">
         <v>335</v>
       </c>
-      <c r="BU2" s="2" t="s">
+      <c r="BU2" t="s">
         <v>97</v>
       </c>
-      <c r="BV2" s="2" t="s">
+      <c r="BV2" t="s">
         <v>336</v>
       </c>
-      <c r="BW2" s="2" t="s">
+      <c r="BW2" t="s">
         <v>337</v>
       </c>
-      <c r="BX2" s="2" t="s">
+      <c r="BX2" t="s">
         <v>338</v>
       </c>
-      <c r="BY2" s="2" t="s">
+      <c r="BY2" t="s">
         <v>339</v>
       </c>
-      <c r="BZ2" s="2" t="s">
+      <c r="BZ2" t="s">
         <v>340</v>
       </c>
-      <c r="CA2" s="2" t="s">
+      <c r="CA2" t="s">
         <v>341</v>
       </c>
-      <c r="CB2" s="2" t="s">
+      <c r="CB2" t="s">
         <v>342</v>
       </c>
-      <c r="CC2" s="2" t="s">
+      <c r="CC2" t="s">
         <v>343</v>
       </c>
-      <c r="CD2" s="2" t="s">
+      <c r="CD2" t="s">
         <v>344</v>
       </c>
-      <c r="CE2" s="2" t="s">
+      <c r="CE2" t="s">
         <v>345</v>
       </c>
-      <c r="CF2" s="2" t="s">
+      <c r="CF2" t="s">
         <v>346</v>
       </c>
-      <c r="CG2" s="2" t="s">
+      <c r="CG2" t="s">
         <v>347</v>
       </c>
-      <c r="CH2" s="2" t="s">
+      <c r="CH2" t="s">
         <v>348</v>
       </c>
-      <c r="CI2" s="2" t="s">
+      <c r="CI2" t="s">
         <v>349</v>
       </c>
-      <c r="CJ2" s="2" t="s">
+      <c r="CJ2" t="s">
         <v>350</v>
       </c>
-      <c r="CK2" s="2" t="s">
+      <c r="CK2" t="s">
         <v>351</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CL2" t="s">
         <v>352</v>
       </c>
-      <c r="CM2" s="2" t="s">
+      <c r="CM2" t="s">
         <v>353</v>
       </c>
-      <c r="CN2" s="2" t="s">
+      <c r="CN2" t="s">
         <v>354</v>
       </c>
-      <c r="CO2" s="2" t="s">
+      <c r="CO2" t="s">
         <v>355</v>
       </c>
-      <c r="CP2" s="2" t="s">
+      <c r="CP2" t="s">
         <v>356</v>
       </c>
-      <c r="CQ2" s="2" t="s">
+      <c r="CQ2" t="s">
         <v>357</v>
       </c>
-      <c r="CR2" s="2" t="s">
+      <c r="CR2" t="s">
         <v>358</v>
       </c>
-      <c r="CS2" s="2" t="s">
+      <c r="CS2" t="s">
         <v>359</v>
       </c>
-      <c r="CT2" s="2" t="s">
+      <c r="CT2" t="s">
         <v>360</v>
       </c>
-      <c r="CU2" s="2" t="s">
+      <c r="CU2" t="s">
         <v>361</v>
       </c>
-      <c r="CV2" s="2" t="s">
+      <c r="CV2" t="s">
         <v>362</v>
       </c>
-      <c r="CW2" s="2" t="s">
+      <c r="CW2" t="s">
         <v>363</v>
       </c>
-      <c r="CX2" s="2" t="s">
+      <c r="CX2" t="s">
         <v>364</v>
       </c>
-      <c r="CY2" s="2" t="s">
+      <c r="CY2" t="s">
         <v>365</v>
       </c>
-      <c r="CZ2" s="2" t="s">
+      <c r="CZ2" t="s">
         <v>366</v>
       </c>
-      <c r="DA2" s="2" t="s">
+      <c r="DA2" t="s">
         <v>367</v>
       </c>
-      <c r="DB2" s="2" t="s">
+      <c r="DB2" t="s">
         <v>368</v>
       </c>
-      <c r="DC2" s="2" t="s">
+      <c r="DC2" t="s">
         <v>369</v>
       </c>
-      <c r="DD2" s="2" t="s">
+      <c r="DD2" t="s">
         <v>370</v>
       </c>
-      <c r="DE2" s="2" t="s">
+      <c r="DE2" t="s">
         <v>371</v>
       </c>
-      <c r="DF2" s="2" t="s">
+      <c r="DF2" t="s">
         <v>372</v>
       </c>
-      <c r="DG2" s="2" t="s">
+      <c r="DG2" t="s">
         <v>373</v>
       </c>
-      <c r="DH2" s="2" t="s">
+      <c r="DH2" t="s">
         <v>374</v>
       </c>
-      <c r="DI2" s="2" t="s">
+      <c r="DI2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
+    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
         <v>118</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>376</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" t="s">
         <v>377</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" t="s">
         <v>378</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" t="s">
         <v>120</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" t="s">
         <v>120</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" t="s">
         <v>123</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" t="s">
         <v>123</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" t="s">
         <v>123</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" t="s">
         <v>123</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" t="s">
         <v>118</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T3" t="s">
         <v>119</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="U3" t="s">
         <v>119</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V3" t="s">
         <v>119</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W3" t="s">
         <v>118</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X3" t="s">
         <v>118</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Y3" t="s">
         <v>118</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="Z3" t="s">
         <v>118</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AA3" t="s">
         <v>119</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AB3" t="s">
         <v>118</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AC3" t="s">
         <v>120</v>
       </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AD3" t="s">
         <v>118</v>
       </c>
-      <c r="AE3" s="2" t="s">
+      <c r="AE3" t="s">
         <v>118</v>
       </c>
-      <c r="AF3" s="2" t="s">
+      <c r="AF3" t="s">
         <v>118</v>
       </c>
-      <c r="AG3" s="2" t="s">
+      <c r="AG3" t="s">
         <v>379</v>
       </c>
-      <c r="AH3" s="2" t="s">
+      <c r="AH3" t="s">
         <v>118</v>
       </c>
-      <c r="AI3" s="2" t="s">
+      <c r="AI3" t="s">
         <v>125</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="AJ3" t="s">
         <v>3</v>
       </c>
-      <c r="AK3" s="2" t="s">
+      <c r="AK3" t="s">
         <v>120</v>
       </c>
-      <c r="AL3" s="2" t="s">
+      <c r="AL3" t="s">
         <v>120</v>
       </c>
-      <c r="AM3" s="2" t="s">
+      <c r="AM3" t="s">
         <v>120</v>
       </c>
-      <c r="AN3" s="2" t="s">
+      <c r="AN3" t="s">
         <v>118</v>
       </c>
-      <c r="AO3" s="2" t="s">
+      <c r="AO3" t="s">
         <v>380</v>
       </c>
-      <c r="AP3" s="2" t="s">
+      <c r="AP3" t="s">
         <v>381</v>
       </c>
-      <c r="AQ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT3" s="2" t="s">
+      <c r="AQ3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" t="s">
         <v>382</v>
       </c>
-      <c r="AU3" s="2" t="s">
+      <c r="AU3" t="s">
         <v>118</v>
       </c>
-      <c r="AV3" s="2" t="s">
+      <c r="AV3" t="s">
         <v>119</v>
       </c>
-      <c r="AW3" s="2" t="s">
+      <c r="AW3" t="s">
         <v>118</v>
       </c>
-      <c r="AX3" s="2" t="s">
+      <c r="AX3" t="s">
         <v>383</v>
       </c>
-      <c r="AY3" s="2" t="s">
+      <c r="AY3" t="s">
         <v>118</v>
       </c>
-      <c r="AZ3" s="2" t="s">
+      <c r="AZ3" t="s">
         <v>119</v>
       </c>
-      <c r="BA3" s="2" t="s">
+      <c r="BA3" t="s">
         <v>118</v>
       </c>
-      <c r="BB3" s="2" t="s">
+      <c r="BB3" t="s">
         <v>120</v>
       </c>
-      <c r="BC3" s="2" t="s">
+      <c r="BC3" t="s">
         <v>119</v>
       </c>
-      <c r="BD3" s="2" t="s">
+      <c r="BD3" t="s">
         <v>120</v>
       </c>
-      <c r="BE3" s="2" t="s">
+      <c r="BE3" t="s">
         <v>120</v>
       </c>
-      <c r="BF3" s="2" t="s">
+      <c r="BF3" t="s">
         <v>119</v>
       </c>
-      <c r="BG3" s="2" t="s">
+      <c r="BG3" t="s">
         <v>118</v>
       </c>
-      <c r="BH3" s="2" t="s">
+      <c r="BH3" t="s">
         <v>382</v>
       </c>
-      <c r="BI3" s="2" t="s">
+      <c r="BI3" t="s">
         <v>118</v>
       </c>
-      <c r="BJ3" s="2" t="s">
+      <c r="BJ3" t="s">
         <v>119</v>
       </c>
-      <c r="BK3" s="2" t="s">
+      <c r="BK3" t="s">
         <v>119</v>
       </c>
-      <c r="BL3" s="2" t="s">
+      <c r="BL3" t="s">
         <v>119</v>
       </c>
-      <c r="BM3" s="2" t="s">
+      <c r="BM3" t="s">
         <v>120</v>
       </c>
-      <c r="BN3" s="2" t="s">
+      <c r="BN3" t="s">
         <v>120</v>
       </c>
-      <c r="BO3" s="2" t="s">
+      <c r="BO3" t="s">
         <v>121</v>
       </c>
-      <c r="BP3" s="2" t="s">
+      <c r="BP3" t="s">
         <v>121</v>
       </c>
-      <c r="BQ3" s="2" t="s">
+      <c r="BQ3" t="s">
         <v>384</v>
       </c>
-      <c r="BR3" s="2" t="s">
+      <c r="BR3" t="s">
         <v>385</v>
       </c>
-      <c r="BS3" s="2" t="s">
+      <c r="BS3" t="s">
         <v>119</v>
       </c>
-      <c r="BT3" s="2" t="s">
+      <c r="BT3" t="s">
         <v>119</v>
       </c>
-      <c r="BU3" s="2" t="s">
+      <c r="BU3" t="s">
         <v>118</v>
       </c>
-      <c r="BV3" s="2" t="s">
+      <c r="BV3" t="s">
         <v>119</v>
       </c>
-      <c r="BW3" s="2" t="s">
+      <c r="BW3" t="s">
         <v>119</v>
       </c>
-      <c r="BX3" s="2" t="s">
+      <c r="BX3" t="s">
         <v>120</v>
       </c>
-      <c r="BY3" s="2" t="s">
+      <c r="BY3" t="s">
         <v>386</v>
       </c>
-      <c r="BZ3" s="2" t="s">
+      <c r="BZ3" t="s">
         <v>118</v>
       </c>
-      <c r="CA3" s="2" t="s">
+      <c r="CA3" t="s">
         <v>386</v>
       </c>
-      <c r="CB3" s="2" t="s">
+      <c r="CB3" t="s">
         <v>122</v>
       </c>
-      <c r="CC3" s="2" t="s">
+      <c r="CC3" t="s">
         <v>387</v>
       </c>
-      <c r="CD3" s="2" t="s">
+      <c r="CD3" t="s">
         <v>122</v>
       </c>
-      <c r="CE3" s="2" t="s">
+      <c r="CE3" t="s">
         <v>122</v>
       </c>
-      <c r="CF3" s="2" t="s">
+      <c r="CF3" t="s">
         <v>122</v>
       </c>
-      <c r="CG3" s="2" t="s">
+      <c r="CG3" t="s">
         <v>388</v>
       </c>
-      <c r="CH3" s="2" t="s">
+      <c r="CH3" t="s">
         <v>389</v>
       </c>
-      <c r="CI3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CJ3" s="2" t="s">
+      <c r="CI3" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" t="s">
         <v>390</v>
       </c>
-      <c r="CK3" s="2" t="s">
+      <c r="CK3" t="s">
         <v>390</v>
       </c>
-      <c r="CL3" s="2" t="s">
+      <c r="CL3" t="s">
         <v>127</v>
       </c>
-      <c r="CM3" s="2" t="s">
+      <c r="CM3" t="s">
         <v>123</v>
       </c>
-      <c r="CN3" s="2" t="s">
+      <c r="CN3" t="s">
         <v>123</v>
       </c>
-      <c r="CO3" s="2" t="s">
+      <c r="CO3" t="s">
         <v>126</v>
       </c>
-      <c r="CP3" s="2" t="s">
+      <c r="CP3" t="s">
         <v>126</v>
       </c>
-      <c r="CQ3" s="2" t="s">
+      <c r="CQ3" t="s">
         <v>126</v>
       </c>
-      <c r="CR3" s="2" t="s">
+      <c r="CR3" t="s">
         <v>387</v>
       </c>
-      <c r="CS3" s="2" t="s">
+      <c r="CS3" t="s">
         <v>126</v>
       </c>
-      <c r="CT3" s="2" t="s">
+      <c r="CT3" t="s">
         <v>118</v>
       </c>
-      <c r="CU3" s="2" t="s">
+      <c r="CU3" t="s">
         <v>127</v>
       </c>
-      <c r="CV3" s="2" t="s">
+      <c r="CV3" t="s">
         <v>391</v>
       </c>
-      <c r="CW3" s="2" t="s">
+      <c r="CW3" t="s">
         <v>392</v>
       </c>
-      <c r="CX3" s="2" t="s">
+      <c r="CX3" t="s">
         <v>392</v>
       </c>
-      <c r="CY3" s="2" t="s">
+      <c r="CY3" t="s">
         <v>391</v>
       </c>
-      <c r="CZ3" s="2" t="s">
+      <c r="CZ3" t="s">
         <v>391</v>
       </c>
-      <c r="DA3" s="2" t="s">
+      <c r="DA3" t="s">
         <v>391</v>
       </c>
-      <c r="DB3" s="2" t="s">
+      <c r="DB3" t="s">
         <v>391</v>
       </c>
-      <c r="DC3" s="2" t="s">
+      <c r="DC3" t="s">
         <v>391</v>
       </c>
-      <c r="DD3" s="2" t="s">
+      <c r="DD3" t="s">
         <v>118</v>
       </c>
-      <c r="DE3" s="2" t="s">
+      <c r="DE3" t="s">
         <v>118</v>
       </c>
-      <c r="DF3" s="2" t="s">
+      <c r="DF3" t="s">
         <v>118</v>
       </c>
-      <c r="DG3" s="2" t="s">
+      <c r="DG3" t="s">
         <v>118</v>
       </c>
-      <c r="DH3" s="2" t="s">
+      <c r="DH3" t="s">
         <v>118</v>
       </c>
-      <c r="DI3" s="2" t="s">
+      <c r="DI3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>394</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" t="s">
         <v>395</v>
       </c>
-      <c r="S5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO5" s="2" t="s">
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="AC5">
+        <v>2</v>
+      </c>
+      <c r="AD5">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="s">
         <v>396</v>
       </c>
-      <c r="AT5" s="2" t="s">
+      <c r="AT5" t="s">
         <v>397</v>
       </c>
-      <c r="AX5" s="2" t="s">
+      <c r="AX5" t="s">
         <v>398</v>
       </c>
-      <c r="AZ5" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD5" s="2">
-        <v>1</v>
-      </c>
-      <c r="BJ5" s="2">
+      <c r="AZ5">
+        <v>1</v>
+      </c>
+      <c r="BD5">
+        <v>1</v>
+      </c>
+      <c r="BJ5">
         <v>1.3</v>
       </c>
-      <c r="BK5" s="2">
-        <v>1</v>
-      </c>
-      <c r="BL5" s="2">
+      <c r="BK5">
+        <v>1</v>
+      </c>
+      <c r="BL5">
         <v>0</v>
       </c>
-      <c r="BO5" s="2" t="s">
+      <c r="BO5" t="s">
         <v>399</v>
       </c>
-      <c r="BP5" s="2" t="s">
+      <c r="BP5" t="s">
         <v>400</v>
       </c>
-      <c r="CB5" s="2" t="s">
+      <c r="CB5" t="s">
         <v>401</v>
       </c>
-      <c r="CG5" s="2" t="s">
+      <c r="CG5" t="s">
         <v>402</v>
       </c>
-      <c r="CN5" s="2" t="s">
+      <c r="CN5" t="s">
         <v>403</v>
       </c>
-      <c r="CR5" s="2">
+      <c r="CR5">
         <v>0.1</v>
       </c>
-      <c r="CY5" s="2" t="s">
+      <c r="CY5" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>405</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>394</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" t="s">
         <v>406</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="R6" t="s">
         <v>407</v>
       </c>
-      <c r="AC6" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO6" s="2" t="s">
+      <c r="AC6">
+        <v>2</v>
+      </c>
+      <c r="AD6">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="s">
         <v>396</v>
       </c>
-      <c r="AT6" s="2" t="s">
+      <c r="AT6" t="s">
         <v>397</v>
       </c>
-      <c r="BD6" s="2">
-        <v>1</v>
-      </c>
-      <c r="CL6" s="2" t="s">
+      <c r="BD6">
+        <v>1</v>
+      </c>
+      <c r="CL6" t="s">
         <v>408</v>
       </c>
-      <c r="CM6" s="2" t="s">
+      <c r="CM6" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>399</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>394</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="Q7" t="s">
         <v>403</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="R7" t="s">
         <v>407</v>
       </c>
-      <c r="AC7" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO7" s="2" t="s">
+      <c r="AC7">
+        <v>2</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="s">
         <v>396</v>
       </c>
-      <c r="AV7" s="2">
+      <c r="AV7">
         <v>99</v>
       </c>
-      <c r="BD7" s="2">
+      <c r="BD7">
         <v>99</v>
       </c>
-      <c r="BS7" s="2">
+      <c r="BS7">
         <v>0.1</v>
       </c>
-      <c r="CL7" s="2" t="s">
+      <c r="CL7" t="s">
         <v>409</v>
       </c>
-      <c r="CM7" s="2" t="s">
+      <c r="CM7" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>410</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>394</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>411</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" t="s">
         <v>412</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" t="s">
         <v>413</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10">
         <v>3</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" t="s">
         <v>414</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" t="s">
         <v>395</v>
       </c>
-      <c r="AC10" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO10" s="2" t="s">
+      <c r="AC10">
+        <v>2</v>
+      </c>
+      <c r="AD10">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="s">
         <v>415</v>
       </c>
-      <c r="AT10" s="2" t="s">
+      <c r="AT10" t="s">
         <v>397</v>
       </c>
-      <c r="AX10" s="2" t="s">
+      <c r="AX10" t="s">
         <v>398</v>
       </c>
-      <c r="AZ10" s="2">
+      <c r="AZ10">
         <v>1.5</v>
       </c>
-      <c r="BD10" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE10" s="2">
-        <v>1</v>
-      </c>
-      <c r="BF10" s="2">
+      <c r="BD10">
+        <v>1</v>
+      </c>
+      <c r="BE10">
+        <v>1</v>
+      </c>
+      <c r="BF10">
         <v>0.1</v>
       </c>
-      <c r="BJ10" s="2">
+      <c r="BJ10">
         <v>1.3</v>
       </c>
-      <c r="BK10" s="2">
-        <v>1</v>
-      </c>
-      <c r="BL10" s="2">
+      <c r="BK10">
+        <v>1</v>
+      </c>
+      <c r="BL10">
         <v>0</v>
       </c>
-      <c r="BO10" s="2" t="s">
+      <c r="BO10" t="s">
         <v>399</v>
       </c>
-      <c r="BP10" s="2" t="s">
+      <c r="BP10" t="s">
         <v>416</v>
       </c>
-      <c r="BT10" s="2">
+      <c r="BT10">
         <v>0.3</v>
       </c>
-      <c r="BV10" s="2">
-        <v>2</v>
-      </c>
-      <c r="BW10" s="2">
-        <v>2</v>
-      </c>
-      <c r="BX10" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY10" s="2" t="s">
+      <c r="BV10">
+        <v>2</v>
+      </c>
+      <c r="BW10">
+        <v>2</v>
+      </c>
+      <c r="BX10">
+        <v>1</v>
+      </c>
+      <c r="BY10" t="s">
         <v>417</v>
       </c>
-      <c r="CB10" s="2" t="s">
+      <c r="CB10" t="s">
         <v>418</v>
       </c>
-      <c r="CG10" s="2" t="s">
+      <c r="CG10" t="s">
         <v>402</v>
       </c>
-      <c r="CN10" s="2" t="s">
+      <c r="CN10" t="s">
         <v>403</v>
       </c>
-      <c r="CR10" s="2">
+      <c r="CR10">
         <v>0.1</v>
       </c>
-      <c r="CY10" s="2" t="s">
+      <c r="CY10" t="s">
         <v>404</v>
       </c>
-      <c r="DD10" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG10" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH10" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="DD10">
+        <v>1</v>
+      </c>
+      <c r="DG10">
+        <v>1</v>
+      </c>
+      <c r="DH10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>416</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>394</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" t="s">
         <v>406</v>
       </c>
-      <c r="AC11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD11" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO11" s="2" t="s">
+      <c r="AC11">
+        <v>2</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="s">
         <v>415</v>
       </c>
-      <c r="AT11" s="2" t="s">
+      <c r="AT11" t="s">
         <v>397</v>
       </c>
-      <c r="BD11" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE11" s="2">
-        <v>1</v>
-      </c>
-      <c r="BF11" s="2">
+      <c r="BD11">
+        <v>1</v>
+      </c>
+      <c r="BE11">
+        <v>1</v>
+      </c>
+      <c r="BF11">
         <v>0.1</v>
       </c>
-      <c r="CL11" s="2" t="s">
+      <c r="CL11" t="s">
         <v>419</v>
       </c>
-      <c r="CM11" s="2" t="s">
+      <c r="CM11" t="s">
         <v>403</v>
       </c>
-      <c r="CN11" s="2" t="s">
+      <c r="CN11" t="s">
         <v>407</v>
       </c>
-      <c r="CR11" s="2">
+      <c r="CR11">
         <v>3</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>420</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s">
         <v>394</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" t="s">
         <v>406</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="Q12" t="s">
         <v>421</v>
       </c>
-      <c r="AC12" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD12" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO12" s="2" t="s">
+      <c r="AC12">
+        <v>2</v>
+      </c>
+      <c r="AD12">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="s">
         <v>396</v>
       </c>
-      <c r="AT12" s="2" t="s">
+      <c r="AT12" t="s">
         <v>397</v>
       </c>
-      <c r="BD12" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE12" s="2">
-        <v>1</v>
-      </c>
-      <c r="BF12" s="2">
+      <c r="BD12">
+        <v>1</v>
+      </c>
+      <c r="BE12">
+        <v>1</v>
+      </c>
+      <c r="BF12">
         <v>0.1</v>
       </c>
-      <c r="CL12" s="2" t="s">
+      <c r="CL12" t="s">
         <v>419</v>
       </c>
-      <c r="CM12" s="2" t="s">
+      <c r="CM12" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>422</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s">
         <v>423</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" t="s">
         <v>424</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" t="s">
         <v>425</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" t="s">
         <v>426</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14">
         <v>3</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" t="s">
         <v>414</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="K14" t="s">
         <v>395</v>
       </c>
-      <c r="AC14" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF14" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG14" s="2" t="s">
+      <c r="AC14">
+        <v>1</v>
+      </c>
+      <c r="AF14">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="s">
         <v>427</v>
       </c>
-      <c r="BD14" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO14" s="2" t="s">
+      <c r="BD14">
+        <v>1</v>
+      </c>
+      <c r="BO14" t="s">
         <v>428</v>
       </c>
-      <c r="BP14" s="2" t="s">
+      <c r="BP14" t="s">
         <v>429</v>
       </c>
-      <c r="BT14" s="2">
+      <c r="BT14">
         <v>9999</v>
       </c>
-      <c r="BV14" s="2">
+      <c r="BV14">
         <v>0</v>
       </c>
-      <c r="BW14" s="2">
+      <c r="BW14">
         <v>25</v>
       </c>
-      <c r="BX14" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY14" s="2" t="s">
+      <c r="BX14">
+        <v>1</v>
+      </c>
+      <c r="BY14" t="s">
         <v>395</v>
       </c>
-      <c r="CN14" s="2" t="s">
+      <c r="CN14" t="s">
         <v>430</v>
       </c>
-      <c r="CO14" s="2">
+      <c r="CO14">
         <v>35</v>
       </c>
-      <c r="CR14" s="2">
+      <c r="CR14">
         <v>9999</v>
       </c>
-      <c r="CU14" s="2" t="s">
+      <c r="CU14" t="s">
         <v>431</v>
       </c>
-      <c r="DD14" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG14" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH14" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
+      <c r="DD14">
+        <v>1</v>
+      </c>
+      <c r="DG14">
+        <v>1</v>
+      </c>
+      <c r="DH14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>428</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s">
         <v>394</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="K15" t="s">
         <v>395</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="O15" t="s">
         <v>432</v>
       </c>
-      <c r="AC15" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD15" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO15" s="2" t="s">
+      <c r="AC15">
+        <v>2</v>
+      </c>
+      <c r="AD15">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="s">
         <v>396</v>
       </c>
-      <c r="AT15" s="2" t="s">
+      <c r="AT15" t="s">
         <v>397</v>
       </c>
-      <c r="AX15" s="2" t="s">
+      <c r="AX15" t="s">
         <v>398</v>
       </c>
-      <c r="AZ15" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD15" s="2">
-        <v>1</v>
-      </c>
-      <c r="BJ15" s="2">
+      <c r="AZ15">
+        <v>1</v>
+      </c>
+      <c r="BD15">
+        <v>1</v>
+      </c>
+      <c r="BJ15">
         <v>1.5</v>
       </c>
-      <c r="BK15" s="2">
-        <v>1</v>
-      </c>
-      <c r="BL15" s="2">
+      <c r="BK15">
+        <v>1</v>
+      </c>
+      <c r="BL15">
         <v>0</v>
       </c>
-      <c r="BO15" s="2" t="s">
+      <c r="BO15" t="s">
         <v>399</v>
       </c>
-      <c r="BP15" s="2" t="s">
+      <c r="BP15" t="s">
         <v>405</v>
       </c>
-      <c r="CB15" s="2" t="s">
+      <c r="CB15" t="s">
         <v>433</v>
       </c>
-      <c r="CG15" s="2" t="s">
+      <c r="CG15" t="s">
         <v>402</v>
       </c>
-      <c r="CN15" s="2" t="s">
+      <c r="CN15" t="s">
         <v>403</v>
       </c>
-      <c r="CR15" s="2">
+      <c r="CR15">
         <v>0.1</v>
       </c>
-      <c r="CY15" s="2" t="s">
+      <c r="CY15" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>429</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s">
         <v>394</v>
       </c>
-      <c r="I16" s="2">
-        <v>1</v>
-      </c>
-      <c r="K16" s="2" t="s">
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="K16" t="s">
         <v>406</v>
       </c>
-      <c r="AC16" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG16" s="2" t="s">
+      <c r="AC16">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="s">
         <v>427</v>
       </c>
-      <c r="BD16" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS16" s="2">
-        <v>0.333</v>
-      </c>
-      <c r="CB16" s="2" t="s">
+      <c r="BD16">
+        <v>1</v>
+      </c>
+      <c r="BS16">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="CB16" t="s">
         <v>435</v>
       </c>
-      <c r="CG16" s="2" t="s">
+      <c r="CG16" t="s">
         <v>402</v>
       </c>
-      <c r="DD16" s="2">
-        <v>1</v>
-      </c>
-      <c r="DF16" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG16" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH16" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
+      <c r="DD16">
+        <v>1</v>
+      </c>
+      <c r="DF16">
+        <v>1</v>
+      </c>
+      <c r="DG16">
+        <v>1</v>
+      </c>
+      <c r="DH16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>436</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s">
         <v>394</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" t="s">
         <v>437</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" t="s">
         <v>438</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" t="s">
         <v>439</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18">
         <v>3</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" t="s">
         <v>414</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="K18" t="s">
         <v>440</v>
       </c>
-      <c r="AC18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG18" s="2" t="s">
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AF18">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="s">
         <v>427</v>
       </c>
-      <c r="AT18" s="2" t="s">
+      <c r="AT18" t="s">
         <v>441</v>
       </c>
-      <c r="BD18" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO18" s="2" t="s">
+      <c r="BD18">
+        <v>1</v>
+      </c>
+      <c r="BO18" t="s">
         <v>442</v>
       </c>
-      <c r="BP18" s="2" t="s">
+      <c r="BP18" t="s">
         <v>443</v>
       </c>
-      <c r="BT18" s="2">
+      <c r="BT18">
         <v>30</v>
       </c>
-      <c r="BV18" s="2">
+      <c r="BV18">
         <v>30</v>
       </c>
-      <c r="BW18" s="2">
+      <c r="BW18">
         <v>40</v>
       </c>
-      <c r="BX18" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY18" s="2" t="s">
+      <c r="BX18">
+        <v>1</v>
+      </c>
+      <c r="BY18" t="s">
         <v>395</v>
       </c>
-      <c r="CN18" s="2" t="s">
+      <c r="CN18" t="s">
         <v>444</v>
       </c>
-      <c r="CO18" s="2">
+      <c r="CO18">
         <v>1.25</v>
       </c>
-      <c r="CR18" s="2">
+      <c r="CR18">
         <v>30</v>
       </c>
-      <c r="CU18" s="2" t="s">
+      <c r="CU18" t="s">
         <v>445</v>
       </c>
-      <c r="DD18" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG18" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
+      <c r="DD18">
+        <v>1</v>
+      </c>
+      <c r="DG18">
+        <v>1</v>
+      </c>
+      <c r="DH18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>446</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s">
         <v>394</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="K19" t="s">
         <v>395</v>
       </c>
-      <c r="O19" s="2" t="s">
+      <c r="O19" t="s">
         <v>447</v>
       </c>
-      <c r="AC19" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD19" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO19" s="2" t="s">
+      <c r="AC19">
+        <v>2</v>
+      </c>
+      <c r="AD19">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="s">
         <v>415</v>
       </c>
-      <c r="AT19" s="2" t="s">
+      <c r="AT19" t="s">
         <v>441</v>
       </c>
-      <c r="AX19" s="2" t="s">
+      <c r="AX19" t="s">
         <v>398</v>
       </c>
-      <c r="AZ19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BJ19" s="2">
+      <c r="AZ19">
+        <v>1</v>
+      </c>
+      <c r="BD19">
+        <v>1</v>
+      </c>
+      <c r="BJ19">
         <v>1.5</v>
       </c>
-      <c r="BK19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BL19" s="2">
+      <c r="BK19">
+        <v>1</v>
+      </c>
+      <c r="BL19">
         <v>0</v>
       </c>
-      <c r="BO19" s="2" t="s">
+      <c r="BO19" t="s">
         <v>399</v>
       </c>
-      <c r="BP19" s="2" t="s">
+      <c r="BP19" t="s">
         <v>405</v>
       </c>
-      <c r="CG19" s="2" t="s">
+      <c r="CG19" t="s">
         <v>402</v>
       </c>
-      <c r="CN19" s="2" t="s">
+      <c r="CN19" t="s">
         <v>448</v>
       </c>
-      <c r="CR19" s="2">
+      <c r="CR19">
         <v>9999</v>
       </c>
-      <c r="CY19" s="2" t="s">
+      <c r="CY19" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>443</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>394</v>
       </c>
-      <c r="I20" s="2">
-        <v>1</v>
-      </c>
-      <c r="K20" s="2" t="s">
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="K20" t="s">
         <v>406</v>
       </c>
-      <c r="AC20" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG20" s="2" t="s">
+      <c r="AC20">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="s">
         <v>427</v>
       </c>
-      <c r="BD20" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS20" s="2">
-        <v>0.333</v>
-      </c>
-      <c r="CB20" s="2" t="s">
+      <c r="BD20">
+        <v>1</v>
+      </c>
+      <c r="BS20">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="CB20" t="s">
         <v>449</v>
       </c>
-      <c r="CG20" s="2" t="s">
+      <c r="CG20" t="s">
         <v>402</v>
       </c>
-      <c r="DD20" s="2">
-        <v>1</v>
-      </c>
-      <c r="DF20" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG20" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH20" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
+      <c r="DD20">
+        <v>1</v>
+      </c>
+      <c r="DF20">
+        <v>1</v>
+      </c>
+      <c r="DG20">
+        <v>1</v>
+      </c>
+      <c r="DH20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>450</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s">
         <v>394</v>
       </c>
-      <c r="I21" s="2">
-        <v>1</v>
-      </c>
-      <c r="K21" s="2" t="s">
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="K21" t="s">
         <v>406</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="L21" t="s">
         <v>451</v>
       </c>
-      <c r="AC21" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG21" s="2" t="s">
+      <c r="AC21">
+        <v>1</v>
+      </c>
+      <c r="AG21" t="s">
         <v>427</v>
       </c>
-      <c r="BD21" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS21" s="2">
-        <v>0.333</v>
-      </c>
-      <c r="CB21" s="2" t="s">
+      <c r="BD21">
+        <v>1</v>
+      </c>
+      <c r="BS21">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="CB21" t="s">
         <v>452</v>
       </c>
-      <c r="CG21" s="2" t="s">
+      <c r="CG21" t="s">
         <v>402</v>
       </c>
-      <c r="DD21" s="2">
-        <v>1</v>
-      </c>
-      <c r="DF21" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG21" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH21" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="s">
+      <c r="DD21">
+        <v>1</v>
+      </c>
+      <c r="DF21">
+        <v>1</v>
+      </c>
+      <c r="DG21">
+        <v>1</v>
+      </c>
+      <c r="DH21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>453</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s">
         <v>394</v>
       </c>
-      <c r="O22" s="2" t="s">
+      <c r="O22" t="s">
         <v>447</v>
       </c>
-      <c r="Q22" s="2" t="s">
+      <c r="Q22" t="s">
         <v>454</v>
       </c>
-      <c r="AC22" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD22" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO22" s="2" t="s">
+      <c r="AC22">
+        <v>2</v>
+      </c>
+      <c r="AD22">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="s">
         <v>396</v>
       </c>
-      <c r="AV22" s="2">
+      <c r="AV22">
         <v>99</v>
       </c>
-      <c r="BD22" s="2">
+      <c r="BD22">
         <v>99</v>
       </c>
-      <c r="BS22" s="2">
-        <v>1</v>
-      </c>
-      <c r="CL22" s="2" t="s">
+      <c r="BS22">
+        <v>1</v>
+      </c>
+      <c r="CL22" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>456</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" t="s">
         <v>394</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="K23" t="s">
         <v>406</v>
       </c>
-      <c r="L23" s="2" t="s">
+      <c r="L23" t="s">
         <v>457</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="O23" t="s">
         <v>447</v>
       </c>
-      <c r="Q23" s="2" t="s">
+      <c r="Q23" t="s">
         <v>454</v>
       </c>
-      <c r="AC23" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD23" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO23" s="2" t="s">
+      <c r="AC23">
+        <v>2</v>
+      </c>
+      <c r="AD23">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="s">
         <v>396</v>
       </c>
-      <c r="AV23" s="2">
+      <c r="AV23">
         <v>99</v>
       </c>
-      <c r="BD23" s="2">
+      <c r="BD23">
         <v>99</v>
       </c>
-      <c r="BS23" s="2">
+      <c r="BS23">
         <v>0.1</v>
       </c>
-      <c r="CM23" s="2" t="s">
+      <c r="CM23" t="s">
         <v>454</v>
       </c>
-      <c r="CU23" s="2" t="s">
+      <c r="CU23" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>459</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" t="s">
         <v>394</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="O24" t="s">
         <v>447</v>
       </c>
-      <c r="AC24" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD24" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO24" s="2" t="s">
+      <c r="AC24">
+        <v>2</v>
+      </c>
+      <c r="AD24">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="s">
         <v>396</v>
       </c>
-      <c r="AT24" s="2" t="s">
+      <c r="AT24" t="s">
         <v>441</v>
       </c>
-      <c r="BD24" s="2">
+      <c r="BD24">
         <v>99</v>
       </c>
-      <c r="BS24" s="2">
+      <c r="BS24">
         <v>0.1</v>
       </c>
-      <c r="CN24" s="2" t="s">
+      <c r="CN24" t="s">
         <v>459</v>
       </c>
-      <c r="CO24" s="2">
+      <c r="CO24">
         <v>-0.5</v>
       </c>
-      <c r="CR24" s="2">
+      <c r="CR24">
         <v>0.2</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>460</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" t="s">
         <v>461</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="K25" t="s">
         <v>406</v>
       </c>
-      <c r="L25" s="2" t="s">
+      <c r="L25" t="s">
         <v>457</v>
       </c>
-      <c r="O25" s="2" t="s">
+      <c r="O25" t="s">
         <v>447</v>
       </c>
-      <c r="AC25" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD25" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO25" s="2" t="s">
+      <c r="AC25">
+        <v>2</v>
+      </c>
+      <c r="AD25">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="s">
         <v>396</v>
       </c>
-      <c r="AT25" s="2" t="s">
+      <c r="AT25" t="s">
         <v>441</v>
       </c>
-      <c r="BD25" s="2">
+      <c r="BD25">
         <v>99</v>
       </c>
-      <c r="BS25" s="2">
+      <c r="BS25">
         <v>0.1</v>
       </c>
-      <c r="CU25" s="2" t="s">
+      <c r="CU25" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>147</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" t="s">
         <v>461</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="K28" t="s">
         <v>406</v>
       </c>
-      <c r="L28" s="2" t="s">
+      <c r="L28" t="s">
         <v>463</v>
       </c>
-      <c r="AC28" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG28" s="2" t="s">
+      <c r="AC28">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="s">
         <v>427</v>
       </c>
-      <c r="BD28" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU28" s="2" t="s">
+      <c r="BD28">
+        <v>1</v>
+      </c>
+      <c r="CU28" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>155</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" t="s">
         <v>465</v>
       </c>
-      <c r="I29" s="2">
-        <v>1</v>
-      </c>
-      <c r="K29" s="2" t="s">
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="K29" t="s">
         <v>406</v>
       </c>
-      <c r="L29" s="2" t="s">
+      <c r="L29" t="s">
         <v>463</v>
       </c>
-      <c r="AC29" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO29" s="2" t="s">
+      <c r="AC29">
+        <v>2</v>
+      </c>
+      <c r="AD29">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="s">
         <v>396</v>
       </c>
-      <c r="AT29" s="2" t="s">
+      <c r="AT29" t="s">
         <v>466</v>
       </c>
-      <c r="BD29" s="2">
+      <c r="BD29">
         <v>4</v>
       </c>
-      <c r="BT29" s="2">
+      <c r="BT29">
         <v>0.2</v>
       </c>
-      <c r="CN29" s="2" t="s">
+      <c r="CN29" t="s">
         <v>467</v>
       </c>
-      <c r="CR29" s="2">
+      <c r="CR29">
         <v>5</v>
       </c>
-      <c r="CU29" s="2" t="s">
+      <c r="CU29" t="s">
         <v>468</v>
       </c>
-      <c r="CY29" s="2" t="s">
+      <c r="CY29" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="s">
+    <row r="30" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>470</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" t="s">
         <v>471</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="K30" t="s">
         <v>406</v>
       </c>
-      <c r="L30" s="2" t="s">
+      <c r="L30" t="s">
         <v>463</v>
       </c>
-      <c r="AC30" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG30" s="2" t="s">
+      <c r="AC30">
+        <v>1</v>
+      </c>
+      <c r="AG30" t="s">
         <v>427</v>
       </c>
-      <c r="BD30" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU30" s="2" t="s">
+      <c r="BD30">
+        <v>1</v>
+      </c>
+      <c r="CU30" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>473</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" t="s">
         <v>394</v>
       </c>
-      <c r="I32" s="2">
-        <v>1</v>
-      </c>
-      <c r="J32" s="2" t="s">
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32" t="s">
         <v>414</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="K32" t="s">
         <v>395</v>
       </c>
-      <c r="AC32" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD32" s="2">
-        <v>1</v>
-      </c>
-      <c r="AV32" s="2">
+      <c r="AC32">
+        <v>2</v>
+      </c>
+      <c r="AD32">
+        <v>1</v>
+      </c>
+      <c r="AV32">
         <v>0.4</v>
       </c>
-      <c r="BD32" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO32" s="2" t="s">
+      <c r="BD32">
+        <v>1</v>
+      </c>
+      <c r="BO32" t="s">
         <v>474</v>
       </c>
-      <c r="BP32" s="2" t="s">
+      <c r="BP32" t="s">
         <v>475</v>
       </c>
-      <c r="BT32" s="2">
+      <c r="BT32">
         <v>6</v>
       </c>
-      <c r="BV32" s="2">
-        <v>1</v>
-      </c>
-      <c r="BW32" s="2">
-        <v>1</v>
-      </c>
-      <c r="BX32" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY32" s="2" t="s">
+      <c r="BV32">
+        <v>1</v>
+      </c>
+      <c r="BW32">
+        <v>1</v>
+      </c>
+      <c r="BX32">
+        <v>1</v>
+      </c>
+      <c r="BY32" t="s">
         <v>476</v>
       </c>
-      <c r="DH32" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="s">
+      <c r="DH32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>475</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" t="s">
         <v>394</v>
       </c>
-      <c r="I33" s="2">
-        <v>1</v>
-      </c>
-      <c r="K33" s="2" t="s">
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="K33" t="s">
         <v>406</v>
       </c>
-      <c r="AC33" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG33" s="2" t="s">
+      <c r="AC33">
+        <v>1</v>
+      </c>
+      <c r="AG33" t="s">
         <v>427</v>
       </c>
-      <c r="AT33" s="2" t="s">
+      <c r="AT33" t="s">
         <v>477</v>
       </c>
-      <c r="AX33" s="2" t="s">
+      <c r="AX33" t="s">
         <v>478</v>
       </c>
-      <c r="AZ33" s="2">
+      <c r="AZ33">
         <v>999</v>
       </c>
-      <c r="BB33" s="2">
-        <v>2</v>
-      </c>
-      <c r="BD33" s="2">
-        <v>1</v>
-      </c>
-      <c r="DD33" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG33" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH33" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="s">
+      <c r="BB33">
+        <v>2</v>
+      </c>
+      <c r="BD33">
+        <v>1</v>
+      </c>
+      <c r="DD33">
+        <v>1</v>
+      </c>
+      <c r="DG33">
+        <v>1</v>
+      </c>
+      <c r="DH33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>479</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" t="s">
         <v>461</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="K34" t="s">
         <v>406</v>
       </c>
-      <c r="L34" s="2" t="s">
+      <c r="L34" t="s">
         <v>480</v>
       </c>
-      <c r="AC34" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG34" s="2" t="s">
+      <c r="AC34">
+        <v>1</v>
+      </c>
+      <c r="AG34" t="s">
         <v>427</v>
       </c>
-      <c r="BD34" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU34" s="2" t="s">
+      <c r="BD34">
+        <v>1</v>
+      </c>
+      <c r="CU34" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>482</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" t="s">
         <v>461</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="K35" t="s">
         <v>406</v>
       </c>
-      <c r="L35" s="2" t="s">
+      <c r="L35" t="s">
         <v>483</v>
       </c>
-      <c r="AC35" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG35" s="2" t="s">
+      <c r="AC35">
+        <v>1</v>
+      </c>
+      <c r="AG35" t="s">
         <v>427</v>
       </c>
-      <c r="BD35" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU35" s="2" t="s">
+      <c r="BD35">
+        <v>1</v>
+      </c>
+      <c r="CU35" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>484</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" t="s">
         <v>394</v>
       </c>
-      <c r="I37" s="2">
-        <v>1</v>
-      </c>
-      <c r="K37" s="2" t="s">
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="K37" t="s">
         <v>406</v>
       </c>
-      <c r="L37" s="2" t="s">
+      <c r="L37" t="s">
         <v>463</v>
       </c>
-      <c r="AC37" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG37" s="2" t="s">
+      <c r="AC37">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="s">
         <v>427</v>
       </c>
-      <c r="BD37" s="2">
-        <v>1</v>
-      </c>
-      <c r="CY37" s="2" t="s">
+      <c r="BD37">
+        <v>1</v>
+      </c>
+      <c r="CY37" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="s">
+    <row r="38" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>486</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" t="s">
         <v>394</v>
       </c>
-      <c r="I38" s="2">
-        <v>1</v>
-      </c>
-      <c r="K38" s="2" t="s">
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="K38" t="s">
         <v>406</v>
       </c>
-      <c r="L38" s="2" t="s">
+      <c r="L38" t="s">
         <v>463</v>
       </c>
-      <c r="X38" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC38" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD38" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO38" s="2" t="s">
+      <c r="X38">
+        <v>1</v>
+      </c>
+      <c r="AC38">
+        <v>2</v>
+      </c>
+      <c r="AD38">
+        <v>1</v>
+      </c>
+      <c r="AO38" t="s">
         <v>396</v>
       </c>
-      <c r="AT38" s="2" t="s">
+      <c r="AT38" t="s">
         <v>466</v>
       </c>
-      <c r="AX38" s="2" t="s">
+      <c r="AX38" t="s">
         <v>398</v>
       </c>
-      <c r="AZ38" s="2">
+      <c r="AZ38">
         <v>1.5</v>
       </c>
-      <c r="BD38" s="2">
+      <c r="BD38">
         <v>99</v>
       </c>
-      <c r="BE38" s="2">
+      <c r="BE38">
         <v>11</v>
       </c>
-      <c r="BF38" s="2">
+      <c r="BF38">
         <v>0.5</v>
       </c>
-      <c r="BO38" s="2" t="s">
+      <c r="BO38" t="s">
         <v>487</v>
       </c>
-      <c r="BP38" s="2" t="s">
+      <c r="BP38" t="s">
         <v>488</v>
       </c>
-      <c r="CB38" s="2" t="s">
+      <c r="CB38" t="s">
         <v>58</v>
       </c>
-      <c r="CG38" s="2" t="s">
+      <c r="CG38" t="s">
         <v>402</v>
       </c>
-      <c r="CL38" s="2" t="s">
+      <c r="CL38" t="s">
         <v>489</v>
       </c>
-      <c r="CU38" s="2" t="s">
+      <c r="CU38" t="s">
         <v>490</v>
       </c>
-      <c r="CY38" s="2" t="s">
+      <c r="CY38" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="s">
+    <row r="39" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>487</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" t="s">
         <v>394</v>
       </c>
-      <c r="I39" s="2">
-        <v>1</v>
-      </c>
-      <c r="K39" s="2" t="s">
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="K39" t="s">
         <v>406</v>
       </c>
-      <c r="L39" s="2" t="s">
+      <c r="L39" t="s">
         <v>463</v>
       </c>
-      <c r="X39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC39" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO39" s="2" t="s">
+      <c r="X39">
+        <v>1</v>
+      </c>
+      <c r="AC39">
+        <v>2</v>
+      </c>
+      <c r="AD39">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="s">
         <v>396</v>
       </c>
-      <c r="AT39" s="2" t="s">
+      <c r="AT39" t="s">
         <v>466</v>
       </c>
-      <c r="BD39" s="2">
+      <c r="BD39">
         <v>99</v>
       </c>
-      <c r="CN39" s="2" t="s">
+      <c r="CN39" t="s">
         <v>492</v>
       </c>
-      <c r="CO39" s="2">
+      <c r="CO39">
         <v>-0.8</v>
       </c>
-      <c r="CR39" s="2">
+      <c r="CR39">
         <v>6</v>
       </c>
-      <c r="CY39" s="2" t="s">
+      <c r="CY39" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="s">
+    <row r="40" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>488</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" t="s">
         <v>394</v>
       </c>
-      <c r="I40" s="2">
-        <v>1</v>
-      </c>
-      <c r="K40" s="2" t="s">
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="K40" t="s">
         <v>406</v>
       </c>
-      <c r="AC40" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG40" s="2" t="s">
+      <c r="AC40">
+        <v>1</v>
+      </c>
+      <c r="AG40" t="s">
         <v>427</v>
       </c>
-      <c r="AT40" s="2" t="s">
+      <c r="AT40" t="s">
         <v>477</v>
       </c>
-      <c r="AX40" s="2" t="s">
+      <c r="AX40" t="s">
         <v>478</v>
       </c>
-      <c r="AZ40" s="2">
+      <c r="AZ40">
         <v>0.09</v>
       </c>
-      <c r="BB40" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD40" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE40" s="2">
+      <c r="BB40">
+        <v>1</v>
+      </c>
+      <c r="BD40">
+        <v>1</v>
+      </c>
+      <c r="BE40">
         <v>11</v>
       </c>
-      <c r="BF40" s="2">
+      <c r="BF40">
         <v>0.5</v>
       </c>
-      <c r="CY40" s="2" t="s">
+      <c r="CY40" t="s">
         <v>491</v>
       </c>
-      <c r="DD40" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG40" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH40" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="549">
-      <c r="CL549" s="2">
+      <c r="DD40">
+        <v>1</v>
+      </c>
+      <c r="DG40">
+        <v>1</v>
+      </c>
+      <c r="DH40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="549" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL549">
         <v>0.15</v>
       </c>
     </row>
-    <row r="551">
-      <c r="CL551" s="2">
+    <row r="551" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL551">
         <v>0.2</v>
       </c>
     </row>
-    <row r="552">
-      <c r="CL552" s="2">
+    <row r="552" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL552">
         <v>0.1</v>
       </c>
     </row>
-    <row r="554">
-      <c r="CL554" s="2">
+    <row r="554" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL554">
         <v>0.2</v>
       </c>
     </row>
-    <row r="561">
-      <c r="CL561" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="563">
-      <c r="CL563" s="2">
+    <row r="561" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL561">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="563" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL563">
         <v>0.4</v>
       </c>
     </row>
-    <row r="564">
-      <c r="CL564" s="2">
+    <row r="564" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL564">
         <v>0.6</v>
       </c>
     </row>
-    <row r="567">
-      <c r="CL567" s="2">
+    <row r="567" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL567">
         <v>0.5</v>
       </c>
     </row>
-    <row r="568">
-      <c r="CL568" s="2">
-        <v>0.667</v>
-      </c>
-    </row>
-    <row r="569">
-      <c r="CL569" s="2">
+    <row r="568" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL568">
+        <v>0.66700000000000004</v>
+      </c>
+    </row>
+    <row r="569" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL569">
         <v>0.2</v>
       </c>
     </row>
@@ -6701,7 +6205,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -6711,224 +6214,224 @@
   <dimension ref="A1:Q293"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1" style="2"/>
-    <col min="2" max="2" width="31.25" customWidth="1" style="2"/>
-    <col min="3" max="6" width="9" customWidth="1" style="2"/>
-    <col min="7" max="7" width="18.75" customWidth="1" style="2"/>
-    <col min="8" max="8" width="15" customWidth="1" style="2"/>
-    <col min="9" max="13" width="9" customWidth="1" style="2"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1" style="2"/>
-    <col min="15" max="15" width="9.5" customWidth="1" style="2"/>
-    <col min="16" max="16" width="22.1640625" customWidth="1" style="2"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="31.25" customWidth="1"/>
+    <col min="3" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>493</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>494</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>495</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>496</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>497</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>498</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" t="s">
         <v>499</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" t="s">
         <v>500</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" t="s">
         <v>501</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" t="s">
         <v>502</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>504</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>505</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>506</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>507</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>508</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>509</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
         <v>510</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" t="s">
         <v>54</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" t="s">
         <v>511</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" t="s">
         <v>512</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" t="s">
         <v>513</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" t="s">
         <v>514</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
         <v>120</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>120</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
         <v>118</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" t="s">
         <v>118</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>391</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" t="s">
         <v>119</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" t="s">
         <v>355</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" t="s">
         <v>118</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" t="s">
         <v>118</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" t="s">
         <v>355</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" t="s">
         <v>118</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>403</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>516</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>241</v>
       </c>
-      <c r="H5" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="s">
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>454</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>515</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>459</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>518</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="Q7" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>520</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>241</v>
       </c>
-      <c r="H8" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="2" t="s">
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="292">
-      <c r="P292" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="P293" s="2">
+    <row r="292" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P293">
         <v>1</v>
       </c>
     </row>
@@ -6936,7 +6439,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6945,45 +6447,45 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="11.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="27.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>523</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>355</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>127</v>
       </c>
     </row>
@@ -6991,7 +6493,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -7000,79 +6501,79 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="27.25" customWidth="1" style="2"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="27.25" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="I1" s="2" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>524</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>525</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>526</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>527</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>350</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>120</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" t="s">
         <v>390</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>127</v>
       </c>
     </row>
@@ -7080,7 +6581,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -7089,122 +6589,122 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28" customWidth="1" style="2"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="11.25" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1" style="2"/>
-    <col min="12" max="12" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1"/>
+    <col min="5" max="10" width="11.25" customWidth="1"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>528</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>529</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>530</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>531</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>532</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>533</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>534</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>535</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>536</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>538</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>539</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>540</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>541</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>542</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>543</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>544</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>545</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>546</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
         <v>525</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>120</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>547</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
         <v>118</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" t="s">
         <v>120</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" t="s">
         <v>120</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" t="s">
         <v>119</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" t="s">
         <v>119</v>
       </c>
     </row>
@@ -7212,7 +6712,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -7222,49 +6721,49 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="16.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="10.25" customWidth="1" style="2"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1" style="2"/>
-    <col min="7" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.25" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>271</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>548</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>549</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>550</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>299</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>551</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1">
+    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -7299,7 +6798,6 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -7308,153 +6806,152 @@
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5" customWidth="1" style="2"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1" style="2"/>
-    <col min="3" max="3" width="21.9140625" customWidth="1" style="2"/>
-    <col min="4" max="4" width="16.25" customWidth="1" style="2"/>
-    <col min="5" max="5" width="14" customWidth="1" style="2"/>
-    <col min="6" max="7" width="15.1640625" customWidth="1" style="2"/>
-    <col min="8" max="8" width="12.9140625" customWidth="1" style="2"/>
-    <col min="9" max="9" width="14" customWidth="1" style="2"/>
+    <col min="1" max="1" width="7.5" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.9140625" customWidth="1"/>
+    <col min="4" max="4" width="16.25" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="7" width="15.1640625" customWidth="1"/>
+    <col min="8" max="8" width="12.9140625" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>553</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>554</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>555</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>556</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>557</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>558</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>559</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>561</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>562</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>563</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>564</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>565</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>566</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>567</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>569</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>570</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" t="s">
         <v>571</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" t="s">
         <v>572</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" t="s">
         <v>573</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>575</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>576</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" t="s">
         <v>577</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 

--- a/Excel/一方通行/酒神.xlsx
+++ b/Excel/一方通行/酒神.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E9CE42-305D-47A2-845A-3BAF2C1A0628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82D1E11-C19E-4868-B9AA-D136D3595111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -47,6 +47,30 @@
   </authors>
   <commentList>
     <comment ref="AK1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>PC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0:干员 1:敌人 2:仅技能条 3:技能+血条</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AM1" authorId="0" shapeId="0" xr:uid="{CA1BB709-EDE9-4030-A1B6-8C153328778E}">
       <text>
         <r>
           <rPr>
@@ -299,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="584">
   <si>
     <t>Id</t>
   </si>
@@ -388,9 +412,6 @@
     <t>可选技能</t>
   </si>
   <si>
-    <t>血条类型</t>
-  </si>
-  <si>
     <t>高度</t>
   </si>
   <si>
@@ -2033,13 +2054,41 @@
   </si>
   <si>
     <t>/Spine/本能的召唤/front/token_10054_phatm2_encdool.skel.bytes</t>
+  </si>
+  <si>
+    <t>血条</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技力条</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpBarType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:蓝</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:绿</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2065,6 +2114,21 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2092,11 +2156,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2442,7 +2512,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BT12"/>
+  <dimension ref="A1:BU12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -2474,28 +2544,28 @@
     <col min="35" max="35" width="15.83203125" customWidth="1"/>
     <col min="36" max="36" width="13.83203125" customWidth="1"/>
     <col min="37" max="37" width="34.5" customWidth="1"/>
-    <col min="38" max="39" width="9.83203125" customWidth="1"/>
-    <col min="40" max="43" width="9" customWidth="1"/>
-    <col min="44" max="44" width="12.5" customWidth="1"/>
-    <col min="45" max="50" width="9" customWidth="1"/>
-    <col min="51" max="51" width="24.33203125" customWidth="1"/>
-    <col min="52" max="52" width="9" customWidth="1"/>
-    <col min="53" max="53" width="17.75" customWidth="1"/>
-    <col min="54" max="54" width="7.83203125" customWidth="1"/>
-    <col min="55" max="56" width="9" customWidth="1"/>
-    <col min="57" max="57" width="24.25" customWidth="1"/>
-    <col min="58" max="58" width="13.25" customWidth="1"/>
-    <col min="59" max="59" width="16.08203125" customWidth="1"/>
-    <col min="60" max="60" width="8" customWidth="1"/>
-    <col min="61" max="64" width="9" customWidth="1"/>
-    <col min="65" max="65" width="39.58203125" customWidth="1"/>
-    <col min="66" max="66" width="14" customWidth="1"/>
-    <col min="67" max="67" width="14.83203125" customWidth="1"/>
-    <col min="68" max="71" width="14" customWidth="1"/>
-    <col min="72" max="72" width="19.1640625" customWidth="1"/>
+    <col min="38" max="40" width="9.83203125" customWidth="1"/>
+    <col min="41" max="44" width="9" customWidth="1"/>
+    <col min="45" max="45" width="12.5" customWidth="1"/>
+    <col min="46" max="51" width="9" customWidth="1"/>
+    <col min="52" max="52" width="24.33203125" customWidth="1"/>
+    <col min="53" max="53" width="9" customWidth="1"/>
+    <col min="54" max="54" width="17.75" customWidth="1"/>
+    <col min="55" max="55" width="7.83203125" customWidth="1"/>
+    <col min="56" max="57" width="9" customWidth="1"/>
+    <col min="58" max="58" width="24.25" customWidth="1"/>
+    <col min="59" max="59" width="13.25" customWidth="1"/>
+    <col min="60" max="60" width="16.08203125" customWidth="1"/>
+    <col min="61" max="61" width="8" customWidth="1"/>
+    <col min="62" max="65" width="9" customWidth="1"/>
+    <col min="66" max="66" width="39.58203125" customWidth="1"/>
+    <col min="67" max="67" width="14" customWidth="1"/>
+    <col min="68" max="68" width="14.83203125" customWidth="1"/>
+    <col min="69" max="72" width="14" customWidth="1"/>
+    <col min="73" max="73" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
         <v>5</v>
       </c>
@@ -2571,280 +2641,286 @@
       <c r="AL1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="AO1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AU1" t="s">
         <v>34</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>35</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>36</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>38</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>39</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>40</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>41</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>42</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BF1" t="s">
         <v>43</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>44</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>45</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>46</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>47</v>
       </c>
-      <c r="BI1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>50</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>51</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>52</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>53</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>54</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>55</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>56</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>57</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>58</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>59</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>60</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>61</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>62</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>63</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>64</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>65</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>66</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>67</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>68</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>69</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>70</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>71</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>72</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>73</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>74</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>75</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>76</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>77</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>78</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>79</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>80</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" t="s">
         <v>81</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AL2" t="s">
         <v>82</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AM2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="AO2" t="s">
         <v>84</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AP2" t="s">
         <v>85</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AQ2" t="s">
         <v>86</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AR2" t="s">
         <v>87</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AS2" t="s">
         <v>88</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AT2" t="s">
         <v>89</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AU2" t="s">
         <v>90</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AV2" t="s">
         <v>91</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AW2" t="s">
         <v>92</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AX2" t="s">
         <v>93</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AY2" t="s">
         <v>94</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AZ2" t="s">
         <v>95</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BA2" t="s">
         <v>96</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BB2" t="s">
         <v>97</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BC2" t="s">
         <v>98</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BD2" t="s">
         <v>99</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BE2" t="s">
         <v>100</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BF2" t="s">
         <v>101</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BG2" t="s">
         <v>102</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BH2" t="s">
         <v>103</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BI2" t="s">
         <v>104</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BJ2" t="s">
         <v>105</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BK2" t="s">
         <v>106</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BL2" t="s">
         <v>107</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BM2" t="s">
         <v>108</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BN2" t="s">
         <v>109</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BO2" t="s">
         <v>110</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BP2" t="s">
         <v>111</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BQ2" t="s">
         <v>112</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BR2" t="s">
         <v>113</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BS2" t="s">
         <v>114</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BT2" t="s">
         <v>115</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BU2" t="s">
         <v>116</v>
       </c>
-      <c r="BT2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:72" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2852,94 +2928,94 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F3" t="s">
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="S3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U3" t="s">
+        <v>118</v>
+      </c>
+      <c r="V3" t="s">
         <v>119</v>
       </c>
-      <c r="V3" t="s">
-        <v>120</v>
-      </c>
       <c r="W3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X3" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA3" t="s">
         <v>119</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AB3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC3" t="s">
         <v>119</v>
       </c>
-      <c r="Z3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>120</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>120</v>
-      </c>
       <c r="AD3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AE3" t="s">
         <v>2</v>
       </c>
       <c r="AF3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AH3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AI3" t="s">
         <v>2</v>
@@ -2948,22 +3024,22 @@
         <v>2</v>
       </c>
       <c r="AK3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP3" t="s">
         <v>121</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>120</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>120</v>
       </c>
       <c r="AQ3" t="s">
         <v>119</v>
@@ -2971,38 +3047,38 @@
       <c r="AR3" t="s">
         <v>118</v>
       </c>
-      <c r="AT3" t="s">
-        <v>119</v>
+      <c r="AS3" t="s">
+        <v>117</v>
       </c>
       <c r="AU3" t="s">
         <v>118</v>
       </c>
       <c r="AV3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="AW3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AZ3" t="s">
         <v>123</v>
       </c>
-      <c r="AX3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AY3" t="s">
+      <c r="BA3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD3" t="s">
         <v>124</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>125</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>2</v>
       </c>
       <c r="BE3" t="s">
         <v>2</v>
@@ -3014,54 +3090,57 @@
         <v>2</v>
       </c>
       <c r="BH3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BN3" t="s">
         <v>126</v>
       </c>
-      <c r="BI3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>122</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>127</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>122</v>
-      </c>
       <c r="BO3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BP3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BQ3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BR3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BS3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BT3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:72" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F4" t="s">
         <v>128</v>
-      </c>
-      <c r="F4" t="s">
-        <v>129</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -3112,78 +3191,84 @@
         <v>4</v>
       </c>
       <c r="AJ4" t="s">
+        <v>129</v>
+      </c>
+      <c r="AK4" t="s">
         <v>130</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>131</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="AP4" t="s">
         <v>132</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AQ4">
+        <v>1</v>
+      </c>
+      <c r="AR4">
+        <v>0.5</v>
+      </c>
+      <c r="AY4">
+        <v>0.25</v>
+      </c>
+      <c r="BD4" t="s">
         <v>133</v>
       </c>
-      <c r="AP4">
-        <v>1</v>
-      </c>
-      <c r="AQ4">
-        <v>0.5</v>
-      </c>
-      <c r="AX4">
-        <v>0.25</v>
-      </c>
-      <c r="BC4" t="s">
+      <c r="BE4" t="s">
         <v>134</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BF4" t="s">
         <v>135</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BG4" t="s">
         <v>136</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BH4" t="s">
         <v>137</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BI4" t="s">
         <v>138</v>
       </c>
-      <c r="BH4" t="s">
+      <c r="BJ4">
+        <v>6</v>
+      </c>
+      <c r="BK4" t="s">
         <v>139</v>
       </c>
-      <c r="BI4">
-        <v>6</v>
-      </c>
-      <c r="BJ4" t="s">
+      <c r="BL4" t="s">
         <v>140</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BO4" t="s">
         <v>141</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BP4" t="s">
         <v>142</v>
       </c>
-      <c r="BO4" t="s">
+      <c r="BR4" t="s">
         <v>143</v>
       </c>
-      <c r="BQ4" t="s">
+      <c r="BS4" t="s">
+        <v>143</v>
+      </c>
+      <c r="BU4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>144</v>
       </c>
-      <c r="BR4" t="s">
-        <v>144</v>
-      </c>
-      <c r="BT4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:72" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" t="s">
         <v>145</v>
-      </c>
-      <c r="B8" t="s">
-        <v>128</v>
-      </c>
-      <c r="F8" t="s">
-        <v>146</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -3231,81 +3316,84 @@
         <v>-1</v>
       </c>
       <c r="AI8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AJ8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AK8" t="s">
+        <v>146</v>
+      </c>
+      <c r="AM8" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="AN8" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="AO8">
+        <v>-0.5</v>
+      </c>
+      <c r="AP8" t="s">
         <v>147</v>
-      </c>
-      <c r="AM8">
-        <v>3</v>
-      </c>
-      <c r="AN8">
-        <v>-0.5</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>148</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
       </c>
       <c r="AQ8">
         <v>0</v>
       </c>
-      <c r="AX8">
+      <c r="AR8">
         <v>0</v>
       </c>
-      <c r="BA8">
-        <v>1</v>
-      </c>
-      <c r="BC8" t="s">
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>1</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>148</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG8" t="s">
         <v>149</v>
       </c>
-      <c r="BE8" t="s">
-        <v>136</v>
-      </c>
-      <c r="BF8" t="s">
+      <c r="BH8" t="s">
         <v>150</v>
       </c>
-      <c r="BG8" t="s">
+      <c r="BI8" t="s">
+        <v>138</v>
+      </c>
+      <c r="BJ8">
+        <v>5</v>
+      </c>
+      <c r="BK8" t="s">
         <v>151</v>
       </c>
-      <c r="BH8" t="s">
-        <v>139</v>
-      </c>
-      <c r="BI8">
-        <v>5</v>
-      </c>
-      <c r="BJ8" t="s">
+      <c r="BO8" t="s">
+        <v>141</v>
+      </c>
+      <c r="BP8" t="s">
         <v>152</v>
       </c>
-      <c r="BN8" t="s">
-        <v>142</v>
-      </c>
-      <c r="BO8" t="s">
+      <c r="BR8" t="s">
         <v>153</v>
       </c>
-      <c r="BQ8" t="s">
+      <c r="BS8" t="s">
+        <v>153</v>
+      </c>
+      <c r="BU8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>154</v>
       </c>
-      <c r="BR8" t="s">
-        <v>154</v>
-      </c>
-      <c r="BT8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:72" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>155</v>
-      </c>
       <c r="B9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -3356,87 +3444,90 @@
         <v>-1</v>
       </c>
       <c r="AI9" t="s">
+        <v>154</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>129</v>
+      </c>
+      <c r="AK9" t="s">
         <v>155</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>130</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>156</v>
-      </c>
-      <c r="AM9">
-        <v>3</v>
-      </c>
-      <c r="AN9">
+      <c r="AM9" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="AN9" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="AO9">
         <v>-0.5</v>
       </c>
-      <c r="AO9" t="s">
-        <v>148</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
+      <c r="AP9" t="s">
+        <v>147</v>
       </c>
       <c r="AQ9">
         <v>0</v>
       </c>
-      <c r="AX9">
+      <c r="AR9">
         <v>0</v>
       </c>
-      <c r="BA9">
-        <v>1</v>
-      </c>
-      <c r="BC9" t="s">
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>1</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>148</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG9" t="s">
         <v>149</v>
       </c>
-      <c r="BE9" t="s">
-        <v>136</v>
-      </c>
-      <c r="BF9" t="s">
+      <c r="BH9" t="s">
         <v>150</v>
       </c>
-      <c r="BG9" t="s">
+      <c r="BI9" t="s">
+        <v>138</v>
+      </c>
+      <c r="BJ9">
+        <v>5</v>
+      </c>
+      <c r="BK9" t="s">
         <v>151</v>
       </c>
-      <c r="BH9" t="s">
-        <v>139</v>
-      </c>
-      <c r="BI9">
-        <v>5</v>
-      </c>
-      <c r="BJ9" t="s">
+      <c r="BO9" t="s">
+        <v>141</v>
+      </c>
+      <c r="BP9" t="s">
         <v>152</v>
       </c>
-      <c r="BN9" t="s">
-        <v>142</v>
-      </c>
-      <c r="BO9" t="s">
+      <c r="BR9" t="s">
         <v>153</v>
       </c>
-      <c r="BQ9" t="s">
-        <v>154</v>
-      </c>
-      <c r="BR9" t="s">
-        <v>154</v>
-      </c>
-      <c r="BT9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="BS9" t="s">
+        <v>153</v>
+      </c>
+      <c r="BU9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" t="s">
         <v>157</v>
       </c>
-      <c r="B10" t="s">
-        <v>128</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
+        <v>157</v>
+      </c>
+      <c r="F10" t="s">
         <v>158</v>
-      </c>
-      <c r="E10" t="s">
-        <v>158</v>
-      </c>
-      <c r="F10" t="s">
-        <v>159</v>
       </c>
       <c r="G10">
         <v>0.01</v>
@@ -3487,90 +3578,93 @@
         <v>-1</v>
       </c>
       <c r="AI10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AJ10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AK10" t="s">
-        <v>160</v>
-      </c>
-      <c r="AM10">
-        <v>3</v>
-      </c>
-      <c r="AN10">
+        <v>159</v>
+      </c>
+      <c r="AM10" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="AN10" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="AO10">
         <v>-0.5</v>
       </c>
-      <c r="AO10" t="s">
-        <v>148</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
+      <c r="AP10" t="s">
+        <v>147</v>
       </c>
       <c r="AQ10">
         <v>0</v>
       </c>
       <c r="AR10">
-        <v>1</v>
-      </c>
-      <c r="AX10">
         <v>0</v>
       </c>
-      <c r="BA10">
-        <v>1</v>
-      </c>
-      <c r="BC10" t="s">
-        <v>149</v>
-      </c>
-      <c r="BE10" t="s">
-        <v>136</v>
+      <c r="AS10">
+        <v>1</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>1</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>148</v>
       </c>
       <c r="BF10" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>160</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>157</v>
+      </c>
+      <c r="BI10" t="s">
+        <v>138</v>
+      </c>
+      <c r="BJ10">
+        <v>5</v>
+      </c>
+      <c r="BK10" t="s">
+        <v>151</v>
+      </c>
+      <c r="BO10" t="s">
+        <v>141</v>
+      </c>
+      <c r="BP10" t="s">
+        <v>142</v>
+      </c>
+      <c r="BR10" t="s">
+        <v>143</v>
+      </c>
+      <c r="BS10" t="s">
+        <v>143</v>
+      </c>
+      <c r="BU10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>161</v>
       </c>
-      <c r="BG10" t="s">
+      <c r="B12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" t="s">
+        <v>157</v>
+      </c>
+      <c r="E12" t="s">
+        <v>157</v>
+      </c>
+      <c r="F12" t="s">
         <v>158</v>
-      </c>
-      <c r="BH10" t="s">
-        <v>139</v>
-      </c>
-      <c r="BI10">
-        <v>5</v>
-      </c>
-      <c r="BJ10" t="s">
-        <v>152</v>
-      </c>
-      <c r="BN10" t="s">
-        <v>142</v>
-      </c>
-      <c r="BO10" t="s">
-        <v>143</v>
-      </c>
-      <c r="BQ10" t="s">
-        <v>144</v>
-      </c>
-      <c r="BR10" t="s">
-        <v>144</v>
-      </c>
-      <c r="BT10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:72" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>162</v>
-      </c>
-      <c r="B12" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E12" t="s">
-        <v>158</v>
-      </c>
-      <c r="F12" t="s">
-        <v>159</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -3615,69 +3709,72 @@
         <v>1</v>
       </c>
       <c r="AI12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AJ12" t="s">
-        <v>130</v>
-      </c>
-      <c r="AM12">
-        <v>3</v>
-      </c>
-      <c r="AN12">
+        <v>129</v>
+      </c>
+      <c r="AM12" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="AN12" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="AO12">
         <v>-0.5</v>
       </c>
-      <c r="AO12" t="s">
+      <c r="AP12" t="s">
+        <v>147</v>
+      </c>
+      <c r="AQ12">
+        <v>99</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>1</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>1</v>
+      </c>
+      <c r="BD12" t="s">
         <v>148</v>
       </c>
-      <c r="AP12">
-        <v>99</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>1</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>1</v>
-      </c>
-      <c r="BC12" t="s">
-        <v>149</v>
-      </c>
-      <c r="BE12" t="s">
-        <v>136</v>
-      </c>
       <c r="BF12" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="BG12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BH12" t="s">
-        <v>139</v>
-      </c>
-      <c r="BI12">
+        <v>157</v>
+      </c>
+      <c r="BI12" t="s">
+        <v>138</v>
+      </c>
+      <c r="BJ12">
         <v>5</v>
       </c>
-      <c r="BJ12" t="s">
-        <v>152</v>
-      </c>
-      <c r="BN12" t="s">
+      <c r="BK12" t="s">
+        <v>151</v>
+      </c>
+      <c r="BO12" t="s">
+        <v>141</v>
+      </c>
+      <c r="BP12" t="s">
         <v>142</v>
       </c>
-      <c r="BO12" t="s">
+      <c r="BR12" t="s">
         <v>143</v>
       </c>
-      <c r="BQ12" t="s">
-        <v>144</v>
-      </c>
-      <c r="BR12" t="s">
-        <v>144</v>
-      </c>
-      <c r="BT12">
+      <c r="BS12" t="s">
+        <v>143</v>
+      </c>
+      <c r="BU12">
         <v>1</v>
       </c>
     </row>
@@ -3785,334 +3882,334 @@
   <sheetData>
     <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1" t="s">
         <v>164</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>165</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>166</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>167</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>168</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>169</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>170</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>171</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>172</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>173</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>174</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>175</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>176</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>177</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>178</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>179</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>180</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
+        <v>180</v>
+      </c>
+      <c r="V1" t="s">
         <v>181</v>
       </c>
-      <c r="U1" t="s">
-        <v>181</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>182</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>183</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>184</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>185</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>186</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>187</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>188</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>189</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>190</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>191</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>192</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>193</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>194</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>195</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>196</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>197</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>198</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>199</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>200</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>201</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>202</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>203</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>204</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>205</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>206</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>207</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>208</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>209</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>210</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>211</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>212</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>213</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>214</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>215</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>216</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>217</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>218</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>219</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
+        <v>219</v>
+      </c>
+      <c r="BK1" t="s">
         <v>220</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>220</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>221</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>222</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>223</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>224</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>225</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>226</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>227</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>228</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>229</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>230</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>231</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>232</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>233</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BY1" t="s">
         <v>234</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BZ1" t="s">
         <v>235</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" t="s">
         <v>236</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CB1" t="s">
         <v>237</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>238</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
         <v>239</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" t="s">
         <v>240</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CF1" t="s">
         <v>241</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CG1" t="s">
         <v>242</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CH1" t="s">
         <v>243</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CI1" t="s">
         <v>244</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CJ1" t="s">
         <v>245</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CK1" t="s">
         <v>246</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CL1" t="s">
         <v>247</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CM1" t="s">
         <v>248</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CN1" t="s">
         <v>249</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CO1" t="s">
         <v>250</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CP1" t="s">
         <v>251</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CQ1" t="s">
         <v>252</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CR1" t="s">
+        <v>229</v>
+      </c>
+      <c r="CS1" t="s">
         <v>253</v>
       </c>
-      <c r="CR1" t="s">
-        <v>230</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CT1" t="s">
         <v>254</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CU1" t="s">
         <v>255</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>256</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>257</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
         <v>258</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CY1" t="s">
         <v>259</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="CZ1" t="s">
+        <v>258</v>
+      </c>
+      <c r="DA1" t="s">
         <v>260</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>259</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="DB1" t="s">
         <v>261</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DC1" t="s">
         <v>262</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DD1" t="s">
         <v>263</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DE1" t="s">
         <v>264</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DF1" t="s">
         <v>265</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DG1" t="s">
         <v>266</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DH1" t="s">
         <v>267</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="DI1" t="s">
         <v>268</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:113" x14ac:dyDescent="0.25">
@@ -4120,337 +4217,337 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F2" t="s">
         <v>270</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" t="s">
         <v>271</v>
       </c>
-      <c r="G2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>272</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>273</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>274</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>275</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>276</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>277</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>278</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>279</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>280</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>281</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>282</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>283</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>284</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>285</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>286</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>287</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>288</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>289</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>290</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>291</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>292</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>293</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>294</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>295</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>296</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>297</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>298</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>299</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" t="s">
         <v>300</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AL2" t="s">
         <v>301</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AM2" t="s">
         <v>302</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>303</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AO2" t="s">
         <v>304</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AP2" t="s">
         <v>305</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>306</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AR2" t="s">
         <v>307</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AS2" t="s">
         <v>308</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AT2" t="s">
         <v>309</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AU2" t="s">
         <v>310</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AV2" t="s">
         <v>311</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>312</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>313</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>314</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>315</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>316</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>317</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>318</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>319</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>320</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>321</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
         <v>322</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>323</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>324</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>325</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>326</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>327</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BM2" t="s">
         <v>328</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BN2" t="s">
         <v>329</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BO2" t="s">
+        <v>81</v>
+      </c>
+      <c r="BP2" t="s">
         <v>330</v>
       </c>
-      <c r="BO2" t="s">
-        <v>82</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="BQ2" t="s">
         <v>331</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BR2" t="s">
         <v>332</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BS2" t="s">
         <v>333</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BT2" t="s">
         <v>334</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BU2" t="s">
+        <v>96</v>
+      </c>
+      <c r="BV2" t="s">
         <v>335</v>
       </c>
-      <c r="BU2" t="s">
-        <v>97</v>
-      </c>
-      <c r="BV2" t="s">
+      <c r="BW2" t="s">
         <v>336</v>
       </c>
-      <c r="BW2" t="s">
+      <c r="BX2" t="s">
         <v>337</v>
       </c>
-      <c r="BX2" t="s">
+      <c r="BY2" t="s">
         <v>338</v>
       </c>
-      <c r="BY2" t="s">
+      <c r="BZ2" t="s">
         <v>339</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CA2" t="s">
         <v>340</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CB2" t="s">
         <v>341</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CC2" t="s">
         <v>342</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CD2" t="s">
         <v>343</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CE2" t="s">
         <v>344</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CF2" t="s">
         <v>345</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CG2" t="s">
         <v>346</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CH2" t="s">
         <v>347</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CI2" t="s">
         <v>348</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CJ2" t="s">
         <v>349</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CK2" t="s">
         <v>350</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CL2" t="s">
         <v>351</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CM2" t="s">
         <v>352</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CN2" t="s">
         <v>353</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CO2" t="s">
         <v>354</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CP2" t="s">
         <v>355</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CQ2" t="s">
         <v>356</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CR2" t="s">
         <v>357</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CS2" t="s">
         <v>358</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CT2" t="s">
         <v>359</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CU2" t="s">
         <v>360</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CV2" t="s">
         <v>361</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CW2" t="s">
         <v>362</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CX2" t="s">
         <v>363</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CY2" t="s">
         <v>364</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="CZ2" t="s">
         <v>365</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DA2" t="s">
         <v>366</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DB2" t="s">
         <v>367</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DC2" t="s">
         <v>368</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DD2" t="s">
         <v>369</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DE2" t="s">
         <v>370</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DF2" t="s">
         <v>371</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DG2" t="s">
         <v>372</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DH2" t="s">
         <v>373</v>
       </c>
-      <c r="DH2" t="s">
+      <c r="DI2" t="s">
         <v>374</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -4470,112 +4567,112 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J3" t="s">
+        <v>375</v>
+      </c>
+      <c r="K3" t="s">
+        <v>376</v>
+      </c>
+      <c r="L3" t="s">
+        <v>377</v>
+      </c>
+      <c r="M3" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" t="s">
+        <v>119</v>
+      </c>
+      <c r="O3" t="s">
+        <v>122</v>
+      </c>
+      <c r="P3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>122</v>
+      </c>
+      <c r="R3" t="s">
+        <v>122</v>
+      </c>
+      <c r="S3" t="s">
+        <v>117</v>
+      </c>
+      <c r="T3" t="s">
         <v>118</v>
       </c>
-      <c r="J3" t="s">
-        <v>376</v>
-      </c>
-      <c r="K3" t="s">
-        <v>377</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="U3" t="s">
+        <v>118</v>
+      </c>
+      <c r="V3" t="s">
+        <v>118</v>
+      </c>
+      <c r="W3" t="s">
+        <v>117</v>
+      </c>
+      <c r="X3" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AG3" t="s">
         <v>378</v>
       </c>
-      <c r="M3" t="s">
-        <v>120</v>
-      </c>
-      <c r="N3" t="s">
-        <v>120</v>
-      </c>
-      <c r="O3" t="s">
-        <v>123</v>
-      </c>
-      <c r="P3" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>123</v>
-      </c>
-      <c r="R3" t="s">
-        <v>123</v>
-      </c>
-      <c r="S3" t="s">
-        <v>118</v>
-      </c>
-      <c r="T3" t="s">
-        <v>119</v>
-      </c>
-      <c r="U3" t="s">
-        <v>119</v>
-      </c>
-      <c r="V3" t="s">
-        <v>119</v>
-      </c>
-      <c r="W3" t="s">
-        <v>118</v>
-      </c>
-      <c r="X3" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>120</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>379</v>
-      </c>
       <c r="AH3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AI3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AJ3" t="s">
         <v>3</v>
       </c>
       <c r="AK3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AL3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AM3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AN3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AO3" t="s">
+        <v>379</v>
+      </c>
+      <c r="AP3" t="s">
         <v>380</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>381</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
@@ -4587,224 +4684,224 @@
         <v>2</v>
       </c>
       <c r="AT3" t="s">
+        <v>381</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AX3" t="s">
         <v>382</v>
       </c>
-      <c r="AU3" t="s">
+      <c r="AY3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AZ3" t="s">
         <v>118</v>
       </c>
-      <c r="AV3" t="s">
+      <c r="BA3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BB3" t="s">
         <v>119</v>
       </c>
-      <c r="AW3" t="s">
+      <c r="BC3" t="s">
         <v>118</v>
       </c>
-      <c r="AX3" t="s">
+      <c r="BD3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>381</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BQ3" t="s">
         <v>383</v>
       </c>
-      <c r="AY3" t="s">
+      <c r="BR3" t="s">
+        <v>384</v>
+      </c>
+      <c r="BS3" t="s">
         <v>118</v>
       </c>
-      <c r="AZ3" t="s">
+      <c r="BT3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX3" t="s">
         <v>119</v>
       </c>
-      <c r="BA3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>382</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BO3" t="s">
+      <c r="BY3" t="s">
+        <v>385</v>
+      </c>
+      <c r="BZ3" t="s">
+        <v>117</v>
+      </c>
+      <c r="CA3" t="s">
+        <v>385</v>
+      </c>
+      <c r="CB3" t="s">
         <v>121</v>
       </c>
-      <c r="BP3" t="s">
+      <c r="CC3" t="s">
+        <v>386</v>
+      </c>
+      <c r="CD3" t="s">
         <v>121</v>
       </c>
-      <c r="BQ3" t="s">
-        <v>384</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>385</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BY3" t="s">
-        <v>386</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>118</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>386</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>122</v>
-      </c>
-      <c r="CC3" t="s">
+      <c r="CE3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CG3" t="s">
         <v>387</v>
       </c>
-      <c r="CD3" t="s">
-        <v>122</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>122</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>122</v>
-      </c>
-      <c r="CG3" t="s">
+      <c r="CH3" t="s">
         <v>388</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>389</v>
       </c>
       <c r="CI3" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" t="s">
+        <v>389</v>
+      </c>
+      <c r="CK3" t="s">
+        <v>389</v>
+      </c>
+      <c r="CL3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CM3" t="s">
+        <v>122</v>
+      </c>
+      <c r="CN3" t="s">
+        <v>122</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CQ3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CR3" t="s">
+        <v>386</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>117</v>
+      </c>
+      <c r="CU3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CV3" t="s">
         <v>390</v>
       </c>
-      <c r="CK3" t="s">
+      <c r="CW3" t="s">
+        <v>391</v>
+      </c>
+      <c r="CX3" t="s">
+        <v>391</v>
+      </c>
+      <c r="CY3" t="s">
         <v>390</v>
       </c>
-      <c r="CL3" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CO3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CQ3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CR3" t="s">
-        <v>387</v>
-      </c>
-      <c r="CS3" t="s">
-        <v>126</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>118</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>127</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>391</v>
-      </c>
-      <c r="CW3" t="s">
-        <v>392</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>392</v>
-      </c>
-      <c r="CY3" t="s">
-        <v>391</v>
-      </c>
       <c r="CZ3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="DA3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="DB3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="DC3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="DD3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="DE3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="DF3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="DG3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="DH3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="DI3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C5" t="s">
+        <v>393</v>
+      </c>
+      <c r="K5" t="s">
         <v>394</v>
-      </c>
-      <c r="K5" t="s">
-        <v>395</v>
       </c>
       <c r="S5">
         <v>1</v>
@@ -4816,13 +4913,13 @@
         <v>1</v>
       </c>
       <c r="AO5" t="s">
+        <v>395</v>
+      </c>
+      <c r="AT5" t="s">
         <v>396</v>
       </c>
-      <c r="AT5" t="s">
+      <c r="AX5" t="s">
         <v>397</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>398</v>
       </c>
       <c r="AZ5">
         <v>1</v>
@@ -4840,39 +4937,39 @@
         <v>0</v>
       </c>
       <c r="BO5" t="s">
+        <v>398</v>
+      </c>
+      <c r="BP5" t="s">
         <v>399</v>
       </c>
-      <c r="BP5" t="s">
+      <c r="CB5" t="s">
         <v>400</v>
       </c>
-      <c r="CB5" t="s">
+      <c r="CG5" t="s">
         <v>401</v>
       </c>
-      <c r="CG5" t="s">
+      <c r="CN5" t="s">
         <v>402</v>
-      </c>
-      <c r="CN5" t="s">
-        <v>403</v>
       </c>
       <c r="CR5">
         <v>0.1</v>
       </c>
       <c r="CY5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>404</v>
+      </c>
+      <c r="C6" t="s">
+        <v>393</v>
+      </c>
+      <c r="K6" t="s">
         <v>405</v>
       </c>
-      <c r="C6" t="s">
-        <v>394</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="R6" t="s">
         <v>406</v>
-      </c>
-      <c r="R6" t="s">
-        <v>407</v>
       </c>
       <c r="AC6">
         <v>2</v>
@@ -4881,33 +4978,33 @@
         <v>1</v>
       </c>
       <c r="AO6" t="s">
+        <v>395</v>
+      </c>
+      <c r="AT6" t="s">
         <v>396</v>
       </c>
-      <c r="AT6" t="s">
-        <v>397</v>
-      </c>
       <c r="BD6">
         <v>1</v>
       </c>
       <c r="CL6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="CM6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Q7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="R7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AC7">
         <v>2</v>
@@ -4916,7 +5013,7 @@
         <v>1</v>
       </c>
       <c r="AO7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AV7">
         <v>99</v>
@@ -4928,36 +5025,36 @@
         <v>0.1</v>
       </c>
       <c r="CL7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="CM7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>409</v>
+      </c>
+      <c r="C10" t="s">
+        <v>393</v>
+      </c>
+      <c r="D10" t="s">
         <v>410</v>
       </c>
-      <c r="C10" t="s">
-        <v>394</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>411</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>412</v>
-      </c>
-      <c r="F10" t="s">
-        <v>413</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="J10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AC10">
         <v>2</v>
@@ -4966,13 +5063,13 @@
         <v>1</v>
       </c>
       <c r="AO10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AT10" t="s">
+        <v>396</v>
+      </c>
+      <c r="AX10" t="s">
         <v>397</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>398</v>
       </c>
       <c r="AZ10">
         <v>1.5</v>
@@ -4996,10 +5093,10 @@
         <v>0</v>
       </c>
       <c r="BO10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="BP10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="BT10">
         <v>0.3</v>
@@ -5014,22 +5111,22 @@
         <v>1</v>
       </c>
       <c r="BY10" t="s">
+        <v>416</v>
+      </c>
+      <c r="CB10" t="s">
         <v>417</v>
       </c>
-      <c r="CB10" t="s">
-        <v>418</v>
-      </c>
       <c r="CG10" t="s">
+        <v>401</v>
+      </c>
+      <c r="CN10" t="s">
         <v>402</v>
-      </c>
-      <c r="CN10" t="s">
-        <v>403</v>
       </c>
       <c r="CR10">
         <v>0.1</v>
       </c>
       <c r="CY10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="DD10">
         <v>1</v>
@@ -5043,13 +5140,13 @@
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AC11">
         <v>2</v>
@@ -5058,10 +5155,10 @@
         <v>1</v>
       </c>
       <c r="AO11" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AT11" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="BD11">
         <v>1</v>
@@ -5073,13 +5170,13 @@
         <v>0.1</v>
       </c>
       <c r="CL11" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="CM11" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="CN11" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="CR11">
         <v>3</v>
@@ -5087,16 +5184,16 @@
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>419</v>
+      </c>
+      <c r="C12" t="s">
+        <v>393</v>
+      </c>
+      <c r="K12" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q12" t="s">
         <v>420</v>
-      </c>
-      <c r="C12" t="s">
-        <v>394</v>
-      </c>
-      <c r="K12" t="s">
-        <v>406</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>421</v>
       </c>
       <c r="AC12">
         <v>2</v>
@@ -5105,10 +5202,10 @@
         <v>1</v>
       </c>
       <c r="AO12" t="s">
+        <v>395</v>
+      </c>
+      <c r="AT12" t="s">
         <v>396</v>
-      </c>
-      <c r="AT12" t="s">
-        <v>397</v>
       </c>
       <c r="BD12">
         <v>1</v>
@@ -5120,36 +5217,36 @@
         <v>0.1</v>
       </c>
       <c r="CL12" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="CM12" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>421</v>
+      </c>
+      <c r="C14" t="s">
         <v>422</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>423</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>424</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>425</v>
-      </c>
-      <c r="F14" t="s">
-        <v>426</v>
       </c>
       <c r="G14">
         <v>3</v>
       </c>
       <c r="J14" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AC14">
         <v>1</v>
@@ -5158,16 +5255,16 @@
         <v>1</v>
       </c>
       <c r="AG14" t="s">
+        <v>426</v>
+      </c>
+      <c r="BD14">
+        <v>1</v>
+      </c>
+      <c r="BO14" t="s">
         <v>427</v>
       </c>
-      <c r="BD14">
-        <v>1</v>
-      </c>
-      <c r="BO14" t="s">
+      <c r="BP14" t="s">
         <v>428</v>
-      </c>
-      <c r="BP14" t="s">
-        <v>429</v>
       </c>
       <c r="BT14">
         <v>9999</v>
@@ -5182,10 +5279,10 @@
         <v>1</v>
       </c>
       <c r="BY14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="CN14" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="CO14">
         <v>35</v>
@@ -5194,7 +5291,7 @@
         <v>9999</v>
       </c>
       <c r="CU14" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="DD14">
         <v>1</v>
@@ -5208,16 +5305,16 @@
     </row>
     <row r="15" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C15" t="s">
+        <v>393</v>
+      </c>
+      <c r="K15" t="s">
         <v>394</v>
       </c>
-      <c r="K15" t="s">
-        <v>395</v>
-      </c>
       <c r="O15" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AC15">
         <v>2</v>
@@ -5226,13 +5323,13 @@
         <v>1</v>
       </c>
       <c r="AO15" t="s">
+        <v>395</v>
+      </c>
+      <c r="AT15" t="s">
         <v>396</v>
       </c>
-      <c r="AT15" t="s">
+      <c r="AX15" t="s">
         <v>397</v>
-      </c>
-      <c r="AX15" t="s">
-        <v>398</v>
       </c>
       <c r="AZ15">
         <v>1</v>
@@ -5250,45 +5347,45 @@
         <v>0</v>
       </c>
       <c r="BO15" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="BP15" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="CB15" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="CG15" t="s">
+        <v>401</v>
+      </c>
+      <c r="CN15" t="s">
         <v>402</v>
-      </c>
-      <c r="CN15" t="s">
-        <v>403</v>
       </c>
       <c r="CR15">
         <v>0.1</v>
       </c>
       <c r="CY15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C16" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I16">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AC16">
         <v>1</v>
       </c>
       <c r="AG16" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BD16">
         <v>1</v>
@@ -5297,10 +5394,10 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="CB16" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="CG16" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="DD16">
         <v>1</v>
@@ -5317,49 +5414,49 @@
     </row>
     <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>435</v>
+      </c>
+      <c r="C18" t="s">
+        <v>393</v>
+      </c>
+      <c r="D18" t="s">
         <v>436</v>
       </c>
-      <c r="C18" t="s">
-        <v>394</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>437</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>438</v>
-      </c>
-      <c r="F18" t="s">
-        <v>439</v>
       </c>
       <c r="G18">
         <v>3</v>
       </c>
       <c r="J18" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K18" t="s">
+        <v>439</v>
+      </c>
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AF18">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>426</v>
+      </c>
+      <c r="AT18" t="s">
         <v>440</v>
       </c>
-      <c r="AC18">
-        <v>1</v>
-      </c>
-      <c r="AF18">
-        <v>1</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>427</v>
-      </c>
-      <c r="AT18" t="s">
+      <c r="BD18">
+        <v>1</v>
+      </c>
+      <c r="BO18" t="s">
         <v>441</v>
       </c>
-      <c r="BD18">
-        <v>1</v>
-      </c>
-      <c r="BO18" t="s">
+      <c r="BP18" t="s">
         <v>442</v>
-      </c>
-      <c r="BP18" t="s">
-        <v>443</v>
       </c>
       <c r="BT18">
         <v>30</v>
@@ -5374,10 +5471,10 @@
         <v>1</v>
       </c>
       <c r="BY18" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="CN18" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="CO18">
         <v>1.25</v>
@@ -5386,7 +5483,7 @@
         <v>30</v>
       </c>
       <c r="CU18" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="DD18">
         <v>1</v>
@@ -5400,16 +5497,16 @@
     </row>
     <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>445</v>
+      </c>
+      <c r="C19" t="s">
+        <v>393</v>
+      </c>
+      <c r="K19" t="s">
+        <v>394</v>
+      </c>
+      <c r="O19" t="s">
         <v>446</v>
-      </c>
-      <c r="C19" t="s">
-        <v>394</v>
-      </c>
-      <c r="K19" t="s">
-        <v>395</v>
-      </c>
-      <c r="O19" t="s">
-        <v>447</v>
       </c>
       <c r="AC19">
         <v>2</v>
@@ -5418,13 +5515,13 @@
         <v>1</v>
       </c>
       <c r="AO19" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AT19" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AX19" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AZ19">
         <v>1</v>
@@ -5442,42 +5539,42 @@
         <v>0</v>
       </c>
       <c r="BO19" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="BP19" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="CG19" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="CN19" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="CR19">
         <v>9999</v>
       </c>
       <c r="CY19" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C20" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AC20">
         <v>1</v>
       </c>
       <c r="AG20" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BD20">
         <v>1</v>
@@ -5486,10 +5583,10 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="CB20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="CG20" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="DD20">
         <v>1</v>
@@ -5506,25 +5603,25 @@
     </row>
     <row r="21" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>449</v>
+      </c>
+      <c r="C21" t="s">
+        <v>393</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="K21" t="s">
+        <v>405</v>
+      </c>
+      <c r="L21" t="s">
         <v>450</v>
       </c>
-      <c r="C21" t="s">
-        <v>394</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="K21" t="s">
-        <v>406</v>
-      </c>
-      <c r="L21" t="s">
-        <v>451</v>
-      </c>
       <c r="AC21">
         <v>1</v>
       </c>
       <c r="AG21" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BD21">
         <v>1</v>
@@ -5533,10 +5630,10 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="CB21" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="CG21" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="DD21">
         <v>1</v>
@@ -5553,16 +5650,16 @@
     </row>
     <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>452</v>
+      </c>
+      <c r="C22" t="s">
+        <v>393</v>
+      </c>
+      <c r="O22" t="s">
+        <v>446</v>
+      </c>
+      <c r="Q22" t="s">
         <v>453</v>
-      </c>
-      <c r="C22" t="s">
-        <v>394</v>
-      </c>
-      <c r="O22" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>454</v>
       </c>
       <c r="AC22">
         <v>2</v>
@@ -5571,7 +5668,7 @@
         <v>1</v>
       </c>
       <c r="AO22" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AV22">
         <v>99</v>
@@ -5583,27 +5680,27 @@
         <v>1</v>
       </c>
       <c r="CL22" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>455</v>
+      </c>
+      <c r="C23" t="s">
+        <v>393</v>
+      </c>
+      <c r="K23" t="s">
+        <v>405</v>
+      </c>
+      <c r="L23" t="s">
         <v>456</v>
       </c>
-      <c r="C23" t="s">
-        <v>394</v>
-      </c>
-      <c r="K23" t="s">
-        <v>406</v>
-      </c>
-      <c r="L23" t="s">
-        <v>457</v>
-      </c>
       <c r="O23" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Q23" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AC23">
         <v>2</v>
@@ -5612,7 +5709,7 @@
         <v>1</v>
       </c>
       <c r="AO23" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AV23">
         <v>99</v>
@@ -5624,21 +5721,21 @@
         <v>0.1</v>
       </c>
       <c r="CM23" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="CU23" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="24" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C24" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O24" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AC24">
         <v>2</v>
@@ -5647,10 +5744,10 @@
         <v>1</v>
       </c>
       <c r="AO24" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AT24" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="BD24">
         <v>99</v>
@@ -5659,7 +5756,7 @@
         <v>0.1</v>
       </c>
       <c r="CN24" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="CO24">
         <v>-0.5</v>
@@ -5670,19 +5767,19 @@
     </row>
     <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>459</v>
+      </c>
+      <c r="C25" t="s">
         <v>460</v>
       </c>
-      <c r="C25" t="s">
-        <v>461</v>
-      </c>
       <c r="K25" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L25" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O25" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AC25">
         <v>2</v>
@@ -5691,10 +5788,10 @@
         <v>1</v>
       </c>
       <c r="AO25" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AT25" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="BD25">
         <v>99</v>
@@ -5703,50 +5800,50 @@
         <v>0.1</v>
       </c>
       <c r="CU25" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="28" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K28" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L28" t="s">
+        <v>462</v>
+      </c>
+      <c r="AC28">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>426</v>
+      </c>
+      <c r="BD28">
+        <v>1</v>
+      </c>
+      <c r="CU28" t="s">
         <v>463</v>
-      </c>
-      <c r="AC28">
-        <v>1</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>427</v>
-      </c>
-      <c r="BD28">
-        <v>1</v>
-      </c>
-      <c r="CU28" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="29" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C29" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I29">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L29" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AC29">
         <v>2</v>
@@ -5755,10 +5852,10 @@
         <v>1</v>
       </c>
       <c r="AO29" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AT29" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="BD29">
         <v>4</v>
@@ -5767,59 +5864,59 @@
         <v>0.2</v>
       </c>
       <c r="CN29" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="CR29">
         <v>5</v>
       </c>
       <c r="CU29" t="s">
+        <v>467</v>
+      </c>
+      <c r="CY29" t="s">
         <v>468</v>
-      </c>
-      <c r="CY29" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="30" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>469</v>
+      </c>
+      <c r="C30" t="s">
         <v>470</v>
       </c>
-      <c r="C30" t="s">
+      <c r="K30" t="s">
+        <v>405</v>
+      </c>
+      <c r="L30" t="s">
+        <v>462</v>
+      </c>
+      <c r="AC30">
+        <v>1</v>
+      </c>
+      <c r="AG30" t="s">
+        <v>426</v>
+      </c>
+      <c r="BD30">
+        <v>1</v>
+      </c>
+      <c r="CU30" t="s">
         <v>471</v>
-      </c>
-      <c r="K30" t="s">
-        <v>406</v>
-      </c>
-      <c r="L30" t="s">
-        <v>463</v>
-      </c>
-      <c r="AC30">
-        <v>1</v>
-      </c>
-      <c r="AG30" t="s">
-        <v>427</v>
-      </c>
-      <c r="BD30">
-        <v>1</v>
-      </c>
-      <c r="CU30" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="32" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C32" t="s">
+        <v>393</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32" t="s">
+        <v>413</v>
+      </c>
+      <c r="K32" t="s">
         <v>394</v>
-      </c>
-      <c r="I32">
-        <v>1</v>
-      </c>
-      <c r="J32" t="s">
-        <v>414</v>
-      </c>
-      <c r="K32" t="s">
-        <v>395</v>
       </c>
       <c r="AC32">
         <v>2</v>
@@ -5834,10 +5931,10 @@
         <v>1</v>
       </c>
       <c r="BO32" t="s">
+        <v>473</v>
+      </c>
+      <c r="BP32" t="s">
         <v>474</v>
-      </c>
-      <c r="BP32" t="s">
-        <v>475</v>
       </c>
       <c r="BT32">
         <v>6</v>
@@ -5852,7 +5949,7 @@
         <v>1</v>
       </c>
       <c r="BY32" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="DH32">
         <v>1</v>
@@ -5860,28 +5957,28 @@
     </row>
     <row r="33" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C33" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I33">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AC33">
         <v>1</v>
       </c>
       <c r="AG33" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AT33" t="s">
+        <v>476</v>
+      </c>
+      <c r="AX33" t="s">
         <v>477</v>
-      </c>
-      <c r="AX33" t="s">
-        <v>478</v>
       </c>
       <c r="AZ33">
         <v>999</v>
@@ -5904,100 +6001,100 @@
     </row>
     <row r="34" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>478</v>
+      </c>
+      <c r="C34" t="s">
+        <v>460</v>
+      </c>
+      <c r="K34" t="s">
+        <v>405</v>
+      </c>
+      <c r="L34" t="s">
         <v>479</v>
       </c>
-      <c r="C34" t="s">
-        <v>461</v>
-      </c>
-      <c r="K34" t="s">
-        <v>406</v>
-      </c>
-      <c r="L34" t="s">
+      <c r="AC34">
+        <v>1</v>
+      </c>
+      <c r="AG34" t="s">
+        <v>426</v>
+      </c>
+      <c r="BD34">
+        <v>1</v>
+      </c>
+      <c r="CU34" t="s">
         <v>480</v>
-      </c>
-      <c r="AC34">
-        <v>1</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>427</v>
-      </c>
-      <c r="BD34">
-        <v>1</v>
-      </c>
-      <c r="CU34" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="35" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>481</v>
+      </c>
+      <c r="C35" t="s">
+        <v>460</v>
+      </c>
+      <c r="K35" t="s">
+        <v>405</v>
+      </c>
+      <c r="L35" t="s">
         <v>482</v>
       </c>
-      <c r="C35" t="s">
-        <v>461</v>
-      </c>
-      <c r="K35" t="s">
-        <v>406</v>
-      </c>
-      <c r="L35" t="s">
-        <v>483</v>
-      </c>
       <c r="AC35">
         <v>1</v>
       </c>
       <c r="AG35" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BD35">
         <v>1</v>
       </c>
       <c r="CU35" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="37" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>483</v>
+      </c>
+      <c r="C37" t="s">
+        <v>393</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="K37" t="s">
+        <v>405</v>
+      </c>
+      <c r="L37" t="s">
+        <v>462</v>
+      </c>
+      <c r="AC37">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="s">
+        <v>426</v>
+      </c>
+      <c r="BD37">
+        <v>1</v>
+      </c>
+      <c r="CY37" t="s">
         <v>484</v>
-      </c>
-      <c r="C37" t="s">
-        <v>394</v>
-      </c>
-      <c r="I37">
-        <v>1</v>
-      </c>
-      <c r="K37" t="s">
-        <v>406</v>
-      </c>
-      <c r="L37" t="s">
-        <v>463</v>
-      </c>
-      <c r="AC37">
-        <v>1</v>
-      </c>
-      <c r="AG37" t="s">
-        <v>427</v>
-      </c>
-      <c r="BD37">
-        <v>1</v>
-      </c>
-      <c r="CY37" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="38" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C38" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I38">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L38" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="X38">
         <v>1</v>
@@ -6009,13 +6106,13 @@
         <v>1</v>
       </c>
       <c r="AO38" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AT38" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AX38" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AZ38">
         <v>1.5</v>
@@ -6030,42 +6127,42 @@
         <v>0.5</v>
       </c>
       <c r="BO38" t="s">
+        <v>486</v>
+      </c>
+      <c r="BP38" t="s">
         <v>487</v>
       </c>
-      <c r="BP38" t="s">
+      <c r="CB38" t="s">
+        <v>57</v>
+      </c>
+      <c r="CG38" t="s">
+        <v>401</v>
+      </c>
+      <c r="CL38" t="s">
         <v>488</v>
       </c>
-      <c r="CB38" t="s">
-        <v>58</v>
-      </c>
-      <c r="CG38" t="s">
-        <v>402</v>
-      </c>
-      <c r="CL38" t="s">
+      <c r="CU38" t="s">
         <v>489</v>
       </c>
-      <c r="CU38" t="s">
+      <c r="CY38" t="s">
         <v>490</v>
-      </c>
-      <c r="CY38" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="39" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C39" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I39">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L39" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="X39">
         <v>1</v>
@@ -6077,16 +6174,16 @@
         <v>1</v>
       </c>
       <c r="AO39" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AT39" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="BD39">
         <v>99</v>
       </c>
       <c r="CN39" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="CO39">
         <v>-0.8</v>
@@ -6095,33 +6192,33 @@
         <v>6</v>
       </c>
       <c r="CY39" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="40" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C40" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I40">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AC40">
         <v>1</v>
       </c>
       <c r="AG40" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AT40" t="s">
+        <v>476</v>
+      </c>
+      <c r="AX40" t="s">
         <v>477</v>
-      </c>
-      <c r="AX40" t="s">
-        <v>478</v>
       </c>
       <c r="AZ40">
         <v>0.09</v>
@@ -6139,7 +6236,7 @@
         <v>0.5</v>
       </c>
       <c r="CY40" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="DD40">
         <v>1</v>
@@ -6234,37 +6331,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F1" t="s">
         <v>493</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>494</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>495</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>496</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>497</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>498</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>499</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>500</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>501</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>502</v>
-      </c>
-      <c r="P1" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -6272,49 +6369,49 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F2" t="s">
         <v>504</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>505</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>506</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>507</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>508</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>509</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M2" t="s">
         <v>510</v>
       </c>
-      <c r="L2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>511</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>512</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>513</v>
       </c>
-      <c r="P2" t="s">
-        <v>514</v>
-      </c>
       <c r="Q2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -6328,101 +6425,101 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J3" t="s">
+        <v>390</v>
+      </c>
+      <c r="K3" t="s">
         <v>118</v>
       </c>
-      <c r="I3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J3" t="s">
-        <v>391</v>
-      </c>
-      <c r="K3" t="s">
-        <v>119</v>
-      </c>
       <c r="L3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="M3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>515</v>
+      </c>
+      <c r="C5" t="s">
+        <v>240</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="s">
         <v>516</v>
-      </c>
-      <c r="C5" t="s">
-        <v>241</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C6" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C7" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q7" t="s">
         <v>518</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>519</v>
+      </c>
+      <c r="C8" t="s">
+        <v>240</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="s">
         <v>520</v>
-      </c>
-      <c r="C8" t="s">
-        <v>241</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="292" spans="16:16" x14ac:dyDescent="0.25">
@@ -6458,7 +6555,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6466,13 +6563,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -6483,10 +6580,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -6510,7 +6607,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -6518,31 +6615,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" t="s">
         <v>524</v>
       </c>
-      <c r="E2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>525</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>526</v>
       </c>
-      <c r="H2" t="s">
-        <v>527</v>
-      </c>
       <c r="I2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -6559,22 +6656,22 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" t="s">
         <v>119</v>
       </c>
-      <c r="F3" t="s">
-        <v>120</v>
-      </c>
       <c r="G3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -6602,34 +6699,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C1" t="s">
         <v>528</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>529</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>530</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>531</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>532</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>533</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>534</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>535</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>536</v>
-      </c>
-      <c r="L1" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -6637,37 +6734,37 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>537</v>
+      </c>
+      <c r="C2" t="s">
         <v>538</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>539</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>540</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>541</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>542</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>543</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>544</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>545</v>
       </c>
-      <c r="J2" t="s">
-        <v>546</v>
-      </c>
       <c r="K2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -6678,34 +6775,34 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
       </c>
       <c r="F3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K3" t="s">
         <v>118</v>
       </c>
-      <c r="G3" t="s">
+      <c r="L3" t="s">
         <v>118</v>
-      </c>
-      <c r="H3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L3" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -6736,31 +6833,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E2" t="s">
         <v>548</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" t="s">
         <v>549</v>
       </c>
-      <c r="F2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I2" t="s">
         <v>550</v>
       </c>
-      <c r="H2" t="s">
-        <v>299</v>
-      </c>
-      <c r="I2" t="s">
-        <v>551</v>
-      </c>
       <c r="J2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -6777,22 +6874,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -6821,28 +6918,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C1" t="s">
         <v>553</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>554</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>555</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>556</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>557</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>558</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>559</v>
-      </c>
-      <c r="I1" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -6850,28 +6947,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C2" t="s">
         <v>561</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>562</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>563</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>564</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>565</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>566</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>567</v>
-      </c>
-      <c r="I2" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -6879,10 +6976,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D3" t="s">
         <v>2</v>
@@ -6911,27 +7008,27 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
+        <v>568</v>
+      </c>
+      <c r="E4" t="s">
         <v>569</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>570</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>571</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>572</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>573</v>
-      </c>
-      <c r="I4" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -6940,13 +7037,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
+        <v>574</v>
+      </c>
+      <c r="E5" t="s">
         <v>575</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>576</v>
-      </c>
-      <c r="F5" t="s">
-        <v>577</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/一方通行/酒神.xlsx
+++ b/Excel/一方通行/酒神.xlsx
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="586">
   <si>
     <t>Id</t>
   </si>
@@ -670,6 +670,9 @@
     <t>Ablititys</t>
   </si>
   <si>
+    <t>StartAnimation</t>
+  </si>
+  <si>
     <t>DefaultAnimation</t>
   </si>
   <si>
@@ -686,6 +689,9 @@
   </si>
   <si>
     <t>ForwardAnimation</t>
+  </si>
+  <si>
+    <t>DieAnimation</t>
   </si>
   <si>
     <t>MaxAnimationScale</t>
@@ -2122,11 +2128,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
@@ -2440,30 +2449,30 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1" style="2"/>
+    <col min="1" max="2" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2476,7 +2485,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BV12"/>
+  <dimension ref="A1:BX12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
@@ -2546,13 +2555,15 @@
     <col min="65" max="65" width="9" customWidth="1" style="2"/>
     <col min="66" max="66" width="9" customWidth="1" style="2"/>
     <col min="67" max="67" width="39.58203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="14" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14.83203125" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="68" max="68" width="9" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14.83203125" customWidth="1" style="2"/>
     <col min="71" max="71" width="14" customWidth="1" style="2"/>
     <col min="72" max="72" width="14" customWidth="1" style="2"/>
     <col min="73" max="73" width="14" customWidth="1" style="2"/>
-    <col min="74" max="74" width="19.1640625" customWidth="1" style="2"/>
+    <col min="74" max="74" width="14" customWidth="1" style="2"/>
+    <col min="75" max="75" width="9" customWidth="1" style="2"/>
+    <col min="76" max="76" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2724,6 +2735,8 @@
       <c r="BT1" s="2"/>
       <c r="BU1" s="2"/>
       <c r="BV1" s="2"/>
+      <c r="BW1" s="2"/>
+      <c r="BX1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
@@ -2944,6 +2957,12 @@
       <c r="BV2" s="2" t="s">
         <v>121</v>
       </c>
+      <c r="BW2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
@@ -2953,7 +2972,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2961,91 +2980,91 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="W3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="AD3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AF3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AJ3" s="2" t="s">
         <v>2</v>
@@ -3054,10 +3073,10 @@
         <v>2</v>
       </c>
       <c r="AL3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AN3" s="2" t="s">
         <v>2</v>
@@ -3066,50 +3085,50 @@
         <v>2</v>
       </c>
       <c r="AP3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AQ3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AR3" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AS3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AS3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="AT3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AX3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AY3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="BA3" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BB3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BC3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BD3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BE3" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BF3" s="2" t="s">
         <v>2</v>
@@ -3124,43 +3143,49 @@
         <v>2</v>
       </c>
       <c r="BJ3" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BK3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BL3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="BM3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BN3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="BO3" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BP3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BQ3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BR3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BS3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BT3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BU3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BV3" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BX3" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="4">
@@ -3168,13 +3193,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
@@ -3239,23 +3264,23 @@
         <v>4</v>
       </c>
       <c r="AK4" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AL4" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AM4" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AN4" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AO4" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AP4" s="2"/>
       <c r="AQ4" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AR4" s="2">
         <v>1</v>
@@ -3277,49 +3302,51 @@
       <c r="BC4" s="2"/>
       <c r="BD4" s="2"/>
       <c r="BE4" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BF4" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BG4" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BH4" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BI4" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BJ4" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BK4" s="2">
         <v>6</v>
       </c>
       <c r="BL4" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BM4" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BN4" s="2"/>
       <c r="BO4" s="2"/>
-      <c r="BP4" s="2" t="s">
-        <v>149</v>
-      </c>
+      <c r="BP4" s="2"/>
       <c r="BQ4" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="BR4" s="2"/>
-      <c r="BS4" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="BR4" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="BS4" s="2"/>
       <c r="BT4" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="BU4" s="2"/>
-      <c r="BV4" s="2">
+        <v>153</v>
+      </c>
+      <c r="BU4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BV4" s="2"/>
+      <c r="BW4" s="2"/>
+      <c r="BX4" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3398,6 +3425,8 @@
       <c r="BT5" s="2"/>
       <c r="BU5" s="2"/>
       <c r="BV5" s="2"/>
+      <c r="BW5" s="2"/>
+      <c r="BX5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2"/>
@@ -3474,6 +3503,8 @@
       <c r="BT6" s="2"/>
       <c r="BU6" s="2"/>
       <c r="BV6" s="2"/>
+      <c r="BW6" s="2"/>
+      <c r="BX6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2"/>
@@ -3550,19 +3581,21 @@
       <c r="BT7" s="2"/>
       <c r="BU7" s="2"/>
       <c r="BV7" s="2"/>
+      <c r="BW7" s="2"/>
+      <c r="BX7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -3624,26 +3657,26 @@
       </c>
       <c r="AI8" s="2"/>
       <c r="AJ8" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AK8" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AL8" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AM8" s="2"/>
       <c r="AN8" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AO8" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AP8" s="2">
         <v>-0.5</v>
       </c>
       <c r="AQ8" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR8" s="2">
         <v>0</v>
@@ -3667,60 +3700,62 @@
       </c>
       <c r="BD8" s="2"/>
       <c r="BE8" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BF8" s="2"/>
       <c r="BG8" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BH8" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BI8" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BJ8" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BK8" s="2">
         <v>5</v>
       </c>
       <c r="BL8" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BM8" s="2"/>
       <c r="BN8" s="2"/>
       <c r="BO8" s="2"/>
-      <c r="BP8" s="2" t="s">
-        <v>149</v>
-      </c>
+      <c r="BP8" s="2"/>
       <c r="BQ8" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="BR8" s="2"/>
-      <c r="BS8" s="2" t="s">
-        <v>162</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="BR8" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="BS8" s="2"/>
       <c r="BT8" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="BU8" s="2"/>
-      <c r="BV8" s="2">
+        <v>164</v>
+      </c>
+      <c r="BU8" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="BV8" s="2"/>
+      <c r="BW8" s="2"/>
+      <c r="BX8" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -3784,26 +3819,26 @@
       </c>
       <c r="AI9" s="2"/>
       <c r="AJ9" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AK9" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM9" s="2"/>
       <c r="AN9" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AO9" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AP9" s="2">
         <v>-0.5</v>
       </c>
       <c r="AQ9" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR9" s="2">
         <v>0</v>
@@ -3827,64 +3862,66 @@
       </c>
       <c r="BD9" s="2"/>
       <c r="BE9" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BF9" s="2"/>
       <c r="BG9" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BH9" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BI9" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BJ9" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BK9" s="2">
         <v>5</v>
       </c>
       <c r="BL9" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BM9" s="2"/>
       <c r="BN9" s="2"/>
       <c r="BO9" s="2"/>
-      <c r="BP9" s="2" t="s">
-        <v>149</v>
-      </c>
+      <c r="BP9" s="2"/>
       <c r="BQ9" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="BR9" s="2"/>
-      <c r="BS9" s="2" t="s">
-        <v>162</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="BR9" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="BS9" s="2"/>
       <c r="BT9" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="BU9" s="2"/>
-      <c r="BV9" s="2">
+        <v>164</v>
+      </c>
+      <c r="BU9" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="BV9" s="2"/>
+      <c r="BW9" s="2"/>
+      <c r="BX9" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G10" s="2">
         <v>0.01</v>
@@ -3948,26 +3985,26 @@
       </c>
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AK10" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AL10" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AM10" s="2"/>
       <c r="AN10" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AO10" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AP10" s="2">
         <v>-0.5</v>
       </c>
       <c r="AQ10" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR10" s="2">
         <v>0</v>
@@ -3993,45 +4030,47 @@
       </c>
       <c r="BD10" s="2"/>
       <c r="BE10" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BF10" s="2"/>
       <c r="BG10" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BH10" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BI10" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BJ10" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BK10" s="2">
         <v>5</v>
       </c>
       <c r="BL10" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BM10" s="2"/>
       <c r="BN10" s="2"/>
       <c r="BO10" s="2"/>
-      <c r="BP10" s="2" t="s">
-        <v>149</v>
-      </c>
+      <c r="BP10" s="2"/>
       <c r="BQ10" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="BR10" s="2"/>
-      <c r="BS10" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="BR10" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="BS10" s="2"/>
       <c r="BT10" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="BU10" s="2"/>
-      <c r="BV10" s="2">
+        <v>153</v>
+      </c>
+      <c r="BU10" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BV10" s="2"/>
+      <c r="BW10" s="2"/>
+      <c r="BX10" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4110,23 +4149,25 @@
       <c r="BT11" s="2"/>
       <c r="BU11" s="2"/>
       <c r="BV11" s="2"/>
+      <c r="BW11" s="2"/>
+      <c r="BX11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -4186,24 +4227,24 @@
       <c r="AH12" s="2"/>
       <c r="AI12" s="2"/>
       <c r="AJ12" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK12" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AL12" s="2"/>
       <c r="AM12" s="2"/>
       <c r="AN12" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AO12" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AP12" s="2">
         <v>-0.5</v>
       </c>
       <c r="AQ12" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR12" s="2">
         <v>99</v>
@@ -4229,45 +4270,47 @@
       </c>
       <c r="BD12" s="2"/>
       <c r="BE12" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BF12" s="2"/>
       <c r="BG12" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BH12" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BI12" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BJ12" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BK12" s="2">
         <v>5</v>
       </c>
       <c r="BL12" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BM12" s="2"/>
       <c r="BN12" s="2"/>
       <c r="BO12" s="2"/>
-      <c r="BP12" s="2" t="s">
-        <v>149</v>
-      </c>
+      <c r="BP12" s="2"/>
       <c r="BQ12" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="BR12" s="2"/>
-      <c r="BS12" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="BR12" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="BS12" s="2"/>
       <c r="BT12" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="BU12" s="2"/>
-      <c r="BV12" s="2">
+        <v>153</v>
+      </c>
+      <c r="BU12" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BV12" s="2"/>
+      <c r="BW12" s="2"/>
+      <c r="BX12" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4285,2510 +4328,2510 @@
   <dimension ref="A1:DI569"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="7.75" customWidth="1" style="2"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1" style="2"/>
-    <col min="9" max="9" width="7.33203125" customWidth="1" style="2"/>
-    <col min="10" max="10" width="15.75" customWidth="1" style="2"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="11.75" customWidth="1" style="2"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1" style="2"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="21.5" customWidth="1" style="2"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1" style="2"/>
-    <col min="22" max="22" width="17.75" customWidth="1" style="2"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1" style="2"/>
-    <col min="24" max="24" width="18.5" customWidth="1" style="2"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1" style="2"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1" style="2"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1" style="2"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1" style="2"/>
-    <col min="32" max="32" width="13.75" customWidth="1" style="2"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1" style="2"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1" style="2"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="12.5" customWidth="1" style="2"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1" style="2"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="15" customWidth="1" style="2"/>
-    <col min="41" max="41" width="13.25" customWidth="1" style="2"/>
-    <col min="42" max="45" width="11.83203125" customWidth="1" style="2"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1" style="2"/>
-    <col min="47" max="47" width="12.25" customWidth="1" style="2"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1" style="2"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1" style="2"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1" style="2"/>
-    <col min="51" max="51" width="9" customWidth="1" style="2"/>
-    <col min="52" max="52" width="7" customWidth="1" style="2"/>
-    <col min="53" max="53" width="11.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="19.75" customWidth="1" style="2"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1" style="2"/>
-    <col min="56" max="56" width="8.5" customWidth="1" style="2"/>
-    <col min="57" max="57" width="13.5" customWidth="1" style="2"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1" style="2"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8.25" customWidth="1" style="2"/>
-    <col min="61" max="67" width="8.33203125" customWidth="1" style="2"/>
-    <col min="68" max="70" width="11.25" customWidth="1" style="2"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1" style="2"/>
-    <col min="72" max="73" width="8" customWidth="1" style="2"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1" style="2"/>
-    <col min="75" max="76" width="8.5" customWidth="1" style="2"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1" style="2"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1" style="2"/>
-    <col min="80" max="80" width="13.5" customWidth="1" style="2"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1" style="2"/>
-    <col min="82" max="82" width="15.75" customWidth="1" style="2"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1" style="2"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1" style="2"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1" style="2"/>
-    <col min="86" max="86" width="9" customWidth="1" style="2"/>
-    <col min="87" max="87" width="16" customWidth="1" style="2"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1" style="2"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1" style="2"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1" style="2"/>
-    <col min="92" max="92" width="21.25" customWidth="1" style="2"/>
-    <col min="93" max="93" width="9.5" customWidth="1" style="2"/>
-    <col min="94" max="98" width="9" customWidth="1" style="2"/>
-    <col min="99" max="99" width="14" customWidth="1" style="2"/>
-    <col min="100" max="100" width="8" customWidth="1" style="2"/>
-    <col min="101" max="101" width="9" customWidth="1" style="2"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1" style="2"/>
-    <col min="103" max="103" width="13.75" customWidth="1" style="2"/>
-    <col min="104" max="104" width="9.5" customWidth="1" style="2"/>
-    <col min="105" max="106" width="9" customWidth="1" style="2"/>
-    <col min="107" max="108" width="9.5" customWidth="1" style="2"/>
-    <col min="109" max="109" width="9" customWidth="1" style="2"/>
-    <col min="110" max="110" width="15.5" customWidth="1" style="2"/>
-    <col min="111" max="111" width="9" customWidth="1" style="2"/>
-    <col min="112" max="113" width="9.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1" style="3"/>
+    <col min="3" max="3" width="7.75" customWidth="1" style="3"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1" style="3"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1" style="3"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1" style="3"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1" style="3"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1" style="3"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1" style="3"/>
+    <col min="10" max="10" width="15.75" customWidth="1" style="3"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1" style="3"/>
+    <col min="14" max="14" width="11.75" customWidth="1" style="3"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1" style="3"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1" style="3"/>
+    <col min="17" max="17" width="21.5" customWidth="1" style="3"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1" style="3"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1" style="3"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1" style="3"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1" style="3"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="3"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1" style="3"/>
+    <col min="24" max="24" width="18.5" customWidth="1" style="3"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1" style="3"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1" style="3"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1" style="3"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1" style="3"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1" style="3"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1" style="3"/>
+    <col min="32" max="32" width="13.75" customWidth="1" style="3"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1" style="3"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1" style="3"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1" style="3"/>
+    <col min="36" max="36" width="12.5" customWidth="1" style="3"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1" style="3"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1" style="3"/>
+    <col min="40" max="40" width="15" customWidth="1" style="3"/>
+    <col min="41" max="41" width="13.25" customWidth="1" style="3"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1" style="3"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1" style="3"/>
+    <col min="47" max="47" width="12.25" customWidth="1" style="3"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1" style="3"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1" style="3"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1" style="3"/>
+    <col min="51" max="51" width="9" customWidth="1" style="3"/>
+    <col min="52" max="52" width="7" customWidth="1" style="3"/>
+    <col min="53" max="53" width="11.75" customWidth="1" style="3"/>
+    <col min="54" max="54" width="19.75" customWidth="1" style="3"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1" style="3"/>
+    <col min="56" max="56" width="8.5" customWidth="1" style="3"/>
+    <col min="57" max="57" width="13.5" customWidth="1" style="3"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1" style="3"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1" style="3"/>
+    <col min="60" max="60" width="8.25" customWidth="1" style="3"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1" style="3"/>
+    <col min="68" max="70" width="11.25" customWidth="1" style="3"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1" style="3"/>
+    <col min="72" max="73" width="8" customWidth="1" style="3"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1" style="3"/>
+    <col min="75" max="76" width="8.5" customWidth="1" style="3"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1" style="3"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1" style="3"/>
+    <col min="80" max="80" width="13.5" customWidth="1" style="3"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1" style="3"/>
+    <col min="82" max="82" width="15.75" customWidth="1" style="3"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1" style="3"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1" style="3"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1" style="3"/>
+    <col min="86" max="86" width="9" customWidth="1" style="3"/>
+    <col min="87" max="87" width="16" customWidth="1" style="3"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1" style="3"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1" style="3"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1" style="3"/>
+    <col min="92" max="92" width="21.25" customWidth="1" style="3"/>
+    <col min="93" max="93" width="9.5" customWidth="1" style="3"/>
+    <col min="94" max="98" width="9" customWidth="1" style="3"/>
+    <col min="99" max="99" width="14" customWidth="1" style="3"/>
+    <col min="100" max="100" width="8" customWidth="1" style="3"/>
+    <col min="101" max="101" width="9" customWidth="1" style="3"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1" style="3"/>
+    <col min="103" max="103" width="13.75" customWidth="1" style="3"/>
+    <col min="104" max="104" width="9.5" customWidth="1" style="3"/>
+    <col min="105" max="106" width="9" customWidth="1" style="3"/>
+    <col min="107" max="108" width="9.5" customWidth="1" style="3"/>
+    <col min="109" max="109" width="9" customWidth="1" style="3"/>
+    <col min="110" max="110" width="15.5" customWidth="1" style="3"/>
+    <col min="111" max="111" width="9" customWidth="1" style="3"/>
+    <col min="112" max="113" width="9.5" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="V1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="U1" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="V1" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AI1" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AK1" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AL1" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AM1" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AN1" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AO1" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AP1" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AR1" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AS1" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AT1" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AU1" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AV1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AW1" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AX1" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="AY1" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BA1" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BB1" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BC1" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BD1" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BE1" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BF1" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="BJ1" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BG1" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BH1" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BJ1" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="BK1" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BL1" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BM1" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BN1" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BO1" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BP1" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BQ1" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BR1" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BS1" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="BV1" s="2" t="s">
+      <c r="BT1" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="BW1" s="2" t="s">
+      <c r="BU1" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="BX1" s="2" t="s">
+      <c r="BV1" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="BY1" s="2" t="s">
+      <c r="BW1" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="BZ1" s="2" t="s">
+      <c r="BX1" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="CA1" s="2" t="s">
+      <c r="BY1" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="CB1" s="2" t="s">
+      <c r="BZ1" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="CC1" s="2" t="s">
+      <c r="CA1" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="CD1" s="2" t="s">
+      <c r="CB1" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="CE1" s="2" t="s">
+      <c r="CC1" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="CF1" s="2" t="s">
+      <c r="CD1" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="CG1" s="2" t="s">
+      <c r="CE1" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CF1" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="CI1" s="2" t="s">
+      <c r="CG1" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CH1" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="CK1" s="2" t="s">
+      <c r="CI1" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CJ1" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="CM1" s="2" t="s">
+      <c r="CK1" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="CN1" s="2" t="s">
+      <c r="CL1" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="CO1" s="2" t="s">
+      <c r="CM1" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="CP1" s="2" t="s">
+      <c r="CN1" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="CQ1" s="2" t="s">
+      <c r="CO1" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="CR1" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CP1" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="CT1" s="2" t="s">
+      <c r="CQ1" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="CU1" s="2" t="s">
+      <c r="CR1" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="CS1" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="CV1" s="2" t="s">
+      <c r="CT1" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="CW1" s="2" t="s">
+      <c r="CU1" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="CX1" s="2" t="s">
+      <c r="CV1" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="CY1" s="2" t="s">
+      <c r="CW1" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="CZ1" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="DA1" s="2" t="s">
+      <c r="CX1" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="DB1" s="2" t="s">
+      <c r="CY1" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="DC1" s="2" t="s">
+      <c r="CZ1" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="DA1" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="DD1" s="2" t="s">
+      <c r="DB1" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="DE1" s="2" t="s">
+      <c r="DC1" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="DF1" s="2" t="s">
+      <c r="DD1" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="DG1" s="2" t="s">
+      <c r="DE1" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="DH1" s="2" t="s">
+      <c r="DF1" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="DI1" s="2" t="s">
+      <c r="DG1" s="3" t="s">
         <v>277</v>
       </c>
+      <c r="DH1" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="DI1" s="3" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="R2" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="S2" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="T2" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="U2" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="V2" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="W2" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="X2" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="Y2" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="Z2" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AA2" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AB2" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AC2" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AD2" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AE2" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AF2" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AG2" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AH2" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AI2" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AK2" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AL2" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AM2" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AN2" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AO2" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AP2" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AQ2" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AR2" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AS2" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AT2" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AU2" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AV2" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="AW2" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="AX2" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="AY2" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="AZ2" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BA2" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BB2" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BC2" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BD2" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BE2" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BF2" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BG2" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BH2" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BI2" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BJ2" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BK2" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BL2" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BM2" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="BN2" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="BO2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="BP2" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BP2" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BQ2" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="BT2" s="2" t="s">
+      <c r="BR2" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="BU2" s="2" t="s">
+      <c r="BS2" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="BT2" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BU2" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="BV2" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="BW2" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="BX2" s="2" t="s">
+      <c r="BV2" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="BY2" s="2" t="s">
+      <c r="BW2" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="BZ2" s="2" t="s">
+      <c r="BX2" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="2" t="s">
+      <c r="BY2" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="CB2" s="2" t="s">
+      <c r="BZ2" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="CC2" s="2" t="s">
+      <c r="CA2" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="CD2" s="2" t="s">
+      <c r="CB2" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="CE2" s="2" t="s">
+      <c r="CC2" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="CF2" s="2" t="s">
+      <c r="CD2" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="CG2" s="2" t="s">
+      <c r="CE2" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="CH2" s="2" t="s">
+      <c r="CF2" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="CI2" s="2" t="s">
+      <c r="CG2" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="CJ2" s="2" t="s">
+      <c r="CH2" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="CK2" s="2" t="s">
+      <c r="CI2" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CJ2" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="CM2" s="2" t="s">
+      <c r="CK2" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="CN2" s="2" t="s">
+      <c r="CL2" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="CO2" s="2" t="s">
+      <c r="CM2" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="CP2" s="2" t="s">
+      <c r="CN2" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="CQ2" s="2" t="s">
+      <c r="CO2" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="CR2" s="2" t="s">
+      <c r="CP2" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="CS2" s="2" t="s">
+      <c r="CQ2" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="CT2" s="2" t="s">
+      <c r="CR2" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="CU2" s="2" t="s">
+      <c r="CS2" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="CV2" s="2" t="s">
+      <c r="CT2" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="CW2" s="2" t="s">
+      <c r="CU2" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="CX2" s="2" t="s">
+      <c r="CV2" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="CY2" s="2" t="s">
+      <c r="CW2" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="CZ2" s="2" t="s">
+      <c r="CX2" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="DA2" s="2" t="s">
+      <c r="CY2" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="DB2" s="2" t="s">
+      <c r="CZ2" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="DC2" s="2" t="s">
+      <c r="DA2" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="DD2" s="2" t="s">
+      <c r="DB2" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="DE2" s="2" t="s">
+      <c r="DC2" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="DF2" s="2" t="s">
+      <c r="DD2" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="DG2" s="2" t="s">
+      <c r="DE2" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="DH2" s="2" t="s">
+      <c r="DF2" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="DI2" s="2" t="s">
+      <c r="DG2" s="3" t="s">
         <v>383</v>
       </c>
+      <c r="DH2" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="DI2" s="3" t="s">
+        <v>385</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="U3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AI3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AO3" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="M3" s="2" t="s">
+      <c r="AR3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="AU3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="AW3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AX3" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="BA3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BC3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BE3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BF3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH3" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="BI3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BJ3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BK3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BL3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BM3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BO3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="BP3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC3" s="2" t="s">
+      <c r="BQ3" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="BR3" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="BS3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="AD3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI3" s="2" t="s">
+      <c r="BT3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BU3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BV3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BW3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BX3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BY3" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="BZ3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CA3" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="CB3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CC3" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="CD3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CE3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CF3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CG3" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="CH3" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="CI3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="CK3" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="CL3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CM3" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="CN3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="CO3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CP3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CR3" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="CS3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CT3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CU3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CV3" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="CW3" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="CX3" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="CY3" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="CZ3" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="DA3" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="DB3" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="DC3" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="DD3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DE3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DF3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DG3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DH3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DI3" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="S5" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD5" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO5" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="AT5" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="AX5" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="AZ5" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD5" s="3">
+        <v>1</v>
+      </c>
+      <c r="BJ5" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="BK5" s="3">
+        <v>1</v>
+      </c>
+      <c r="BL5" s="3">
+        <v>0</v>
+      </c>
+      <c r="BO5" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="BP5" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="CB5" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="CG5" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="CN5" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="CR5" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CY5" s="3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="AT6" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="BD6" s="3">
+        <v>1</v>
+      </c>
+      <c r="CL6" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="CM6" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="AV7" s="3">
+        <v>99</v>
+      </c>
+      <c r="BD7" s="3">
+        <v>99</v>
+      </c>
+      <c r="BS7" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CL7" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="CM7" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="G10" s="3">
         <v>3</v>
       </c>
-      <c r="AK3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
+      <c r="J10" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC10" s="3">
         <v>2</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AD10" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO10" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="AT10" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="AX10" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="AZ10" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="BD10" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE10" s="3">
+        <v>1</v>
+      </c>
+      <c r="BF10" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="BJ10" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="BK10" s="3">
+        <v>1</v>
+      </c>
+      <c r="BL10" s="3">
+        <v>0</v>
+      </c>
+      <c r="BO10" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="BP10" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="BT10" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="BV10" s="3">
         <v>2</v>
       </c>
-      <c r="AS3" s="2" t="s">
+      <c r="BW10" s="3">
         <v>2</v>
       </c>
-      <c r="AT3" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AV3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AW3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="AY3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BW3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BX3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BY3" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="BZ3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CA3" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="CB3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CC3" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="CD3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CE3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CF3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CG3" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="CH3" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="CI3" s="2" t="s">
+      <c r="BX10" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY10" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="CB10" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="CG10" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="CN10" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="CR10" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CY10" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="DD10" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG10" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="AC11" s="3">
         <v>2</v>
       </c>
-      <c r="CJ3" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="CK3" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="CL3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CM3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CP3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CQ3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CR3" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="CS3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CT3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CU3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CV3" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="CW3" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="CX3" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="CY3" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="CZ3" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="DA3" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="DB3" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="DC3" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="DD3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DF3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DG3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DH3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DI3" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="S5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="2">
+      <c r="AD11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO11" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="AT11" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="BD11" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE11" s="3">
+        <v>1</v>
+      </c>
+      <c r="BF11" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CL11" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="CM11" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="CN11" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="CR11" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="AC12" s="3">
         <v>2</v>
       </c>
-      <c r="AD5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO5" s="2" t="s">
+      <c r="AD12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO12" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="AT12" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="BD12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BF12" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CL12" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="CM12" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="G14" s="3">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="BD14" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO14" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="BP14" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="BT14" s="3">
+        <v>9999</v>
+      </c>
+      <c r="BV14" s="3">
+        <v>0</v>
+      </c>
+      <c r="BW14" s="3">
+        <v>25</v>
+      </c>
+      <c r="BX14" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY14" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="CN14" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="CO14" s="3">
+        <v>35</v>
+      </c>
+      <c r="CR14" s="3">
+        <v>9999</v>
+      </c>
+      <c r="CU14" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="DD14" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG14" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="AT5" s="2" t="s">
+      <c r="K15" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="AX5" s="2" t="s">
+      <c r="O15" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO15" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="AZ5" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD5" s="2">
-        <v>1</v>
-      </c>
-      <c r="BJ5" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="BK5" s="2">
-        <v>1</v>
-      </c>
-      <c r="BL5" s="2">
+      <c r="AT15" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="AX15" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="AZ15" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD15" s="3">
+        <v>1</v>
+      </c>
+      <c r="BJ15" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="BK15" s="3">
+        <v>1</v>
+      </c>
+      <c r="BL15" s="3">
         <v>0</v>
       </c>
-      <c r="BO5" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="BP5" s="2" t="s">
+      <c r="BO15" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="BP15" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="CB15" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="CG15" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="CN15" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="CR15" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CY15" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="I16" s="3">
+        <v>1</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="AC16" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="BD16" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS16" s="3">
+        <v>0.333</v>
+      </c>
+      <c r="CB16" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="CG16" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="DD16" s="3">
+        <v>1</v>
+      </c>
+      <c r="DF16" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG16" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH16" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="G18" s="3">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="AT18" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="BD18" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO18" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="BP18" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="BT18" s="3">
+        <v>30</v>
+      </c>
+      <c r="BV18" s="3">
+        <v>30</v>
+      </c>
+      <c r="BW18" s="3">
+        <v>40</v>
+      </c>
+      <c r="BX18" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY18" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="CN18" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="CO18" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="CR18" s="3">
+        <v>30</v>
+      </c>
+      <c r="CU18" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="DD18" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG18" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH18" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="AC19" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD19" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO19" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="AT19" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="AX19" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="CB5" s="2" t="s">
+      <c r="AZ19" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD19" s="3">
+        <v>1</v>
+      </c>
+      <c r="BJ19" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="BK19" s="3">
+        <v>1</v>
+      </c>
+      <c r="BL19" s="3">
+        <v>0</v>
+      </c>
+      <c r="BO19" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="CG5" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="CN5" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="CR5" s="2">
+      <c r="BP19" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="CG19" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="CN19" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="CR19" s="3">
+        <v>9999</v>
+      </c>
+      <c r="CY19" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="BD20" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS20" s="3">
+        <v>0.333</v>
+      </c>
+      <c r="CB20" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="CG20" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="DD20" s="3">
+        <v>1</v>
+      </c>
+      <c r="DF20" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG20" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH20" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="BD21" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS21" s="3">
+        <v>0.333</v>
+      </c>
+      <c r="CB21" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="CG21" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="DD21" s="3">
+        <v>1</v>
+      </c>
+      <c r="DF21" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG21" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO22" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="AV22" s="3">
+        <v>99</v>
+      </c>
+      <c r="BD22" s="3">
+        <v>99</v>
+      </c>
+      <c r="BS22" s="3">
+        <v>1</v>
+      </c>
+      <c r="CL22" s="3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO23" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="AV23" s="3">
+        <v>99</v>
+      </c>
+      <c r="BD23" s="3">
+        <v>99</v>
+      </c>
+      <c r="BS23" s="3">
         <v>0.1</v>
       </c>
-      <c r="CY5" s="2" t="s">
+      <c r="CM23" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="CU23" s="3" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO24" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="AT24" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="BD24" s="3">
+        <v>99</v>
+      </c>
+      <c r="BS24" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CN24" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="CO24" s="3">
+        <v>-0.5</v>
+      </c>
+      <c r="CR24" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO25" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="AT25" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="BD25" s="3">
+        <v>99</v>
+      </c>
+      <c r="BS25" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CU25" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG28" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="BD28" s="3">
+        <v>1</v>
+      </c>
+      <c r="CU28" s="3" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="I29" s="3">
+        <v>1</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO29" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="AT29" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="BD29" s="3">
+        <v>4</v>
+      </c>
+      <c r="BT29" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="CN29" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="CR29" s="3">
+        <v>5</v>
+      </c>
+      <c r="CU29" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="CY29" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="BD30" s="3">
+        <v>1</v>
+      </c>
+      <c r="CU30" s="3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>1</v>
+      </c>
+      <c r="AV32" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="BD32" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO32" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="BP32" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="BT32" s="3">
+        <v>6</v>
+      </c>
+      <c r="BV32" s="3">
+        <v>1</v>
+      </c>
+      <c r="BW32" s="3">
+        <v>1</v>
+      </c>
+      <c r="BX32" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY32" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="DH32" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="I33" s="3">
+        <v>1</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="AC33" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="AT33" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="AX33" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="AZ33" s="3">
+        <v>999</v>
+      </c>
+      <c r="BB33" s="3">
+        <v>2</v>
+      </c>
+      <c r="BD33" s="3">
+        <v>1</v>
+      </c>
+      <c r="DD33" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG33" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH33" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG34" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="BD34" s="3">
+        <v>1</v>
+      </c>
+      <c r="CU34" s="3" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="AC35" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG35" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="BD35" s="3">
+        <v>1</v>
+      </c>
+      <c r="CU35" s="3" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="I37" s="3">
+        <v>1</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="AC37" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG37" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="BD37" s="3">
+        <v>1</v>
+      </c>
+      <c r="CY37" s="3" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="I38" s="3">
+        <v>1</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="X38" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC38" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD38" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO38" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="AT38" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="AX38" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="AZ38" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="BD38" s="3">
+        <v>99</v>
+      </c>
+      <c r="BE38" s="3">
+        <v>11</v>
+      </c>
+      <c r="BF38" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="BO38" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="BP38" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="CB38" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="CG38" s="3" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="AC6" s="2">
+      <c r="CL38" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="CU38" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="CY38" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="I39" s="3">
+        <v>1</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="X39" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC39" s="3">
         <v>2</v>
       </c>
-      <c r="AD6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO6" s="2" t="s">
+      <c r="AD39" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO39" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="AT39" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="BD39" s="3">
+        <v>99</v>
+      </c>
+      <c r="CN39" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="CO39" s="3">
+        <v>-0.8</v>
+      </c>
+      <c r="CR39" s="3">
+        <v>6</v>
+      </c>
+      <c r="CY39" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="AT6" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="BD6" s="2">
-        <v>1</v>
-      </c>
-      <c r="CL6" s="2" t="s">
+      <c r="I40" s="3">
+        <v>1</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="CM6" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="AC7" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO7" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="AV7" s="2">
-        <v>99</v>
-      </c>
-      <c r="BD7" s="2">
-        <v>99</v>
-      </c>
-      <c r="BS7" s="2">
+      <c r="AC40" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG40" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="AT40" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="AX40" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="AZ40" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="BB40" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD40" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE40" s="3">
+        <v>11</v>
+      </c>
+      <c r="BF40" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="CY40" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="DD40" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG40" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH40" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="CL549" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="CL551" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="CL552" s="3">
         <v>0.1</v>
       </c>
-      <c r="CL7" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="CM7" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="G10" s="2">
-        <v>3</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="AC10" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO10" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="AT10" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="AX10" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="AZ10" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="BD10" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE10" s="2">
-        <v>1</v>
-      </c>
-      <c r="BF10" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="BJ10" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="BK10" s="2">
-        <v>1</v>
-      </c>
-      <c r="BL10" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO10" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="BP10" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="BT10" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="BV10" s="2">
-        <v>2</v>
-      </c>
-      <c r="BW10" s="2">
-        <v>2</v>
-      </c>
-      <c r="BX10" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY10" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="CB10" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="CG10" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="CN10" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="CR10" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CY10" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="DD10" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG10" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH10" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="AC11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD11" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO11" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="AT11" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="BD11" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE11" s="2">
-        <v>1</v>
-      </c>
-      <c r="BF11" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CL11" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="CM11" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="CN11" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="CR11" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="AC12" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD12" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO12" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="AT12" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="BD12" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE12" s="2">
-        <v>1</v>
-      </c>
-      <c r="BF12" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CL12" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="CM12" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="G14" s="2">
-        <v>3</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="AC14" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF14" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG14" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="BD14" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO14" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="BP14" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="BT14" s="2">
-        <v>9999</v>
-      </c>
-      <c r="BV14" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW14" s="2">
-        <v>25</v>
-      </c>
-      <c r="BX14" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY14" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="CN14" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="CO14" s="2">
-        <v>35</v>
-      </c>
-      <c r="CR14" s="2">
-        <v>9999</v>
-      </c>
-      <c r="CU14" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="DD14" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG14" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH14" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="AC15" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD15" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO15" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="AT15" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="AX15" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="AZ15" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD15" s="2">
-        <v>1</v>
-      </c>
-      <c r="BJ15" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="BK15" s="2">
-        <v>1</v>
-      </c>
-      <c r="BL15" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO15" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="BP15" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="CB15" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="CG15" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="CN15" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="CR15" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CY15" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="I16" s="2">
-        <v>1</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="AC16" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG16" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="BD16" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS16" s="2">
-        <v>0.333</v>
-      </c>
-      <c r="CB16" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="CG16" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="DD16" s="2">
-        <v>1</v>
-      </c>
-      <c r="DF16" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG16" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH16" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="G18" s="2">
-        <v>3</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="AC18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG18" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="AT18" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="BD18" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO18" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="BP18" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="BT18" s="2">
-        <v>30</v>
-      </c>
-      <c r="BV18" s="2">
-        <v>30</v>
-      </c>
-      <c r="BW18" s="2">
-        <v>40</v>
-      </c>
-      <c r="BX18" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY18" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="CN18" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="CO18" s="2">
-        <v>1.25</v>
-      </c>
-      <c r="CR18" s="2">
-        <v>30</v>
-      </c>
-      <c r="CU18" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="DD18" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG18" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="AC19" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD19" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO19" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="AT19" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="AX19" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="AZ19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BJ19" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="BK19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BL19" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO19" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="BP19" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="CG19" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="CN19" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="CR19" s="2">
-        <v>9999</v>
-      </c>
-      <c r="CY19" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="I20" s="2">
-        <v>1</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="AC20" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG20" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="BD20" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS20" s="2">
-        <v>0.333</v>
-      </c>
-      <c r="CB20" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="CG20" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="DD20" s="2">
-        <v>1</v>
-      </c>
-      <c r="DF20" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG20" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH20" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="I21" s="2">
-        <v>1</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="AC21" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG21" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="BD21" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS21" s="2">
-        <v>0.333</v>
-      </c>
-      <c r="CB21" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="CG21" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="DD21" s="2">
-        <v>1</v>
-      </c>
-      <c r="DF21" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG21" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH21" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="AC22" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD22" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO22" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="AV22" s="2">
-        <v>99</v>
-      </c>
-      <c r="BD22" s="2">
-        <v>99</v>
-      </c>
-      <c r="BS22" s="2">
-        <v>1</v>
-      </c>
-      <c r="CL22" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="AC23" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD23" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO23" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="AV23" s="2">
-        <v>99</v>
-      </c>
-      <c r="BD23" s="2">
-        <v>99</v>
-      </c>
-      <c r="BS23" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CM23" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="CU23" s="2" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="AC24" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD24" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO24" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="AT24" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="BD24" s="2">
-        <v>99</v>
-      </c>
-      <c r="BS24" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CN24" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="CO24" s="2">
-        <v>-0.5</v>
-      </c>
-      <c r="CR24" s="2">
+    </row>
+    <row r="554">
+      <c r="CL554" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="AC25" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD25" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO25" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="AT25" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="BD25" s="2">
-        <v>99</v>
-      </c>
-      <c r="BS25" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CU25" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="AC28" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG28" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="BD28" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU28" s="2" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="I29" s="2">
-        <v>1</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="AC29" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD29" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO29" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="AT29" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="BD29" s="2">
-        <v>4</v>
-      </c>
-      <c r="BT29" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="CN29" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="CR29" s="2">
-        <v>5</v>
-      </c>
-      <c r="CU29" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="CY29" s="2" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="AC30" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG30" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="BD30" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU30" s="2" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="I32" s="2">
-        <v>1</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="AC32" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD32" s="2">
-        <v>1</v>
-      </c>
-      <c r="AV32" s="2">
+    <row r="561">
+      <c r="CL561" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="CL563" s="3">
         <v>0.4</v>
       </c>
-      <c r="BD32" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO32" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="BP32" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="BT32" s="2">
-        <v>6</v>
-      </c>
-      <c r="BV32" s="2">
-        <v>1</v>
-      </c>
-      <c r="BW32" s="2">
-        <v>1</v>
-      </c>
-      <c r="BX32" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY32" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="DH32" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="I33" s="2">
-        <v>1</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="AC33" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG33" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="AT33" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="AX33" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="AZ33" s="2">
-        <v>999</v>
-      </c>
-      <c r="BB33" s="2">
-        <v>2</v>
-      </c>
-      <c r="BD33" s="2">
-        <v>1</v>
-      </c>
-      <c r="DD33" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG33" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH33" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="AC34" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG34" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="BD34" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU34" s="2" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="AC35" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG35" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="BD35" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU35" s="2" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="I37" s="2">
-        <v>1</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="AC37" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG37" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="BD37" s="2">
-        <v>1</v>
-      </c>
-      <c r="CY37" s="2" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="I38" s="2">
-        <v>1</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="X38" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC38" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD38" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO38" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="AT38" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="AX38" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="AZ38" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="BD38" s="2">
-        <v>99</v>
-      </c>
-      <c r="BE38" s="2">
-        <v>11</v>
-      </c>
-      <c r="BF38" s="2">
+    </row>
+    <row r="564">
+      <c r="CL564" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="CL567" s="3">
         <v>0.5</v>
       </c>
-      <c r="BO38" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="BP38" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="CB38" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="CG38" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="CL38" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="CU38" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="CY38" s="2" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="I39" s="2">
-        <v>1</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="X39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC39" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO39" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="AT39" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="BD39" s="2">
-        <v>99</v>
-      </c>
-      <c r="CN39" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="CO39" s="2">
-        <v>-0.8</v>
-      </c>
-      <c r="CR39" s="2">
-        <v>6</v>
-      </c>
-      <c r="CY39" s="2" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="I40" s="2">
-        <v>1</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="AC40" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG40" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="AT40" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="AX40" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="AZ40" s="2">
-        <v>0.09</v>
-      </c>
-      <c r="BB40" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD40" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE40" s="2">
-        <v>11</v>
-      </c>
-      <c r="BF40" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="CY40" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="DD40" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG40" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH40" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="549">
-      <c r="CL549" s="2">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="551">
-      <c r="CL551" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="552">
-      <c r="CL552" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="554">
-      <c r="CL554" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="561">
-      <c r="CL561" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="563">
-      <c r="CL563" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="564">
-      <c r="CL564" s="2">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="567">
-      <c r="CL567" s="2">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="568">
-      <c r="CL568" s="2">
+      <c r="CL568" s="3">
         <v>0.667</v>
       </c>
     </row>
     <row r="569">
-      <c r="CL569" s="2">
+      <c r="CL569" s="3">
         <v>0.2</v>
       </c>
     </row>
@@ -6806,224 +6849,224 @@
   <dimension ref="A1:Q293"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1" style="2"/>
-    <col min="2" max="2" width="31.25" customWidth="1" style="2"/>
-    <col min="3" max="6" width="9" customWidth="1" style="2"/>
-    <col min="7" max="7" width="18.75" customWidth="1" style="2"/>
-    <col min="8" max="8" width="15" customWidth="1" style="2"/>
-    <col min="9" max="13" width="9" customWidth="1" style="2"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1" style="2"/>
-    <col min="15" max="15" width="9.5" customWidth="1" style="2"/>
-    <col min="16" max="16" width="22.1640625" customWidth="1" style="2"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="13" customWidth="1" style="3"/>
+    <col min="2" max="2" width="31.25" customWidth="1" style="3"/>
+    <col min="3" max="6" width="9" customWidth="1" style="3"/>
+    <col min="7" max="7" width="18.75" customWidth="1" style="3"/>
+    <col min="8" max="8" width="15" customWidth="1" style="3"/>
+    <col min="9" max="13" width="9" customWidth="1" style="3"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1" style="3"/>
+    <col min="15" max="15" width="9.5" customWidth="1" style="3"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1" style="3"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>510</v>
       </c>
+      <c r="O1" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>512</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>369</v>
+      <c r="O2" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>132</v>
+      <c r="L3" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>522</v>
+      <c r="A4" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="s">
+      <c r="A5" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>455</v>
+      <c r="J6" s="3" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>526</v>
+      <c r="A7" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>528</v>
+      <c r="A8" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="292">
-      <c r="P292" s="2">
+      <c r="P292" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="293">
-      <c r="P293" s="2">
+      <c r="P293" s="3">
         <v>1</v>
       </c>
     </row>
@@ -7040,46 +7083,46 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="11.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="27.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="11.25" customWidth="1" style="3"/>
+    <col min="3" max="3" width="9" customWidth="1" style="3"/>
+    <col min="4" max="4" width="27.5" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>529</v>
+      <c r="C1" s="3" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>369</v>
+      <c r="C2" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>132</v>
+      <c r="C3" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -7095,80 +7138,80 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="27.25" customWidth="1" style="2"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
+    <col min="2" max="2" width="9" customWidth="1" style="3"/>
+    <col min="3" max="3" width="27.25" customWidth="1" style="3"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1" style="3"/>
+    <col min="5" max="10" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="I1" s="2" t="s">
-        <v>254</v>
+      <c r="I1" s="3" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>369</v>
+      <c r="G2" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>132</v>
+      <c r="F3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -7184,123 +7227,123 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28" customWidth="1" style="2"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="11.25" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1" style="2"/>
-    <col min="12" max="12" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
+    <col min="2" max="2" width="28" customWidth="1" style="3"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1" style="3"/>
+    <col min="5" max="10" width="11.25" customWidth="1" style="3"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1" style="3"/>
+    <col min="12" max="12" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>544</v>
       </c>
+      <c r="K1" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="I2" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -7317,45 +7360,45 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="16.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="10.25" customWidth="1" style="2"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1" style="2"/>
-    <col min="7" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="16.25" customWidth="1" style="3"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1" style="3"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1" style="3"/>
+    <col min="5" max="5" width="10.25" customWidth="1" style="3"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1" style="3"/>
+    <col min="7" max="9" width="9" customWidth="1" style="3"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -7373,22 +7416,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -7403,147 +7446,147 @@
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5" customWidth="1" style="2"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1" style="2"/>
-    <col min="3" max="3" width="21.9140625" customWidth="1" style="2"/>
-    <col min="4" max="4" width="16.25" customWidth="1" style="2"/>
-    <col min="5" max="5" width="14" customWidth="1" style="2"/>
-    <col min="6" max="7" width="15.1640625" customWidth="1" style="2"/>
-    <col min="8" max="8" width="12.9140625" customWidth="1" style="2"/>
-    <col min="9" max="9" width="14" customWidth="1" style="2"/>
+    <col min="1" max="1" width="7.5" customWidth="1" style="3"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1" style="3"/>
+    <col min="3" max="3" width="21.9140625" customWidth="1" style="3"/>
+    <col min="4" max="4" width="16.25" customWidth="1" style="3"/>
+    <col min="5" max="5" width="14" customWidth="1" style="3"/>
+    <col min="6" max="7" width="15.1640625" customWidth="1" style="3"/>
+    <col min="8" max="8" width="12.9140625" customWidth="1" style="3"/>
+    <col min="9" max="9" width="14" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>566</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>568</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>574</v>
       </c>
+      <c r="H2" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>576</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>580</v>
       </c>
+      <c r="H4" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>582</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="A5" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>583</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>585</v>
       </c>
     </row>
   </sheetData>
